--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -20481,7 +20481,7 @@
       <c r="A41" s="47" t="n"/>
       <c r="B41" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (    )</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C41" s="18" t="n"/>
@@ -20496,7 +20496,7 @@
       <c r="A42" s="47" t="n"/>
       <c r="B42" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
@@ -20542,7 +20542,7 @@
       <c r="A44" s="50" t="n"/>
       <c r="B44" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
@@ -21045,7 +21045,7 @@
       <c r="A71" s="47" t="n"/>
       <c r="B71" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS ()</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C71" s="18" t="inlineStr">
@@ -21068,7 +21068,7 @@
       <c r="A72" s="47" t="n"/>
       <c r="B72" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C72" s="18" t="inlineStr">
@@ -21091,7 +21091,7 @@
       <c r="A73" s="50" t="n"/>
       <c r="B73" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C73" s="18" t="inlineStr">
@@ -21495,7 +21495,7 @@
       <c r="A95" s="43" t="n"/>
       <c r="B95" s="79" t="inlineStr">
         <is>
-          <t>AISLADAS ()</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C95" s="18" t="inlineStr">
@@ -21518,7 +21518,7 @@
       <c r="A96" s="47" t="n"/>
       <c r="B96" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (    )</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C96" s="18" t="n"/>
@@ -21556,7 +21556,7 @@
       <c r="A98" s="47" t="n"/>
       <c r="B98" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C98" s="18" t="inlineStr">
@@ -21579,7 +21579,7 @@
       <c r="A99" s="47" t="n"/>
       <c r="B99" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C99" s="18" t="inlineStr">
@@ -21602,7 +21602,7 @@
       <c r="A100" s="47" t="n"/>
       <c r="B100" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C100" s="18" t="inlineStr">
@@ -21625,7 +21625,7 @@
       <c r="A101" s="47" t="n"/>
       <c r="B101" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C101" s="18" t="inlineStr">
@@ -21648,7 +21648,7 @@
       <c r="A102" s="50" t="n"/>
       <c r="B102" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C102" s="18" t="inlineStr">
@@ -22122,7 +22122,7 @@
       <c r="A128" s="43" t="n"/>
       <c r="B128" s="79" t="inlineStr">
         <is>
-          <t>AISLADAS ()</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
@@ -22145,7 +22145,7 @@
       <c r="A129" s="47" t="n"/>
       <c r="B129" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS ()</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
@@ -22168,7 +22168,7 @@
       <c r="A130" s="47" t="n"/>
       <c r="B130" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C130" s="18" t="inlineStr">
@@ -22191,7 +22191,7 @@
       <c r="A131" s="50" t="n"/>
       <c r="B131" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C131" s="18" t="inlineStr">
@@ -22672,7 +22672,7 @@
       <c r="A156" s="47" t="n"/>
       <c r="B156" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS ()</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C156" s="18" t="inlineStr">
@@ -22695,7 +22695,7 @@
       <c r="A157" s="47" t="n"/>
       <c r="B157" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C157" s="18" t="inlineStr">
@@ -22718,7 +22718,7 @@
       <c r="A158" s="50" t="n"/>
       <c r="B158" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C158" s="18" t="n"/>
@@ -23207,7 +23207,7 @@
       <c r="A185" s="47" t="n"/>
       <c r="B185" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (    )</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C185" s="18" t="n"/>
@@ -23222,7 +23222,7 @@
       <c r="A186" s="47" t="n"/>
       <c r="B186" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C186" s="18" t="inlineStr">
@@ -23245,7 +23245,7 @@
       <c r="A187" s="47" t="n"/>
       <c r="B187" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C187" s="18" t="inlineStr">
@@ -23268,7 +23268,7 @@
       <c r="A188" s="50" t="n"/>
       <c r="B188" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C188" s="18" t="inlineStr">
@@ -23734,7 +23734,7 @@
       <c r="A214" s="43" t="n"/>
       <c r="B214" s="79" t="inlineStr">
         <is>
-          <t>AISLADAS ()</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C214" s="18" t="inlineStr">
@@ -23757,7 +23757,7 @@
       <c r="A215" s="47" t="n"/>
       <c r="B215" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (    )</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C215" s="18" t="n"/>
@@ -23772,7 +23772,7 @@
       <c r="A216" s="47" t="n"/>
       <c r="B216" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C216" s="18" t="inlineStr">
@@ -23795,7 +23795,7 @@
       <c r="A217" s="47" t="n"/>
       <c r="B217" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C217" s="18" t="inlineStr">
@@ -23818,7 +23818,7 @@
       <c r="A218" s="50" t="n"/>
       <c r="B218" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C218" s="18" t="inlineStr">
@@ -24361,7 +24361,7 @@
       <c r="A247" s="47" t="n"/>
       <c r="B247" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS ()</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C247" s="18" t="inlineStr">
@@ -24384,7 +24384,7 @@
       <c r="A248" s="47" t="n"/>
       <c r="B248" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C248" s="18" t="inlineStr">
@@ -24407,7 +24407,7 @@
       <c r="A249" s="50" t="n"/>
       <c r="B249" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C249" s="18" t="n"/>
@@ -24896,7 +24896,7 @@
       <c r="A276" s="47" t="n"/>
       <c r="B276" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (    )</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C276" s="18" t="n"/>
@@ -24911,7 +24911,7 @@
       <c r="A277" s="47" t="n"/>
       <c r="B277" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C277" s="18" t="inlineStr">
@@ -24934,7 +24934,7 @@
       <c r="A278" s="47" t="n"/>
       <c r="B278" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C278" s="18" t="inlineStr">
@@ -24957,7 +24957,7 @@
       <c r="A279" s="50" t="n"/>
       <c r="B279" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C279" s="18" t="inlineStr">
@@ -25460,7 +25460,7 @@
       <c r="A306" s="47" t="n"/>
       <c r="B306" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS ()</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C306" s="18" t="inlineStr">
@@ -25483,7 +25483,7 @@
       <c r="A307" s="47" t="n"/>
       <c r="B307" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C307" s="18" t="inlineStr">
@@ -25506,7 +25506,7 @@
       <c r="A308" s="50" t="n"/>
       <c r="B308" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C308" s="18" t="inlineStr">
@@ -25980,7 +25980,7 @@
       <c r="A334" s="43" t="n"/>
       <c r="B334" s="79" t="inlineStr">
         <is>
-          <t>AISLADAS ()</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C334" s="18" t="inlineStr">
@@ -26003,7 +26003,7 @@
       <c r="A335" s="47" t="n"/>
       <c r="B335" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS ()</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C335" s="18" t="inlineStr">
@@ -26026,7 +26026,7 @@
       <c r="A336" s="47" t="n"/>
       <c r="B336" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C336" s="18" t="inlineStr">
@@ -26049,7 +26049,7 @@
       <c r="A337" s="50" t="n"/>
       <c r="B337" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C337" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -20496,7 +20496,7 @@
       <c r="A42" s="47" t="n"/>
       <c r="B42" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (cocina)</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
@@ -20542,7 +20542,7 @@
       <c r="A44" s="50" t="n"/>
       <c r="B44" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (escalera)</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -1645,26 +1645,26 @@
       </c>
       <c r="L8" s="20" t="n"/>
     </row>
-    <row r="9" ht="47" customHeight="1">
+    <row r="9" ht="62" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
         <is>
           <t>07 - Hall / ingreso</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="C9" s="26" t="n">
         <v>2.15</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>7.568</v>
+        <v>8.6</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>9</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>0.840888888888889</v>
+        <v>0.955555555555556</v>
       </c>
       <c r="G9" s="19" t="n">
         <v>10.5</v>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="I9" s="19" t="n">
-        <v>0.280296296296296</v>
+        <v>0.318518518518519</v>
       </c>
       <c r="J9" s="19" t="n">
         <v>1.6</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="L9" s="23" t="inlineStr">
         <is>
-          <t>CORREGIDO: la planilla original repetia los valores del local 03 (0,66 y 0,22). Con 7,53 m2 corresponden 0,84 y 0,28. Cumple igual.</t>
+          <t>CORREGIDO: la planilla original repetia los valores del local 03 (0,66 y 0,22). Con 4,00 x 2,15 = 8,60 m2 corresponden 0,96 y 0,32. Cumple igual.</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
       <c r="A8" s="116" t="n"/>
       <c r="B8" s="117" t="inlineStr">
         <is>
-          <t>valores del local 03 (Lavadero, 6,0 m2). Con sus 3,50 x 2,15 = 7,53 m2 corresponden</t>
+          <t>valores del local 03 (Lavadero, 6,0 m2). Con sus 4,00 x 2,15 = 8,60 m2 corresponden</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       <c r="A9" s="116" t="n"/>
       <c r="B9" s="117" t="inlineStr">
         <is>
-          <t>0,84 y 0,28. No cambia el resultado, pero el numero no cerraba con la superficie</t>
+          <t>0,96 y 0,32. No cambia el resultado, pero el numero no cerraba con la superficie</t>
         </is>
       </c>
     </row>
@@ -20817,7 +20817,7 @@
       <c r="D58" s="12" t="n"/>
       <c r="E58" s="39" t="n"/>
       <c r="F58" s="87" t="n">
-        <v>1924.1</v>
+        <v>2050.7</v>
       </c>
       <c r="G58" s="53" t="n"/>
     </row>
@@ -20832,7 +20832,7 @@
       <c r="D59" s="12" t="n"/>
       <c r="E59" s="14" t="n"/>
       <c r="F59" s="85" t="n">
-        <v>7649.7</v>
+        <v>7776.3</v>
       </c>
       <c r="G59" s="53" t="n"/>
     </row>
@@ -20876,7 +20876,7 @@
         </is>
       </c>
       <c r="C62" s="59" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D62" s="12" t="n"/>
       <c r="E62" s="39" t="n"/>
@@ -20891,7 +20891,7 @@
         </is>
       </c>
       <c r="C63" s="59" t="n">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D63" s="12" t="n"/>
       <c r="E63" s="39" t="n"/>
@@ -21027,17 +21027,17 @@
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>3.52 x 3.00</t>
+          <t>4.00 x 3.00</t>
         </is>
       </c>
       <c r="D70" s="19" t="n">
-        <v>10.56</v>
+        <v>12</v>
       </c>
       <c r="E70" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F70" s="80" t="n">
-        <v>211.2</v>
+        <v>240</v>
       </c>
       <c r="G70" s="53" t="n"/>
     </row>
@@ -21068,22 +21068,22 @@
       <c r="A72" s="47" t="n"/>
       <c r="B72" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (vestidor)</t>
         </is>
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>3.52 x 3.00</t>
+          <t>4.00 x 3.00</t>
         </is>
       </c>
       <c r="D72" s="19" t="n">
-        <v>10.56</v>
+        <v>12</v>
       </c>
       <c r="E72" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F72" s="80" t="n">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="G72" s="53" t="n"/>
     </row>
@@ -21091,7 +21091,7 @@
       <c r="A73" s="50" t="n"/>
       <c r="B73" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (living comedor)</t>
         </is>
       </c>
       <c r="C73" s="18" t="inlineStr">
@@ -21170,13 +21170,13 @@
         </is>
       </c>
       <c r="D77" s="19" t="n">
-        <v>7.57</v>
+        <v>8.6</v>
       </c>
       <c r="E77" s="59" t="n">
         <v>15</v>
       </c>
       <c r="F77" s="80" t="n">
-        <v>113.6</v>
+        <v>129</v>
       </c>
       <c r="G77" s="53" t="n"/>
     </row>
@@ -21210,13 +21210,13 @@
         </is>
       </c>
       <c r="D79" s="19" t="n">
-        <v>7.57</v>
+        <v>8.6</v>
       </c>
       <c r="E79" s="59" t="n">
         <v>10</v>
       </c>
       <c r="F79" s="80" t="n">
-        <v>75.7</v>
+        <v>86</v>
       </c>
       <c r="G79" s="53" t="n"/>
     </row>
@@ -21280,17 +21280,17 @@
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>7.57 m2 x 3.00</t>
+          <t>8.60 m2 x 3.00</t>
         </is>
       </c>
       <c r="D83" s="19" t="n">
-        <v>22.71</v>
+        <v>25.8</v>
       </c>
       <c r="E83" s="59" t="n">
         <v>9</v>
       </c>
       <c r="F83" s="80" t="n">
-        <v>204.4</v>
+        <v>232.2</v>
       </c>
       <c r="G83" s="53" t="n"/>
     </row>
@@ -21324,7 +21324,7 @@
       <c r="D85" s="18" t="n"/>
       <c r="E85" s="20" t="n"/>
       <c r="F85" s="85" t="n">
-        <v>1798.2</v>
+        <v>1916.5</v>
       </c>
       <c r="G85" s="53" t="n"/>
     </row>
@@ -21341,13 +21341,13 @@
       </c>
       <c r="C86" s="47" t="inlineStr">
         <is>
-          <t>1798.20  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+          <t>1916.50  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
       <c r="D86" s="12" t="n"/>
       <c r="E86" s="14" t="n"/>
       <c r="F86" s="85" t="n">
-        <v>1924.1</v>
+        <v>2050.7</v>
       </c>
       <c r="G86" s="53" t="n"/>
     </row>
@@ -21375,7 +21375,7 @@
       <c r="D88" s="12" t="n"/>
       <c r="E88" s="14" t="n"/>
       <c r="F88" s="85" t="n">
-        <v>1924.1</v>
+        <v>2050.7</v>
       </c>
       <c r="G88" s="53" t="n"/>
     </row>

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -21045,7 +21045,7 @@
       <c r="A71" s="47" t="n"/>
       <c r="B71" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>AISLADAS (SE)</t>
         </is>
       </c>
       <c r="C71" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -639,10 +639,10 @@
       <left style="thin">
         <color rgb="00000000"/>
       </left>
-      <right style="dotted">
+      <right style="thin">
         <color rgb="00000000"/>
       </right>
-      <top style="thin">
+      <top style="dotted">
         <color rgb="00000000"/>
       </top>
       <bottom style="thin">
@@ -653,10 +653,10 @@
       <left style="thin">
         <color rgb="00000000"/>
       </left>
-      <right style="thin">
+      <right style="dotted">
         <color rgb="00000000"/>
       </right>
-      <top style="dotted">
+      <top style="thin">
         <color rgb="00000000"/>
       </top>
       <bottom style="thin">
@@ -898,11 +898,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -919,8 +919,8 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -19691,7 +19691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G357"/>
+  <dimension ref="A1:G358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.1" customWidth="1" min="1" max="1"/>
@@ -20817,7 +20817,7 @@
       <c r="D58" s="12" t="n"/>
       <c r="E58" s="39" t="n"/>
       <c r="F58" s="87" t="n">
-        <v>2050.7</v>
+        <v>2339.6</v>
       </c>
       <c r="G58" s="53" t="n"/>
     </row>
@@ -20832,7 +20832,7 @@
       <c r="D59" s="12" t="n"/>
       <c r="E59" s="14" t="n"/>
       <c r="F59" s="85" t="n">
-        <v>7776.3</v>
+        <v>8065.2</v>
       </c>
       <c r="G59" s="53" t="n"/>
     </row>
@@ -20876,7 +20876,7 @@
         </is>
       </c>
       <c r="C62" s="59" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D62" s="12" t="n"/>
       <c r="E62" s="39" t="n"/>
@@ -20891,7 +20891,7 @@
         </is>
       </c>
       <c r="C63" s="59" t="n">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D63" s="12" t="n"/>
       <c r="E63" s="39" t="n"/>
@@ -20979,10 +20979,10 @@
       <c r="G67" s="53" t="n"/>
     </row>
     <row r="68" ht="19.8" customHeight="1">
-      <c r="A68" s="89" t="n"/>
-      <c r="B68" s="90" t="inlineStr">
-        <is>
-          <t>PF01 (2)</t>
+      <c r="A68" s="43" t="n"/>
+      <c r="B68" s="79" t="inlineStr">
+        <is>
+          <t>PF01</t>
         </is>
       </c>
       <c r="C68" s="18" t="inlineStr">
@@ -21002,65 +21002,65 @@
       <c r="G68" s="53" t="n"/>
     </row>
     <row r="69" ht="19.8" customHeight="1">
-      <c r="A69" s="36" t="inlineStr">
+      <c r="A69" s="50" t="n"/>
+      <c r="B69" s="82" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>1.50 x 3.00</t>
+        </is>
+      </c>
+      <c r="D69" s="19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E69" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F69" s="80" t="n">
+        <v>270</v>
+      </c>
+      <c r="G69" s="53" t="n"/>
+    </row>
+    <row r="70" ht="19.8" customHeight="1">
+      <c r="A70" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B69" s="78" t="inlineStr">
+      <c r="B70" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C69" s="47" t="n"/>
-      <c r="D69" s="18" t="n"/>
-      <c r="E69" s="18" t="n"/>
-      <c r="F69" s="20" t="n"/>
-      <c r="G69" s="53" t="n"/>
-    </row>
-    <row r="70" ht="19.8" customHeight="1">
-      <c r="A70" s="43" t="n"/>
-      <c r="B70" s="79" t="inlineStr">
+      <c r="C70" s="47" t="n"/>
+      <c r="D70" s="18" t="n"/>
+      <c r="E70" s="18" t="n"/>
+      <c r="F70" s="20" t="n"/>
+      <c r="G70" s="53" t="n"/>
+    </row>
+    <row r="71" ht="19.8" customHeight="1">
+      <c r="A71" s="43" t="n"/>
+      <c r="B71" s="79" t="inlineStr">
         <is>
           <t>AISLADAS (SO)</t>
         </is>
       </c>
-      <c r="C70" s="18" t="inlineStr">
+      <c r="C71" s="18" t="inlineStr">
         <is>
           <t>4.00 x 3.00</t>
         </is>
       </c>
-      <c r="D70" s="19" t="n">
+      <c r="D71" s="19" t="n">
         <v>12</v>
-      </c>
-      <c r="E70" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F70" s="80" t="n">
-        <v>240</v>
-      </c>
-      <c r="G70" s="53" t="n"/>
-    </row>
-    <row r="71" ht="19.8" customHeight="1">
-      <c r="A71" s="47" t="n"/>
-      <c r="B71" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS (SE)</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="inlineStr">
-        <is>
-          <t>2.15 x 3.00</t>
-        </is>
-      </c>
-      <c r="D71" s="19" t="n">
-        <v>6.45</v>
       </c>
       <c r="E71" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F71" s="80" t="n">
-        <v>129</v>
+        <v>240</v>
       </c>
       <c r="G71" s="53" t="n"/>
     </row>
@@ -21068,510 +21068,510 @@
       <c r="A72" s="47" t="n"/>
       <c r="B72" s="81" t="inlineStr">
         <is>
+          <t>AISLADAS (SE)</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>2.15 x 3.00</t>
+        </is>
+      </c>
+      <c r="D72" s="19" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="E72" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F72" s="80" t="n">
+        <v>129</v>
+      </c>
+      <c r="G72" s="53" t="n"/>
+    </row>
+    <row r="73" ht="19.8" customHeight="1">
+      <c r="A73" s="47" t="n"/>
+      <c r="B73" s="81" t="inlineStr">
+        <is>
           <t>INTERIORES (vestidor)</t>
         </is>
       </c>
-      <c r="C72" s="18" t="inlineStr">
+      <c r="C73" s="18" t="inlineStr">
         <is>
           <t>4.00 x 3.00</t>
         </is>
       </c>
-      <c r="D72" s="19" t="n">
+      <c r="D73" s="19" t="n">
         <v>12</v>
-      </c>
-      <c r="E72" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F72" s="80" t="n">
-        <v>300</v>
-      </c>
-      <c r="G72" s="53" t="n"/>
-    </row>
-    <row r="73" ht="19.8" customHeight="1">
-      <c r="A73" s="50" t="n"/>
-      <c r="B73" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES (living comedor)</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="inlineStr">
-        <is>
-          <t>2.15 x 3.00</t>
-        </is>
-      </c>
-      <c r="D73" s="19" t="n">
-        <v>6.45</v>
       </c>
       <c r="E73" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F73" s="80" t="n">
+        <v>300</v>
+      </c>
+      <c r="G73" s="53" t="n"/>
+    </row>
+    <row r="74" ht="19.8" customHeight="1">
+      <c r="A74" s="50" t="n"/>
+      <c r="B74" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES (living comedor)</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>2.15 x 3.00</t>
+        </is>
+      </c>
+      <c r="D74" s="19" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="E74" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F74" s="80" t="n">
         <v>161.3</v>
       </c>
-      <c r="G73" s="53" t="n"/>
-    </row>
-    <row r="74" ht="19.8" customHeight="1">
-      <c r="A74" s="36" t="inlineStr">
+      <c r="G74" s="53" t="n"/>
+    </row>
+    <row r="75" ht="19.8" customHeight="1">
+      <c r="A75" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B74" s="78" t="inlineStr">
+      <c r="B75" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C74" s="47" t="n"/>
-      <c r="D74" s="18" t="n"/>
-      <c r="E74" s="18" t="n"/>
-      <c r="F74" s="20" t="n"/>
-      <c r="G74" s="53" t="n"/>
-    </row>
-    <row r="75" ht="19.8" customHeight="1">
-      <c r="A75" s="43" t="n"/>
-      <c r="B75" s="79" t="inlineStr">
+      <c r="C75" s="47" t="n"/>
+      <c r="D75" s="18" t="n"/>
+      <c r="E75" s="18" t="n"/>
+      <c r="F75" s="20" t="n"/>
+      <c r="G75" s="53" t="n"/>
+    </row>
+    <row r="76" ht="19.8" customHeight="1">
+      <c r="A76" s="43" t="n"/>
+      <c r="B76" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C75" s="18" t="n"/>
-      <c r="D75" s="19" t="n"/>
-      <c r="E75" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F75" s="80" t="n"/>
-      <c r="G75" s="53" t="n"/>
-    </row>
-    <row r="76" ht="19.8" customHeight="1">
-      <c r="A76" s="47" t="n"/>
-      <c r="B76" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C76" s="18" t="n"/>
       <c r="D76" s="19" t="n"/>
       <c r="E76" s="59" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F76" s="80" t="n"/>
       <c r="G76" s="53" t="n"/>
     </row>
     <row r="77" ht="19.8" customHeight="1">
-      <c r="A77" s="50" t="n"/>
-      <c r="B77" s="82" t="inlineStr">
+      <c r="A77" s="47" t="n"/>
+      <c r="B77" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="n"/>
+      <c r="D77" s="19" t="n"/>
+      <c r="E77" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F77" s="80" t="n"/>
+      <c r="G77" s="53" t="n"/>
+    </row>
+    <row r="78" ht="19.8" customHeight="1">
+      <c r="A78" s="50" t="n"/>
+      <c r="B78" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C77" s="18" t="inlineStr">
+      <c r="C78" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D77" s="19" t="n">
+      <c r="D78" s="19" t="n">
         <v>8.6</v>
       </c>
-      <c r="E77" s="59" t="n">
+      <c r="E78" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F77" s="80" t="n">
+      <c r="F78" s="80" t="n">
         <v>129</v>
       </c>
-      <c r="G77" s="53" t="n"/>
-    </row>
-    <row r="78" ht="19.8" customHeight="1">
-      <c r="A78" s="36" t="inlineStr">
+      <c r="G78" s="53" t="n"/>
+    </row>
+    <row r="79" ht="19.8" customHeight="1">
+      <c r="A79" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B78" s="78" t="inlineStr">
+      <c r="B79" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C78" s="47" t="n"/>
-      <c r="D78" s="18" t="n"/>
-      <c r="E78" s="18" t="n"/>
-      <c r="F78" s="20" t="n"/>
-      <c r="G78" s="53" t="n"/>
-    </row>
-    <row r="79" ht="19.8" customHeight="1">
-      <c r="A79" s="43" t="n"/>
-      <c r="B79" s="79" t="inlineStr">
+      <c r="C79" s="47" t="n"/>
+      <c r="D79" s="18" t="n"/>
+      <c r="E79" s="18" t="n"/>
+      <c r="F79" s="20" t="n"/>
+      <c r="G79" s="53" t="n"/>
+    </row>
+    <row r="80" ht="19.8" customHeight="1">
+      <c r="A80" s="43" t="n"/>
+      <c r="B80" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C79" s="18" t="inlineStr">
+      <c r="C80" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D79" s="19" t="n">
+      <c r="D80" s="19" t="n">
         <v>8.6</v>
       </c>
-      <c r="E79" s="59" t="n">
+      <c r="E80" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F79" s="80" t="n">
+      <c r="F80" s="80" t="n">
         <v>86</v>
       </c>
-      <c r="G79" s="53" t="n"/>
-    </row>
-    <row r="80" ht="19.8" customHeight="1">
-      <c r="A80" s="50" t="n"/>
-      <c r="B80" s="82" t="inlineStr">
+      <c r="G80" s="53" t="n"/>
+    </row>
+    <row r="81" ht="19.8" customHeight="1">
+      <c r="A81" s="50" t="n"/>
+      <c r="B81" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C80" s="18" t="n"/>
-      <c r="D80" s="24" t="n"/>
-      <c r="E80" s="59" t="n">
+      <c r="C81" s="18" t="n"/>
+      <c r="D81" s="24" t="n"/>
+      <c r="E81" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F80" s="80" t="n"/>
-      <c r="G80" s="53" t="n"/>
-    </row>
-    <row r="81" ht="19.8" customHeight="1">
-      <c r="A81" s="36" t="inlineStr">
+      <c r="F81" s="80" t="n"/>
+      <c r="G81" s="53" t="n"/>
+    </row>
+    <row r="82" ht="19.8" customHeight="1">
+      <c r="A82" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B81" s="78" t="inlineStr">
+      <c r="B82" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C81" s="83" t="n"/>
-      <c r="D81" s="36" t="inlineStr">
+      <c r="C82" s="83" t="n"/>
+      <c r="D82" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E81" s="47" t="n"/>
-      <c r="F81" s="20" t="n"/>
-      <c r="G81" s="53" t="n"/>
-    </row>
-    <row r="82" ht="19.8" customHeight="1">
-      <c r="A82" s="43" t="n"/>
-      <c r="B82" s="79" t="inlineStr">
+      <c r="E82" s="47" t="n"/>
+      <c r="F82" s="20" t="n"/>
+      <c r="G82" s="53" t="n"/>
+    </row>
+    <row r="83" ht="19.8" customHeight="1">
+      <c r="A83" s="43" t="n"/>
+      <c r="B83" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C82" s="18" t="n"/>
-      <c r="D82" s="22" t="n"/>
-      <c r="E82" s="59" t="n">
+      <c r="C83" s="18" t="n"/>
+      <c r="D83" s="22" t="n"/>
+      <c r="E83" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="F82" s="80" t="n"/>
-      <c r="G82" s="53" t="n"/>
-    </row>
-    <row r="83" ht="19.8" customHeight="1">
-      <c r="A83" s="47" t="n"/>
-      <c r="B83" s="81" t="inlineStr">
+      <c r="F83" s="80" t="n"/>
+      <c r="G83" s="53" t="n"/>
+    </row>
+    <row r="84" ht="19.8" customHeight="1">
+      <c r="A84" s="47" t="n"/>
+      <c r="B84" s="81" t="inlineStr">
         <is>
           <t>DOS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C83" s="18" t="inlineStr">
+      <c r="C84" s="18" t="inlineStr">
         <is>
           <t>8.60 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D83" s="19" t="n">
+      <c r="D84" s="19" t="n">
         <v>25.8</v>
       </c>
-      <c r="E83" s="59" t="n">
+      <c r="E84" s="59" t="n">
         <v>9</v>
       </c>
-      <c r="F83" s="80" t="n">
+      <c r="F84" s="80" t="n">
         <v>232.2</v>
       </c>
-      <c r="G83" s="53" t="n"/>
-    </row>
-    <row r="84" ht="19.8" customHeight="1">
-      <c r="A84" s="50" t="n"/>
-      <c r="B84" s="82" t="inlineStr">
+      <c r="G84" s="53" t="n"/>
+    </row>
+    <row r="85" ht="19.8" customHeight="1">
+      <c r="A85" s="50" t="n"/>
+      <c r="B85" s="82" t="inlineStr">
         <is>
           <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C84" s="18" t="n"/>
-      <c r="D84" s="19" t="n"/>
-      <c r="E84" s="59" t="n">
+      <c r="C85" s="18" t="n"/>
+      <c r="D85" s="19" t="n"/>
+      <c r="E85" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F84" s="84" t="n"/>
-      <c r="G84" s="53" t="n"/>
-    </row>
-    <row r="85" ht="19.8" customHeight="1">
-      <c r="A85" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B85" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C85" s="47" t="n"/>
-      <c r="D85" s="18" t="n"/>
-      <c r="E85" s="20" t="n"/>
-      <c r="F85" s="85" t="n">
-        <v>1916.5</v>
-      </c>
+      <c r="F85" s="84" t="n"/>
       <c r="G85" s="53" t="n"/>
     </row>
     <row r="86" ht="19.8" customHeight="1">
       <c r="A86" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B86" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C86" s="47" t="n"/>
+      <c r="D86" s="18" t="n"/>
+      <c r="E86" s="20" t="n"/>
+      <c r="F86" s="85" t="n">
+        <v>2186.5</v>
+      </c>
+      <c r="G86" s="53" t="n"/>
+    </row>
+    <row r="87" ht="19.8" customHeight="1">
+      <c r="A87" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B86" s="78" t="inlineStr">
+      <c r="B87" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C86" s="47" t="inlineStr">
-        <is>
-          <t>1916.50  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
-      <c r="D86" s="12" t="n"/>
-      <c r="E86" s="14" t="n"/>
-      <c r="F86" s="85" t="n">
-        <v>2050.7</v>
-      </c>
-      <c r="G86" s="53" t="n"/>
-    </row>
-    <row r="87" ht="19.8" customHeight="1">
-      <c r="A87" s="43" t="n"/>
-      <c r="B87" s="86" t="inlineStr">
+      <c r="C87" s="47" t="inlineStr">
+        <is>
+          <t>2186.50  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="n"/>
+      <c r="E87" s="14" t="n"/>
+      <c r="F87" s="85" t="n">
+        <v>2339.6</v>
+      </c>
+      <c r="G87" s="53" t="n"/>
+    </row>
+    <row r="88" ht="19.8" customHeight="1">
+      <c r="A88" s="43" t="n"/>
+      <c r="B88" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C87" s="18" t="n"/>
-      <c r="D87" s="12" t="n"/>
-      <c r="E87" s="39" t="n"/>
-      <c r="F87" s="87" t="n"/>
-      <c r="G87" s="53" t="n"/>
-    </row>
-    <row r="88" ht="19.8" customHeight="1">
-      <c r="A88" s="83" t="n"/>
-      <c r="B88" s="78" t="inlineStr">
+      <c r="C88" s="18" t="n"/>
+      <c r="D88" s="12" t="n"/>
+      <c r="E88" s="39" t="n"/>
+      <c r="F88" s="87" t="n"/>
+      <c r="G88" s="53" t="n"/>
+    </row>
+    <row r="89" ht="19.8" customHeight="1">
+      <c r="A89" s="83" t="n"/>
+      <c r="B89" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C88" s="47" t="n"/>
-      <c r="D88" s="12" t="n"/>
-      <c r="E88" s="14" t="n"/>
-      <c r="F88" s="85" t="n">
-        <v>2050.7</v>
-      </c>
-      <c r="G88" s="53" t="n"/>
-    </row>
-    <row r="89" ht="19.8" customHeight="1">
-      <c r="A89" s="91" t="n"/>
-      <c r="B89" s="78" t="inlineStr">
+      <c r="C89" s="47" t="n"/>
+      <c r="D89" s="12" t="n"/>
+      <c r="E89" s="14" t="n"/>
+      <c r="F89" s="85" t="n">
+        <v>2339.6</v>
+      </c>
+      <c r="G89" s="53" t="n"/>
+    </row>
+    <row r="90" ht="19.8" customHeight="1">
+      <c r="A90" s="89" t="n"/>
+      <c r="B90" s="78" t="inlineStr">
         <is>
           <t>SIN EMISOR</t>
         </is>
       </c>
-      <c r="C89" s="47" t="inlineStr">
+      <c r="C90" s="47" t="inlineStr">
         <is>
           <t>la cubre el radiador de 06 - Living / comedor</t>
         </is>
       </c>
-      <c r="D89" s="12" t="n"/>
-      <c r="E89" s="39" t="n"/>
-      <c r="F89" s="61" t="n"/>
-      <c r="G89" s="53" t="n"/>
-    </row>
-    <row r="90" ht="19.8" customHeight="1">
-      <c r="A90" s="8" t="inlineStr">
+      <c r="D90" s="12" t="n"/>
+      <c r="E90" s="39" t="n"/>
+      <c r="F90" s="61" t="n"/>
+      <c r="G90" s="53" t="n"/>
+    </row>
+    <row r="91" ht="19.8" customHeight="1">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>LOCAL  08 - Vestidor   (PB)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B90" s="3" t="n"/>
-      <c r="C90" s="11" t="n"/>
-      <c r="D90" s="11" t="n"/>
-      <c r="E90" s="11" t="n"/>
-      <c r="F90" s="42" t="n"/>
-      <c r="G90" s="53" t="n"/>
-    </row>
-    <row r="91" ht="32" customHeight="1">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="B91" s="3" t="n"/>
+      <c r="C91" s="11" t="n"/>
+      <c r="D91" s="11" t="n"/>
+      <c r="E91" s="11" t="n"/>
+      <c r="F91" s="42" t="n"/>
+      <c r="G91" s="53" t="n"/>
+    </row>
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G91" s="53" t="n"/>
-    </row>
-    <row r="92" ht="19.8" customHeight="1">
-      <c r="A92" s="36" t="inlineStr">
+      <c r="G92" s="53" t="n"/>
+    </row>
+    <row r="93" ht="19.8" customHeight="1">
+      <c r="A93" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B92" s="78" t="inlineStr">
+      <c r="B93" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C92" s="43" t="n"/>
-      <c r="D92" s="58" t="n"/>
-      <c r="E92" s="58" t="n"/>
-      <c r="F92" s="61" t="n"/>
-      <c r="G92" s="53" t="n"/>
-    </row>
-    <row r="93" ht="19.8" customHeight="1">
-      <c r="A93" s="89" t="n"/>
-      <c r="B93" s="90" t="inlineStr">
+      <c r="C93" s="43" t="n"/>
+      <c r="D93" s="58" t="n"/>
+      <c r="E93" s="58" t="n"/>
+      <c r="F93" s="61" t="n"/>
+      <c r="G93" s="53" t="n"/>
+    </row>
+    <row r="94" ht="19.8" customHeight="1">
+      <c r="A94" s="90" t="n"/>
+      <c r="B94" s="91" t="inlineStr">
         <is>
           <t>(sin aberturas)</t>
         </is>
       </c>
-      <c r="C93" s="18" t="n"/>
-      <c r="D93" s="19" t="n"/>
-      <c r="E93" s="59" t="n">
+      <c r="C94" s="18" t="n"/>
+      <c r="D94" s="19" t="n"/>
+      <c r="E94" s="59" t="n">
         <v>60</v>
       </c>
-      <c r="F93" s="80" t="n"/>
-      <c r="G93" s="53" t="n"/>
-    </row>
-    <row r="94" ht="19.8" customHeight="1">
-      <c r="A94" s="36" t="inlineStr">
+      <c r="F94" s="80" t="n"/>
+      <c r="G94" s="53" t="n"/>
+    </row>
+    <row r="95" ht="19.8" customHeight="1">
+      <c r="A95" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B94" s="78" t="inlineStr">
+      <c r="B95" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C94" s="47" t="n"/>
-      <c r="D94" s="18" t="n"/>
-      <c r="E94" s="18" t="n"/>
-      <c r="F94" s="20" t="n"/>
-      <c r="G94" s="53" t="n"/>
-    </row>
-    <row r="95" ht="19.8" customHeight="1">
-      <c r="A95" s="43" t="n"/>
-      <c r="B95" s="79" t="inlineStr">
+      <c r="C95" s="47" t="n"/>
+      <c r="D95" s="18" t="n"/>
+      <c r="E95" s="18" t="n"/>
+      <c r="F95" s="20" t="n"/>
+      <c r="G95" s="53" t="n"/>
+    </row>
+    <row r="96" ht="19.8" customHeight="1">
+      <c r="A96" s="43" t="n"/>
+      <c r="B96" s="79" t="inlineStr">
         <is>
           <t>AISLADAS</t>
         </is>
       </c>
-      <c r="C95" s="18" t="inlineStr">
+      <c r="C96" s="18" t="inlineStr">
         <is>
           <t>1.70 x 3.00</t>
         </is>
       </c>
-      <c r="D95" s="19" t="n">
+      <c r="D96" s="19" t="n">
         <v>5.1</v>
       </c>
-      <c r="E95" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F95" s="80" t="n">
-        <v>102</v>
-      </c>
-      <c r="G95" s="53" t="n"/>
-    </row>
-    <row r="96" ht="19.8" customHeight="1">
-      <c r="A96" s="47" t="n"/>
-      <c r="B96" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C96" s="18" t="n"/>
-      <c r="D96" s="19" t="n"/>
       <c r="E96" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F96" s="80" t="n"/>
+      <c r="F96" s="80" t="n">
+        <v>102</v>
+      </c>
       <c r="G96" s="53" t="n"/>
     </row>
     <row r="97" ht="19.8" customHeight="1">
       <c r="A97" s="47" t="n"/>
       <c r="B97" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (resto del lado largo)</t>
-        </is>
-      </c>
-      <c r="C97" s="18" t="inlineStr">
-        <is>
-          <t>3.17 x 3.00</t>
-        </is>
-      </c>
-      <c r="D97" s="19" t="n">
-        <v>9.51</v>
-      </c>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="n"/>
+      <c r="D97" s="19" t="n"/>
       <c r="E97" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F97" s="80" t="n">
-        <v>237.8</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F97" s="80" t="n"/>
       <c r="G97" s="53" t="n"/>
     </row>
     <row r="98" ht="19.8" customHeight="1">
       <c r="A98" s="47" t="n"/>
       <c r="B98" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (resto del lado largo)</t>
         </is>
       </c>
       <c r="C98" s="18" t="inlineStr">
         <is>
-          <t>3.38 x 3.00</t>
+          <t>3.17 x 3.00</t>
         </is>
       </c>
       <c r="D98" s="19" t="n">
-        <v>10.14</v>
+        <v>9.51</v>
       </c>
       <c r="E98" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F98" s="80" t="n">
-        <v>253.5</v>
+        <v>237.8</v>
       </c>
       <c r="G98" s="53" t="n"/>
     </row>
@@ -21584,17 +21584,17 @@
       </c>
       <c r="C99" s="18" t="inlineStr">
         <is>
-          <t>1.66 x 3.00</t>
+          <t>3.38 x 3.00</t>
         </is>
       </c>
       <c r="D99" s="19" t="n">
-        <v>4.98</v>
+        <v>10.14</v>
       </c>
       <c r="E99" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F99" s="80" t="n">
-        <v>124.5</v>
+        <v>253.5</v>
       </c>
       <c r="G99" s="53" t="n"/>
     </row>
@@ -21607,17 +21607,17 @@
       </c>
       <c r="C100" s="18" t="inlineStr">
         <is>
-          <t>1.49 x 3.00</t>
+          <t>1.66 x 3.00</t>
         </is>
       </c>
       <c r="D100" s="19" t="n">
-        <v>4.47</v>
+        <v>4.98</v>
       </c>
       <c r="E100" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F100" s="80" t="n">
-        <v>111.8</v>
+        <v>124.5</v>
       </c>
       <c r="G100" s="53" t="n"/>
     </row>
@@ -21630,353 +21630,361 @@
       </c>
       <c r="C101" s="18" t="inlineStr">
         <is>
-          <t>1.09 x 3.00</t>
+          <t>1.49 x 3.00</t>
         </is>
       </c>
       <c r="D101" s="19" t="n">
-        <v>3.27</v>
+        <v>4.47</v>
       </c>
       <c r="E101" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F101" s="80" t="n">
-        <v>81.8</v>
+        <v>111.8</v>
       </c>
       <c r="G101" s="53" t="n"/>
     </row>
     <row r="102" ht="19.8" customHeight="1">
-      <c r="A102" s="50" t="n"/>
-      <c r="B102" s="82" t="inlineStr">
+      <c r="A102" s="47" t="n"/>
+      <c r="B102" s="81" t="inlineStr">
         <is>
           <t>INTERIORES</t>
         </is>
       </c>
       <c r="C102" s="18" t="inlineStr">
         <is>
-          <t>0.57 x 3.00</t>
+          <t>1.09 x 3.00</t>
         </is>
       </c>
       <c r="D102" s="19" t="n">
-        <v>1.71</v>
+        <v>3.27</v>
       </c>
       <c r="E102" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F102" s="80" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="G102" s="53" t="n"/>
+    </row>
+    <row r="103" ht="19.8" customHeight="1">
+      <c r="A103" s="50" t="n"/>
+      <c r="B103" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="inlineStr">
+        <is>
+          <t>0.57 x 3.00</t>
+        </is>
+      </c>
+      <c r="D103" s="19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E103" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F103" s="80" t="n">
         <v>42.8</v>
       </c>
-      <c r="G102" s="53" t="n"/>
-    </row>
-    <row r="103" ht="19.8" customHeight="1">
-      <c r="A103" s="36" t="inlineStr">
+      <c r="G103" s="53" t="n"/>
+    </row>
+    <row r="104" ht="19.8" customHeight="1">
+      <c r="A104" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B103" s="78" t="inlineStr">
+      <c r="B104" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C103" s="47" t="n"/>
-      <c r="D103" s="18" t="n"/>
-      <c r="E103" s="18" t="n"/>
-      <c r="F103" s="20" t="n"/>
-      <c r="G103" s="53" t="n"/>
-    </row>
-    <row r="104" ht="19.8" customHeight="1">
-      <c r="A104" s="43" t="n"/>
-      <c r="B104" s="79" t="inlineStr">
+      <c r="C104" s="47" t="n"/>
+      <c r="D104" s="18" t="n"/>
+      <c r="E104" s="18" t="n"/>
+      <c r="F104" s="20" t="n"/>
+      <c r="G104" s="53" t="n"/>
+    </row>
+    <row r="105" ht="19.8" customHeight="1">
+      <c r="A105" s="43" t="n"/>
+      <c r="B105" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C104" s="18" t="n"/>
-      <c r="D104" s="19" t="n"/>
-      <c r="E104" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F104" s="80" t="n"/>
-      <c r="G104" s="53" t="n"/>
-    </row>
-    <row r="105" ht="19.8" customHeight="1">
-      <c r="A105" s="47" t="n"/>
-      <c r="B105" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C105" s="18" t="n"/>
       <c r="D105" s="19" t="n"/>
       <c r="E105" s="59" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F105" s="80" t="n"/>
       <c r="G105" s="53" t="n"/>
     </row>
     <row r="106" ht="19.8" customHeight="1">
-      <c r="A106" s="50" t="n"/>
-      <c r="B106" s="82" t="inlineStr">
+      <c r="A106" s="47" t="n"/>
+      <c r="B106" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="n"/>
+      <c r="D106" s="19" t="n"/>
+      <c r="E106" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F106" s="80" t="n"/>
+      <c r="G106" s="53" t="n"/>
+    </row>
+    <row r="107" ht="19.8" customHeight="1">
+      <c r="A107" s="50" t="n"/>
+      <c r="B107" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C106" s="18" t="inlineStr">
+      <c r="C107" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D106" s="19" t="n">
+      <c r="D107" s="19" t="n">
         <v>7.23</v>
       </c>
-      <c r="E106" s="59" t="n">
+      <c r="E107" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F106" s="80" t="n">
+      <c r="F107" s="80" t="n">
         <v>108.5</v>
       </c>
-      <c r="G106" s="53" t="n"/>
-    </row>
-    <row r="107" ht="19.8" customHeight="1">
-      <c r="A107" s="36" t="inlineStr">
+      <c r="G107" s="53" t="n"/>
+    </row>
+    <row r="108" ht="19.8" customHeight="1">
+      <c r="A108" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B107" s="78" t="inlineStr">
+      <c r="B108" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C107" s="47" t="n"/>
-      <c r="D107" s="18" t="n"/>
-      <c r="E107" s="18" t="n"/>
-      <c r="F107" s="20" t="n"/>
-      <c r="G107" s="53" t="n"/>
-    </row>
-    <row r="108" ht="19.8" customHeight="1">
-      <c r="A108" s="43" t="n"/>
-      <c r="B108" s="79" t="inlineStr">
+      <c r="C108" s="47" t="n"/>
+      <c r="D108" s="18" t="n"/>
+      <c r="E108" s="18" t="n"/>
+      <c r="F108" s="20" t="n"/>
+      <c r="G108" s="53" t="n"/>
+    </row>
+    <row r="109" ht="19.8" customHeight="1">
+      <c r="A109" s="43" t="n"/>
+      <c r="B109" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C108" s="18" t="inlineStr">
+      <c r="C109" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D108" s="19" t="n">
+      <c r="D109" s="19" t="n">
         <v>7.23</v>
       </c>
-      <c r="E108" s="59" t="n">
+      <c r="E109" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F108" s="80" t="n">
+      <c r="F109" s="80" t="n">
         <v>72.3</v>
       </c>
-      <c r="G108" s="53" t="n"/>
-    </row>
-    <row r="109" ht="19.8" customHeight="1">
-      <c r="A109" s="50" t="n"/>
-      <c r="B109" s="82" t="inlineStr">
+      <c r="G109" s="53" t="n"/>
+    </row>
+    <row r="110" ht="19.8" customHeight="1">
+      <c r="A110" s="50" t="n"/>
+      <c r="B110" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C109" s="18" t="n"/>
-      <c r="D109" s="24" t="n"/>
-      <c r="E109" s="59" t="n">
+      <c r="C110" s="18" t="n"/>
+      <c r="D110" s="24" t="n"/>
+      <c r="E110" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F109" s="80" t="n"/>
-      <c r="G109" s="53" t="n"/>
-    </row>
-    <row r="110" ht="19.8" customHeight="1">
-      <c r="A110" s="36" t="inlineStr">
+      <c r="F110" s="80" t="n"/>
+      <c r="G110" s="53" t="n"/>
+    </row>
+    <row r="111" ht="19.8" customHeight="1">
+      <c r="A111" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B110" s="78" t="inlineStr">
+      <c r="B111" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C110" s="83" t="n"/>
-      <c r="D110" s="36" t="inlineStr">
+      <c r="C111" s="83" t="n"/>
+      <c r="D111" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E110" s="47" t="n"/>
-      <c r="F110" s="20" t="n"/>
-      <c r="G110" s="53" t="n"/>
-    </row>
-    <row r="111" ht="19.8" customHeight="1">
-      <c r="A111" s="43" t="n"/>
-      <c r="B111" s="79" t="inlineStr">
+      <c r="E111" s="47" t="n"/>
+      <c r="F111" s="20" t="n"/>
+      <c r="G111" s="53" t="n"/>
+    </row>
+    <row r="112" ht="19.8" customHeight="1">
+      <c r="A112" s="43" t="n"/>
+      <c r="B112" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C111" s="18" t="inlineStr">
+      <c r="C112" s="18" t="inlineStr">
         <is>
           <t>7.23 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D111" s="22" t="n">
+      <c r="D112" s="22" t="n">
         <v>21.69</v>
       </c>
-      <c r="E111" s="59" t="n">
+      <c r="E112" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="F111" s="80" t="n">
+      <c r="F112" s="80" t="n">
         <v>130.1</v>
       </c>
-      <c r="G111" s="53" t="n"/>
-    </row>
-    <row r="112" ht="19.8" customHeight="1">
-      <c r="A112" s="47" t="n"/>
-      <c r="B112" s="81" t="inlineStr">
+      <c r="G112" s="53" t="n"/>
+    </row>
+    <row r="113" ht="19.8" customHeight="1">
+      <c r="A113" s="47" t="n"/>
+      <c r="B113" s="81" t="inlineStr">
         <is>
           <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C112" s="18" t="n"/>
-      <c r="D112" s="19" t="n"/>
-      <c r="E112" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F112" s="80" t="n"/>
-      <c r="G112" s="53" t="n"/>
-    </row>
-    <row r="113" ht="19.8" customHeight="1">
-      <c r="A113" s="50" t="n"/>
-      <c r="B113" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C113" s="18" t="n"/>
       <c r="D113" s="19" t="n"/>
       <c r="E113" s="59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F113" s="80" t="n"/>
+      <c r="G113" s="53" t="n"/>
+    </row>
+    <row r="114" ht="19.8" customHeight="1">
+      <c r="A114" s="50" t="n"/>
+      <c r="B114" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="n"/>
+      <c r="D114" s="19" t="n"/>
+      <c r="E114" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F113" s="84" t="n"/>
-      <c r="G113" s="53" t="n"/>
-    </row>
-    <row r="114" ht="19.8" customHeight="1">
-      <c r="A114" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B114" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C114" s="47" t="n"/>
-      <c r="D114" s="18" t="n"/>
-      <c r="E114" s="20" t="n"/>
-      <c r="F114" s="85" t="n">
-        <v>1265.1</v>
-      </c>
+      <c r="F114" s="84" t="n"/>
       <c r="G114" s="53" t="n"/>
     </row>
     <row r="115" ht="19.8" customHeight="1">
       <c r="A115" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B115" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C115" s="47" t="n"/>
+      <c r="D115" s="18" t="n"/>
+      <c r="E115" s="20" t="n"/>
+      <c r="F115" s="85" t="n">
+        <v>1265.1</v>
+      </c>
+      <c r="G115" s="53" t="n"/>
+    </row>
+    <row r="116" ht="19.8" customHeight="1">
+      <c r="A116" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B115" s="78" t="inlineStr">
+      <c r="B116" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C115" s="47" t="inlineStr">
+      <c r="C116" s="47" t="inlineStr">
         <is>
           <t>1265.10  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D115" s="12" t="n"/>
-      <c r="E115" s="14" t="n"/>
-      <c r="F115" s="85" t="n">
+      <c r="D116" s="12" t="n"/>
+      <c r="E116" s="14" t="n"/>
+      <c r="F116" s="85" t="n">
         <v>1353.7</v>
       </c>
-      <c r="G115" s="53" t="n"/>
-    </row>
-    <row r="116" ht="19.8" customHeight="1">
-      <c r="A116" s="43" t="n"/>
-      <c r="B116" s="86" t="inlineStr">
+      <c r="G116" s="53" t="n"/>
+    </row>
+    <row r="117" ht="19.8" customHeight="1">
+      <c r="A117" s="43" t="n"/>
+      <c r="B117" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C116" s="18" t="n"/>
-      <c r="D116" s="12" t="n"/>
-      <c r="E116" s="39" t="n"/>
-      <c r="F116" s="87" t="n"/>
-      <c r="G116" s="53" t="n"/>
-    </row>
-    <row r="117" ht="19.8" customHeight="1">
-      <c r="A117" s="83" t="n"/>
-      <c r="B117" s="78" t="inlineStr">
+      <c r="C117" s="18" t="n"/>
+      <c r="D117" s="12" t="n"/>
+      <c r="E117" s="39" t="n"/>
+      <c r="F117" s="87" t="n"/>
+      <c r="G117" s="53" t="n"/>
+    </row>
+    <row r="118" ht="19.8" customHeight="1">
+      <c r="A118" s="83" t="n"/>
+      <c r="B118" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C117" s="47" t="n"/>
-      <c r="D117" s="12" t="n"/>
-      <c r="E117" s="14" t="n"/>
-      <c r="F117" s="85" t="n">
+      <c r="C118" s="47" t="n"/>
+      <c r="D118" s="12" t="n"/>
+      <c r="E118" s="14" t="n"/>
+      <c r="F118" s="85" t="n">
         <v>1353.7</v>
       </c>
-      <c r="G117" s="53" t="n"/>
-    </row>
-    <row r="118" ht="19.8" customHeight="1">
-      <c r="A118" s="47" t="n"/>
-      <c r="B118" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C118" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
-      </c>
-      <c r="D118" s="12" t="n"/>
-      <c r="E118" s="39" t="n"/>
-      <c r="F118" s="61" t="n"/>
       <c r="G118" s="53" t="n"/>
     </row>
     <row r="119" ht="19.8" customHeight="1">
       <c r="A119" s="47" t="n"/>
-      <c r="B119" s="60" t="inlineStr">
-        <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C119" s="19" t="n">
-        <v>274.4</v>
+      <c r="B119" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C119" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
       </c>
       <c r="D119" s="12" t="n"/>
       <c r="E119" s="39" t="n"/>
-      <c r="F119" s="20" t="n"/>
+      <c r="F119" s="61" t="n"/>
       <c r="G119" s="53" t="n"/>
     </row>
     <row r="120" ht="19.8" customHeight="1">
       <c r="A120" s="47" t="n"/>
       <c r="B120" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
-        </is>
-      </c>
-      <c r="C120" s="59" t="n">
-        <v>5</v>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C120" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D120" s="12" t="n"/>
       <c r="E120" s="39" t="n"/>
@@ -21987,11 +21995,11 @@
       <c r="A121" s="47" t="n"/>
       <c r="B121" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C121" s="59" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="D121" s="12" t="n"/>
       <c r="E121" s="39" t="n"/>
@@ -21999,16 +22007,14 @@
       <c r="G121" s="53" t="n"/>
     </row>
     <row r="122" ht="19.8" customHeight="1">
-      <c r="A122" s="50" t="n"/>
+      <c r="A122" s="47" t="n"/>
       <c r="B122" s="60" t="inlineStr">
         <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C122" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
+          <t>Ancho del radiador (cm)</t>
+        </is>
+      </c>
+      <c r="C122" s="59" t="n">
+        <v>40</v>
       </c>
       <c r="D122" s="12" t="n"/>
       <c r="E122" s="39" t="n"/>
@@ -22016,151 +22022,145 @@
       <c r="G122" s="53" t="n"/>
     </row>
     <row r="123" ht="19.8" customHeight="1">
-      <c r="A123" s="8" t="inlineStr">
+      <c r="A123" s="50" t="n"/>
+      <c r="B123" s="60" t="inlineStr">
+        <is>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C123" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="n"/>
+      <c r="E123" s="39" t="n"/>
+      <c r="F123" s="20" t="n"/>
+      <c r="G123" s="53" t="n"/>
+    </row>
+    <row r="124" ht="19.8" customHeight="1">
+      <c r="A124" s="8" t="inlineStr">
         <is>
           <t>LOCAL  Escalera   (PB)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B123" s="11" t="n"/>
-      <c r="C123" s="11" t="n"/>
-      <c r="D123" s="11" t="n"/>
-      <c r="E123" s="11" t="n"/>
-      <c r="F123" s="42" t="n"/>
-      <c r="G123" s="53" t="n"/>
-    </row>
-    <row r="124" ht="32" customHeight="1">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="B124" s="11" t="n"/>
+      <c r="C124" s="11" t="n"/>
+      <c r="D124" s="11" t="n"/>
+      <c r="E124" s="11" t="n"/>
+      <c r="F124" s="42" t="n"/>
+      <c r="G124" s="53" t="n"/>
+    </row>
+    <row r="125" ht="32" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G124" s="53" t="n"/>
-    </row>
-    <row r="125" ht="19.8" customHeight="1">
-      <c r="A125" s="36" t="inlineStr">
+      <c r="G125" s="53" t="n"/>
+    </row>
+    <row r="126" ht="19.8" customHeight="1">
+      <c r="A126" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B125" s="78" t="inlineStr">
+      <c r="B126" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C125" s="43" t="n"/>
-      <c r="D125" s="58" t="n"/>
-      <c r="E125" s="58" t="n"/>
-      <c r="F125" s="61" t="n"/>
-      <c r="G125" s="53" t="n"/>
-    </row>
-    <row r="126" ht="19.8" customHeight="1">
-      <c r="A126" s="89" t="n"/>
-      <c r="B126" s="90" t="inlineStr">
+      <c r="C126" s="43" t="n"/>
+      <c r="D126" s="58" t="n"/>
+      <c r="E126" s="58" t="n"/>
+      <c r="F126" s="61" t="n"/>
+      <c r="G126" s="53" t="n"/>
+    </row>
+    <row r="127" ht="19.8" customHeight="1">
+      <c r="A127" s="90" t="n"/>
+      <c r="B127" s="91" t="inlineStr">
         <is>
           <t>PF05</t>
         </is>
       </c>
-      <c r="C126" s="18" t="inlineStr">
+      <c r="C127" s="18" t="inlineStr">
         <is>
           <t>0.75 x 2.52</t>
         </is>
       </c>
-      <c r="D126" s="19" t="n">
+      <c r="D127" s="19" t="n">
         <v>1.89</v>
       </c>
-      <c r="E126" s="59" t="n">
+      <c r="E127" s="59" t="n">
         <v>60</v>
       </c>
-      <c r="F126" s="80" t="n">
+      <c r="F127" s="80" t="n">
         <v>113.4</v>
       </c>
-      <c r="G126" s="53" t="n"/>
-    </row>
-    <row r="127" ht="19.8" customHeight="1">
-      <c r="A127" s="36" t="inlineStr">
+      <c r="G127" s="53" t="n"/>
+    </row>
+    <row r="128" ht="19.8" customHeight="1">
+      <c r="A128" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B127" s="78" t="inlineStr">
+      <c r="B128" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C127" s="47" t="n"/>
-      <c r="D127" s="18" t="n"/>
-      <c r="E127" s="18" t="n"/>
-      <c r="F127" s="20" t="n"/>
-      <c r="G127" s="53" t="n"/>
-    </row>
-    <row r="128" ht="19.8" customHeight="1">
-      <c r="A128" s="43" t="n"/>
-      <c r="B128" s="79" t="inlineStr">
+      <c r="C128" s="47" t="n"/>
+      <c r="D128" s="18" t="n"/>
+      <c r="E128" s="18" t="n"/>
+      <c r="F128" s="20" t="n"/>
+      <c r="G128" s="53" t="n"/>
+    </row>
+    <row r="129" ht="19.8" customHeight="1">
+      <c r="A129" s="43" t="n"/>
+      <c r="B129" s="79" t="inlineStr">
         <is>
           <t>AISLADAS</t>
         </is>
       </c>
-      <c r="C128" s="18" t="inlineStr">
+      <c r="C129" s="18" t="inlineStr">
         <is>
           <t>4.06 x 3.00</t>
         </is>
       </c>
-      <c r="D128" s="19" t="n">
+      <c r="D129" s="19" t="n">
         <v>12.18</v>
-      </c>
-      <c r="E128" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F128" s="80" t="n">
-        <v>243.6</v>
-      </c>
-      <c r="G128" s="53" t="n"/>
-    </row>
-    <row r="129" ht="19.8" customHeight="1">
-      <c r="A129" s="47" t="n"/>
-      <c r="B129" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C129" s="18" t="inlineStr">
-        <is>
-          <t>1.73 x 3.00</t>
-        </is>
-      </c>
-      <c r="D129" s="19" t="n">
-        <v>5.19</v>
       </c>
       <c r="E129" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F129" s="80" t="n">
-        <v>103.8</v>
+        <v>243.6</v>
       </c>
       <c r="G129" s="53" t="n"/>
     </row>
@@ -22168,488 +22168,488 @@
       <c r="A130" s="47" t="n"/>
       <c r="B130" s="81" t="inlineStr">
         <is>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C130" s="18" t="inlineStr">
+        <is>
+          <t>1.73 x 3.00</t>
+        </is>
+      </c>
+      <c r="D130" s="19" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="E130" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F130" s="80" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="G130" s="53" t="n"/>
+    </row>
+    <row r="131" ht="19.8" customHeight="1">
+      <c r="A131" s="47" t="n"/>
+      <c r="B131" s="81" t="inlineStr">
+        <is>
           <t>INTERIORES</t>
         </is>
       </c>
-      <c r="C130" s="18" t="inlineStr">
+      <c r="C131" s="18" t="inlineStr">
         <is>
           <t>4.06 x 3.00</t>
         </is>
       </c>
-      <c r="D130" s="19" t="n">
+      <c r="D131" s="19" t="n">
         <v>12.18</v>
-      </c>
-      <c r="E130" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F130" s="80" t="n">
-        <v>304.5</v>
-      </c>
-      <c r="G130" s="53" t="n"/>
-    </row>
-    <row r="131" ht="19.8" customHeight="1">
-      <c r="A131" s="50" t="n"/>
-      <c r="B131" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C131" s="18" t="inlineStr">
-        <is>
-          <t>1.73 x 3.00</t>
-        </is>
-      </c>
-      <c r="D131" s="19" t="n">
-        <v>5.19</v>
       </c>
       <c r="E131" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F131" s="80" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="G131" s="53" t="n"/>
+    </row>
+    <row r="132" ht="19.8" customHeight="1">
+      <c r="A132" s="50" t="n"/>
+      <c r="B132" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="inlineStr">
+        <is>
+          <t>1.73 x 3.00</t>
+        </is>
+      </c>
+      <c r="D132" s="19" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="E132" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F132" s="80" t="n">
         <v>129.8</v>
       </c>
-      <c r="G131" s="53" t="n"/>
-    </row>
-    <row r="132" ht="19.8" customHeight="1">
-      <c r="A132" s="36" t="inlineStr">
+      <c r="G132" s="53" t="n"/>
+    </row>
+    <row r="133" ht="19.8" customHeight="1">
+      <c r="A133" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B132" s="78" t="inlineStr">
+      <c r="B133" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C132" s="47" t="n"/>
-      <c r="D132" s="18" t="n"/>
-      <c r="E132" s="18" t="n"/>
-      <c r="F132" s="20" t="n"/>
-      <c r="G132" s="53" t="n"/>
-    </row>
-    <row r="133" ht="19.8" customHeight="1">
-      <c r="A133" s="43" t="n"/>
-      <c r="B133" s="79" t="inlineStr">
+      <c r="C133" s="47" t="n"/>
+      <c r="D133" s="18" t="n"/>
+      <c r="E133" s="18" t="n"/>
+      <c r="F133" s="20" t="n"/>
+      <c r="G133" s="53" t="n"/>
+    </row>
+    <row r="134" ht="19.8" customHeight="1">
+      <c r="A134" s="43" t="n"/>
+      <c r="B134" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C133" s="18" t="n"/>
-      <c r="D133" s="19" t="n"/>
-      <c r="E133" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F133" s="80" t="n"/>
-      <c r="G133" s="53" t="n"/>
-    </row>
-    <row r="134" ht="19.8" customHeight="1">
-      <c r="A134" s="47" t="n"/>
-      <c r="B134" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C134" s="18" t="n"/>
       <c r="D134" s="19" t="n"/>
       <c r="E134" s="59" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F134" s="80" t="n"/>
       <c r="G134" s="53" t="n"/>
     </row>
     <row r="135" ht="19.8" customHeight="1">
-      <c r="A135" s="50" t="n"/>
-      <c r="B135" s="82" t="inlineStr">
+      <c r="A135" s="47" t="n"/>
+      <c r="B135" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C135" s="18" t="n"/>
+      <c r="D135" s="19" t="n"/>
+      <c r="E135" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F135" s="80" t="n"/>
+      <c r="G135" s="53" t="n"/>
+    </row>
+    <row r="136" ht="19.8" customHeight="1">
+      <c r="A136" s="50" t="n"/>
+      <c r="B136" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C135" s="18" t="inlineStr">
+      <c r="C136" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D135" s="19" t="n">
+      <c r="D136" s="19" t="n">
         <v>7.02</v>
       </c>
-      <c r="E135" s="59" t="n">
+      <c r="E136" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F135" s="80" t="n">
+      <c r="F136" s="80" t="n">
         <v>105.3</v>
       </c>
-      <c r="G135" s="53" t="n"/>
-    </row>
-    <row r="136" ht="19.8" customHeight="1">
-      <c r="A136" s="36" t="inlineStr">
+      <c r="G136" s="53" t="n"/>
+    </row>
+    <row r="137" ht="19.8" customHeight="1">
+      <c r="A137" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B136" s="78" t="inlineStr">
+      <c r="B137" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C136" s="47" t="n"/>
-      <c r="D136" s="18" t="n"/>
-      <c r="E136" s="18" t="n"/>
-      <c r="F136" s="20" t="n"/>
-      <c r="G136" s="53" t="n"/>
-    </row>
-    <row r="137" ht="19.8" customHeight="1">
-      <c r="A137" s="43" t="n"/>
-      <c r="B137" s="79" t="inlineStr">
+      <c r="C137" s="47" t="n"/>
+      <c r="D137" s="18" t="n"/>
+      <c r="E137" s="18" t="n"/>
+      <c r="F137" s="20" t="n"/>
+      <c r="G137" s="53" t="n"/>
+    </row>
+    <row r="138" ht="19.8" customHeight="1">
+      <c r="A138" s="43" t="n"/>
+      <c r="B138" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C137" s="18" t="inlineStr">
+      <c r="C138" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D137" s="19" t="n">
+      <c r="D138" s="19" t="n">
         <v>7.02</v>
       </c>
-      <c r="E137" s="59" t="n">
+      <c r="E138" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F137" s="80" t="n">
+      <c r="F138" s="80" t="n">
         <v>70.2</v>
       </c>
-      <c r="G137" s="53" t="n"/>
-    </row>
-    <row r="138" ht="19.8" customHeight="1">
-      <c r="A138" s="50" t="n"/>
-      <c r="B138" s="82" t="inlineStr">
+      <c r="G138" s="53" t="n"/>
+    </row>
+    <row r="139" ht="19.8" customHeight="1">
+      <c r="A139" s="50" t="n"/>
+      <c r="B139" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C138" s="18" t="n"/>
-      <c r="D138" s="24" t="n"/>
-      <c r="E138" s="59" t="n">
+      <c r="C139" s="18" t="n"/>
+      <c r="D139" s="24" t="n"/>
+      <c r="E139" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F138" s="80" t="n"/>
-      <c r="G138" s="53" t="n"/>
-    </row>
-    <row r="139" ht="19.8" customHeight="1">
-      <c r="A139" s="36" t="inlineStr">
+      <c r="F139" s="80" t="n"/>
+      <c r="G139" s="53" t="n"/>
+    </row>
+    <row r="140" ht="19.8" customHeight="1">
+      <c r="A140" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B139" s="78" t="inlineStr">
+      <c r="B140" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C139" s="83" t="n"/>
-      <c r="D139" s="36" t="inlineStr">
+      <c r="C140" s="83" t="n"/>
+      <c r="D140" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E139" s="47" t="n"/>
-      <c r="F139" s="20" t="n"/>
-      <c r="G139" s="53" t="n"/>
-    </row>
-    <row r="140" ht="19.8" customHeight="1">
-      <c r="A140" s="43" t="n"/>
-      <c r="B140" s="79" t="inlineStr">
+      <c r="E140" s="47" t="n"/>
+      <c r="F140" s="20" t="n"/>
+      <c r="G140" s="53" t="n"/>
+    </row>
+    <row r="141" ht="19.8" customHeight="1">
+      <c r="A141" s="43" t="n"/>
+      <c r="B141" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C140" s="18" t="n"/>
-      <c r="D140" s="22" t="n"/>
-      <c r="E140" s="59" t="n">
+      <c r="C141" s="18" t="n"/>
+      <c r="D141" s="22" t="n"/>
+      <c r="E141" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="F140" s="80" t="n"/>
-      <c r="G140" s="53" t="n"/>
-    </row>
-    <row r="141" ht="19.8" customHeight="1">
-      <c r="A141" s="47" t="n"/>
-      <c r="B141" s="81" t="inlineStr">
+      <c r="F141" s="80" t="n"/>
+      <c r="G141" s="53" t="n"/>
+    </row>
+    <row r="142" ht="19.8" customHeight="1">
+      <c r="A142" s="47" t="n"/>
+      <c r="B142" s="81" t="inlineStr">
         <is>
           <t>DOS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C141" s="18" t="inlineStr">
+      <c r="C142" s="18" t="inlineStr">
         <is>
           <t>7.02 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D141" s="19" t="n">
+      <c r="D142" s="19" t="n">
         <v>21.06</v>
       </c>
-      <c r="E141" s="59" t="n">
+      <c r="E142" s="59" t="n">
         <v>9</v>
       </c>
-      <c r="F141" s="80" t="n">
+      <c r="F142" s="80" t="n">
         <v>189.5</v>
       </c>
-      <c r="G141" s="53" t="n"/>
-    </row>
-    <row r="142" ht="19.8" customHeight="1">
-      <c r="A142" s="50" t="n"/>
-      <c r="B142" s="82" t="inlineStr">
+      <c r="G142" s="53" t="n"/>
+    </row>
+    <row r="143" ht="19.8" customHeight="1">
+      <c r="A143" s="50" t="n"/>
+      <c r="B143" s="82" t="inlineStr">
         <is>
           <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C142" s="18" t="n"/>
-      <c r="D142" s="19" t="n"/>
-      <c r="E142" s="59" t="n">
+      <c r="C143" s="18" t="n"/>
+      <c r="D143" s="19" t="n"/>
+      <c r="E143" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F142" s="84" t="n"/>
-      <c r="G142" s="53" t="n"/>
-    </row>
-    <row r="143" ht="19.8" customHeight="1">
-      <c r="A143" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B143" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C143" s="47" t="n"/>
-      <c r="D143" s="18" t="n"/>
-      <c r="E143" s="20" t="n"/>
-      <c r="F143" s="85" t="n">
-        <v>1260.1</v>
-      </c>
+      <c r="F143" s="84" t="n"/>
       <c r="G143" s="53" t="n"/>
     </row>
     <row r="144" ht="19.8" customHeight="1">
       <c r="A144" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B144" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C144" s="47" t="n"/>
+      <c r="D144" s="18" t="n"/>
+      <c r="E144" s="20" t="n"/>
+      <c r="F144" s="85" t="n">
+        <v>1260.1</v>
+      </c>
+      <c r="G144" s="53" t="n"/>
+    </row>
+    <row r="145" ht="19.8" customHeight="1">
+      <c r="A145" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B144" s="78" t="inlineStr">
+      <c r="B145" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C144" s="47" t="inlineStr">
+      <c r="C145" s="47" t="inlineStr">
         <is>
           <t>1260.10  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D144" s="12" t="n"/>
-      <c r="E144" s="14" t="n"/>
-      <c r="F144" s="85" t="n">
+      <c r="D145" s="12" t="n"/>
+      <c r="E145" s="14" t="n"/>
+      <c r="F145" s="85" t="n">
         <v>1348.3</v>
       </c>
-      <c r="G144" s="53" t="n"/>
-    </row>
-    <row r="145" ht="19.8" customHeight="1">
-      <c r="A145" s="43" t="n"/>
-      <c r="B145" s="86" t="inlineStr">
+      <c r="G145" s="53" t="n"/>
+    </row>
+    <row r="146" ht="19.8" customHeight="1">
+      <c r="A146" s="43" t="n"/>
+      <c r="B146" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C145" s="18" t="n"/>
-      <c r="D145" s="12" t="n"/>
-      <c r="E145" s="39" t="n"/>
-      <c r="F145" s="87" t="n"/>
-      <c r="G145" s="53" t="n"/>
-    </row>
-    <row r="146" ht="19.8" customHeight="1">
-      <c r="A146" s="83" t="n"/>
-      <c r="B146" s="78" t="inlineStr">
+      <c r="C146" s="18" t="n"/>
+      <c r="D146" s="12" t="n"/>
+      <c r="E146" s="39" t="n"/>
+      <c r="F146" s="87" t="n"/>
+      <c r="G146" s="53" t="n"/>
+    </row>
+    <row r="147" ht="19.8" customHeight="1">
+      <c r="A147" s="83" t="n"/>
+      <c r="B147" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C146" s="47" t="n"/>
-      <c r="D146" s="12" t="n"/>
-      <c r="E146" s="14" t="n"/>
-      <c r="F146" s="85" t="n">
+      <c r="C147" s="47" t="n"/>
+      <c r="D147" s="12" t="n"/>
+      <c r="E147" s="14" t="n"/>
+      <c r="F147" s="85" t="n">
         <v>1348.3</v>
       </c>
-      <c r="G146" s="53" t="n"/>
-    </row>
-    <row r="147" ht="19.8" customHeight="1">
-      <c r="A147" s="91" t="n"/>
-      <c r="B147" s="78" t="inlineStr">
+      <c r="G147" s="53" t="n"/>
+    </row>
+    <row r="148" ht="19.8" customHeight="1">
+      <c r="A148" s="89" t="n"/>
+      <c r="B148" s="78" t="inlineStr">
         <is>
           <t>SIN EMISOR</t>
         </is>
       </c>
-      <c r="C147" s="47" t="inlineStr">
+      <c r="C148" s="47" t="inlineStr">
         <is>
           <t>la cubre el radiador de 14 - Play room</t>
         </is>
       </c>
-      <c r="D147" s="12" t="n"/>
-      <c r="E147" s="39" t="n"/>
-      <c r="F147" s="61" t="n"/>
-      <c r="G147" s="53" t="n"/>
-    </row>
-    <row r="148" ht="19.8" customHeight="1">
-      <c r="A148" s="8" t="inlineStr">
+      <c r="D148" s="12" t="n"/>
+      <c r="E148" s="39" t="n"/>
+      <c r="F148" s="61" t="n"/>
+      <c r="G148" s="53" t="n"/>
+    </row>
+    <row r="149" ht="19.8" customHeight="1">
+      <c r="A149" s="8" t="inlineStr">
         <is>
           <t>LOCAL  09 - Dormitorio suite   (PB)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B148" s="3" t="n"/>
-      <c r="C148" s="11" t="n"/>
-      <c r="D148" s="11" t="n"/>
-      <c r="E148" s="11" t="n"/>
-      <c r="F148" s="42" t="n"/>
-      <c r="G148" s="53" t="n"/>
-    </row>
-    <row r="149" ht="32" customHeight="1">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="B149" s="3" t="n"/>
+      <c r="C149" s="11" t="n"/>
+      <c r="D149" s="11" t="n"/>
+      <c r="E149" s="11" t="n"/>
+      <c r="F149" s="42" t="n"/>
+      <c r="G149" s="53" t="n"/>
+    </row>
+    <row r="150" ht="32" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G149" s="53" t="n"/>
-    </row>
-    <row r="150" ht="19.8" customHeight="1">
-      <c r="A150" s="36" t="inlineStr">
+      <c r="G150" s="53" t="n"/>
+    </row>
+    <row r="151" ht="19.8" customHeight="1">
+      <c r="A151" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B150" s="78" t="inlineStr">
+      <c r="B151" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C150" s="43" t="n"/>
-      <c r="D150" s="58" t="n"/>
-      <c r="E150" s="58" t="n"/>
-      <c r="F150" s="61" t="n"/>
-      <c r="G150" s="53" t="n"/>
-    </row>
-    <row r="151" ht="19.8" customHeight="1">
-      <c r="A151" s="43" t="n"/>
-      <c r="B151" s="79" t="inlineStr">
+      <c r="C151" s="43" t="n"/>
+      <c r="D151" s="58" t="n"/>
+      <c r="E151" s="58" t="n"/>
+      <c r="F151" s="61" t="n"/>
+      <c r="G151" s="53" t="n"/>
+    </row>
+    <row r="152" ht="19.8" customHeight="1">
+      <c r="A152" s="43" t="n"/>
+      <c r="B152" s="79" t="inlineStr">
         <is>
           <t>VA01 (2)</t>
         </is>
       </c>
-      <c r="C151" s="18" t="inlineStr">
+      <c r="C152" s="18" t="inlineStr">
         <is>
           <t>0.75 x 3.00</t>
         </is>
       </c>
-      <c r="D151" s="19" t="n">
+      <c r="D152" s="19" t="n">
         <v>2.25</v>
-      </c>
-      <c r="E151" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F151" s="80" t="n">
-        <v>135</v>
-      </c>
-      <c r="G151" s="53" t="n"/>
-    </row>
-    <row r="152" ht="19.8" customHeight="1">
-      <c r="A152" s="50" t="n"/>
-      <c r="B152" s="82" t="inlineStr">
-        <is>
-          <t>PV03</t>
-        </is>
-      </c>
-      <c r="C152" s="18" t="inlineStr">
-        <is>
-          <t>1.76 x 3.00</t>
-        </is>
-      </c>
-      <c r="D152" s="19" t="n">
-        <v>5.28</v>
       </c>
       <c r="E152" s="59" t="n">
         <v>60</v>
       </c>
       <c r="F152" s="80" t="n">
+        <v>135</v>
+      </c>
+      <c r="G152" s="53" t="n"/>
+    </row>
+    <row r="153" ht="19.8" customHeight="1">
+      <c r="A153" s="50" t="n"/>
+      <c r="B153" s="82" t="inlineStr">
+        <is>
+          <t>PV03</t>
+        </is>
+      </c>
+      <c r="C153" s="18" t="inlineStr">
+        <is>
+          <t>1.76 x 3.00</t>
+        </is>
+      </c>
+      <c r="D153" s="19" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="E153" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F153" s="80" t="n">
         <v>316.8</v>
       </c>
-      <c r="G152" s="53" t="n"/>
-    </row>
-    <row r="153" ht="19.8" customHeight="1">
-      <c r="A153" s="36" t="inlineStr">
+      <c r="G153" s="53" t="n"/>
+    </row>
+    <row r="154" ht="19.8" customHeight="1">
+      <c r="A154" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B153" s="78" t="inlineStr">
+      <c r="B154" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C153" s="47" t="n"/>
-      <c r="D153" s="18" t="n"/>
-      <c r="E153" s="18" t="n"/>
-      <c r="F153" s="20" t="n"/>
-      <c r="G153" s="53" t="n"/>
-    </row>
-    <row r="154" ht="19.8" customHeight="1">
-      <c r="A154" s="43" t="n"/>
-      <c r="B154" s="79" t="inlineStr">
+      <c r="C154" s="47" t="n"/>
+      <c r="D154" s="18" t="n"/>
+      <c r="E154" s="18" t="n"/>
+      <c r="F154" s="20" t="n"/>
+      <c r="G154" s="53" t="n"/>
+    </row>
+    <row r="155" ht="19.8" customHeight="1">
+      <c r="A155" s="43" t="n"/>
+      <c r="B155" s="79" t="inlineStr">
         <is>
           <t>AISLADAS (NE)</t>
-        </is>
-      </c>
-      <c r="C154" s="18" t="inlineStr">
-        <is>
-          <t>3.50 x 3.00</t>
-        </is>
-      </c>
-      <c r="D154" s="19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="E154" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F154" s="80" t="n">
-        <v>210</v>
-      </c>
-      <c r="G154" s="53" t="n"/>
-    </row>
-    <row r="155" ht="19.8" customHeight="1">
-      <c r="A155" s="47" t="n"/>
-      <c r="B155" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS (SO)</t>
         </is>
       </c>
       <c r="C155" s="18" t="inlineStr">
@@ -22672,7 +22672,7 @@
       <c r="A156" s="47" t="n"/>
       <c r="B156" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>AISLADAS (SO)</t>
         </is>
       </c>
       <c r="C156" s="18" t="inlineStr">
@@ -22695,7 +22695,7 @@
       <c r="A157" s="47" t="n"/>
       <c r="B157" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C157" s="18" t="inlineStr">
@@ -22707,338 +22707,346 @@
         <v>10.5</v>
       </c>
       <c r="E157" s="59" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F157" s="80" t="n">
-        <v>262.5</v>
+        <v>210</v>
       </c>
       <c r="G157" s="53" t="n"/>
     </row>
     <row r="158" ht="19.8" customHeight="1">
-      <c r="A158" s="50" t="n"/>
-      <c r="B158" s="82" t="inlineStr">
+      <c r="A158" s="47" t="n"/>
+      <c r="B158" s="81" t="inlineStr">
         <is>
           <t>INTERIORES</t>
         </is>
       </c>
-      <c r="C158" s="18" t="n"/>
-      <c r="D158" s="19" t="n"/>
+      <c r="C158" s="18" t="inlineStr">
+        <is>
+          <t>3.50 x 3.00</t>
+        </is>
+      </c>
+      <c r="D158" s="19" t="n">
+        <v>10.5</v>
+      </c>
       <c r="E158" s="59" t="n">
         <v>25</v>
       </c>
-      <c r="F158" s="80" t="n"/>
+      <c r="F158" s="80" t="n">
+        <v>262.5</v>
+      </c>
       <c r="G158" s="53" t="n"/>
     </row>
     <row r="159" ht="19.8" customHeight="1">
-      <c r="A159" s="36" t="inlineStr">
+      <c r="A159" s="50" t="n"/>
+      <c r="B159" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="n"/>
+      <c r="D159" s="19" t="n"/>
+      <c r="E159" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F159" s="80" t="n"/>
+      <c r="G159" s="53" t="n"/>
+    </row>
+    <row r="160" ht="19.8" customHeight="1">
+      <c r="A160" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B159" s="78" t="inlineStr">
+      <c r="B160" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C159" s="47" t="n"/>
-      <c r="D159" s="18" t="n"/>
-      <c r="E159" s="18" t="n"/>
-      <c r="F159" s="20" t="n"/>
-      <c r="G159" s="53" t="n"/>
-    </row>
-    <row r="160" ht="19.8" customHeight="1">
-      <c r="A160" s="43" t="n"/>
-      <c r="B160" s="79" t="inlineStr">
+      <c r="C160" s="47" t="n"/>
+      <c r="D160" s="18" t="n"/>
+      <c r="E160" s="18" t="n"/>
+      <c r="F160" s="20" t="n"/>
+      <c r="G160" s="53" t="n"/>
+    </row>
+    <row r="161" ht="19.8" customHeight="1">
+      <c r="A161" s="43" t="n"/>
+      <c r="B161" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C160" s="18" t="n"/>
-      <c r="D160" s="19" t="n"/>
-      <c r="E160" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F160" s="80" t="n"/>
-      <c r="G160" s="53" t="n"/>
-    </row>
-    <row r="161" ht="19.8" customHeight="1">
-      <c r="A161" s="47" t="n"/>
-      <c r="B161" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C161" s="18" t="n"/>
       <c r="D161" s="19" t="n"/>
       <c r="E161" s="59" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F161" s="80" t="n"/>
       <c r="G161" s="53" t="n"/>
     </row>
     <row r="162" ht="19.8" customHeight="1">
-      <c r="A162" s="50" t="n"/>
-      <c r="B162" s="82" t="inlineStr">
+      <c r="A162" s="47" t="n"/>
+      <c r="B162" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C162" s="18" t="n"/>
+      <c r="D162" s="19" t="n"/>
+      <c r="E162" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F162" s="80" t="n"/>
+      <c r="G162" s="53" t="n"/>
+    </row>
+    <row r="163" ht="19.8" customHeight="1">
+      <c r="A163" s="50" t="n"/>
+      <c r="B163" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C162" s="18" t="inlineStr">
+      <c r="C163" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D162" s="19" t="n">
+      <c r="D163" s="19" t="n">
         <v>12.25</v>
       </c>
-      <c r="E162" s="59" t="n">
+      <c r="E163" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F162" s="80" t="n">
+      <c r="F163" s="80" t="n">
         <v>183.8</v>
       </c>
-      <c r="G162" s="53" t="n"/>
-    </row>
-    <row r="163" ht="19.8" customHeight="1">
-      <c r="A163" s="36" t="inlineStr">
+      <c r="G163" s="53" t="n"/>
+    </row>
+    <row r="164" ht="19.8" customHeight="1">
+      <c r="A164" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B163" s="78" t="inlineStr">
+      <c r="B164" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C163" s="47" t="n"/>
-      <c r="D163" s="18" t="n"/>
-      <c r="E163" s="18" t="n"/>
-      <c r="F163" s="20" t="n"/>
-      <c r="G163" s="53" t="n"/>
-    </row>
-    <row r="164" ht="19.8" customHeight="1">
-      <c r="A164" s="43" t="n"/>
-      <c r="B164" s="79" t="inlineStr">
+      <c r="C164" s="47" t="n"/>
+      <c r="D164" s="18" t="n"/>
+      <c r="E164" s="18" t="n"/>
+      <c r="F164" s="20" t="n"/>
+      <c r="G164" s="53" t="n"/>
+    </row>
+    <row r="165" ht="19.8" customHeight="1">
+      <c r="A165" s="43" t="n"/>
+      <c r="B165" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C164" s="18" t="inlineStr">
+      <c r="C165" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D164" s="19" t="n">
+      <c r="D165" s="19" t="n">
         <v>12.25</v>
       </c>
-      <c r="E164" s="59" t="n">
+      <c r="E165" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F164" s="80" t="n">
+      <c r="F165" s="80" t="n">
         <v>122.5</v>
       </c>
-      <c r="G164" s="53" t="n"/>
-    </row>
-    <row r="165" ht="19.8" customHeight="1">
-      <c r="A165" s="50" t="n"/>
-      <c r="B165" s="82" t="inlineStr">
+      <c r="G165" s="53" t="n"/>
+    </row>
+    <row r="166" ht="19.8" customHeight="1">
+      <c r="A166" s="50" t="n"/>
+      <c r="B166" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C165" s="18" t="n"/>
-      <c r="D165" s="24" t="n"/>
-      <c r="E165" s="59" t="n">
+      <c r="C166" s="18" t="n"/>
+      <c r="D166" s="24" t="n"/>
+      <c r="E166" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F165" s="80" t="n"/>
-      <c r="G165" s="53" t="n"/>
-    </row>
-    <row r="166" ht="19.8" customHeight="1">
-      <c r="A166" s="36" t="inlineStr">
+      <c r="F166" s="80" t="n"/>
+      <c r="G166" s="53" t="n"/>
+    </row>
+    <row r="167" ht="19.8" customHeight="1">
+      <c r="A167" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B166" s="78" t="inlineStr">
+      <c r="B167" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C166" s="83" t="n"/>
-      <c r="D166" s="36" t="inlineStr">
+      <c r="C167" s="83" t="n"/>
+      <c r="D167" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E166" s="47" t="n"/>
-      <c r="F166" s="20" t="n"/>
-      <c r="G166" s="53" t="n"/>
-    </row>
-    <row r="167" ht="19.8" customHeight="1">
-      <c r="A167" s="43" t="n"/>
-      <c r="B167" s="79" t="inlineStr">
+      <c r="E167" s="47" t="n"/>
+      <c r="F167" s="20" t="n"/>
+      <c r="G167" s="53" t="n"/>
+    </row>
+    <row r="168" ht="19.8" customHeight="1">
+      <c r="A168" s="43" t="n"/>
+      <c r="B168" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C167" s="18" t="n"/>
-      <c r="D167" s="22" t="n"/>
-      <c r="E167" s="59" t="n">
+      <c r="C168" s="18" t="n"/>
+      <c r="D168" s="22" t="n"/>
+      <c r="E168" s="59" t="n">
         <v>6</v>
-      </c>
-      <c r="F167" s="80" t="n"/>
-      <c r="G167" s="53" t="n"/>
-    </row>
-    <row r="168" ht="19.8" customHeight="1">
-      <c r="A168" s="47" t="n"/>
-      <c r="B168" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C168" s="18" t="n"/>
-      <c r="D168" s="19" t="n"/>
-      <c r="E168" s="59" t="n">
-        <v>9</v>
       </c>
       <c r="F168" s="80" t="n"/>
       <c r="G168" s="53" t="n"/>
     </row>
     <row r="169" ht="19.8" customHeight="1">
-      <c r="A169" s="50" t="n"/>
-      <c r="B169" s="82" t="inlineStr">
+      <c r="A169" s="47" t="n"/>
+      <c r="B169" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C169" s="18" t="n"/>
+      <c r="D169" s="19" t="n"/>
+      <c r="E169" s="59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F169" s="80" t="n"/>
+      <c r="G169" s="53" t="n"/>
+    </row>
+    <row r="170" ht="19.8" customHeight="1">
+      <c r="A170" s="50" t="n"/>
+      <c r="B170" s="82" t="inlineStr">
         <is>
           <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C169" s="18" t="inlineStr">
+      <c r="C170" s="18" t="inlineStr">
         <is>
           <t>12.25 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D169" s="19" t="n">
+      <c r="D170" s="19" t="n">
         <v>36.75</v>
       </c>
-      <c r="E169" s="59" t="n">
+      <c r="E170" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F169" s="84" t="n">
+      <c r="F170" s="84" t="n">
         <v>441</v>
-      </c>
-      <c r="G169" s="53" t="n"/>
-    </row>
-    <row r="170" ht="19.8" customHeight="1">
-      <c r="A170" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B170" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C170" s="47" t="n"/>
-      <c r="D170" s="18" t="n"/>
-      <c r="E170" s="20" t="n"/>
-      <c r="F170" s="85" t="n">
-        <v>2091.6</v>
       </c>
       <c r="G170" s="53" t="n"/>
     </row>
     <row r="171" ht="19.8" customHeight="1">
       <c r="A171" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B171" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C171" s="47" t="n"/>
+      <c r="D171" s="18" t="n"/>
+      <c r="E171" s="20" t="n"/>
+      <c r="F171" s="85" t="n">
+        <v>2091.6</v>
+      </c>
+      <c r="G171" s="53" t="n"/>
+    </row>
+    <row r="172" ht="19.8" customHeight="1">
+      <c r="A172" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B171" s="78" t="inlineStr">
+      <c r="B172" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C171" s="47" t="inlineStr">
+      <c r="C172" s="47" t="inlineStr">
         <is>
           <t>2091.60  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D171" s="12" t="n"/>
-      <c r="E171" s="14" t="n"/>
-      <c r="F171" s="85" t="n">
+      <c r="D172" s="12" t="n"/>
+      <c r="E172" s="14" t="n"/>
+      <c r="F172" s="85" t="n">
         <v>2238</v>
       </c>
-      <c r="G171" s="53" t="n"/>
-    </row>
-    <row r="172" ht="19.8" customHeight="1">
-      <c r="A172" s="43" t="n"/>
-      <c r="B172" s="86" t="inlineStr">
+      <c r="G172" s="53" t="n"/>
+    </row>
+    <row r="173" ht="19.8" customHeight="1">
+      <c r="A173" s="43" t="n"/>
+      <c r="B173" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C172" s="18" t="n"/>
-      <c r="D172" s="12" t="n"/>
-      <c r="E172" s="39" t="n"/>
-      <c r="F172" s="87" t="n"/>
-      <c r="G172" s="53" t="n"/>
-    </row>
-    <row r="173" ht="19.8" customHeight="1">
-      <c r="A173" s="83" t="n"/>
-      <c r="B173" s="78" t="inlineStr">
+      <c r="C173" s="18" t="n"/>
+      <c r="D173" s="12" t="n"/>
+      <c r="E173" s="39" t="n"/>
+      <c r="F173" s="87" t="n"/>
+      <c r="G173" s="53" t="n"/>
+    </row>
+    <row r="174" ht="19.8" customHeight="1">
+      <c r="A174" s="83" t="n"/>
+      <c r="B174" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C173" s="47" t="n"/>
-      <c r="D173" s="12" t="n"/>
-      <c r="E173" s="14" t="n"/>
-      <c r="F173" s="85" t="n">
+      <c r="C174" s="47" t="n"/>
+      <c r="D174" s="12" t="n"/>
+      <c r="E174" s="14" t="n"/>
+      <c r="F174" s="85" t="n">
         <v>2238</v>
       </c>
-      <c r="G173" s="53" t="n"/>
-    </row>
-    <row r="174" ht="19.8" customHeight="1">
-      <c r="A174" s="47" t="n"/>
-      <c r="B174" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C174" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
-      </c>
-      <c r="D174" s="12" t="n"/>
-      <c r="E174" s="39" t="n"/>
-      <c r="F174" s="61" t="n"/>
       <c r="G174" s="53" t="n"/>
     </row>
     <row r="175" ht="19.8" customHeight="1">
       <c r="A175" s="47" t="n"/>
-      <c r="B175" s="60" t="inlineStr">
-        <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C175" s="19" t="n">
-        <v>274.4</v>
+      <c r="B175" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C175" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
       </c>
       <c r="D175" s="12" t="n"/>
       <c r="E175" s="39" t="n"/>
-      <c r="F175" s="20" t="n"/>
+      <c r="F175" s="61" t="n"/>
       <c r="G175" s="53" t="n"/>
     </row>
     <row r="176" ht="19.8" customHeight="1">
       <c r="A176" s="47" t="n"/>
       <c r="B176" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
-        </is>
-      </c>
-      <c r="C176" s="59" t="n">
-        <v>9</v>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C176" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D176" s="12" t="n"/>
       <c r="E176" s="39" t="n"/>
@@ -23049,11 +23057,11 @@
       <c r="A177" s="47" t="n"/>
       <c r="B177" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C177" s="59" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="D177" s="12" t="n"/>
       <c r="E177" s="39" t="n"/>
@@ -23061,16 +23069,14 @@
       <c r="G177" s="53" t="n"/>
     </row>
     <row r="178" ht="19.8" customHeight="1">
-      <c r="A178" s="50" t="n"/>
+      <c r="A178" s="47" t="n"/>
       <c r="B178" s="60" t="inlineStr">
         <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C178" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
+          <t>Ancho del radiador (cm)</t>
+        </is>
+      </c>
+      <c r="C178" s="59" t="n">
+        <v>72</v>
       </c>
       <c r="D178" s="12" t="n"/>
       <c r="E178" s="39" t="n"/>
@@ -23078,167 +23084,161 @@
       <c r="G178" s="53" t="n"/>
     </row>
     <row r="179" ht="19.8" customHeight="1">
-      <c r="A179" s="8" t="inlineStr">
+      <c r="A179" s="50" t="n"/>
+      <c r="B179" s="60" t="inlineStr">
+        <is>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C179" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
+      </c>
+      <c r="D179" s="12" t="n"/>
+      <c r="E179" s="39" t="n"/>
+      <c r="F179" s="20" t="n"/>
+      <c r="G179" s="53" t="n"/>
+    </row>
+    <row r="180" ht="19.8" customHeight="1">
+      <c r="A180" s="8" t="inlineStr">
         <is>
           <t>LOCAL  10 - Bano suite   (PB)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B179" s="11" t="n"/>
-      <c r="C179" s="11" t="n"/>
-      <c r="D179" s="11" t="n"/>
-      <c r="E179" s="11" t="n"/>
-      <c r="F179" s="42" t="n"/>
-      <c r="G179" s="53" t="n"/>
-    </row>
-    <row r="180" ht="32" customHeight="1">
-      <c r="A180" s="2" t="inlineStr">
+      <c r="B180" s="11" t="n"/>
+      <c r="C180" s="11" t="n"/>
+      <c r="D180" s="11" t="n"/>
+      <c r="E180" s="11" t="n"/>
+      <c r="F180" s="42" t="n"/>
+      <c r="G180" s="53" t="n"/>
+    </row>
+    <row r="181" ht="32" customHeight="1">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G180" s="53" t="n"/>
-    </row>
-    <row r="181" ht="19.8" customHeight="1">
-      <c r="A181" s="36" t="inlineStr">
+      <c r="G181" s="53" t="n"/>
+    </row>
+    <row r="182" ht="19.8" customHeight="1">
+      <c r="A182" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B181" s="78" t="inlineStr">
+      <c r="B182" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C181" s="43" t="n"/>
-      <c r="D181" s="58" t="n"/>
-      <c r="E181" s="58" t="n"/>
-      <c r="F181" s="61" t="n"/>
-      <c r="G181" s="53" t="n"/>
-    </row>
-    <row r="182" ht="19.8" customHeight="1">
-      <c r="A182" s="89" t="n"/>
-      <c r="B182" s="90" t="inlineStr">
+      <c r="C182" s="43" t="n"/>
+      <c r="D182" s="58" t="n"/>
+      <c r="E182" s="58" t="n"/>
+      <c r="F182" s="61" t="n"/>
+      <c r="G182" s="53" t="n"/>
+    </row>
+    <row r="183" ht="19.8" customHeight="1">
+      <c r="A183" s="90" t="n"/>
+      <c r="B183" s="91" t="inlineStr">
         <is>
           <t>VA02</t>
         </is>
       </c>
-      <c r="C182" s="18" t="inlineStr">
+      <c r="C183" s="18" t="inlineStr">
         <is>
           <t>0.75 x 2.15</t>
         </is>
       </c>
-      <c r="D182" s="19" t="n">
+      <c r="D183" s="19" t="n">
         <v>1.61</v>
       </c>
-      <c r="E182" s="59" t="n">
+      <c r="E183" s="59" t="n">
         <v>60</v>
       </c>
-      <c r="F182" s="80" t="n">
+      <c r="F183" s="80" t="n">
         <v>96.59999999999999</v>
       </c>
-      <c r="G182" s="53" t="n"/>
-    </row>
-    <row r="183" ht="19.8" customHeight="1">
-      <c r="A183" s="36" t="inlineStr">
+      <c r="G183" s="53" t="n"/>
+    </row>
+    <row r="184" ht="19.8" customHeight="1">
+      <c r="A184" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B183" s="78" t="inlineStr">
+      <c r="B184" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C183" s="47" t="n"/>
-      <c r="D183" s="18" t="n"/>
-      <c r="E183" s="18" t="n"/>
-      <c r="F183" s="20" t="n"/>
-      <c r="G183" s="53" t="n"/>
-    </row>
-    <row r="184" ht="19.8" customHeight="1">
-      <c r="A184" s="43" t="n"/>
-      <c r="B184" s="79" t="inlineStr">
+      <c r="C184" s="47" t="n"/>
+      <c r="D184" s="18" t="n"/>
+      <c r="E184" s="18" t="n"/>
+      <c r="F184" s="20" t="n"/>
+      <c r="G184" s="53" t="n"/>
+    </row>
+    <row r="185" ht="19.8" customHeight="1">
+      <c r="A185" s="43" t="n"/>
+      <c r="B185" s="79" t="inlineStr">
         <is>
           <t>AISLADAS (NE)</t>
         </is>
       </c>
-      <c r="C184" s="18" t="inlineStr">
+      <c r="C185" s="18" t="inlineStr">
         <is>
           <t>3.38 x 3.00</t>
         </is>
       </c>
-      <c r="D184" s="19" t="n">
+      <c r="D185" s="19" t="n">
         <v>10.14</v>
       </c>
-      <c r="E184" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F184" s="80" t="n">
-        <v>202.8</v>
-      </c>
-      <c r="G184" s="53" t="n"/>
-    </row>
-    <row r="185" ht="19.8" customHeight="1">
-      <c r="A185" s="47" t="n"/>
-      <c r="B185" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C185" s="18" t="n"/>
-      <c r="D185" s="19" t="n"/>
       <c r="E185" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F185" s="80" t="n"/>
+      <c r="F185" s="80" t="n">
+        <v>202.8</v>
+      </c>
       <c r="G185" s="53" t="n"/>
     </row>
     <row r="186" ht="19.8" customHeight="1">
       <c r="A186" s="47" t="n"/>
       <c r="B186" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C186" s="18" t="inlineStr">
-        <is>
-          <t>1.72 x 3.00</t>
-        </is>
-      </c>
-      <c r="D186" s="19" t="n">
-        <v>5.16</v>
-      </c>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C186" s="18" t="n"/>
+      <c r="D186" s="19" t="n"/>
       <c r="E186" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F186" s="80" t="n">
-        <v>129</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F186" s="80" t="n"/>
       <c r="G186" s="53" t="n"/>
     </row>
     <row r="187" ht="19.8" customHeight="1">
@@ -23250,353 +23250,361 @@
       </c>
       <c r="C187" s="18" t="inlineStr">
         <is>
-          <t>3.38 x 3.00</t>
+          <t>1.72 x 3.00</t>
         </is>
       </c>
       <c r="D187" s="19" t="n">
-        <v>10.14</v>
+        <v>5.16</v>
       </c>
       <c r="E187" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F187" s="80" t="n">
-        <v>253.5</v>
+        <v>129</v>
       </c>
       <c r="G187" s="53" t="n"/>
     </row>
     <row r="188" ht="19.8" customHeight="1">
-      <c r="A188" s="50" t="n"/>
-      <c r="B188" s="82" t="inlineStr">
+      <c r="A188" s="47" t="n"/>
+      <c r="B188" s="81" t="inlineStr">
         <is>
           <t>INTERIORES</t>
         </is>
       </c>
       <c r="C188" s="18" t="inlineStr">
         <is>
-          <t>1.72 x 3.00</t>
+          <t>3.38 x 3.00</t>
         </is>
       </c>
       <c r="D188" s="19" t="n">
-        <v>5.16</v>
+        <v>10.14</v>
       </c>
       <c r="E188" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F188" s="80" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="G188" s="53" t="n"/>
+    </row>
+    <row r="189" ht="19.8" customHeight="1">
+      <c r="A189" s="50" t="n"/>
+      <c r="B189" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C189" s="18" t="inlineStr">
+        <is>
+          <t>1.72 x 3.00</t>
+        </is>
+      </c>
+      <c r="D189" s="19" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="E189" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F189" s="80" t="n">
         <v>129</v>
       </c>
-      <c r="G188" s="53" t="n"/>
-    </row>
-    <row r="189" ht="19.8" customHeight="1">
-      <c r="A189" s="36" t="inlineStr">
+      <c r="G189" s="53" t="n"/>
+    </row>
+    <row r="190" ht="19.8" customHeight="1">
+      <c r="A190" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B189" s="78" t="inlineStr">
+      <c r="B190" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C189" s="47" t="n"/>
-      <c r="D189" s="18" t="n"/>
-      <c r="E189" s="18" t="n"/>
-      <c r="F189" s="20" t="n"/>
-      <c r="G189" s="53" t="n"/>
-    </row>
-    <row r="190" ht="19.8" customHeight="1">
-      <c r="A190" s="43" t="n"/>
-      <c r="B190" s="79" t="inlineStr">
+      <c r="C190" s="47" t="n"/>
+      <c r="D190" s="18" t="n"/>
+      <c r="E190" s="18" t="n"/>
+      <c r="F190" s="20" t="n"/>
+      <c r="G190" s="53" t="n"/>
+    </row>
+    <row r="191" ht="19.8" customHeight="1">
+      <c r="A191" s="43" t="n"/>
+      <c r="B191" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C190" s="18" t="n"/>
-      <c r="D190" s="19" t="n"/>
-      <c r="E190" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F190" s="80" t="n"/>
-      <c r="G190" s="53" t="n"/>
-    </row>
-    <row r="191" ht="19.8" customHeight="1">
-      <c r="A191" s="47" t="n"/>
-      <c r="B191" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C191" s="18" t="n"/>
       <c r="D191" s="19" t="n"/>
       <c r="E191" s="59" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F191" s="80" t="n"/>
       <c r="G191" s="53" t="n"/>
     </row>
     <row r="192" ht="19.8" customHeight="1">
-      <c r="A192" s="50" t="n"/>
-      <c r="B192" s="82" t="inlineStr">
+      <c r="A192" s="47" t="n"/>
+      <c r="B192" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C192" s="18" t="n"/>
+      <c r="D192" s="19" t="n"/>
+      <c r="E192" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F192" s="80" t="n"/>
+      <c r="G192" s="53" t="n"/>
+    </row>
+    <row r="193" ht="19.8" customHeight="1">
+      <c r="A193" s="50" t="n"/>
+      <c r="B193" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C192" s="18" t="inlineStr">
+      <c r="C193" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D192" s="19" t="n">
+      <c r="D193" s="19" t="n">
         <v>5.81</v>
       </c>
-      <c r="E192" s="59" t="n">
+      <c r="E193" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F192" s="80" t="n">
+      <c r="F193" s="80" t="n">
         <v>87.2</v>
       </c>
-      <c r="G192" s="53" t="n"/>
-    </row>
-    <row r="193" ht="19.8" customHeight="1">
-      <c r="A193" s="36" t="inlineStr">
+      <c r="G193" s="53" t="n"/>
+    </row>
+    <row r="194" ht="19.8" customHeight="1">
+      <c r="A194" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B193" s="78" t="inlineStr">
+      <c r="B194" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C193" s="47" t="n"/>
-      <c r="D193" s="18" t="n"/>
-      <c r="E193" s="18" t="n"/>
-      <c r="F193" s="20" t="n"/>
-      <c r="G193" s="53" t="n"/>
-    </row>
-    <row r="194" ht="19.8" customHeight="1">
-      <c r="A194" s="43" t="n"/>
-      <c r="B194" s="79" t="inlineStr">
+      <c r="C194" s="47" t="n"/>
+      <c r="D194" s="18" t="n"/>
+      <c r="E194" s="18" t="n"/>
+      <c r="F194" s="20" t="n"/>
+      <c r="G194" s="53" t="n"/>
+    </row>
+    <row r="195" ht="19.8" customHeight="1">
+      <c r="A195" s="43" t="n"/>
+      <c r="B195" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C194" s="18" t="inlineStr">
+      <c r="C195" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D194" s="19" t="n">
+      <c r="D195" s="19" t="n">
         <v>5.81</v>
       </c>
-      <c r="E194" s="59" t="n">
+      <c r="E195" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F194" s="80" t="n">
+      <c r="F195" s="80" t="n">
         <v>58.1</v>
       </c>
-      <c r="G194" s="53" t="n"/>
-    </row>
-    <row r="195" ht="19.8" customHeight="1">
-      <c r="A195" s="50" t="n"/>
-      <c r="B195" s="82" t="inlineStr">
+      <c r="G195" s="53" t="n"/>
+    </row>
+    <row r="196" ht="19.8" customHeight="1">
+      <c r="A196" s="50" t="n"/>
+      <c r="B196" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C195" s="18" t="n"/>
-      <c r="D195" s="24" t="n"/>
-      <c r="E195" s="59" t="n">
+      <c r="C196" s="18" t="n"/>
+      <c r="D196" s="24" t="n"/>
+      <c r="E196" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F195" s="80" t="n"/>
-      <c r="G195" s="53" t="n"/>
-    </row>
-    <row r="196" ht="19.8" customHeight="1">
-      <c r="A196" s="36" t="inlineStr">
+      <c r="F196" s="80" t="n"/>
+      <c r="G196" s="53" t="n"/>
+    </row>
+    <row r="197" ht="19.8" customHeight="1">
+      <c r="A197" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B196" s="78" t="inlineStr">
+      <c r="B197" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C196" s="83" t="n"/>
-      <c r="D196" s="36" t="inlineStr">
+      <c r="C197" s="83" t="n"/>
+      <c r="D197" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E196" s="47" t="n"/>
-      <c r="F196" s="20" t="n"/>
-      <c r="G196" s="53" t="n"/>
-    </row>
-    <row r="197" ht="19.8" customHeight="1">
-      <c r="A197" s="43" t="n"/>
-      <c r="B197" s="79" t="inlineStr">
+      <c r="E197" s="47" t="n"/>
+      <c r="F197" s="20" t="n"/>
+      <c r="G197" s="53" t="n"/>
+    </row>
+    <row r="198" ht="19.8" customHeight="1">
+      <c r="A198" s="43" t="n"/>
+      <c r="B198" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C197" s="18" t="inlineStr">
+      <c r="C198" s="18" t="inlineStr">
         <is>
           <t>5.81 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D197" s="22" t="n">
+      <c r="D198" s="22" t="n">
         <v>17.43</v>
       </c>
-      <c r="E197" s="59" t="n">
+      <c r="E198" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="F197" s="80" t="n">
+      <c r="F198" s="80" t="n">
         <v>104.6</v>
       </c>
-      <c r="G197" s="53" t="n"/>
-    </row>
-    <row r="198" ht="19.8" customHeight="1">
-      <c r="A198" s="47" t="n"/>
-      <c r="B198" s="81" t="inlineStr">
+      <c r="G198" s="53" t="n"/>
+    </row>
+    <row r="199" ht="19.8" customHeight="1">
+      <c r="A199" s="47" t="n"/>
+      <c r="B199" s="81" t="inlineStr">
         <is>
           <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C198" s="18" t="n"/>
-      <c r="D198" s="19" t="n"/>
-      <c r="E198" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F198" s="80" t="n"/>
-      <c r="G198" s="53" t="n"/>
-    </row>
-    <row r="199" ht="19.8" customHeight="1">
-      <c r="A199" s="50" t="n"/>
-      <c r="B199" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C199" s="18" t="n"/>
       <c r="D199" s="19" t="n"/>
       <c r="E199" s="59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F199" s="80" t="n"/>
+      <c r="G199" s="53" t="n"/>
+    </row>
+    <row r="200" ht="19.8" customHeight="1">
+      <c r="A200" s="50" t="n"/>
+      <c r="B200" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C200" s="18" t="n"/>
+      <c r="D200" s="19" t="n"/>
+      <c r="E200" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F199" s="84" t="n"/>
-      <c r="G199" s="53" t="n"/>
-    </row>
-    <row r="200" ht="19.8" customHeight="1">
-      <c r="A200" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B200" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C200" s="47" t="n"/>
-      <c r="D200" s="18" t="n"/>
-      <c r="E200" s="20" t="n"/>
-      <c r="F200" s="85" t="n">
-        <v>1060.8</v>
-      </c>
+      <c r="F200" s="84" t="n"/>
       <c r="G200" s="53" t="n"/>
     </row>
     <row r="201" ht="19.8" customHeight="1">
       <c r="A201" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B201" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C201" s="47" t="n"/>
+      <c r="D201" s="18" t="n"/>
+      <c r="E201" s="20" t="n"/>
+      <c r="F201" s="85" t="n">
+        <v>1060.8</v>
+      </c>
+      <c r="G201" s="53" t="n"/>
+    </row>
+    <row r="202" ht="19.8" customHeight="1">
+      <c r="A202" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B201" s="78" t="inlineStr">
+      <c r="B202" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C201" s="47" t="inlineStr">
+      <c r="C202" s="47" t="inlineStr">
         <is>
           <t>1060.80  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D201" s="12" t="n"/>
-      <c r="E201" s="14" t="n"/>
-      <c r="F201" s="85" t="n">
+      <c r="D202" s="12" t="n"/>
+      <c r="E202" s="14" t="n"/>
+      <c r="F202" s="85" t="n">
         <v>1135.1</v>
       </c>
-      <c r="G201" s="53" t="n"/>
-    </row>
-    <row r="202" ht="19.8" customHeight="1">
-      <c r="A202" s="43" t="n"/>
-      <c r="B202" s="86" t="inlineStr">
+      <c r="G202" s="53" t="n"/>
+    </row>
+    <row r="203" ht="19.8" customHeight="1">
+      <c r="A203" s="43" t="n"/>
+      <c r="B203" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C202" s="18" t="n"/>
-      <c r="D202" s="12" t="n"/>
-      <c r="E202" s="39" t="n"/>
-      <c r="F202" s="87" t="n"/>
-      <c r="G202" s="53" t="n"/>
-    </row>
-    <row r="203" ht="19.8" customHeight="1">
-      <c r="A203" s="83" t="n"/>
-      <c r="B203" s="78" t="inlineStr">
+      <c r="C203" s="18" t="n"/>
+      <c r="D203" s="12" t="n"/>
+      <c r="E203" s="39" t="n"/>
+      <c r="F203" s="87" t="n"/>
+      <c r="G203" s="53" t="n"/>
+    </row>
+    <row r="204" ht="19.8" customHeight="1">
+      <c r="A204" s="83" t="n"/>
+      <c r="B204" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C203" s="47" t="n"/>
-      <c r="D203" s="12" t="n"/>
-      <c r="E203" s="14" t="n"/>
-      <c r="F203" s="85" t="n">
+      <c r="C204" s="47" t="n"/>
+      <c r="D204" s="12" t="n"/>
+      <c r="E204" s="14" t="n"/>
+      <c r="F204" s="85" t="n">
         <v>1135.1</v>
       </c>
-      <c r="G203" s="53" t="n"/>
-    </row>
-    <row r="204" ht="19.8" customHeight="1">
-      <c r="A204" s="47" t="n"/>
-      <c r="B204" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C204" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
-      </c>
-      <c r="D204" s="12" t="n"/>
-      <c r="E204" s="39" t="n"/>
-      <c r="F204" s="61" t="n"/>
       <c r="G204" s="53" t="n"/>
     </row>
     <row r="205" ht="19.8" customHeight="1">
       <c r="A205" s="47" t="n"/>
-      <c r="B205" s="60" t="inlineStr">
-        <is>
-          <t>Kcal/h del toallero Scala/Domino 80</t>
-        </is>
-      </c>
-      <c r="C205" s="59" t="n">
-        <v>708</v>
+      <c r="B205" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C205" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
       </c>
       <c r="D205" s="12" t="n"/>
       <c r="E205" s="39" t="n"/>
-      <c r="F205" s="20" t="n"/>
+      <c r="F205" s="61" t="n"/>
       <c r="G205" s="53" t="n"/>
     </row>
     <row r="206" ht="19.8" customHeight="1">
       <c r="A206" s="47" t="n"/>
       <c r="B206" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 150</t>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
         </is>
       </c>
       <c r="C206" s="59" t="n">
-        <v>1315</v>
+        <v>708</v>
       </c>
       <c r="D206" s="12" t="n"/>
       <c r="E206" s="39" t="n"/>
@@ -23607,11 +23615,11 @@
       <c r="A207" s="47" t="n"/>
       <c r="B207" s="60" t="inlineStr">
         <is>
-          <t>Toalleros necesarios</t>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
         </is>
       </c>
       <c r="C207" s="59" t="n">
-        <v>1</v>
+        <v>1315</v>
       </c>
       <c r="D207" s="12" t="n"/>
       <c r="E207" s="39" t="n"/>
@@ -23619,16 +23627,14 @@
       <c r="G207" s="53" t="n"/>
     </row>
     <row r="208" ht="19.8" customHeight="1">
-      <c r="A208" s="50" t="n"/>
+      <c r="A208" s="47" t="n"/>
       <c r="B208" s="60" t="inlineStr">
         <is>
-          <t>Toallero adoptado</t>
-        </is>
-      </c>
-      <c r="C208" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
-        </is>
+          <t>Toalleros necesarios</t>
+        </is>
+      </c>
+      <c r="C208" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="D208" s="12" t="n"/>
       <c r="E208" s="39" t="n"/>
@@ -23636,159 +23642,153 @@
       <c r="G208" s="53" t="n"/>
     </row>
     <row r="209" ht="19.8" customHeight="1">
-      <c r="A209" s="8" t="inlineStr">
+      <c r="A209" s="50" t="n"/>
+      <c r="B209" s="60" t="inlineStr">
+        <is>
+          <t>Toallero adoptado</t>
+        </is>
+      </c>
+      <c r="C209" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
+        </is>
+      </c>
+      <c r="D209" s="12" t="n"/>
+      <c r="E209" s="39" t="n"/>
+      <c r="F209" s="20" t="n"/>
+      <c r="G209" s="53" t="n"/>
+    </row>
+    <row r="210" ht="19.8" customHeight="1">
+      <c r="A210" s="8" t="inlineStr">
         <is>
           <t>LOCAL  11 - Bano visitas   (PB)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B209" s="11" t="n"/>
-      <c r="C209" s="11" t="n"/>
-      <c r="D209" s="11" t="n"/>
-      <c r="E209" s="11" t="n"/>
-      <c r="F209" s="42" t="n"/>
-      <c r="G209" s="53" t="n"/>
-    </row>
-    <row r="210" ht="32" customHeight="1">
-      <c r="A210" s="2" t="inlineStr">
+      <c r="B210" s="11" t="n"/>
+      <c r="C210" s="11" t="n"/>
+      <c r="D210" s="11" t="n"/>
+      <c r="E210" s="11" t="n"/>
+      <c r="F210" s="42" t="n"/>
+      <c r="G210" s="53" t="n"/>
+    </row>
+    <row r="211" ht="32" customHeight="1">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
+      <c r="C211" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G210" s="53" t="n"/>
-    </row>
-    <row r="211" ht="19.8" customHeight="1">
-      <c r="A211" s="36" t="inlineStr">
+      <c r="G211" s="53" t="n"/>
+    </row>
+    <row r="212" ht="19.8" customHeight="1">
+      <c r="A212" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B211" s="78" t="inlineStr">
+      <c r="B212" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C211" s="43" t="n"/>
-      <c r="D211" s="58" t="n"/>
-      <c r="E211" s="58" t="n"/>
-      <c r="F211" s="61" t="n"/>
-      <c r="G211" s="53" t="n"/>
-    </row>
-    <row r="212" ht="19.8" customHeight="1">
-      <c r="A212" s="89" t="n"/>
-      <c r="B212" s="90" t="inlineStr">
+      <c r="C212" s="43" t="n"/>
+      <c r="D212" s="58" t="n"/>
+      <c r="E212" s="58" t="n"/>
+      <c r="F212" s="61" t="n"/>
+      <c r="G212" s="53" t="n"/>
+    </row>
+    <row r="213" ht="19.8" customHeight="1">
+      <c r="A213" s="90" t="n"/>
+      <c r="B213" s="91" t="inlineStr">
         <is>
           <t>(sin aberturas)</t>
         </is>
       </c>
-      <c r="C212" s="18" t="n"/>
-      <c r="D212" s="19" t="n"/>
-      <c r="E212" s="59" t="n">
+      <c r="C213" s="18" t="n"/>
+      <c r="D213" s="19" t="n"/>
+      <c r="E213" s="59" t="n">
         <v>60</v>
       </c>
-      <c r="F212" s="80" t="n"/>
-      <c r="G212" s="53" t="n"/>
-    </row>
-    <row r="213" ht="19.8" customHeight="1">
-      <c r="A213" s="36" t="inlineStr">
+      <c r="F213" s="80" t="n"/>
+      <c r="G213" s="53" t="n"/>
+    </row>
+    <row r="214" ht="19.8" customHeight="1">
+      <c r="A214" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B213" s="78" t="inlineStr">
+      <c r="B214" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C213" s="47" t="n"/>
-      <c r="D213" s="18" t="n"/>
-      <c r="E213" s="18" t="n"/>
-      <c r="F213" s="20" t="n"/>
-      <c r="G213" s="53" t="n"/>
-    </row>
-    <row r="214" ht="19.8" customHeight="1">
-      <c r="A214" s="43" t="n"/>
-      <c r="B214" s="79" t="inlineStr">
+      <c r="C214" s="47" t="n"/>
+      <c r="D214" s="18" t="n"/>
+      <c r="E214" s="18" t="n"/>
+      <c r="F214" s="20" t="n"/>
+      <c r="G214" s="53" t="n"/>
+    </row>
+    <row r="215" ht="19.8" customHeight="1">
+      <c r="A215" s="43" t="n"/>
+      <c r="B215" s="79" t="inlineStr">
         <is>
           <t>AISLADAS</t>
         </is>
       </c>
-      <c r="C214" s="18" t="inlineStr">
+      <c r="C215" s="18" t="inlineStr">
         <is>
           <t>1.30 x 3.00</t>
         </is>
       </c>
-      <c r="D214" s="19" t="n">
+      <c r="D215" s="19" t="n">
         <v>3.9</v>
       </c>
-      <c r="E214" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F214" s="80" t="n">
-        <v>78</v>
-      </c>
-      <c r="G214" s="53" t="n"/>
-    </row>
-    <row r="215" ht="19.8" customHeight="1">
-      <c r="A215" s="47" t="n"/>
-      <c r="B215" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C215" s="18" t="n"/>
-      <c r="D215" s="19" t="n"/>
       <c r="E215" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F215" s="80" t="n"/>
+      <c r="F215" s="80" t="n">
+        <v>78</v>
+      </c>
       <c r="G215" s="53" t="n"/>
     </row>
     <row r="216" ht="19.8" customHeight="1">
       <c r="A216" s="47" t="n"/>
       <c r="B216" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C216" s="18" t="inlineStr">
-        <is>
-          <t>2.40 x 3.00</t>
-        </is>
-      </c>
-      <c r="D216" s="19" t="n">
-        <v>7.2</v>
-      </c>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C216" s="18" t="n"/>
+      <c r="D216" s="19" t="n"/>
       <c r="E216" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F216" s="80" t="n">
-        <v>180</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F216" s="80" t="n"/>
       <c r="G216" s="53" t="n"/>
     </row>
     <row r="217" ht="19.8" customHeight="1">
@@ -23815,338 +23815,346 @@
       <c r="G217" s="53" t="n"/>
     </row>
     <row r="218" ht="19.8" customHeight="1">
-      <c r="A218" s="50" t="n"/>
-      <c r="B218" s="82" t="inlineStr">
+      <c r="A218" s="47" t="n"/>
+      <c r="B218" s="81" t="inlineStr">
         <is>
           <t>INTERIORES</t>
         </is>
       </c>
       <c r="C218" s="18" t="inlineStr">
         <is>
-          <t>1.30 x 3.00</t>
+          <t>2.40 x 3.00</t>
         </is>
       </c>
       <c r="D218" s="19" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="E218" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F218" s="80" t="n">
+        <v>180</v>
+      </c>
+      <c r="G218" s="53" t="n"/>
+    </row>
+    <row r="219" ht="19.8" customHeight="1">
+      <c r="A219" s="50" t="n"/>
+      <c r="B219" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C219" s="18" t="inlineStr">
+        <is>
+          <t>1.30 x 3.00</t>
+        </is>
+      </c>
+      <c r="D219" s="19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E219" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F219" s="80" t="n">
         <v>97.5</v>
       </c>
-      <c r="G218" s="53" t="n"/>
-    </row>
-    <row r="219" ht="19.8" customHeight="1">
-      <c r="A219" s="36" t="inlineStr">
+      <c r="G219" s="53" t="n"/>
+    </row>
+    <row r="220" ht="19.8" customHeight="1">
+      <c r="A220" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B219" s="78" t="inlineStr">
+      <c r="B220" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C219" s="47" t="n"/>
-      <c r="D219" s="18" t="n"/>
-      <c r="E219" s="18" t="n"/>
-      <c r="F219" s="20" t="n"/>
-      <c r="G219" s="53" t="n"/>
-    </row>
-    <row r="220" ht="19.8" customHeight="1">
-      <c r="A220" s="43" t="n"/>
-      <c r="B220" s="79" t="inlineStr">
+      <c r="C220" s="47" t="n"/>
+      <c r="D220" s="18" t="n"/>
+      <c r="E220" s="18" t="n"/>
+      <c r="F220" s="20" t="n"/>
+      <c r="G220" s="53" t="n"/>
+    </row>
+    <row r="221" ht="19.8" customHeight="1">
+      <c r="A221" s="43" t="n"/>
+      <c r="B221" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C220" s="18" t="n"/>
-      <c r="D220" s="19" t="n"/>
-      <c r="E220" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F220" s="80" t="n"/>
-      <c r="G220" s="53" t="n"/>
-    </row>
-    <row r="221" ht="19.8" customHeight="1">
-      <c r="A221" s="47" t="n"/>
-      <c r="B221" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C221" s="18" t="n"/>
       <c r="D221" s="19" t="n"/>
       <c r="E221" s="59" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F221" s="80" t="n"/>
       <c r="G221" s="53" t="n"/>
     </row>
     <row r="222" ht="19.8" customHeight="1">
-      <c r="A222" s="50" t="n"/>
-      <c r="B222" s="82" t="inlineStr">
+      <c r="A222" s="47" t="n"/>
+      <c r="B222" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C222" s="18" t="n"/>
+      <c r="D222" s="19" t="n"/>
+      <c r="E222" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F222" s="80" t="n"/>
+      <c r="G222" s="53" t="n"/>
+    </row>
+    <row r="223" ht="19.8" customHeight="1">
+      <c r="A223" s="50" t="n"/>
+      <c r="B223" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C222" s="18" t="inlineStr">
+      <c r="C223" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D222" s="19" t="n">
+      <c r="D223" s="19" t="n">
         <v>3.12</v>
       </c>
-      <c r="E222" s="59" t="n">
+      <c r="E223" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F222" s="80" t="n">
+      <c r="F223" s="80" t="n">
         <v>46.8</v>
       </c>
-      <c r="G222" s="53" t="n"/>
-    </row>
-    <row r="223" ht="19.8" customHeight="1">
-      <c r="A223" s="36" t="inlineStr">
+      <c r="G223" s="53" t="n"/>
+    </row>
+    <row r="224" ht="19.8" customHeight="1">
+      <c r="A224" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B223" s="78" t="inlineStr">
+      <c r="B224" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C223" s="47" t="n"/>
-      <c r="D223" s="18" t="n"/>
-      <c r="E223" s="18" t="n"/>
-      <c r="F223" s="20" t="n"/>
-      <c r="G223" s="53" t="n"/>
-    </row>
-    <row r="224" ht="19.8" customHeight="1">
-      <c r="A224" s="43" t="n"/>
-      <c r="B224" s="79" t="inlineStr">
+      <c r="C224" s="47" t="n"/>
+      <c r="D224" s="18" t="n"/>
+      <c r="E224" s="18" t="n"/>
+      <c r="F224" s="20" t="n"/>
+      <c r="G224" s="53" t="n"/>
+    </row>
+    <row r="225" ht="19.8" customHeight="1">
+      <c r="A225" s="43" t="n"/>
+      <c r="B225" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C224" s="18" t="inlineStr">
+      <c r="C225" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D224" s="19" t="n">
+      <c r="D225" s="19" t="n">
         <v>3.12</v>
       </c>
-      <c r="E224" s="59" t="n">
+      <c r="E225" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F224" s="80" t="n">
+      <c r="F225" s="80" t="n">
         <v>31.2</v>
       </c>
-      <c r="G224" s="53" t="n"/>
-    </row>
-    <row r="225" ht="19.8" customHeight="1">
-      <c r="A225" s="50" t="n"/>
-      <c r="B225" s="82" t="inlineStr">
+      <c r="G225" s="53" t="n"/>
+    </row>
+    <row r="226" ht="19.8" customHeight="1">
+      <c r="A226" s="50" t="n"/>
+      <c r="B226" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C225" s="18" t="n"/>
-      <c r="D225" s="24" t="n"/>
-      <c r="E225" s="59" t="n">
+      <c r="C226" s="18" t="n"/>
+      <c r="D226" s="24" t="n"/>
+      <c r="E226" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F225" s="80" t="n"/>
-      <c r="G225" s="53" t="n"/>
-    </row>
-    <row r="226" ht="19.8" customHeight="1">
-      <c r="A226" s="36" t="inlineStr">
+      <c r="F226" s="80" t="n"/>
+      <c r="G226" s="53" t="n"/>
+    </row>
+    <row r="227" ht="19.8" customHeight="1">
+      <c r="A227" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B226" s="78" t="inlineStr">
+      <c r="B227" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C226" s="83" t="n"/>
-      <c r="D226" s="36" t="inlineStr">
+      <c r="C227" s="83" t="n"/>
+      <c r="D227" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E226" s="47" t="n"/>
-      <c r="F226" s="20" t="n"/>
-      <c r="G226" s="53" t="n"/>
-    </row>
-    <row r="227" ht="19.8" customHeight="1">
-      <c r="A227" s="43" t="n"/>
-      <c r="B227" s="79" t="inlineStr">
+      <c r="E227" s="47" t="n"/>
+      <c r="F227" s="20" t="n"/>
+      <c r="G227" s="53" t="n"/>
+    </row>
+    <row r="228" ht="19.8" customHeight="1">
+      <c r="A228" s="43" t="n"/>
+      <c r="B228" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C227" s="18" t="inlineStr">
+      <c r="C228" s="18" t="inlineStr">
         <is>
           <t>3.12 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D227" s="22" t="n">
+      <c r="D228" s="22" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="E227" s="59" t="n">
+      <c r="E228" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="F227" s="80" t="n">
+      <c r="F228" s="80" t="n">
         <v>56.2</v>
       </c>
-      <c r="G227" s="53" t="n"/>
-    </row>
-    <row r="228" ht="19.8" customHeight="1">
-      <c r="A228" s="47" t="n"/>
-      <c r="B228" s="81" t="inlineStr">
+      <c r="G228" s="53" t="n"/>
+    </row>
+    <row r="229" ht="19.8" customHeight="1">
+      <c r="A229" s="47" t="n"/>
+      <c r="B229" s="81" t="inlineStr">
         <is>
           <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C228" s="18" t="n"/>
-      <c r="D228" s="19" t="n"/>
-      <c r="E228" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F228" s="80" t="n"/>
-      <c r="G228" s="53" t="n"/>
-    </row>
-    <row r="229" ht="19.8" customHeight="1">
-      <c r="A229" s="50" t="n"/>
-      <c r="B229" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C229" s="18" t="n"/>
       <c r="D229" s="19" t="n"/>
       <c r="E229" s="59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F229" s="80" t="n"/>
+      <c r="G229" s="53" t="n"/>
+    </row>
+    <row r="230" ht="19.8" customHeight="1">
+      <c r="A230" s="50" t="n"/>
+      <c r="B230" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C230" s="18" t="n"/>
+      <c r="D230" s="19" t="n"/>
+      <c r="E230" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F229" s="84" t="n"/>
-      <c r="G229" s="53" t="n"/>
-    </row>
-    <row r="230" ht="19.8" customHeight="1">
-      <c r="A230" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B230" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C230" s="47" t="n"/>
-      <c r="D230" s="18" t="n"/>
-      <c r="E230" s="20" t="n"/>
-      <c r="F230" s="85" t="n">
-        <v>669.7</v>
-      </c>
+      <c r="F230" s="84" t="n"/>
       <c r="G230" s="53" t="n"/>
     </row>
     <row r="231" ht="19.8" customHeight="1">
       <c r="A231" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B231" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C231" s="47" t="n"/>
+      <c r="D231" s="18" t="n"/>
+      <c r="E231" s="20" t="n"/>
+      <c r="F231" s="85" t="n">
+        <v>669.7</v>
+      </c>
+      <c r="G231" s="53" t="n"/>
+    </row>
+    <row r="232" ht="19.8" customHeight="1">
+      <c r="A232" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B231" s="78" t="inlineStr">
+      <c r="B232" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C231" s="47" t="inlineStr">
+      <c r="C232" s="47" t="inlineStr">
         <is>
           <t>669.70  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D231" s="12" t="n"/>
-      <c r="E231" s="14" t="n"/>
-      <c r="F231" s="85" t="n">
+      <c r="D232" s="12" t="n"/>
+      <c r="E232" s="14" t="n"/>
+      <c r="F232" s="85" t="n">
         <v>716.6</v>
       </c>
-      <c r="G231" s="53" t="n"/>
-    </row>
-    <row r="232" ht="19.8" customHeight="1">
-      <c r="A232" s="43" t="n"/>
-      <c r="B232" s="86" t="inlineStr">
+      <c r="G232" s="53" t="n"/>
+    </row>
+    <row r="233" ht="19.8" customHeight="1">
+      <c r="A233" s="43" t="n"/>
+      <c r="B233" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C232" s="18" t="n"/>
-      <c r="D232" s="12" t="n"/>
-      <c r="E232" s="39" t="n"/>
-      <c r="F232" s="87" t="n"/>
-      <c r="G232" s="53" t="n"/>
-    </row>
-    <row r="233" ht="19.8" customHeight="1">
-      <c r="A233" s="83" t="n"/>
-      <c r="B233" s="78" t="inlineStr">
+      <c r="C233" s="18" t="n"/>
+      <c r="D233" s="12" t="n"/>
+      <c r="E233" s="39" t="n"/>
+      <c r="F233" s="87" t="n"/>
+      <c r="G233" s="53" t="n"/>
+    </row>
+    <row r="234" ht="19.8" customHeight="1">
+      <c r="A234" s="83" t="n"/>
+      <c r="B234" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C233" s="47" t="n"/>
-      <c r="D233" s="12" t="n"/>
-      <c r="E233" s="14" t="n"/>
-      <c r="F233" s="85" t="n">
+      <c r="C234" s="47" t="n"/>
+      <c r="D234" s="12" t="n"/>
+      <c r="E234" s="14" t="n"/>
+      <c r="F234" s="85" t="n">
         <v>716.6</v>
       </c>
-      <c r="G233" s="53" t="n"/>
-    </row>
-    <row r="234" ht="19.8" customHeight="1">
-      <c r="A234" s="47" t="n"/>
-      <c r="B234" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C234" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
-      </c>
-      <c r="D234" s="12" t="n"/>
-      <c r="E234" s="39" t="n"/>
-      <c r="F234" s="61" t="n"/>
       <c r="G234" s="53" t="n"/>
     </row>
     <row r="235" ht="19.8" customHeight="1">
       <c r="A235" s="47" t="n"/>
-      <c r="B235" s="60" t="inlineStr">
-        <is>
-          <t>Kcal/h del toallero Scala/Domino 80</t>
-        </is>
-      </c>
-      <c r="C235" s="59" t="n">
-        <v>708</v>
+      <c r="B235" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C235" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
       </c>
       <c r="D235" s="12" t="n"/>
       <c r="E235" s="39" t="n"/>
-      <c r="F235" s="20" t="n"/>
+      <c r="F235" s="61" t="n"/>
       <c r="G235" s="53" t="n"/>
     </row>
     <row r="236" ht="19.8" customHeight="1">
       <c r="A236" s="47" t="n"/>
       <c r="B236" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 150</t>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
         </is>
       </c>
       <c r="C236" s="59" t="n">
-        <v>1315</v>
+        <v>708</v>
       </c>
       <c r="D236" s="12" t="n"/>
       <c r="E236" s="39" t="n"/>
@@ -24157,11 +24165,11 @@
       <c r="A237" s="47" t="n"/>
       <c r="B237" s="60" t="inlineStr">
         <is>
-          <t>Toalleros necesarios</t>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
         </is>
       </c>
       <c r="C237" s="59" t="n">
-        <v>1</v>
+        <v>1315</v>
       </c>
       <c r="D237" s="12" t="n"/>
       <c r="E237" s="39" t="n"/>
@@ -24169,16 +24177,14 @@
       <c r="G237" s="53" t="n"/>
     </row>
     <row r="238" ht="19.8" customHeight="1">
-      <c r="A238" s="50" t="n"/>
+      <c r="A238" s="47" t="n"/>
       <c r="B238" s="60" t="inlineStr">
         <is>
-          <t>Toallero adoptado</t>
-        </is>
-      </c>
-      <c r="C238" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
-        </is>
+          <t>Toalleros necesarios</t>
+        </is>
+      </c>
+      <c r="C238" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="D238" s="12" t="n"/>
       <c r="E238" s="39" t="n"/>
@@ -24186,159 +24192,153 @@
       <c r="G238" s="53" t="n"/>
     </row>
     <row r="239" ht="19.8" customHeight="1">
-      <c r="A239" s="8" t="inlineStr">
+      <c r="A239" s="50" t="n"/>
+      <c r="B239" s="60" t="inlineStr">
+        <is>
+          <t>Toallero adoptado</t>
+        </is>
+      </c>
+      <c r="C239" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
+        </is>
+      </c>
+      <c r="D239" s="12" t="n"/>
+      <c r="E239" s="39" t="n"/>
+      <c r="F239" s="20" t="n"/>
+      <c r="G239" s="53" t="n"/>
+    </row>
+    <row r="240" ht="19.8" customHeight="1">
+      <c r="A240" s="8" t="inlineStr">
         <is>
           <t>LOCAL  13 - Dormitorio Norte   (PA)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B239" s="11" t="n"/>
-      <c r="C239" s="11" t="n"/>
-      <c r="D239" s="11" t="n"/>
-      <c r="E239" s="11" t="n"/>
-      <c r="F239" s="42" t="n"/>
-      <c r="G239" s="53" t="n"/>
-    </row>
-    <row r="240" ht="32" customHeight="1">
-      <c r="A240" s="2" t="inlineStr">
+      <c r="B240" s="11" t="n"/>
+      <c r="C240" s="11" t="n"/>
+      <c r="D240" s="11" t="n"/>
+      <c r="E240" s="11" t="n"/>
+      <c r="F240" s="42" t="n"/>
+      <c r="G240" s="53" t="n"/>
+    </row>
+    <row r="241" ht="32" customHeight="1">
+      <c r="A241" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C240" s="2" t="inlineStr">
+      <c r="C241" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G240" s="53" t="n"/>
-    </row>
-    <row r="241" ht="19.8" customHeight="1">
-      <c r="A241" s="36" t="inlineStr">
+      <c r="G241" s="53" t="n"/>
+    </row>
+    <row r="242" ht="19.8" customHeight="1">
+      <c r="A242" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B241" s="78" t="inlineStr">
+      <c r="B242" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C241" s="43" t="n"/>
-      <c r="D241" s="58" t="n"/>
-      <c r="E241" s="58" t="n"/>
-      <c r="F241" s="61" t="n"/>
-      <c r="G241" s="53" t="n"/>
-    </row>
-    <row r="242" ht="19.8" customHeight="1">
-      <c r="A242" s="43" t="n"/>
-      <c r="B242" s="79" t="inlineStr">
+      <c r="C242" s="43" t="n"/>
+      <c r="D242" s="58" t="n"/>
+      <c r="E242" s="58" t="n"/>
+      <c r="F242" s="61" t="n"/>
+      <c r="G242" s="53" t="n"/>
+    </row>
+    <row r="243" ht="19.8" customHeight="1">
+      <c r="A243" s="43" t="n"/>
+      <c r="B243" s="79" t="inlineStr">
         <is>
           <t>VA04</t>
         </is>
       </c>
-      <c r="C242" s="18" t="inlineStr">
+      <c r="C243" s="18" t="inlineStr">
         <is>
           <t>2.00 x 2.52</t>
         </is>
       </c>
-      <c r="D242" s="19" t="n">
+      <c r="D243" s="19" t="n">
         <v>5.04</v>
-      </c>
-      <c r="E242" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F242" s="80" t="n">
-        <v>302.4</v>
-      </c>
-      <c r="G242" s="53" t="n"/>
-    </row>
-    <row r="243" ht="19.8" customHeight="1">
-      <c r="A243" s="50" t="n"/>
-      <c r="B243" s="82" t="inlineStr">
-        <is>
-          <t>VA05</t>
-        </is>
-      </c>
-      <c r="C243" s="18" t="inlineStr">
-        <is>
-          <t>1.40 x 2.52</t>
-        </is>
-      </c>
-      <c r="D243" s="19" t="n">
-        <v>3.53</v>
       </c>
       <c r="E243" s="59" t="n">
         <v>60</v>
       </c>
       <c r="F243" s="80" t="n">
+        <v>302.4</v>
+      </c>
+      <c r="G243" s="53" t="n"/>
+    </row>
+    <row r="244" ht="19.8" customHeight="1">
+      <c r="A244" s="50" t="n"/>
+      <c r="B244" s="82" t="inlineStr">
+        <is>
+          <t>VA05</t>
+        </is>
+      </c>
+      <c r="C244" s="18" t="inlineStr">
+        <is>
+          <t>1.40 x 2.52</t>
+        </is>
+      </c>
+      <c r="D244" s="19" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="E244" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F244" s="80" t="n">
         <v>211.8</v>
       </c>
-      <c r="G243" s="53" t="n"/>
-    </row>
-    <row r="244" ht="19.8" customHeight="1">
-      <c r="A244" s="36" t="inlineStr">
+      <c r="G244" s="53" t="n"/>
+    </row>
+    <row r="245" ht="19.8" customHeight="1">
+      <c r="A245" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B244" s="78" t="inlineStr">
+      <c r="B245" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C244" s="47" t="n"/>
-      <c r="D244" s="18" t="n"/>
-      <c r="E244" s="18" t="n"/>
-      <c r="F244" s="20" t="n"/>
-      <c r="G244" s="53" t="n"/>
-    </row>
-    <row r="245" ht="19.8" customHeight="1">
-      <c r="A245" s="43" t="n"/>
-      <c r="B245" s="79" t="inlineStr">
+      <c r="C245" s="47" t="n"/>
+      <c r="D245" s="18" t="n"/>
+      <c r="E245" s="18" t="n"/>
+      <c r="F245" s="20" t="n"/>
+      <c r="G245" s="53" t="n"/>
+    </row>
+    <row r="246" ht="19.8" customHeight="1">
+      <c r="A246" s="43" t="n"/>
+      <c r="B246" s="79" t="inlineStr">
         <is>
           <t>AISLADAS (NO)</t>
-        </is>
-      </c>
-      <c r="C245" s="18" t="inlineStr">
-        <is>
-          <t>4.25 x 3.00</t>
-        </is>
-      </c>
-      <c r="D245" s="19" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="E245" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F245" s="80" t="n">
-        <v>255</v>
-      </c>
-      <c r="G245" s="53" t="n"/>
-    </row>
-    <row r="246" ht="19.8" customHeight="1">
-      <c r="A246" s="47" t="n"/>
-      <c r="B246" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS (SE)</t>
         </is>
       </c>
       <c r="C246" s="18" t="inlineStr">
@@ -24361,22 +24361,22 @@
       <c r="A247" s="47" t="n"/>
       <c r="B247" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>AISLADAS (SE)</t>
         </is>
       </c>
       <c r="C247" s="18" t="inlineStr">
         <is>
-          <t>4.00 x 3.00</t>
+          <t>4.25 x 3.00</t>
         </is>
       </c>
       <c r="D247" s="19" t="n">
-        <v>12</v>
+        <v>12.75</v>
       </c>
       <c r="E247" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F247" s="80" t="n">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="G247" s="53" t="n"/>
     </row>
@@ -24384,7 +24384,7 @@
       <c r="A248" s="47" t="n"/>
       <c r="B248" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C248" s="18" t="inlineStr">
@@ -24396,338 +24396,346 @@
         <v>12</v>
       </c>
       <c r="E248" s="59" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F248" s="80" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="G248" s="53" t="n"/>
     </row>
     <row r="249" ht="19.8" customHeight="1">
-      <c r="A249" s="50" t="n"/>
-      <c r="B249" s="82" t="inlineStr">
+      <c r="A249" s="47" t="n"/>
+      <c r="B249" s="81" t="inlineStr">
         <is>
           <t>INTERIORES</t>
         </is>
       </c>
-      <c r="C249" s="18" t="n"/>
-      <c r="D249" s="19" t="n"/>
+      <c r="C249" s="18" t="inlineStr">
+        <is>
+          <t>4.00 x 3.00</t>
+        </is>
+      </c>
+      <c r="D249" s="19" t="n">
+        <v>12</v>
+      </c>
       <c r="E249" s="59" t="n">
         <v>25</v>
       </c>
-      <c r="F249" s="80" t="n"/>
+      <c r="F249" s="80" t="n">
+        <v>300</v>
+      </c>
       <c r="G249" s="53" t="n"/>
     </row>
     <row r="250" ht="19.8" customHeight="1">
-      <c r="A250" s="36" t="inlineStr">
+      <c r="A250" s="50" t="n"/>
+      <c r="B250" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C250" s="18" t="n"/>
+      <c r="D250" s="19" t="n"/>
+      <c r="E250" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F250" s="80" t="n"/>
+      <c r="G250" s="53" t="n"/>
+    </row>
+    <row r="251" ht="19.8" customHeight="1">
+      <c r="A251" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B250" s="78" t="inlineStr">
+      <c r="B251" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C250" s="47" t="n"/>
-      <c r="D250" s="18" t="n"/>
-      <c r="E250" s="18" t="n"/>
-      <c r="F250" s="20" t="n"/>
-      <c r="G250" s="53" t="n"/>
-    </row>
-    <row r="251" ht="19.8" customHeight="1">
-      <c r="A251" s="43" t="n"/>
-      <c r="B251" s="79" t="inlineStr">
+      <c r="C251" s="47" t="n"/>
+      <c r="D251" s="18" t="n"/>
+      <c r="E251" s="18" t="n"/>
+      <c r="F251" s="20" t="n"/>
+      <c r="G251" s="53" t="n"/>
+    </row>
+    <row r="252" ht="19.8" customHeight="1">
+      <c r="A252" s="43" t="n"/>
+      <c r="B252" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
         </is>
       </c>
-      <c r="C251" s="18" t="n"/>
-      <c r="D251" s="19" t="n"/>
-      <c r="E251" s="59" t="n">
+      <c r="C252" s="18" t="n"/>
+      <c r="D252" s="19" t="n"/>
+      <c r="E252" s="59" t="n">
         <v>30</v>
       </c>
-      <c r="F251" s="80" t="n"/>
-      <c r="G251" s="53" t="n"/>
-    </row>
-    <row r="252" ht="19.8" customHeight="1">
-      <c r="A252" s="47" t="n"/>
-      <c r="B252" s="81" t="inlineStr">
+      <c r="F252" s="80" t="n"/>
+      <c r="G252" s="53" t="n"/>
+    </row>
+    <row r="253" ht="19.8" customHeight="1">
+      <c r="A253" s="47" t="n"/>
+      <c r="B253" s="81" t="inlineStr">
         <is>
           <t>TECHO AISLADO</t>
         </is>
       </c>
-      <c r="C252" s="18" t="inlineStr">
+      <c r="C253" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D252" s="19" t="n">
+      <c r="D253" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="E252" s="59" t="n">
+      <c r="E253" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F252" s="80" t="n">
+      <c r="F253" s="80" t="n">
         <v>340</v>
       </c>
-      <c r="G252" s="53" t="n"/>
-    </row>
-    <row r="253" ht="19.8" customHeight="1">
-      <c r="A253" s="50" t="n"/>
-      <c r="B253" s="82" t="inlineStr">
+      <c r="G253" s="53" t="n"/>
+    </row>
+    <row r="254" ht="19.8" customHeight="1">
+      <c r="A254" s="50" t="n"/>
+      <c r="B254" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C253" s="18" t="n"/>
-      <c r="D253" s="19" t="n"/>
-      <c r="E253" s="59" t="n">
+      <c r="C254" s="18" t="n"/>
+      <c r="D254" s="19" t="n"/>
+      <c r="E254" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F253" s="80" t="n"/>
-      <c r="G253" s="53" t="n"/>
-    </row>
-    <row r="254" ht="19.8" customHeight="1">
-      <c r="A254" s="36" t="inlineStr">
+      <c r="F254" s="80" t="n"/>
+      <c r="G254" s="53" t="n"/>
+    </row>
+    <row r="255" ht="19.8" customHeight="1">
+      <c r="A255" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B254" s="78" t="inlineStr">
+      <c r="B255" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C254" s="47" t="n"/>
-      <c r="D254" s="18" t="n"/>
-      <c r="E254" s="18" t="n"/>
-      <c r="F254" s="20" t="n"/>
-      <c r="G254" s="53" t="n"/>
-    </row>
-    <row r="255" ht="19.8" customHeight="1">
-      <c r="A255" s="43" t="n"/>
-      <c r="B255" s="79" t="inlineStr">
+      <c r="C255" s="47" t="n"/>
+      <c r="D255" s="18" t="n"/>
+      <c r="E255" s="18" t="n"/>
+      <c r="F255" s="20" t="n"/>
+      <c r="G255" s="53" t="n"/>
+    </row>
+    <row r="256" ht="19.8" customHeight="1">
+      <c r="A256" s="43" t="n"/>
+      <c r="B256" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C255" s="18" t="n"/>
-      <c r="D255" s="19" t="n"/>
-      <c r="E255" s="59" t="n">
+      <c r="C256" s="18" t="n"/>
+      <c r="D256" s="19" t="n"/>
+      <c r="E256" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F255" s="80" t="n"/>
-      <c r="G255" s="53" t="n"/>
-    </row>
-    <row r="256" ht="19.8" customHeight="1">
-      <c r="A256" s="50" t="n"/>
-      <c r="B256" s="82" t="inlineStr">
+      <c r="F256" s="80" t="n"/>
+      <c r="G256" s="53" t="n"/>
+    </row>
+    <row r="257" ht="19.8" customHeight="1">
+      <c r="A257" s="50" t="n"/>
+      <c r="B257" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C256" s="18" t="inlineStr">
+      <c r="C257" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D256" s="24" t="n">
+      <c r="D257" s="24" t="n">
         <v>17</v>
       </c>
-      <c r="E256" s="59" t="n">
+      <c r="E257" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F256" s="80" t="n">
+      <c r="F257" s="80" t="n">
         <v>255</v>
       </c>
-      <c r="G256" s="53" t="n"/>
-    </row>
-    <row r="257" ht="19.8" customHeight="1">
-      <c r="A257" s="36" t="inlineStr">
+      <c r="G257" s="53" t="n"/>
+    </row>
+    <row r="258" ht="19.8" customHeight="1">
+      <c r="A258" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B257" s="78" t="inlineStr">
+      <c r="B258" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C257" s="83" t="n"/>
-      <c r="D257" s="36" t="inlineStr">
+      <c r="C258" s="83" t="n"/>
+      <c r="D258" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E257" s="47" t="n"/>
-      <c r="F257" s="20" t="n"/>
-      <c r="G257" s="53" t="n"/>
-    </row>
-    <row r="258" ht="19.8" customHeight="1">
-      <c r="A258" s="43" t="n"/>
-      <c r="B258" s="79" t="inlineStr">
+      <c r="E258" s="47" t="n"/>
+      <c r="F258" s="20" t="n"/>
+      <c r="G258" s="53" t="n"/>
+    </row>
+    <row r="259" ht="19.8" customHeight="1">
+      <c r="A259" s="43" t="n"/>
+      <c r="B259" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C258" s="18" t="n"/>
-      <c r="D258" s="22" t="n"/>
-      <c r="E258" s="59" t="n">
+      <c r="C259" s="18" t="n"/>
+      <c r="D259" s="22" t="n"/>
+      <c r="E259" s="59" t="n">
         <v>6</v>
-      </c>
-      <c r="F258" s="80" t="n"/>
-      <c r="G258" s="53" t="n"/>
-    </row>
-    <row r="259" ht="19.8" customHeight="1">
-      <c r="A259" s="47" t="n"/>
-      <c r="B259" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C259" s="18" t="n"/>
-      <c r="D259" s="19" t="n"/>
-      <c r="E259" s="59" t="n">
-        <v>9</v>
       </c>
       <c r="F259" s="80" t="n"/>
       <c r="G259" s="53" t="n"/>
     </row>
     <row r="260" ht="19.8" customHeight="1">
-      <c r="A260" s="50" t="n"/>
-      <c r="B260" s="82" t="inlineStr">
+      <c r="A260" s="47" t="n"/>
+      <c r="B260" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C260" s="18" t="n"/>
+      <c r="D260" s="19" t="n"/>
+      <c r="E260" s="59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F260" s="80" t="n"/>
+      <c r="G260" s="53" t="n"/>
+    </row>
+    <row r="261" ht="19.8" customHeight="1">
+      <c r="A261" s="50" t="n"/>
+      <c r="B261" s="82" t="inlineStr">
         <is>
           <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C260" s="18" t="inlineStr">
+      <c r="C261" s="18" t="inlineStr">
         <is>
           <t>17.00 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D260" s="19" t="n">
+      <c r="D261" s="19" t="n">
         <v>51</v>
       </c>
-      <c r="E260" s="59" t="n">
+      <c r="E261" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F260" s="84" t="n">
+      <c r="F261" s="84" t="n">
         <v>612</v>
-      </c>
-      <c r="G260" s="53" t="n"/>
-    </row>
-    <row r="261" ht="19.8" customHeight="1">
-      <c r="A261" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B261" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C261" s="47" t="n"/>
-      <c r="D261" s="18" t="n"/>
-      <c r="E261" s="20" t="n"/>
-      <c r="F261" s="85" t="n">
-        <v>2771.2</v>
       </c>
       <c r="G261" s="53" t="n"/>
     </row>
     <row r="262" ht="19.8" customHeight="1">
       <c r="A262" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B262" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C262" s="47" t="n"/>
+      <c r="D262" s="18" t="n"/>
+      <c r="E262" s="20" t="n"/>
+      <c r="F262" s="85" t="n">
+        <v>2771.2</v>
+      </c>
+      <c r="G262" s="53" t="n"/>
+    </row>
+    <row r="263" ht="19.8" customHeight="1">
+      <c r="A263" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B262" s="78" t="inlineStr">
+      <c r="B263" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C262" s="47" t="inlineStr">
+      <c r="C263" s="47" t="inlineStr">
         <is>
           <t>2771.20  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D262" s="12" t="n"/>
-      <c r="E262" s="14" t="n"/>
-      <c r="F262" s="85" t="n">
+      <c r="D263" s="12" t="n"/>
+      <c r="E263" s="14" t="n"/>
+      <c r="F263" s="85" t="n">
         <v>2965.2</v>
       </c>
-      <c r="G262" s="53" t="n"/>
-    </row>
-    <row r="263" ht="19.8" customHeight="1">
-      <c r="A263" s="43" t="n"/>
-      <c r="B263" s="86" t="inlineStr">
+      <c r="G263" s="53" t="n"/>
+    </row>
+    <row r="264" ht="19.8" customHeight="1">
+      <c r="A264" s="43" t="n"/>
+      <c r="B264" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C263" s="18" t="n"/>
-      <c r="D263" s="12" t="n"/>
-      <c r="E263" s="39" t="n"/>
-      <c r="F263" s="87" t="n"/>
-      <c r="G263" s="53" t="n"/>
-    </row>
-    <row r="264" ht="19.8" customHeight="1">
-      <c r="A264" s="83" t="n"/>
-      <c r="B264" s="78" t="inlineStr">
+      <c r="C264" s="18" t="n"/>
+      <c r="D264" s="12" t="n"/>
+      <c r="E264" s="39" t="n"/>
+      <c r="F264" s="87" t="n"/>
+      <c r="G264" s="53" t="n"/>
+    </row>
+    <row r="265" ht="19.8" customHeight="1">
+      <c r="A265" s="83" t="n"/>
+      <c r="B265" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C264" s="47" t="n"/>
-      <c r="D264" s="12" t="n"/>
-      <c r="E264" s="14" t="n"/>
-      <c r="F264" s="85" t="n">
+      <c r="C265" s="47" t="n"/>
+      <c r="D265" s="12" t="n"/>
+      <c r="E265" s="14" t="n"/>
+      <c r="F265" s="85" t="n">
         <v>2965.2</v>
       </c>
-      <c r="G264" s="53" t="n"/>
-    </row>
-    <row r="265" ht="19.8" customHeight="1">
-      <c r="A265" s="47" t="n"/>
-      <c r="B265" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C265" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
-      </c>
-      <c r="D265" s="12" t="n"/>
-      <c r="E265" s="39" t="n"/>
-      <c r="F265" s="61" t="n"/>
       <c r="G265" s="53" t="n"/>
     </row>
     <row r="266" ht="19.8" customHeight="1">
       <c r="A266" s="47" t="n"/>
-      <c r="B266" s="60" t="inlineStr">
-        <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C266" s="19" t="n">
-        <v>274.4</v>
+      <c r="B266" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C266" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
       </c>
       <c r="D266" s="12" t="n"/>
       <c r="E266" s="39" t="n"/>
-      <c r="F266" s="20" t="n"/>
+      <c r="F266" s="61" t="n"/>
       <c r="G266" s="53" t="n"/>
     </row>
     <row r="267" ht="19.8" customHeight="1">
       <c r="A267" s="47" t="n"/>
       <c r="B267" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
-        </is>
-      </c>
-      <c r="C267" s="59" t="n">
-        <v>11</v>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C267" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D267" s="12" t="n"/>
       <c r="E267" s="39" t="n"/>
@@ -24738,11 +24746,11 @@
       <c r="A268" s="47" t="n"/>
       <c r="B268" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C268" s="59" t="n">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="D268" s="12" t="n"/>
       <c r="E268" s="39" t="n"/>
@@ -24750,16 +24758,14 @@
       <c r="G268" s="53" t="n"/>
     </row>
     <row r="269" ht="19.8" customHeight="1">
-      <c r="A269" s="50" t="n"/>
+      <c r="A269" s="47" t="n"/>
       <c r="B269" s="60" t="inlineStr">
         <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C269" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
+          <t>Ancho del radiador (cm)</t>
+        </is>
+      </c>
+      <c r="C269" s="59" t="n">
+        <v>88</v>
       </c>
       <c r="D269" s="12" t="n"/>
       <c r="E269" s="39" t="n"/>
@@ -24767,167 +24773,161 @@
       <c r="G269" s="53" t="n"/>
     </row>
     <row r="270" ht="19.8" customHeight="1">
-      <c r="A270" s="8" t="inlineStr">
+      <c r="A270" s="50" t="n"/>
+      <c r="B270" s="60" t="inlineStr">
+        <is>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C270" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
+      </c>
+      <c r="D270" s="12" t="n"/>
+      <c r="E270" s="39" t="n"/>
+      <c r="F270" s="20" t="n"/>
+      <c r="G270" s="53" t="n"/>
+    </row>
+    <row r="271" ht="19.8" customHeight="1">
+      <c r="A271" s="8" t="inlineStr">
         <is>
           <t>LOCAL  14 - Play room   (PA)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B270" s="11" t="n"/>
-      <c r="C270" s="11" t="n"/>
-      <c r="D270" s="11" t="n"/>
-      <c r="E270" s="11" t="n"/>
-      <c r="F270" s="42" t="n"/>
-      <c r="G270" s="53" t="n"/>
-    </row>
-    <row r="271" ht="32" customHeight="1">
-      <c r="A271" s="2" t="inlineStr">
+      <c r="B271" s="11" t="n"/>
+      <c r="C271" s="11" t="n"/>
+      <c r="D271" s="11" t="n"/>
+      <c r="E271" s="11" t="n"/>
+      <c r="F271" s="42" t="n"/>
+      <c r="G271" s="53" t="n"/>
+    </row>
+    <row r="272" ht="32" customHeight="1">
+      <c r="A272" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B271" s="2" t="inlineStr">
+      <c r="B272" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C271" s="2" t="inlineStr">
+      <c r="C272" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D271" s="2" t="inlineStr">
+      <c r="D272" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E271" s="2" t="inlineStr">
+      <c r="E272" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F271" s="2" t="inlineStr">
+      <c r="F272" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G271" s="53" t="n"/>
-    </row>
-    <row r="272" ht="19.8" customHeight="1">
-      <c r="A272" s="36" t="inlineStr">
+      <c r="G272" s="53" t="n"/>
+    </row>
+    <row r="273" ht="19.8" customHeight="1">
+      <c r="A273" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B272" s="78" t="inlineStr">
+      <c r="B273" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C272" s="43" t="n"/>
-      <c r="D272" s="58" t="n"/>
-      <c r="E272" s="58" t="n"/>
-      <c r="F272" s="61" t="n"/>
-      <c r="G272" s="53" t="n"/>
-    </row>
-    <row r="273" ht="19.8" customHeight="1">
-      <c r="A273" s="89" t="n"/>
-      <c r="B273" s="90" t="inlineStr">
+      <c r="C273" s="43" t="n"/>
+      <c r="D273" s="58" t="n"/>
+      <c r="E273" s="58" t="n"/>
+      <c r="F273" s="61" t="n"/>
+      <c r="G273" s="53" t="n"/>
+    </row>
+    <row r="274" ht="19.8" customHeight="1">
+      <c r="A274" s="90" t="n"/>
+      <c r="B274" s="91" t="inlineStr">
         <is>
           <t>VA04 (2)</t>
         </is>
       </c>
-      <c r="C273" s="18" t="inlineStr">
+      <c r="C274" s="18" t="inlineStr">
         <is>
           <t>2.00 x 2.52</t>
         </is>
       </c>
-      <c r="D273" s="19" t="n">
+      <c r="D274" s="19" t="n">
         <v>5.04</v>
       </c>
-      <c r="E273" s="59" t="n">
+      <c r="E274" s="59" t="n">
         <v>60</v>
       </c>
-      <c r="F273" s="80" t="n">
+      <c r="F274" s="80" t="n">
         <v>302.4</v>
       </c>
-      <c r="G273" s="53" t="n"/>
-    </row>
-    <row r="274" ht="19.8" customHeight="1">
-      <c r="A274" s="36" t="inlineStr">
+      <c r="G274" s="53" t="n"/>
+    </row>
+    <row r="275" ht="19.8" customHeight="1">
+      <c r="A275" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B274" s="78" t="inlineStr">
+      <c r="B275" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C274" s="47" t="n"/>
-      <c r="D274" s="18" t="n"/>
-      <c r="E274" s="18" t="n"/>
-      <c r="F274" s="20" t="n"/>
-      <c r="G274" s="53" t="n"/>
-    </row>
-    <row r="275" ht="19.8" customHeight="1">
-      <c r="A275" s="43" t="n"/>
-      <c r="B275" s="79" t="inlineStr">
+      <c r="C275" s="47" t="n"/>
+      <c r="D275" s="18" t="n"/>
+      <c r="E275" s="18" t="n"/>
+      <c r="F275" s="20" t="n"/>
+      <c r="G275" s="53" t="n"/>
+    </row>
+    <row r="276" ht="19.8" customHeight="1">
+      <c r="A276" s="43" t="n"/>
+      <c r="B276" s="79" t="inlineStr">
         <is>
           <t>AISLADAS (NO)</t>
         </is>
       </c>
-      <c r="C275" s="18" t="inlineStr">
+      <c r="C276" s="18" t="inlineStr">
         <is>
           <t>4.13 x 3.00</t>
         </is>
       </c>
-      <c r="D275" s="19" t="n">
+      <c r="D276" s="19" t="n">
         <v>12.39</v>
       </c>
-      <c r="E275" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F275" s="80" t="n">
-        <v>247.8</v>
-      </c>
-      <c r="G275" s="53" t="n"/>
-    </row>
-    <row r="276" ht="19.8" customHeight="1">
-      <c r="A276" s="47" t="n"/>
-      <c r="B276" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C276" s="18" t="n"/>
-      <c r="D276" s="19" t="n"/>
       <c r="E276" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F276" s="80" t="n"/>
+      <c r="F276" s="80" t="n">
+        <v>247.8</v>
+      </c>
       <c r="G276" s="53" t="n"/>
     </row>
     <row r="277" ht="19.8" customHeight="1">
       <c r="A277" s="47" t="n"/>
       <c r="B277" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C277" s="18" t="inlineStr">
-        <is>
-          <t>4.08 x 3.00</t>
-        </is>
-      </c>
-      <c r="D277" s="19" t="n">
-        <v>12.24</v>
-      </c>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C277" s="18" t="n"/>
+      <c r="D277" s="19" t="n"/>
       <c r="E277" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F277" s="80" t="n">
-        <v>306</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F277" s="80" t="n"/>
       <c r="G277" s="53" t="n"/>
     </row>
     <row r="278" ht="19.8" customHeight="1">
@@ -24939,359 +24939,367 @@
       </c>
       <c r="C278" s="18" t="inlineStr">
         <is>
-          <t>4.13 x 3.00</t>
+          <t>4.08 x 3.00</t>
         </is>
       </c>
       <c r="D278" s="19" t="n">
-        <v>12.39</v>
+        <v>12.24</v>
       </c>
       <c r="E278" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F278" s="80" t="n">
-        <v>309.8</v>
+        <v>306</v>
       </c>
       <c r="G278" s="53" t="n"/>
     </row>
     <row r="279" ht="19.8" customHeight="1">
-      <c r="A279" s="50" t="n"/>
-      <c r="B279" s="82" t="inlineStr">
+      <c r="A279" s="47" t="n"/>
+      <c r="B279" s="81" t="inlineStr">
         <is>
           <t>INTERIORES</t>
         </is>
       </c>
       <c r="C279" s="18" t="inlineStr">
         <is>
-          <t>4.08 x 3.00</t>
+          <t>4.13 x 3.00</t>
         </is>
       </c>
       <c r="D279" s="19" t="n">
-        <v>12.24</v>
+        <v>12.39</v>
       </c>
       <c r="E279" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F279" s="80" t="n">
+        <v>309.8</v>
+      </c>
+      <c r="G279" s="53" t="n"/>
+    </row>
+    <row r="280" ht="19.8" customHeight="1">
+      <c r="A280" s="50" t="n"/>
+      <c r="B280" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C280" s="18" t="inlineStr">
+        <is>
+          <t>4.08 x 3.00</t>
+        </is>
+      </c>
+      <c r="D280" s="19" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="E280" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F280" s="80" t="n">
         <v>306</v>
       </c>
-      <c r="G279" s="53" t="n"/>
-    </row>
-    <row r="280" ht="19.8" customHeight="1">
-      <c r="A280" s="36" t="inlineStr">
+      <c r="G280" s="53" t="n"/>
+    </row>
+    <row r="281" ht="19.8" customHeight="1">
+      <c r="A281" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B280" s="78" t="inlineStr">
+      <c r="B281" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C280" s="47" t="n"/>
-      <c r="D280" s="18" t="n"/>
-      <c r="E280" s="18" t="n"/>
-      <c r="F280" s="20" t="n"/>
-      <c r="G280" s="53" t="n"/>
-    </row>
-    <row r="281" ht="19.8" customHeight="1">
-      <c r="A281" s="43" t="n"/>
-      <c r="B281" s="79" t="inlineStr">
+      <c r="C281" s="47" t="n"/>
+      <c r="D281" s="18" t="n"/>
+      <c r="E281" s="18" t="n"/>
+      <c r="F281" s="20" t="n"/>
+      <c r="G281" s="53" t="n"/>
+    </row>
+    <row r="282" ht="19.8" customHeight="1">
+      <c r="A282" s="43" t="n"/>
+      <c r="B282" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
         </is>
       </c>
-      <c r="C281" s="18" t="n"/>
-      <c r="D281" s="19" t="n"/>
-      <c r="E281" s="59" t="n">
+      <c r="C282" s="18" t="n"/>
+      <c r="D282" s="19" t="n"/>
+      <c r="E282" s="59" t="n">
         <v>30</v>
       </c>
-      <c r="F281" s="80" t="n"/>
-      <c r="G281" s="53" t="n"/>
-    </row>
-    <row r="282" ht="19.8" customHeight="1">
-      <c r="A282" s="47" t="n"/>
-      <c r="B282" s="81" t="inlineStr">
+      <c r="F282" s="80" t="n"/>
+      <c r="G282" s="53" t="n"/>
+    </row>
+    <row r="283" ht="19.8" customHeight="1">
+      <c r="A283" s="47" t="n"/>
+      <c r="B283" s="81" t="inlineStr">
         <is>
           <t>TECHO AISLADO</t>
         </is>
       </c>
-      <c r="C282" s="18" t="inlineStr">
+      <c r="C283" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D282" s="19" t="n">
+      <c r="D283" s="19" t="n">
         <v>16.85</v>
       </c>
-      <c r="E282" s="59" t="n">
+      <c r="E283" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F282" s="80" t="n">
+      <c r="F283" s="80" t="n">
         <v>337</v>
       </c>
-      <c r="G282" s="53" t="n"/>
-    </row>
-    <row r="283" ht="19.8" customHeight="1">
-      <c r="A283" s="50" t="n"/>
-      <c r="B283" s="82" t="inlineStr">
+      <c r="G283" s="53" t="n"/>
+    </row>
+    <row r="284" ht="19.8" customHeight="1">
+      <c r="A284" s="50" t="n"/>
+      <c r="B284" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C283" s="18" t="n"/>
-      <c r="D283" s="19" t="n"/>
-      <c r="E283" s="59" t="n">
+      <c r="C284" s="18" t="n"/>
+      <c r="D284" s="19" t="n"/>
+      <c r="E284" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F283" s="80" t="n"/>
-      <c r="G283" s="53" t="n"/>
-    </row>
-    <row r="284" ht="19.8" customHeight="1">
-      <c r="A284" s="36" t="inlineStr">
+      <c r="F284" s="80" t="n"/>
+      <c r="G284" s="53" t="n"/>
+    </row>
+    <row r="285" ht="19.8" customHeight="1">
+      <c r="A285" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B284" s="78" t="inlineStr">
+      <c r="B285" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C284" s="47" t="n"/>
-      <c r="D284" s="18" t="n"/>
-      <c r="E284" s="18" t="n"/>
-      <c r="F284" s="20" t="n"/>
-      <c r="G284" s="53" t="n"/>
-    </row>
-    <row r="285" ht="19.8" customHeight="1">
-      <c r="A285" s="43" t="n"/>
-      <c r="B285" s="79" t="inlineStr">
+      <c r="C285" s="47" t="n"/>
+      <c r="D285" s="18" t="n"/>
+      <c r="E285" s="18" t="n"/>
+      <c r="F285" s="20" t="n"/>
+      <c r="G285" s="53" t="n"/>
+    </row>
+    <row r="286" ht="19.8" customHeight="1">
+      <c r="A286" s="43" t="n"/>
+      <c r="B286" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C285" s="18" t="n"/>
-      <c r="D285" s="19" t="n"/>
-      <c r="E285" s="59" t="n">
+      <c r="C286" s="18" t="n"/>
+      <c r="D286" s="19" t="n"/>
+      <c r="E286" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F285" s="80" t="n"/>
-      <c r="G285" s="53" t="n"/>
-    </row>
-    <row r="286" ht="19.8" customHeight="1">
-      <c r="A286" s="50" t="n"/>
-      <c r="B286" s="82" t="inlineStr">
+      <c r="F286" s="80" t="n"/>
+      <c r="G286" s="53" t="n"/>
+    </row>
+    <row r="287" ht="19.8" customHeight="1">
+      <c r="A287" s="50" t="n"/>
+      <c r="B287" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C286" s="18" t="inlineStr">
+      <c r="C287" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D286" s="24" t="n">
+      <c r="D287" s="24" t="n">
         <v>16.85</v>
       </c>
-      <c r="E286" s="59" t="n">
+      <c r="E287" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F286" s="80" t="n">
+      <c r="F287" s="80" t="n">
         <v>252.8</v>
       </c>
-      <c r="G286" s="53" t="n"/>
-    </row>
-    <row r="287" ht="19.8" customHeight="1">
-      <c r="A287" s="36" t="inlineStr">
+      <c r="G287" s="53" t="n"/>
+    </row>
+    <row r="288" ht="19.8" customHeight="1">
+      <c r="A288" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B287" s="78" t="inlineStr">
+      <c r="B288" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C287" s="83" t="n"/>
-      <c r="D287" s="36" t="inlineStr">
+      <c r="C288" s="83" t="n"/>
+      <c r="D288" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E287" s="47" t="n"/>
-      <c r="F287" s="20" t="n"/>
-      <c r="G287" s="53" t="n"/>
-    </row>
-    <row r="288" ht="19.8" customHeight="1">
-      <c r="A288" s="43" t="n"/>
-      <c r="B288" s="79" t="inlineStr">
+      <c r="E288" s="47" t="n"/>
+      <c r="F288" s="20" t="n"/>
+      <c r="G288" s="53" t="n"/>
+    </row>
+    <row r="289" ht="19.8" customHeight="1">
+      <c r="A289" s="43" t="n"/>
+      <c r="B289" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C288" s="18" t="inlineStr">
+      <c r="C289" s="18" t="inlineStr">
         <is>
           <t>16.85 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D288" s="22" t="n">
+      <c r="D289" s="22" t="n">
         <v>50.55</v>
       </c>
-      <c r="E288" s="59" t="n">
+      <c r="E289" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="F288" s="80" t="n">
+      <c r="F289" s="80" t="n">
         <v>303.3</v>
       </c>
-      <c r="G288" s="53" t="n"/>
-    </row>
-    <row r="289" ht="19.8" customHeight="1">
-      <c r="A289" s="47" t="n"/>
-      <c r="B289" s="81" t="inlineStr">
+      <c r="G289" s="53" t="n"/>
+    </row>
+    <row r="290" ht="19.8" customHeight="1">
+      <c r="A290" s="47" t="n"/>
+      <c r="B290" s="81" t="inlineStr">
         <is>
           <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C289" s="18" t="n"/>
-      <c r="D289" s="19" t="n"/>
-      <c r="E289" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F289" s="80" t="n"/>
-      <c r="G289" s="53" t="n"/>
-    </row>
-    <row r="290" ht="19.8" customHeight="1">
-      <c r="A290" s="50" t="n"/>
-      <c r="B290" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C290" s="18" t="n"/>
       <c r="D290" s="19" t="n"/>
       <c r="E290" s="59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F290" s="80" t="n"/>
+      <c r="G290" s="53" t="n"/>
+    </row>
+    <row r="291" ht="19.8" customHeight="1">
+      <c r="A291" s="50" t="n"/>
+      <c r="B291" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C291" s="18" t="n"/>
+      <c r="D291" s="19" t="n"/>
+      <c r="E291" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F290" s="84" t="n"/>
-      <c r="G290" s="53" t="n"/>
-    </row>
-    <row r="291" ht="19.8" customHeight="1">
-      <c r="A291" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B291" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C291" s="47" t="n"/>
-      <c r="D291" s="18" t="n"/>
-      <c r="E291" s="20" t="n"/>
-      <c r="F291" s="85" t="n">
-        <v>2365.1</v>
-      </c>
+      <c r="F291" s="84" t="n"/>
       <c r="G291" s="53" t="n"/>
     </row>
     <row r="292" ht="19.8" customHeight="1">
       <c r="A292" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B292" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C292" s="47" t="n"/>
+      <c r="D292" s="18" t="n"/>
+      <c r="E292" s="20" t="n"/>
+      <c r="F292" s="85" t="n">
+        <v>2365.1</v>
+      </c>
+      <c r="G292" s="53" t="n"/>
+    </row>
+    <row r="293" ht="19.8" customHeight="1">
+      <c r="A293" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B292" s="78" t="inlineStr">
+      <c r="B293" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C292" s="47" t="inlineStr">
+      <c r="C293" s="47" t="inlineStr">
         <is>
           <t>2365.10  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D292" s="12" t="n"/>
-      <c r="E292" s="14" t="n"/>
-      <c r="F292" s="85" t="n">
+      <c r="D293" s="12" t="n"/>
+      <c r="E293" s="14" t="n"/>
+      <c r="F293" s="85" t="n">
         <v>2530.7</v>
       </c>
-      <c r="G292" s="53" t="n"/>
-    </row>
-    <row r="293" ht="19.8" customHeight="1">
-      <c r="A293" s="43" t="n"/>
-      <c r="B293" s="86" t="inlineStr">
+      <c r="G293" s="53" t="n"/>
+    </row>
+    <row r="294" ht="19.8" customHeight="1">
+      <c r="A294" s="43" t="n"/>
+      <c r="B294" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C293" s="18" t="inlineStr">
+      <c r="C294" s="18" t="inlineStr">
         <is>
           <t>Escalera</t>
         </is>
       </c>
-      <c r="D293" s="12" t="n"/>
-      <c r="E293" s="39" t="n"/>
-      <c r="F293" s="87" t="n">
+      <c r="D294" s="12" t="n"/>
+      <c r="E294" s="39" t="n"/>
+      <c r="F294" s="87" t="n">
         <v>1348.3</v>
       </c>
-      <c r="G293" s="53" t="n"/>
-    </row>
-    <row r="294" ht="19.8" customHeight="1">
-      <c r="A294" s="83" t="n"/>
-      <c r="B294" s="78" t="inlineStr">
+      <c r="G294" s="53" t="n"/>
+    </row>
+    <row r="295" ht="19.8" customHeight="1">
+      <c r="A295" s="83" t="n"/>
+      <c r="B295" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C294" s="47" t="n"/>
-      <c r="D294" s="12" t="n"/>
-      <c r="E294" s="14" t="n"/>
-      <c r="F294" s="85" t="n">
+      <c r="C295" s="47" t="n"/>
+      <c r="D295" s="12" t="n"/>
+      <c r="E295" s="14" t="n"/>
+      <c r="F295" s="85" t="n">
         <v>3879</v>
       </c>
-      <c r="G294" s="53" t="n"/>
-    </row>
-    <row r="295" ht="19.8" customHeight="1">
-      <c r="A295" s="47" t="n"/>
-      <c r="B295" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C295" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
-      </c>
-      <c r="D295" s="12" t="n"/>
-      <c r="E295" s="39" t="n"/>
-      <c r="F295" s="61" t="n"/>
       <c r="G295" s="53" t="n"/>
     </row>
     <row r="296" ht="19.8" customHeight="1">
       <c r="A296" s="47" t="n"/>
-      <c r="B296" s="60" t="inlineStr">
-        <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C296" s="19" t="n">
-        <v>274.4</v>
+      <c r="B296" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C296" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
       </c>
       <c r="D296" s="12" t="n"/>
       <c r="E296" s="39" t="n"/>
-      <c r="F296" s="20" t="n"/>
+      <c r="F296" s="61" t="n"/>
       <c r="G296" s="53" t="n"/>
     </row>
     <row r="297" ht="19.8" customHeight="1">
       <c r="A297" s="47" t="n"/>
       <c r="B297" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
-        </is>
-      </c>
-      <c r="C297" s="59" t="n">
-        <v>15</v>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C297" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D297" s="12" t="n"/>
       <c r="E297" s="39" t="n"/>
@@ -25302,11 +25310,11 @@
       <c r="A298" s="47" t="n"/>
       <c r="B298" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C298" s="59" t="n">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="D298" s="12" t="n"/>
       <c r="E298" s="39" t="n"/>
@@ -25314,16 +25322,14 @@
       <c r="G298" s="53" t="n"/>
     </row>
     <row r="299" ht="19.8" customHeight="1">
-      <c r="A299" s="50" t="n"/>
+      <c r="A299" s="47" t="n"/>
       <c r="B299" s="60" t="inlineStr">
         <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C299" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
+          <t>Ancho del radiador (cm)</t>
+        </is>
+      </c>
+      <c r="C299" s="59" t="n">
+        <v>120</v>
       </c>
       <c r="D299" s="12" t="n"/>
       <c r="E299" s="39" t="n"/>
@@ -25331,151 +25337,145 @@
       <c r="G299" s="53" t="n"/>
     </row>
     <row r="300" ht="19.8" customHeight="1">
-      <c r="A300" s="8" t="inlineStr">
+      <c r="A300" s="50" t="n"/>
+      <c r="B300" s="60" t="inlineStr">
+        <is>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C300" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
+      </c>
+      <c r="D300" s="12" t="n"/>
+      <c r="E300" s="39" t="n"/>
+      <c r="F300" s="20" t="n"/>
+      <c r="G300" s="53" t="n"/>
+    </row>
+    <row r="301" ht="19.8" customHeight="1">
+      <c r="A301" s="8" t="inlineStr">
         <is>
           <t>LOCAL  15 - Dormitorio Sur   (PA)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B300" s="11" t="n"/>
-      <c r="C300" s="11" t="n"/>
-      <c r="D300" s="11" t="n"/>
-      <c r="E300" s="11" t="n"/>
-      <c r="F300" s="42" t="n"/>
-      <c r="G300" s="53" t="n"/>
-    </row>
-    <row r="301" ht="32" customHeight="1">
-      <c r="A301" s="2" t="inlineStr">
+      <c r="B301" s="11" t="n"/>
+      <c r="C301" s="11" t="n"/>
+      <c r="D301" s="11" t="n"/>
+      <c r="E301" s="11" t="n"/>
+      <c r="F301" s="42" t="n"/>
+      <c r="G301" s="53" t="n"/>
+    </row>
+    <row r="302" ht="32" customHeight="1">
+      <c r="A302" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B301" s="2" t="inlineStr">
+      <c r="B302" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C301" s="2" t="inlineStr">
+      <c r="C302" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D301" s="2" t="inlineStr">
+      <c r="D302" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E301" s="2" t="inlineStr">
+      <c r="E302" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F301" s="2" t="inlineStr">
+      <c r="F302" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G301" s="53" t="n"/>
-    </row>
-    <row r="302" ht="19.8" customHeight="1">
-      <c r="A302" s="36" t="inlineStr">
+      <c r="G302" s="53" t="n"/>
+    </row>
+    <row r="303" ht="19.8" customHeight="1">
+      <c r="A303" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B302" s="78" t="inlineStr">
+      <c r="B303" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C302" s="43" t="n"/>
-      <c r="D302" s="58" t="n"/>
-      <c r="E302" s="58" t="n"/>
-      <c r="F302" s="61" t="n"/>
-      <c r="G302" s="53" t="n"/>
-    </row>
-    <row r="303" ht="19.8" customHeight="1">
-      <c r="A303" s="89" t="n"/>
-      <c r="B303" s="90" t="inlineStr">
+      <c r="C303" s="43" t="n"/>
+      <c r="D303" s="58" t="n"/>
+      <c r="E303" s="58" t="n"/>
+      <c r="F303" s="61" t="n"/>
+      <c r="G303" s="53" t="n"/>
+    </row>
+    <row r="304" ht="19.8" customHeight="1">
+      <c r="A304" s="90" t="n"/>
+      <c r="B304" s="91" t="inlineStr">
         <is>
           <t>PV04</t>
         </is>
       </c>
-      <c r="C303" s="18" t="inlineStr">
+      <c r="C304" s="18" t="inlineStr">
         <is>
           <t>2.06 x 3.00</t>
         </is>
       </c>
-      <c r="D303" s="19" t="n">
+      <c r="D304" s="19" t="n">
         <v>6.18</v>
       </c>
-      <c r="E303" s="59" t="n">
+      <c r="E304" s="59" t="n">
         <v>60</v>
       </c>
-      <c r="F303" s="80" t="n">
+      <c r="F304" s="80" t="n">
         <v>370.8</v>
       </c>
-      <c r="G303" s="53" t="n"/>
-    </row>
-    <row r="304" ht="19.8" customHeight="1">
-      <c r="A304" s="36" t="inlineStr">
+      <c r="G304" s="53" t="n"/>
+    </row>
+    <row r="305" ht="19.8" customHeight="1">
+      <c r="A305" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B304" s="78" t="inlineStr">
+      <c r="B305" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C304" s="47" t="n"/>
-      <c r="D304" s="18" t="n"/>
-      <c r="E304" s="18" t="n"/>
-      <c r="F304" s="20" t="n"/>
-      <c r="G304" s="53" t="n"/>
-    </row>
-    <row r="305" ht="19.8" customHeight="1">
-      <c r="A305" s="43" t="n"/>
-      <c r="B305" s="79" t="inlineStr">
+      <c r="C305" s="47" t="n"/>
+      <c r="D305" s="18" t="n"/>
+      <c r="E305" s="18" t="n"/>
+      <c r="F305" s="20" t="n"/>
+      <c r="G305" s="53" t="n"/>
+    </row>
+    <row r="306" ht="19.8" customHeight="1">
+      <c r="A306" s="43" t="n"/>
+      <c r="B306" s="79" t="inlineStr">
         <is>
           <t>AISLADAS (SE)</t>
         </is>
       </c>
-      <c r="C305" s="18" t="inlineStr">
+      <c r="C306" s="18" t="inlineStr">
         <is>
           <t>4.05 x 3.00</t>
         </is>
       </c>
-      <c r="D305" s="19" t="n">
+      <c r="D306" s="19" t="n">
         <v>12.15</v>
-      </c>
-      <c r="E305" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F305" s="80" t="n">
-        <v>243</v>
-      </c>
-      <c r="G305" s="53" t="n"/>
-    </row>
-    <row r="306" ht="19.8" customHeight="1">
-      <c r="A306" s="47" t="n"/>
-      <c r="B306" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C306" s="18" t="inlineStr">
-        <is>
-          <t>3.50 x 3.00</t>
-        </is>
-      </c>
-      <c r="D306" s="19" t="n">
-        <v>10.5</v>
       </c>
       <c r="E306" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F306" s="80" t="n">
-        <v>210</v>
+        <v>243</v>
       </c>
       <c r="G306" s="53" t="n"/>
     </row>
@@ -25483,358 +25483,366 @@
       <c r="A307" s="47" t="n"/>
       <c r="B307" s="81" t="inlineStr">
         <is>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C307" s="18" t="inlineStr">
+        <is>
+          <t>3.50 x 3.00</t>
+        </is>
+      </c>
+      <c r="D307" s="19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E307" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F307" s="80" t="n">
+        <v>210</v>
+      </c>
+      <c r="G307" s="53" t="n"/>
+    </row>
+    <row r="308" ht="19.8" customHeight="1">
+      <c r="A308" s="47" t="n"/>
+      <c r="B308" s="81" t="inlineStr">
+        <is>
           <t>INTERIORES</t>
         </is>
       </c>
-      <c r="C307" s="18" t="inlineStr">
+      <c r="C308" s="18" t="inlineStr">
         <is>
           <t>4.05 x 3.00</t>
         </is>
       </c>
-      <c r="D307" s="19" t="n">
+      <c r="D308" s="19" t="n">
         <v>12.15</v>
-      </c>
-      <c r="E307" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F307" s="80" t="n">
-        <v>303.8</v>
-      </c>
-      <c r="G307" s="53" t="n"/>
-    </row>
-    <row r="308" ht="19.8" customHeight="1">
-      <c r="A308" s="50" t="n"/>
-      <c r="B308" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C308" s="18" t="inlineStr">
-        <is>
-          <t>3.50 x 3.00</t>
-        </is>
-      </c>
-      <c r="D308" s="19" t="n">
-        <v>10.5</v>
       </c>
       <c r="E308" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F308" s="80" t="n">
+        <v>303.8</v>
+      </c>
+      <c r="G308" s="53" t="n"/>
+    </row>
+    <row r="309" ht="19.8" customHeight="1">
+      <c r="A309" s="50" t="n"/>
+      <c r="B309" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C309" s="18" t="inlineStr">
+        <is>
+          <t>3.50 x 3.00</t>
+        </is>
+      </c>
+      <c r="D309" s="19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E309" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F309" s="80" t="n">
         <v>262.5</v>
       </c>
-      <c r="G308" s="53" t="n"/>
-    </row>
-    <row r="309" ht="19.8" customHeight="1">
-      <c r="A309" s="36" t="inlineStr">
+      <c r="G309" s="53" t="n"/>
+    </row>
+    <row r="310" ht="19.8" customHeight="1">
+      <c r="A310" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B309" s="78" t="inlineStr">
+      <c r="B310" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C309" s="47" t="n"/>
-      <c r="D309" s="18" t="n"/>
-      <c r="E309" s="18" t="n"/>
-      <c r="F309" s="20" t="n"/>
-      <c r="G309" s="53" t="n"/>
-    </row>
-    <row r="310" ht="19.8" customHeight="1">
-      <c r="A310" s="43" t="n"/>
-      <c r="B310" s="79" t="inlineStr">
+      <c r="C310" s="47" t="n"/>
+      <c r="D310" s="18" t="n"/>
+      <c r="E310" s="18" t="n"/>
+      <c r="F310" s="20" t="n"/>
+      <c r="G310" s="53" t="n"/>
+    </row>
+    <row r="311" ht="19.8" customHeight="1">
+      <c r="A311" s="43" t="n"/>
+      <c r="B311" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
         </is>
       </c>
-      <c r="C310" s="18" t="n"/>
-      <c r="D310" s="19" t="n"/>
-      <c r="E310" s="59" t="n">
+      <c r="C311" s="18" t="n"/>
+      <c r="D311" s="19" t="n"/>
+      <c r="E311" s="59" t="n">
         <v>30</v>
       </c>
-      <c r="F310" s="80" t="n"/>
-      <c r="G310" s="53" t="n"/>
-    </row>
-    <row r="311" ht="19.8" customHeight="1">
-      <c r="A311" s="47" t="n"/>
-      <c r="B311" s="81" t="inlineStr">
+      <c r="F311" s="80" t="n"/>
+      <c r="G311" s="53" t="n"/>
+    </row>
+    <row r="312" ht="19.8" customHeight="1">
+      <c r="A312" s="47" t="n"/>
+      <c r="B312" s="81" t="inlineStr">
         <is>
           <t>TECHO AISLADO</t>
         </is>
       </c>
-      <c r="C311" s="18" t="inlineStr">
+      <c r="C312" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D311" s="19" t="n">
+      <c r="D312" s="19" t="n">
         <v>14.17</v>
       </c>
-      <c r="E311" s="59" t="n">
+      <c r="E312" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F311" s="80" t="n">
+      <c r="F312" s="80" t="n">
         <v>283.4</v>
       </c>
-      <c r="G311" s="53" t="n"/>
-    </row>
-    <row r="312" ht="19.8" customHeight="1">
-      <c r="A312" s="50" t="n"/>
-      <c r="B312" s="82" t="inlineStr">
+      <c r="G312" s="53" t="n"/>
+    </row>
+    <row r="313" ht="19.8" customHeight="1">
+      <c r="A313" s="50" t="n"/>
+      <c r="B313" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C312" s="18" t="n"/>
-      <c r="D312" s="19" t="n"/>
-      <c r="E312" s="59" t="n">
+      <c r="C313" s="18" t="n"/>
+      <c r="D313" s="19" t="n"/>
+      <c r="E313" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F312" s="80" t="n"/>
-      <c r="G312" s="53" t="n"/>
-    </row>
-    <row r="313" ht="19.8" customHeight="1">
-      <c r="A313" s="36" t="inlineStr">
+      <c r="F313" s="80" t="n"/>
+      <c r="G313" s="53" t="n"/>
+    </row>
+    <row r="314" ht="19.8" customHeight="1">
+      <c r="A314" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B313" s="78" t="inlineStr">
+      <c r="B314" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C313" s="47" t="n"/>
-      <c r="D313" s="18" t="n"/>
-      <c r="E313" s="18" t="n"/>
-      <c r="F313" s="20" t="n"/>
-      <c r="G313" s="53" t="n"/>
-    </row>
-    <row r="314" ht="19.8" customHeight="1">
-      <c r="A314" s="43" t="n"/>
-      <c r="B314" s="79" t="inlineStr">
+      <c r="C314" s="47" t="n"/>
+      <c r="D314" s="18" t="n"/>
+      <c r="E314" s="18" t="n"/>
+      <c r="F314" s="20" t="n"/>
+      <c r="G314" s="53" t="n"/>
+    </row>
+    <row r="315" ht="19.8" customHeight="1">
+      <c r="A315" s="43" t="n"/>
+      <c r="B315" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C314" s="18" t="n"/>
-      <c r="D314" s="19" t="n"/>
-      <c r="E314" s="59" t="n">
+      <c r="C315" s="18" t="n"/>
+      <c r="D315" s="19" t="n"/>
+      <c r="E315" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F314" s="80" t="n"/>
-      <c r="G314" s="53" t="n"/>
-    </row>
-    <row r="315" ht="19.8" customHeight="1">
-      <c r="A315" s="50" t="n"/>
-      <c r="B315" s="82" t="inlineStr">
+      <c r="F315" s="80" t="n"/>
+      <c r="G315" s="53" t="n"/>
+    </row>
+    <row r="316" ht="19.8" customHeight="1">
+      <c r="A316" s="50" t="n"/>
+      <c r="B316" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C315" s="18" t="inlineStr">
+      <c r="C316" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D315" s="24" t="n">
+      <c r="D316" s="24" t="n">
         <v>14.17</v>
       </c>
-      <c r="E315" s="59" t="n">
+      <c r="E316" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F315" s="80" t="n">
+      <c r="F316" s="80" t="n">
         <v>212.6</v>
       </c>
-      <c r="G315" s="53" t="n"/>
-    </row>
-    <row r="316" ht="19.8" customHeight="1">
-      <c r="A316" s="36" t="inlineStr">
+      <c r="G316" s="53" t="n"/>
+    </row>
+    <row r="317" ht="19.8" customHeight="1">
+      <c r="A317" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B316" s="78" t="inlineStr">
+      <c r="B317" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C316" s="83" t="n"/>
-      <c r="D316" s="36" t="inlineStr">
+      <c r="C317" s="83" t="n"/>
+      <c r="D317" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E316" s="47" t="n"/>
-      <c r="F316" s="20" t="n"/>
-      <c r="G316" s="53" t="n"/>
-    </row>
-    <row r="317" ht="19.8" customHeight="1">
-      <c r="A317" s="43" t="n"/>
-      <c r="B317" s="79" t="inlineStr">
+      <c r="E317" s="47" t="n"/>
+      <c r="F317" s="20" t="n"/>
+      <c r="G317" s="53" t="n"/>
+    </row>
+    <row r="318" ht="19.8" customHeight="1">
+      <c r="A318" s="43" t="n"/>
+      <c r="B318" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C317" s="18" t="n"/>
-      <c r="D317" s="22" t="n"/>
-      <c r="E317" s="59" t="n">
+      <c r="C318" s="18" t="n"/>
+      <c r="D318" s="22" t="n"/>
+      <c r="E318" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="F317" s="80" t="n"/>
-      <c r="G317" s="53" t="n"/>
-    </row>
-    <row r="318" ht="19.8" customHeight="1">
-      <c r="A318" s="47" t="n"/>
-      <c r="B318" s="81" t="inlineStr">
+      <c r="F318" s="80" t="n"/>
+      <c r="G318" s="53" t="n"/>
+    </row>
+    <row r="319" ht="19.8" customHeight="1">
+      <c r="A319" s="47" t="n"/>
+      <c r="B319" s="81" t="inlineStr">
         <is>
           <t>DOS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C318" s="18" t="inlineStr">
+      <c r="C319" s="18" t="inlineStr">
         <is>
           <t>14.17 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D318" s="19" t="n">
+      <c r="D319" s="19" t="n">
         <v>42.51</v>
       </c>
-      <c r="E318" s="59" t="n">
+      <c r="E319" s="59" t="n">
         <v>9</v>
       </c>
-      <c r="F318" s="80" t="n">
+      <c r="F319" s="80" t="n">
         <v>382.6</v>
       </c>
-      <c r="G318" s="53" t="n"/>
-    </row>
-    <row r="319" ht="19.8" customHeight="1">
-      <c r="A319" s="50" t="n"/>
-      <c r="B319" s="82" t="inlineStr">
+      <c r="G319" s="53" t="n"/>
+    </row>
+    <row r="320" ht="19.8" customHeight="1">
+      <c r="A320" s="50" t="n"/>
+      <c r="B320" s="82" t="inlineStr">
         <is>
           <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C319" s="18" t="n"/>
-      <c r="D319" s="19" t="n"/>
-      <c r="E319" s="59" t="n">
+      <c r="C320" s="18" t="n"/>
+      <c r="D320" s="19" t="n"/>
+      <c r="E320" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F319" s="84" t="n"/>
-      <c r="G319" s="53" t="n"/>
-    </row>
-    <row r="320" ht="19.8" customHeight="1">
-      <c r="A320" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B320" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C320" s="47" t="n"/>
-      <c r="D320" s="18" t="n"/>
-      <c r="E320" s="20" t="n"/>
-      <c r="F320" s="85" t="n">
-        <v>2268.7</v>
-      </c>
+      <c r="F320" s="84" t="n"/>
       <c r="G320" s="53" t="n"/>
     </row>
     <row r="321" ht="19.8" customHeight="1">
       <c r="A321" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B321" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C321" s="47" t="n"/>
+      <c r="D321" s="18" t="n"/>
+      <c r="E321" s="20" t="n"/>
+      <c r="F321" s="85" t="n">
+        <v>2268.7</v>
+      </c>
+      <c r="G321" s="53" t="n"/>
+    </row>
+    <row r="322" ht="19.8" customHeight="1">
+      <c r="A322" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B321" s="78" t="inlineStr">
+      <c r="B322" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C321" s="47" t="inlineStr">
+      <c r="C322" s="47" t="inlineStr">
         <is>
           <t>2268.70  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D321" s="12" t="n"/>
-      <c r="E321" s="14" t="n"/>
-      <c r="F321" s="85" t="n">
+      <c r="D322" s="12" t="n"/>
+      <c r="E322" s="14" t="n"/>
+      <c r="F322" s="85" t="n">
         <v>2427.5</v>
       </c>
-      <c r="G321" s="53" t="n"/>
-    </row>
-    <row r="322" ht="19.8" customHeight="1">
-      <c r="A322" s="43" t="n"/>
-      <c r="B322" s="86" t="inlineStr">
+      <c r="G322" s="53" t="n"/>
+    </row>
+    <row r="323" ht="19.8" customHeight="1">
+      <c r="A323" s="43" t="n"/>
+      <c r="B323" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C322" s="18" t="n"/>
-      <c r="D322" s="12" t="n"/>
-      <c r="E322" s="39" t="n"/>
-      <c r="F322" s="87" t="n"/>
-      <c r="G322" s="53" t="n"/>
-    </row>
-    <row r="323" ht="19.8" customHeight="1">
-      <c r="A323" s="83" t="n"/>
-      <c r="B323" s="78" t="inlineStr">
+      <c r="C323" s="18" t="n"/>
+      <c r="D323" s="12" t="n"/>
+      <c r="E323" s="39" t="n"/>
+      <c r="F323" s="87" t="n"/>
+      <c r="G323" s="53" t="n"/>
+    </row>
+    <row r="324" ht="19.8" customHeight="1">
+      <c r="A324" s="83" t="n"/>
+      <c r="B324" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C323" s="47" t="n"/>
-      <c r="D323" s="12" t="n"/>
-      <c r="E323" s="14" t="n"/>
-      <c r="F323" s="85" t="n">
+      <c r="C324" s="47" t="n"/>
+      <c r="D324" s="12" t="n"/>
+      <c r="E324" s="14" t="n"/>
+      <c r="F324" s="85" t="n">
         <v>2427.5</v>
       </c>
-      <c r="G323" s="53" t="n"/>
-    </row>
-    <row r="324" ht="19.8" customHeight="1">
-      <c r="A324" s="47" t="n"/>
-      <c r="B324" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C324" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
-      </c>
-      <c r="D324" s="12" t="n"/>
-      <c r="E324" s="39" t="n"/>
-      <c r="F324" s="61" t="n"/>
       <c r="G324" s="53" t="n"/>
     </row>
     <row r="325" ht="19.8" customHeight="1">
       <c r="A325" s="47" t="n"/>
-      <c r="B325" s="60" t="inlineStr">
-        <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C325" s="19" t="n">
-        <v>274.4</v>
+      <c r="B325" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C325" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
       </c>
       <c r="D325" s="12" t="n"/>
       <c r="E325" s="39" t="n"/>
-      <c r="F325" s="20" t="n"/>
+      <c r="F325" s="61" t="n"/>
       <c r="G325" s="53" t="n"/>
     </row>
     <row r="326" ht="19.8" customHeight="1">
       <c r="A326" s="47" t="n"/>
       <c r="B326" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
-        </is>
-      </c>
-      <c r="C326" s="59" t="n">
-        <v>9</v>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C326" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D326" s="12" t="n"/>
       <c r="E326" s="39" t="n"/>
@@ -25845,11 +25853,11 @@
       <c r="A327" s="47" t="n"/>
       <c r="B327" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C327" s="59" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="D327" s="12" t="n"/>
       <c r="E327" s="39" t="n"/>
@@ -25857,16 +25865,14 @@
       <c r="G327" s="53" t="n"/>
     </row>
     <row r="328" ht="19.8" customHeight="1">
-      <c r="A328" s="50" t="n"/>
+      <c r="A328" s="47" t="n"/>
       <c r="B328" s="60" t="inlineStr">
         <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C328" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
+          <t>Ancho del radiador (cm)</t>
+        </is>
+      </c>
+      <c r="C328" s="59" t="n">
+        <v>72</v>
       </c>
       <c r="D328" s="12" t="n"/>
       <c r="E328" s="39" t="n"/>
@@ -25874,151 +25880,145 @@
       <c r="G328" s="53" t="n"/>
     </row>
     <row r="329" ht="19.8" customHeight="1">
-      <c r="A329" s="8" t="inlineStr">
+      <c r="A329" s="50" t="n"/>
+      <c r="B329" s="60" t="inlineStr">
+        <is>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C329" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
+      </c>
+      <c r="D329" s="12" t="n"/>
+      <c r="E329" s="39" t="n"/>
+      <c r="F329" s="20" t="n"/>
+      <c r="G329" s="53" t="n"/>
+    </row>
+    <row r="330" ht="19.8" customHeight="1">
+      <c r="A330" s="8" t="inlineStr">
         <is>
           <t>LOCAL  17 - Bano   (PA)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B329" s="11" t="n"/>
-      <c r="C329" s="11" t="n"/>
-      <c r="D329" s="11" t="n"/>
-      <c r="E329" s="11" t="n"/>
-      <c r="F329" s="42" t="n"/>
-      <c r="G329" s="53" t="n"/>
-    </row>
-    <row r="330" ht="32" customHeight="1">
-      <c r="A330" s="2" t="inlineStr">
+      <c r="B330" s="11" t="n"/>
+      <c r="C330" s="11" t="n"/>
+      <c r="D330" s="11" t="n"/>
+      <c r="E330" s="11" t="n"/>
+      <c r="F330" s="42" t="n"/>
+      <c r="G330" s="53" t="n"/>
+    </row>
+    <row r="331" ht="32" customHeight="1">
+      <c r="A331" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B330" s="2" t="inlineStr">
+      <c r="B331" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C330" s="2" t="inlineStr">
+      <c r="C331" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D330" s="2" t="inlineStr">
+      <c r="D331" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E330" s="2" t="inlineStr">
+      <c r="E331" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F330" s="2" t="inlineStr">
+      <c r="F331" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G330" s="53" t="n"/>
-    </row>
-    <row r="331" ht="19.8" customHeight="1">
-      <c r="A331" s="36" t="inlineStr">
+      <c r="G331" s="53" t="n"/>
+    </row>
+    <row r="332" ht="19.8" customHeight="1">
+      <c r="A332" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B331" s="78" t="inlineStr">
+      <c r="B332" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C331" s="43" t="n"/>
-      <c r="D331" s="58" t="n"/>
-      <c r="E331" s="58" t="n"/>
-      <c r="F331" s="61" t="n"/>
-      <c r="G331" s="53" t="n"/>
-    </row>
-    <row r="332" ht="19.8" customHeight="1">
-      <c r="A332" s="89" t="n"/>
-      <c r="B332" s="90" t="inlineStr">
+      <c r="C332" s="43" t="n"/>
+      <c r="D332" s="58" t="n"/>
+      <c r="E332" s="58" t="n"/>
+      <c r="F332" s="61" t="n"/>
+      <c r="G332" s="53" t="n"/>
+    </row>
+    <row r="333" ht="19.8" customHeight="1">
+      <c r="A333" s="90" t="n"/>
+      <c r="B333" s="91" t="inlineStr">
         <is>
           <t>VA03</t>
         </is>
       </c>
-      <c r="C332" s="18" t="inlineStr">
+      <c r="C333" s="18" t="inlineStr">
         <is>
           <t>0.75 x 2.52</t>
         </is>
       </c>
-      <c r="D332" s="19" t="n">
+      <c r="D333" s="19" t="n">
         <v>1.89</v>
       </c>
-      <c r="E332" s="59" t="n">
+      <c r="E333" s="59" t="n">
         <v>60</v>
       </c>
-      <c r="F332" s="80" t="n">
+      <c r="F333" s="80" t="n">
         <v>113.4</v>
       </c>
-      <c r="G332" s="53" t="n"/>
-    </row>
-    <row r="333" ht="19.8" customHeight="1">
-      <c r="A333" s="36" t="inlineStr">
+      <c r="G333" s="53" t="n"/>
+    </row>
+    <row r="334" ht="19.8" customHeight="1">
+      <c r="A334" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B333" s="78" t="inlineStr">
+      <c r="B334" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C333" s="47" t="n"/>
-      <c r="D333" s="18" t="n"/>
-      <c r="E333" s="18" t="n"/>
-      <c r="F333" s="20" t="n"/>
-      <c r="G333" s="53" t="n"/>
-    </row>
-    <row r="334" ht="19.8" customHeight="1">
-      <c r="A334" s="43" t="n"/>
-      <c r="B334" s="79" t="inlineStr">
+      <c r="C334" s="47" t="n"/>
+      <c r="D334" s="18" t="n"/>
+      <c r="E334" s="18" t="n"/>
+      <c r="F334" s="20" t="n"/>
+      <c r="G334" s="53" t="n"/>
+    </row>
+    <row r="335" ht="19.8" customHeight="1">
+      <c r="A335" s="43" t="n"/>
+      <c r="B335" s="79" t="inlineStr">
         <is>
           <t>AISLADAS</t>
         </is>
       </c>
-      <c r="C334" s="18" t="inlineStr">
+      <c r="C335" s="18" t="inlineStr">
         <is>
           <t>2.20 x 3.00</t>
         </is>
       </c>
-      <c r="D334" s="19" t="n">
+      <c r="D335" s="19" t="n">
         <v>6.6</v>
-      </c>
-      <c r="E334" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F334" s="80" t="n">
-        <v>132</v>
-      </c>
-      <c r="G334" s="53" t="n"/>
-    </row>
-    <row r="335" ht="19.8" customHeight="1">
-      <c r="A335" s="47" t="n"/>
-      <c r="B335" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C335" s="18" t="inlineStr">
-        <is>
-          <t>1.60 x 3.00</t>
-        </is>
-      </c>
-      <c r="D335" s="19" t="n">
-        <v>4.8</v>
       </c>
       <c r="E335" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F335" s="80" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="G335" s="53" t="n"/>
     </row>
@@ -26026,358 +26026,366 @@
       <c r="A336" s="47" t="n"/>
       <c r="B336" s="81" t="inlineStr">
         <is>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C336" s="18" t="inlineStr">
+        <is>
+          <t>1.60 x 3.00</t>
+        </is>
+      </c>
+      <c r="D336" s="19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E336" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F336" s="80" t="n">
+        <v>96</v>
+      </c>
+      <c r="G336" s="53" t="n"/>
+    </row>
+    <row r="337" ht="19.8" customHeight="1">
+      <c r="A337" s="47" t="n"/>
+      <c r="B337" s="81" t="inlineStr">
+        <is>
           <t>INTERIORES</t>
         </is>
       </c>
-      <c r="C336" s="18" t="inlineStr">
+      <c r="C337" s="18" t="inlineStr">
         <is>
           <t>2.20 x 3.00</t>
         </is>
       </c>
-      <c r="D336" s="19" t="n">
+      <c r="D337" s="19" t="n">
         <v>6.6</v>
-      </c>
-      <c r="E336" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F336" s="80" t="n">
-        <v>165</v>
-      </c>
-      <c r="G336" s="53" t="n"/>
-    </row>
-    <row r="337" ht="19.8" customHeight="1">
-      <c r="A337" s="50" t="n"/>
-      <c r="B337" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C337" s="18" t="inlineStr">
-        <is>
-          <t>1.60 x 3.00</t>
-        </is>
-      </c>
-      <c r="D337" s="19" t="n">
-        <v>4.8</v>
       </c>
       <c r="E337" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F337" s="80" t="n">
+        <v>165</v>
+      </c>
+      <c r="G337" s="53" t="n"/>
+    </row>
+    <row r="338" ht="19.8" customHeight="1">
+      <c r="A338" s="50" t="n"/>
+      <c r="B338" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C338" s="18" t="inlineStr">
+        <is>
+          <t>1.60 x 3.00</t>
+        </is>
+      </c>
+      <c r="D338" s="19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E338" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F338" s="80" t="n">
         <v>120</v>
       </c>
-      <c r="G337" s="53" t="n"/>
-    </row>
-    <row r="338" ht="19.8" customHeight="1">
-      <c r="A338" s="36" t="inlineStr">
+      <c r="G338" s="53" t="n"/>
+    </row>
+    <row r="339" ht="19.8" customHeight="1">
+      <c r="A339" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B338" s="78" t="inlineStr">
+      <c r="B339" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C338" s="47" t="n"/>
-      <c r="D338" s="18" t="n"/>
-      <c r="E338" s="18" t="n"/>
-      <c r="F338" s="20" t="n"/>
-      <c r="G338" s="53" t="n"/>
-    </row>
-    <row r="339" ht="19.8" customHeight="1">
-      <c r="A339" s="43" t="n"/>
-      <c r="B339" s="79" t="inlineStr">
+      <c r="C339" s="47" t="n"/>
+      <c r="D339" s="18" t="n"/>
+      <c r="E339" s="18" t="n"/>
+      <c r="F339" s="20" t="n"/>
+      <c r="G339" s="53" t="n"/>
+    </row>
+    <row r="340" ht="19.8" customHeight="1">
+      <c r="A340" s="43" t="n"/>
+      <c r="B340" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
         </is>
       </c>
-      <c r="C339" s="18" t="n"/>
-      <c r="D339" s="19" t="n"/>
-      <c r="E339" s="59" t="n">
+      <c r="C340" s="18" t="n"/>
+      <c r="D340" s="19" t="n"/>
+      <c r="E340" s="59" t="n">
         <v>30</v>
       </c>
-      <c r="F339" s="80" t="n"/>
-      <c r="G339" s="53" t="n"/>
-    </row>
-    <row r="340" ht="19.8" customHeight="1">
-      <c r="A340" s="47" t="n"/>
-      <c r="B340" s="81" t="inlineStr">
+      <c r="F340" s="80" t="n"/>
+      <c r="G340" s="53" t="n"/>
+    </row>
+    <row r="341" ht="19.8" customHeight="1">
+      <c r="A341" s="47" t="n"/>
+      <c r="B341" s="81" t="inlineStr">
         <is>
           <t>TECHO AISLADO</t>
         </is>
       </c>
-      <c r="C340" s="18" t="inlineStr">
+      <c r="C341" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D340" s="19" t="n">
+      <c r="D341" s="19" t="n">
         <v>3.52</v>
       </c>
-      <c r="E340" s="59" t="n">
+      <c r="E341" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F340" s="80" t="n">
+      <c r="F341" s="80" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="G340" s="53" t="n"/>
-    </row>
-    <row r="341" ht="19.8" customHeight="1">
-      <c r="A341" s="50" t="n"/>
-      <c r="B341" s="82" t="inlineStr">
+      <c r="G341" s="53" t="n"/>
+    </row>
+    <row r="342" ht="19.8" customHeight="1">
+      <c r="A342" s="50" t="n"/>
+      <c r="B342" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C341" s="18" t="n"/>
-      <c r="D341" s="19" t="n"/>
-      <c r="E341" s="59" t="n">
+      <c r="C342" s="18" t="n"/>
+      <c r="D342" s="19" t="n"/>
+      <c r="E342" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F341" s="80" t="n"/>
-      <c r="G341" s="53" t="n"/>
-    </row>
-    <row r="342" ht="19.8" customHeight="1">
-      <c r="A342" s="36" t="inlineStr">
+      <c r="F342" s="80" t="n"/>
+      <c r="G342" s="53" t="n"/>
+    </row>
+    <row r="343" ht="19.8" customHeight="1">
+      <c r="A343" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B342" s="78" t="inlineStr">
+      <c r="B343" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C342" s="47" t="n"/>
-      <c r="D342" s="18" t="n"/>
-      <c r="E342" s="18" t="n"/>
-      <c r="F342" s="20" t="n"/>
-      <c r="G342" s="53" t="n"/>
-    </row>
-    <row r="343" ht="19.8" customHeight="1">
-      <c r="A343" s="43" t="n"/>
-      <c r="B343" s="79" t="inlineStr">
+      <c r="C343" s="47" t="n"/>
+      <c r="D343" s="18" t="n"/>
+      <c r="E343" s="18" t="n"/>
+      <c r="F343" s="20" t="n"/>
+      <c r="G343" s="53" t="n"/>
+    </row>
+    <row r="344" ht="19.8" customHeight="1">
+      <c r="A344" s="43" t="n"/>
+      <c r="B344" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C343" s="18" t="n"/>
-      <c r="D343" s="19" t="n"/>
-      <c r="E343" s="59" t="n">
+      <c r="C344" s="18" t="n"/>
+      <c r="D344" s="19" t="n"/>
+      <c r="E344" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F343" s="80" t="n"/>
-      <c r="G343" s="53" t="n"/>
-    </row>
-    <row r="344" ht="19.8" customHeight="1">
-      <c r="A344" s="50" t="n"/>
-      <c r="B344" s="82" t="inlineStr">
+      <c r="F344" s="80" t="n"/>
+      <c r="G344" s="53" t="n"/>
+    </row>
+    <row r="345" ht="19.8" customHeight="1">
+      <c r="A345" s="50" t="n"/>
+      <c r="B345" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C344" s="18" t="inlineStr">
+      <c r="C345" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D344" s="24" t="n">
+      <c r="D345" s="24" t="n">
         <v>3.52</v>
       </c>
-      <c r="E344" s="59" t="n">
+      <c r="E345" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F344" s="80" t="n">
+      <c r="F345" s="80" t="n">
         <v>52.8</v>
       </c>
-      <c r="G344" s="53" t="n"/>
-    </row>
-    <row r="345" ht="19.8" customHeight="1">
-      <c r="A345" s="36" t="inlineStr">
+      <c r="G345" s="53" t="n"/>
+    </row>
+    <row r="346" ht="19.8" customHeight="1">
+      <c r="A346" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B345" s="78" t="inlineStr">
+      <c r="B346" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C345" s="83" t="n"/>
-      <c r="D345" s="36" t="inlineStr">
+      <c r="C346" s="83" t="n"/>
+      <c r="D346" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E345" s="47" t="n"/>
-      <c r="F345" s="20" t="n"/>
-      <c r="G345" s="53" t="n"/>
-    </row>
-    <row r="346" ht="19.8" customHeight="1">
-      <c r="A346" s="43" t="n"/>
-      <c r="B346" s="79" t="inlineStr">
+      <c r="E346" s="47" t="n"/>
+      <c r="F346" s="20" t="n"/>
+      <c r="G346" s="53" t="n"/>
+    </row>
+    <row r="347" ht="19.8" customHeight="1">
+      <c r="A347" s="43" t="n"/>
+      <c r="B347" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C346" s="18" t="n"/>
-      <c r="D346" s="22" t="n"/>
-      <c r="E346" s="59" t="n">
+      <c r="C347" s="18" t="n"/>
+      <c r="D347" s="22" t="n"/>
+      <c r="E347" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="F346" s="80" t="n"/>
-      <c r="G346" s="53" t="n"/>
-    </row>
-    <row r="347" ht="19.8" customHeight="1">
-      <c r="A347" s="47" t="n"/>
-      <c r="B347" s="81" t="inlineStr">
+      <c r="F347" s="80" t="n"/>
+      <c r="G347" s="53" t="n"/>
+    </row>
+    <row r="348" ht="19.8" customHeight="1">
+      <c r="A348" s="47" t="n"/>
+      <c r="B348" s="81" t="inlineStr">
         <is>
           <t>DOS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C347" s="18" t="inlineStr">
+      <c r="C348" s="18" t="inlineStr">
         <is>
           <t>3.52 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D347" s="19" t="n">
+      <c r="D348" s="19" t="n">
         <v>10.56</v>
       </c>
-      <c r="E347" s="59" t="n">
+      <c r="E348" s="59" t="n">
         <v>9</v>
       </c>
-      <c r="F347" s="80" t="n">
+      <c r="F348" s="80" t="n">
         <v>95</v>
       </c>
-      <c r="G347" s="53" t="n"/>
-    </row>
-    <row r="348" ht="19.8" customHeight="1">
-      <c r="A348" s="50" t="n"/>
-      <c r="B348" s="82" t="inlineStr">
+      <c r="G348" s="53" t="n"/>
+    </row>
+    <row r="349" ht="19.8" customHeight="1">
+      <c r="A349" s="50" t="n"/>
+      <c r="B349" s="82" t="inlineStr">
         <is>
           <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C348" s="18" t="n"/>
-      <c r="D348" s="19" t="n"/>
-      <c r="E348" s="59" t="n">
+      <c r="C349" s="18" t="n"/>
+      <c r="D349" s="19" t="n"/>
+      <c r="E349" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F348" s="84" t="n"/>
-      <c r="G348" s="53" t="n"/>
-    </row>
-    <row r="349" ht="19.8" customHeight="1">
-      <c r="A349" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B349" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C349" s="47" t="n"/>
-      <c r="D349" s="18" t="n"/>
-      <c r="E349" s="20" t="n"/>
-      <c r="F349" s="85" t="n">
-        <v>844.6</v>
-      </c>
+      <c r="F349" s="84" t="n"/>
       <c r="G349" s="53" t="n"/>
     </row>
     <row r="350" ht="19.8" customHeight="1">
       <c r="A350" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B350" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C350" s="47" t="n"/>
+      <c r="D350" s="18" t="n"/>
+      <c r="E350" s="20" t="n"/>
+      <c r="F350" s="85" t="n">
+        <v>844.6</v>
+      </c>
+      <c r="G350" s="53" t="n"/>
+    </row>
+    <row r="351" ht="19.8" customHeight="1">
+      <c r="A351" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B350" s="78" t="inlineStr">
+      <c r="B351" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C350" s="47" t="inlineStr">
+      <c r="C351" s="47" t="inlineStr">
         <is>
           <t>844.60  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D350" s="12" t="n"/>
-      <c r="E350" s="14" t="n"/>
-      <c r="F350" s="85" t="n">
+      <c r="D351" s="12" t="n"/>
+      <c r="E351" s="14" t="n"/>
+      <c r="F351" s="85" t="n">
         <v>903.7</v>
       </c>
-      <c r="G350" s="53" t="n"/>
-    </row>
-    <row r="351" ht="19.8" customHeight="1">
-      <c r="A351" s="43" t="n"/>
-      <c r="B351" s="86" t="inlineStr">
+      <c r="G351" s="53" t="n"/>
+    </row>
+    <row r="352" ht="19.8" customHeight="1">
+      <c r="A352" s="43" t="n"/>
+      <c r="B352" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C351" s="18" t="n"/>
-      <c r="D351" s="12" t="n"/>
-      <c r="E351" s="39" t="n"/>
-      <c r="F351" s="87" t="n"/>
-      <c r="G351" s="53" t="n"/>
-    </row>
-    <row r="352" ht="19.8" customHeight="1">
-      <c r="A352" s="83" t="n"/>
-      <c r="B352" s="78" t="inlineStr">
+      <c r="C352" s="18" t="n"/>
+      <c r="D352" s="12" t="n"/>
+      <c r="E352" s="39" t="n"/>
+      <c r="F352" s="87" t="n"/>
+      <c r="G352" s="53" t="n"/>
+    </row>
+    <row r="353" ht="19.8" customHeight="1">
+      <c r="A353" s="83" t="n"/>
+      <c r="B353" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C352" s="47" t="n"/>
-      <c r="D352" s="12" t="n"/>
-      <c r="E352" s="14" t="n"/>
-      <c r="F352" s="85" t="n">
+      <c r="C353" s="47" t="n"/>
+      <c r="D353" s="12" t="n"/>
+      <c r="E353" s="14" t="n"/>
+      <c r="F353" s="85" t="n">
         <v>903.7</v>
       </c>
-      <c r="G352" s="53" t="n"/>
-    </row>
-    <row r="353" ht="19.8" customHeight="1">
-      <c r="A353" s="47" t="n"/>
-      <c r="B353" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C353" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
-      </c>
-      <c r="D353" s="12" t="n"/>
-      <c r="E353" s="39" t="n"/>
-      <c r="F353" s="61" t="n"/>
       <c r="G353" s="53" t="n"/>
     </row>
     <row r="354" ht="19.8" customHeight="1">
       <c r="A354" s="47" t="n"/>
-      <c r="B354" s="60" t="inlineStr">
-        <is>
-          <t>Kcal/h del toallero Scala/Domino 80</t>
-        </is>
-      </c>
-      <c r="C354" s="59" t="n">
-        <v>708</v>
+      <c r="B354" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C354" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
       </c>
       <c r="D354" s="12" t="n"/>
       <c r="E354" s="39" t="n"/>
-      <c r="F354" s="20" t="n"/>
+      <c r="F354" s="61" t="n"/>
       <c r="G354" s="53" t="n"/>
     </row>
     <row r="355" ht="19.8" customHeight="1">
       <c r="A355" s="47" t="n"/>
       <c r="B355" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 150</t>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
         </is>
       </c>
       <c r="C355" s="59" t="n">
-        <v>1315</v>
+        <v>708</v>
       </c>
       <c r="D355" s="12" t="n"/>
       <c r="E355" s="39" t="n"/>
@@ -26388,11 +26396,11 @@
       <c r="A356" s="47" t="n"/>
       <c r="B356" s="60" t="inlineStr">
         <is>
-          <t>Toalleros necesarios</t>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
         </is>
       </c>
       <c r="C356" s="59" t="n">
-        <v>1</v>
+        <v>1315</v>
       </c>
       <c r="D356" s="12" t="n"/>
       <c r="E356" s="39" t="n"/>
@@ -26400,46 +26408,63 @@
       <c r="G356" s="53" t="n"/>
     </row>
     <row r="357" ht="19.8" customHeight="1">
-      <c r="A357" s="50" t="n"/>
-      <c r="B357" s="72" t="inlineStr">
+      <c r="A357" s="47" t="n"/>
+      <c r="B357" s="60" t="inlineStr">
+        <is>
+          <t>Toalleros necesarios</t>
+        </is>
+      </c>
+      <c r="C357" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D357" s="12" t="n"/>
+      <c r="E357" s="39" t="n"/>
+      <c r="F357" s="20" t="n"/>
+      <c r="G357" s="53" t="n"/>
+    </row>
+    <row r="358" ht="19.8" customHeight="1">
+      <c r="A358" s="50" t="n"/>
+      <c r="B358" s="72" t="inlineStr">
         <is>
           <t>Toallero adoptado</t>
         </is>
       </c>
-      <c r="C357" s="30" t="inlineStr">
+      <c r="C358" s="30" t="inlineStr">
         <is>
           <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
         </is>
       </c>
-      <c r="D357" s="11" t="n"/>
-      <c r="E357" s="92" t="n"/>
-      <c r="F357" s="31" t="n"/>
-      <c r="G357" s="53" t="n"/>
+      <c r="D358" s="11" t="n"/>
+      <c r="E358" s="92" t="n"/>
+      <c r="F358" s="31" t="n"/>
+      <c r="G358" s="53" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="101">
-    <mergeCell ref="C321:E321"/>
     <mergeCell ref="C202:E202"/>
     <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C329:E329"/>
+    <mergeCell ref="A301:F301"/>
     <mergeCell ref="C297:E297"/>
-    <mergeCell ref="A239:F239"/>
     <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C123:E123"/>
     <mergeCell ref="C268:E268"/>
     <mergeCell ref="C299:E299"/>
-    <mergeCell ref="C292:E292"/>
     <mergeCell ref="C57:E57"/>
     <mergeCell ref="C355:E355"/>
     <mergeCell ref="C293:E293"/>
-    <mergeCell ref="A329:F329"/>
     <mergeCell ref="C204:E204"/>
     <mergeCell ref="C357:E357"/>
     <mergeCell ref="C325:E325"/>
     <mergeCell ref="C206:E206"/>
+    <mergeCell ref="A124:F124"/>
     <mergeCell ref="C205:E205"/>
+    <mergeCell ref="C270:E270"/>
     <mergeCell ref="C118:E118"/>
     <mergeCell ref="C238:E238"/>
     <mergeCell ref="C176:E176"/>
     <mergeCell ref="C232:E232"/>
+    <mergeCell ref="A149:F149"/>
     <mergeCell ref="C356:E356"/>
     <mergeCell ref="C59:E59"/>
     <mergeCell ref="C295:E295"/>
@@ -26447,8 +26472,10 @@
     <mergeCell ref="C178:E178"/>
     <mergeCell ref="C61:E61"/>
     <mergeCell ref="C233:E233"/>
+    <mergeCell ref="A240:F240"/>
     <mergeCell ref="C32:E32"/>
     <mergeCell ref="C296:E296"/>
+    <mergeCell ref="C209:E209"/>
     <mergeCell ref="C352:E352"/>
     <mergeCell ref="C145:E145"/>
     <mergeCell ref="C323:E323"/>
@@ -26464,21 +26491,18 @@
     <mergeCell ref="C88:E88"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C324:E324"/>
-    <mergeCell ref="C231:E231"/>
+    <mergeCell ref="C63:E63"/>
     <mergeCell ref="C121:E121"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A330:F330"/>
+    <mergeCell ref="C117:E117"/>
     <mergeCell ref="C173:E173"/>
-    <mergeCell ref="C117:E117"/>
     <mergeCell ref="C236:E236"/>
-    <mergeCell ref="C350:E350"/>
-    <mergeCell ref="A179:F179"/>
-    <mergeCell ref="C115:E115"/>
+    <mergeCell ref="A210:F210"/>
+    <mergeCell ref="C300:E300"/>
     <mergeCell ref="C207:E207"/>
     <mergeCell ref="C328:E328"/>
-    <mergeCell ref="C262:E262"/>
-    <mergeCell ref="C144:E144"/>
     <mergeCell ref="C122:E122"/>
+    <mergeCell ref="A180:F180"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="C264:E264"/>
     <mergeCell ref="C326:E326"/>
@@ -26487,36 +26511,35 @@
     <mergeCell ref="C263:E263"/>
     <mergeCell ref="C354:E354"/>
     <mergeCell ref="C30:E30"/>
-    <mergeCell ref="A270:F270"/>
     <mergeCell ref="C235:E235"/>
     <mergeCell ref="C62:E62"/>
-    <mergeCell ref="A300:F300"/>
     <mergeCell ref="C234:E234"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C172:E172"/>
     <mergeCell ref="C353:E353"/>
     <mergeCell ref="C64:E64"/>
     <mergeCell ref="C147:E147"/>
-    <mergeCell ref="C171:E171"/>
+    <mergeCell ref="A271:F271"/>
     <mergeCell ref="A65:F65"/>
     <mergeCell ref="C177:E177"/>
     <mergeCell ref="C146:E146"/>
-    <mergeCell ref="C201:E201"/>
+    <mergeCell ref="C148:E148"/>
+    <mergeCell ref="C90:E90"/>
     <mergeCell ref="C120:E120"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="C203:E203"/>
     <mergeCell ref="C119:E119"/>
-    <mergeCell ref="A209:F209"/>
+    <mergeCell ref="A91:F91"/>
     <mergeCell ref="C174:E174"/>
+    <mergeCell ref="C358:E358"/>
     <mergeCell ref="C327:E327"/>
     <mergeCell ref="C237:E237"/>
     <mergeCell ref="C351:E351"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="C179:E179"/>
+    <mergeCell ref="C239:E239"/>
     <mergeCell ref="C175:E175"/>
     <mergeCell ref="C58:E58"/>
     <mergeCell ref="C294:E294"/>
-    <mergeCell ref="A123:F123"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="C265:E265"/>
   </mergeCells>

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -19938,7 +19938,7 @@
       <c r="A12" s="47" t="n"/>
       <c r="B12" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (galeria y living)</t>
+          <t>INTERIORES (SE, galeria y living)</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -19961,7 +19961,7 @@
       <c r="A13" s="50" t="n"/>
       <c r="B13" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (deposito y lavadero)</t>
+          <t>INTERIORES (NE, deposito y lavadero)</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
@@ -20519,7 +20519,7 @@
       <c r="A43" s="47" t="n"/>
       <c r="B43" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (galeria, con la PV01)</t>
+          <t>INTERIORES (NO, galeria, con la PV01)</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
@@ -21091,7 +21091,7 @@
       <c r="A73" s="47" t="n"/>
       <c r="B73" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (vestidor)</t>
+          <t>INTERIORES (NE, vestidor)</t>
         </is>
       </c>
       <c r="C73" s="18" t="inlineStr">
@@ -21114,7 +21114,7 @@
       <c r="A74" s="50" t="n"/>
       <c r="B74" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (living comedor)</t>
+          <t>INTERIORES (NO, living comedor)</t>
         </is>
       </c>
       <c r="C74" s="18" t="inlineStr">
@@ -22145,7 +22145,7 @@
       <c r="A129" s="43" t="n"/>
       <c r="B129" s="79" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>AISLADAS (NE)</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
@@ -22191,7 +22191,7 @@
       <c r="A131" s="47" t="n"/>
       <c r="B131" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (SO)</t>
         </is>
       </c>
       <c r="C131" s="18" t="inlineStr">
@@ -23268,7 +23268,7 @@
       <c r="A188" s="47" t="n"/>
       <c r="B188" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (SO)</t>
         </is>
       </c>
       <c r="C188" s="18" t="inlineStr">
@@ -24957,7 +24957,7 @@
       <c r="A279" s="47" t="n"/>
       <c r="B279" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (SE)</t>
         </is>
       </c>
       <c r="C279" s="18" t="inlineStr">
@@ -25506,7 +25506,7 @@
       <c r="A308" s="47" t="n"/>
       <c r="B308" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (NO)</t>
         </is>
       </c>
       <c r="C308" s="18" t="inlineStr">
@@ -26003,7 +26003,7 @@
       <c r="A335" s="43" t="n"/>
       <c r="B335" s="79" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>AISLADAS (NE)</t>
         </is>
       </c>
       <c r="C335" s="18" t="inlineStr">
@@ -26049,7 +26049,7 @@
       <c r="A337" s="47" t="n"/>
       <c r="B337" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (SO)</t>
         </is>
       </c>
       <c r="C337" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -19691,7 +19691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G358"/>
+  <dimension ref="A1:G357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.1" customWidth="1" min="1" max="1"/>
@@ -22586,7 +22586,7 @@
       <c r="A152" s="43" t="n"/>
       <c r="B152" s="79" t="inlineStr">
         <is>
-          <t>VA01 (2)</t>
+          <t>VA01</t>
         </is>
       </c>
       <c r="C152" s="18" t="inlineStr">
@@ -24856,7 +24856,7 @@
       <c r="A274" s="90" t="n"/>
       <c r="B274" s="91" t="inlineStr">
         <is>
-          <t>VA04 (2)</t>
+          <t>VA04</t>
         </is>
       </c>
       <c r="C274" s="18" t="inlineStr">
@@ -24934,7 +24934,7 @@
       <c r="A278" s="47" t="n"/>
       <c r="B278" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (NE)</t>
         </is>
       </c>
       <c r="C278" s="18" t="inlineStr">
@@ -24954,8 +24954,8 @@
       <c r="G278" s="53" t="n"/>
     </row>
     <row r="279" ht="19.8" customHeight="1">
-      <c r="A279" s="47" t="n"/>
-      <c r="B279" s="81" t="inlineStr">
+      <c r="A279" s="50" t="n"/>
+      <c r="B279" s="82" t="inlineStr">
         <is>
           <t>INTERIORES (SE)</t>
         </is>
@@ -24977,329 +24977,321 @@
       <c r="G279" s="53" t="n"/>
     </row>
     <row r="280" ht="19.8" customHeight="1">
-      <c r="A280" s="50" t="n"/>
-      <c r="B280" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C280" s="18" t="inlineStr">
-        <is>
-          <t>4.08 x 3.00</t>
-        </is>
-      </c>
-      <c r="D280" s="19" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="E280" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F280" s="80" t="n">
-        <v>306</v>
-      </c>
+      <c r="A280" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B280" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C280" s="47" t="n"/>
+      <c r="D280" s="18" t="n"/>
+      <c r="E280" s="18" t="n"/>
+      <c r="F280" s="20" t="n"/>
       <c r="G280" s="53" t="n"/>
     </row>
     <row r="281" ht="19.8" customHeight="1">
-      <c r="A281" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B281" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C281" s="47" t="n"/>
-      <c r="D281" s="18" t="n"/>
-      <c r="E281" s="18" t="n"/>
-      <c r="F281" s="20" t="n"/>
+      <c r="A281" s="43" t="n"/>
+      <c r="B281" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C281" s="18" t="n"/>
+      <c r="D281" s="19" t="n"/>
+      <c r="E281" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F281" s="80" t="n"/>
       <c r="G281" s="53" t="n"/>
     </row>
     <row r="282" ht="19.8" customHeight="1">
-      <c r="A282" s="43" t="n"/>
-      <c r="B282" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C282" s="18" t="n"/>
-      <c r="D282" s="19" t="n"/>
+      <c r="A282" s="47" t="n"/>
+      <c r="B282" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C282" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D282" s="19" t="n">
+        <v>16.85</v>
+      </c>
       <c r="E282" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F282" s="80" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F282" s="80" t="n">
+        <v>337</v>
+      </c>
       <c r="G282" s="53" t="n"/>
     </row>
     <row r="283" ht="19.8" customHeight="1">
-      <c r="A283" s="47" t="n"/>
-      <c r="B283" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C283" s="18" t="inlineStr">
+      <c r="A283" s="50" t="n"/>
+      <c r="B283" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C283" s="18" t="n"/>
+      <c r="D283" s="19" t="n"/>
+      <c r="E283" s="59" t="n">
+        <v>15</v>
+      </c>
+      <c r="F283" s="80" t="n"/>
+      <c r="G283" s="53" t="n"/>
+    </row>
+    <row r="284" ht="19.8" customHeight="1">
+      <c r="A284" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B284" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C284" s="47" t="n"/>
+      <c r="D284" s="18" t="n"/>
+      <c r="E284" s="18" t="n"/>
+      <c r="F284" s="20" t="n"/>
+      <c r="G284" s="53" t="n"/>
+    </row>
+    <row r="285" ht="19.8" customHeight="1">
+      <c r="A285" s="43" t="n"/>
+      <c r="B285" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C285" s="18" t="n"/>
+      <c r="D285" s="19" t="n"/>
+      <c r="E285" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F285" s="80" t="n"/>
+      <c r="G285" s="53" t="n"/>
+    </row>
+    <row r="286" ht="19.8" customHeight="1">
+      <c r="A286" s="50" t="n"/>
+      <c r="B286" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C286" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D283" s="19" t="n">
+      <c r="D286" s="24" t="n">
         <v>16.85</v>
       </c>
-      <c r="E283" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F283" s="80" t="n">
-        <v>337</v>
-      </c>
-      <c r="G283" s="53" t="n"/>
-    </row>
-    <row r="284" ht="19.8" customHeight="1">
-      <c r="A284" s="50" t="n"/>
-      <c r="B284" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C284" s="18" t="n"/>
-      <c r="D284" s="19" t="n"/>
-      <c r="E284" s="59" t="n">
+      <c r="E286" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F284" s="80" t="n"/>
-      <c r="G284" s="53" t="n"/>
-    </row>
-    <row r="285" ht="19.8" customHeight="1">
-      <c r="A285" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B285" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C285" s="47" t="n"/>
-      <c r="D285" s="18" t="n"/>
-      <c r="E285" s="18" t="n"/>
-      <c r="F285" s="20" t="n"/>
-      <c r="G285" s="53" t="n"/>
-    </row>
-    <row r="286" ht="19.8" customHeight="1">
-      <c r="A286" s="43" t="n"/>
-      <c r="B286" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C286" s="18" t="n"/>
-      <c r="D286" s="19" t="n"/>
-      <c r="E286" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F286" s="80" t="n"/>
+      <c r="F286" s="80" t="n">
+        <v>252.8</v>
+      </c>
       <c r="G286" s="53" t="n"/>
     </row>
     <row r="287" ht="19.8" customHeight="1">
-      <c r="A287" s="50" t="n"/>
-      <c r="B287" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C287" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D287" s="24" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="E287" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F287" s="80" t="n">
-        <v>252.8</v>
-      </c>
+      <c r="A287" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B287" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C287" s="83" t="n"/>
+      <c r="D287" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E287" s="47" t="n"/>
+      <c r="F287" s="20" t="n"/>
       <c r="G287" s="53" t="n"/>
     </row>
     <row r="288" ht="19.8" customHeight="1">
-      <c r="A288" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B288" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C288" s="83" t="n"/>
-      <c r="D288" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E288" s="47" t="n"/>
-      <c r="F288" s="20" t="n"/>
+      <c r="A288" s="43" t="n"/>
+      <c r="B288" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C288" s="18" t="inlineStr">
+        <is>
+          <t>16.85 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D288" s="22" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="E288" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F288" s="80" t="n">
+        <v>303.3</v>
+      </c>
       <c r="G288" s="53" t="n"/>
     </row>
     <row r="289" ht="19.8" customHeight="1">
-      <c r="A289" s="43" t="n"/>
-      <c r="B289" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C289" s="18" t="inlineStr">
-        <is>
-          <t>16.85 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D289" s="22" t="n">
-        <v>50.55</v>
-      </c>
+      <c r="A289" s="47" t="n"/>
+      <c r="B289" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C289" s="18" t="n"/>
+      <c r="D289" s="19" t="n"/>
       <c r="E289" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F289" s="80" t="n">
-        <v>303.3</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F289" s="80" t="n"/>
       <c r="G289" s="53" t="n"/>
     </row>
     <row r="290" ht="19.8" customHeight="1">
-      <c r="A290" s="47" t="n"/>
-      <c r="B290" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
+      <c r="A290" s="50" t="n"/>
+      <c r="B290" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C290" s="18" t="n"/>
       <c r="D290" s="19" t="n"/>
       <c r="E290" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F290" s="80" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="F290" s="84" t="n"/>
       <c r="G290" s="53" t="n"/>
     </row>
     <row r="291" ht="19.8" customHeight="1">
-      <c r="A291" s="50" t="n"/>
-      <c r="B291" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C291" s="18" t="n"/>
-      <c r="D291" s="19" t="n"/>
-      <c r="E291" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F291" s="84" t="n"/>
+      <c r="A291" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B291" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C291" s="47" t="n"/>
+      <c r="D291" s="18" t="n"/>
+      <c r="E291" s="20" t="n"/>
+      <c r="F291" s="85" t="n">
+        <v>2059.1</v>
+      </c>
       <c r="G291" s="53" t="n"/>
     </row>
     <row r="292" ht="19.8" customHeight="1">
       <c r="A292" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B292" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C292" s="47" t="n"/>
-      <c r="D292" s="18" t="n"/>
-      <c r="E292" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C292" s="47" t="inlineStr">
+        <is>
+          <t>2059.10  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D292" s="12" t="n"/>
+      <c r="E292" s="14" t="n"/>
       <c r="F292" s="85" t="n">
-        <v>2365.1</v>
+        <v>2203.2</v>
       </c>
       <c r="G292" s="53" t="n"/>
     </row>
     <row r="293" ht="19.8" customHeight="1">
-      <c r="A293" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B293" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C293" s="47" t="inlineStr">
-        <is>
-          <t>2365.10  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+      <c r="A293" s="43" t="n"/>
+      <c r="B293" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C293" s="18" t="inlineStr">
+        <is>
+          <t>Escalera</t>
         </is>
       </c>
       <c r="D293" s="12" t="n"/>
-      <c r="E293" s="14" t="n"/>
-      <c r="F293" s="85" t="n">
-        <v>2530.7</v>
+      <c r="E293" s="39" t="n"/>
+      <c r="F293" s="87" t="n">
+        <v>1348.3</v>
       </c>
       <c r="G293" s="53" t="n"/>
     </row>
     <row r="294" ht="19.8" customHeight="1">
-      <c r="A294" s="43" t="n"/>
-      <c r="B294" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C294" s="18" t="inlineStr">
-        <is>
-          <t>Escalera</t>
-        </is>
-      </c>
+      <c r="A294" s="83" t="n"/>
+      <c r="B294" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C294" s="47" t="n"/>
       <c r="D294" s="12" t="n"/>
-      <c r="E294" s="39" t="n"/>
-      <c r="F294" s="87" t="n">
-        <v>1348.3</v>
+      <c r="E294" s="14" t="n"/>
+      <c r="F294" s="85" t="n">
+        <v>3551.5</v>
       </c>
       <c r="G294" s="53" t="n"/>
     </row>
     <row r="295" ht="19.8" customHeight="1">
-      <c r="A295" s="83" t="n"/>
-      <c r="B295" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C295" s="47" t="n"/>
+      <c r="A295" s="47" t="n"/>
+      <c r="B295" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C295" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D295" s="12" t="n"/>
-      <c r="E295" s="14" t="n"/>
-      <c r="F295" s="85" t="n">
-        <v>3879</v>
-      </c>
+      <c r="E295" s="39" t="n"/>
+      <c r="F295" s="61" t="n"/>
       <c r="G295" s="53" t="n"/>
     </row>
     <row r="296" ht="19.8" customHeight="1">
       <c r="A296" s="47" t="n"/>
-      <c r="B296" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C296" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B296" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C296" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D296" s="12" t="n"/>
       <c r="E296" s="39" t="n"/>
-      <c r="F296" s="61" t="n"/>
+      <c r="F296" s="20" t="n"/>
       <c r="G296" s="53" t="n"/>
     </row>
     <row r="297" ht="19.8" customHeight="1">
       <c r="A297" s="47" t="n"/>
       <c r="B297" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C297" s="19" t="n">
-        <v>274.4</v>
+          <t>Elementos necesarios</t>
+        </is>
+      </c>
+      <c r="C297" s="59" t="n">
+        <v>13</v>
       </c>
       <c r="D297" s="12" t="n"/>
       <c r="E297" s="39" t="n"/>
@@ -25310,11 +25302,11 @@
       <c r="A298" s="47" t="n"/>
       <c r="B298" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
+          <t>Ancho del radiador (cm)</t>
         </is>
       </c>
       <c r="C298" s="59" t="n">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="D298" s="12" t="n"/>
       <c r="E298" s="39" t="n"/>
@@ -25322,14 +25314,16 @@
       <c r="G298" s="53" t="n"/>
     </row>
     <row r="299" ht="19.8" customHeight="1">
-      <c r="A299" s="47" t="n"/>
+      <c r="A299" s="50" t="n"/>
       <c r="B299" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
-        </is>
-      </c>
-      <c r="C299" s="59" t="n">
-        <v>120</v>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C299" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
       </c>
       <c r="D299" s="12" t="n"/>
       <c r="E299" s="39" t="n"/>
@@ -25337,145 +25331,151 @@
       <c r="G299" s="53" t="n"/>
     </row>
     <row r="300" ht="19.8" customHeight="1">
-      <c r="A300" s="50" t="n"/>
-      <c r="B300" s="60" t="inlineStr">
-        <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C300" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
-      </c>
-      <c r="D300" s="12" t="n"/>
-      <c r="E300" s="39" t="n"/>
-      <c r="F300" s="20" t="n"/>
+      <c r="A300" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  15 - Dormitorio Sur   (PA)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B300" s="11" t="n"/>
+      <c r="C300" s="11" t="n"/>
+      <c r="D300" s="11" t="n"/>
+      <c r="E300" s="11" t="n"/>
+      <c r="F300" s="42" t="n"/>
       <c r="G300" s="53" t="n"/>
     </row>
-    <row r="301" ht="19.8" customHeight="1">
-      <c r="A301" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  15 - Dormitorio Sur   (PA)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B301" s="11" t="n"/>
-      <c r="C301" s="11" t="n"/>
-      <c r="D301" s="11" t="n"/>
-      <c r="E301" s="11" t="n"/>
-      <c r="F301" s="42" t="n"/>
+    <row r="301" ht="32" customHeight="1">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G301" s="53" t="n"/>
     </row>
-    <row r="302" ht="32" customHeight="1">
-      <c r="A302" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B302" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C302" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D302" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E302" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F302" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="302" ht="19.8" customHeight="1">
+      <c r="A302" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B302" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C302" s="43" t="n"/>
+      <c r="D302" s="58" t="n"/>
+      <c r="E302" s="58" t="n"/>
+      <c r="F302" s="61" t="n"/>
       <c r="G302" s="53" t="n"/>
     </row>
     <row r="303" ht="19.8" customHeight="1">
-      <c r="A303" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B303" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C303" s="43" t="n"/>
-      <c r="D303" s="58" t="n"/>
-      <c r="E303" s="58" t="n"/>
-      <c r="F303" s="61" t="n"/>
+      <c r="A303" s="90" t="n"/>
+      <c r="B303" s="91" t="inlineStr">
+        <is>
+          <t>PV04</t>
+        </is>
+      </c>
+      <c r="C303" s="18" t="inlineStr">
+        <is>
+          <t>2.06 x 3.00</t>
+        </is>
+      </c>
+      <c r="D303" s="19" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="E303" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F303" s="80" t="n">
+        <v>370.8</v>
+      </c>
       <c r="G303" s="53" t="n"/>
     </row>
     <row r="304" ht="19.8" customHeight="1">
-      <c r="A304" s="90" t="n"/>
-      <c r="B304" s="91" t="inlineStr">
-        <is>
-          <t>PV04</t>
-        </is>
-      </c>
-      <c r="C304" s="18" t="inlineStr">
-        <is>
-          <t>2.06 x 3.00</t>
-        </is>
-      </c>
-      <c r="D304" s="19" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="E304" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F304" s="80" t="n">
-        <v>370.8</v>
-      </c>
+      <c r="A304" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B304" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C304" s="47" t="n"/>
+      <c r="D304" s="18" t="n"/>
+      <c r="E304" s="18" t="n"/>
+      <c r="F304" s="20" t="n"/>
       <c r="G304" s="53" t="n"/>
     </row>
     <row r="305" ht="19.8" customHeight="1">
-      <c r="A305" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B305" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C305" s="47" t="n"/>
-      <c r="D305" s="18" t="n"/>
-      <c r="E305" s="18" t="n"/>
-      <c r="F305" s="20" t="n"/>
+      <c r="A305" s="43" t="n"/>
+      <c r="B305" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS (SE)</t>
+        </is>
+      </c>
+      <c r="C305" s="18" t="inlineStr">
+        <is>
+          <t>4.05 x 3.00</t>
+        </is>
+      </c>
+      <c r="D305" s="19" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="E305" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F305" s="80" t="n">
+        <v>243</v>
+      </c>
       <c r="G305" s="53" t="n"/>
     </row>
     <row r="306" ht="19.8" customHeight="1">
-      <c r="A306" s="43" t="n"/>
-      <c r="B306" s="79" t="inlineStr">
-        <is>
-          <t>AISLADAS (SE)</t>
+      <c r="A306" s="47" t="n"/>
+      <c r="B306" s="81" t="inlineStr">
+        <is>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C306" s="18" t="inlineStr">
         <is>
-          <t>4.05 x 3.00</t>
+          <t>3.50 x 3.00</t>
         </is>
       </c>
       <c r="D306" s="19" t="n">
-        <v>12.15</v>
+        <v>10.5</v>
       </c>
       <c r="E306" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F306" s="80" t="n">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="G306" s="53" t="n"/>
     </row>
@@ -25483,366 +25483,358 @@
       <c r="A307" s="47" t="n"/>
       <c r="B307" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>INTERIORES (NO)</t>
         </is>
       </c>
       <c r="C307" s="18" t="inlineStr">
         <is>
+          <t>4.05 x 3.00</t>
+        </is>
+      </c>
+      <c r="D307" s="19" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="E307" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F307" s="80" t="n">
+        <v>303.8</v>
+      </c>
+      <c r="G307" s="53" t="n"/>
+    </row>
+    <row r="308" ht="19.8" customHeight="1">
+      <c r="A308" s="50" t="n"/>
+      <c r="B308" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C308" s="18" t="inlineStr">
+        <is>
           <t>3.50 x 3.00</t>
         </is>
       </c>
-      <c r="D307" s="19" t="n">
+      <c r="D308" s="19" t="n">
         <v>10.5</v>
-      </c>
-      <c r="E307" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F307" s="80" t="n">
-        <v>210</v>
-      </c>
-      <c r="G307" s="53" t="n"/>
-    </row>
-    <row r="308" ht="19.8" customHeight="1">
-      <c r="A308" s="47" t="n"/>
-      <c r="B308" s="81" t="inlineStr">
-        <is>
-          <t>INTERIORES (NO)</t>
-        </is>
-      </c>
-      <c r="C308" s="18" t="inlineStr">
-        <is>
-          <t>4.05 x 3.00</t>
-        </is>
-      </c>
-      <c r="D308" s="19" t="n">
-        <v>12.15</v>
       </c>
       <c r="E308" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F308" s="80" t="n">
-        <v>303.8</v>
+        <v>262.5</v>
       </c>
       <c r="G308" s="53" t="n"/>
     </row>
     <row r="309" ht="19.8" customHeight="1">
-      <c r="A309" s="50" t="n"/>
-      <c r="B309" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C309" s="18" t="inlineStr">
-        <is>
-          <t>3.50 x 3.00</t>
-        </is>
-      </c>
-      <c r="D309" s="19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="E309" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F309" s="80" t="n">
-        <v>262.5</v>
-      </c>
+      <c r="A309" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B309" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C309" s="47" t="n"/>
+      <c r="D309" s="18" t="n"/>
+      <c r="E309" s="18" t="n"/>
+      <c r="F309" s="20" t="n"/>
       <c r="G309" s="53" t="n"/>
     </row>
     <row r="310" ht="19.8" customHeight="1">
-      <c r="A310" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B310" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C310" s="47" t="n"/>
-      <c r="D310" s="18" t="n"/>
-      <c r="E310" s="18" t="n"/>
-      <c r="F310" s="20" t="n"/>
+      <c r="A310" s="43" t="n"/>
+      <c r="B310" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C310" s="18" t="n"/>
+      <c r="D310" s="19" t="n"/>
+      <c r="E310" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F310" s="80" t="n"/>
       <c r="G310" s="53" t="n"/>
     </row>
     <row r="311" ht="19.8" customHeight="1">
-      <c r="A311" s="43" t="n"/>
-      <c r="B311" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C311" s="18" t="n"/>
-      <c r="D311" s="19" t="n"/>
+      <c r="A311" s="47" t="n"/>
+      <c r="B311" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C311" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D311" s="19" t="n">
+        <v>14.17</v>
+      </c>
       <c r="E311" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F311" s="80" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F311" s="80" t="n">
+        <v>283.4</v>
+      </c>
       <c r="G311" s="53" t="n"/>
     </row>
     <row r="312" ht="19.8" customHeight="1">
-      <c r="A312" s="47" t="n"/>
-      <c r="B312" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C312" s="18" t="inlineStr">
+      <c r="A312" s="50" t="n"/>
+      <c r="B312" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C312" s="18" t="n"/>
+      <c r="D312" s="19" t="n"/>
+      <c r="E312" s="59" t="n">
+        <v>15</v>
+      </c>
+      <c r="F312" s="80" t="n"/>
+      <c r="G312" s="53" t="n"/>
+    </row>
+    <row r="313" ht="19.8" customHeight="1">
+      <c r="A313" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B313" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C313" s="47" t="n"/>
+      <c r="D313" s="18" t="n"/>
+      <c r="E313" s="18" t="n"/>
+      <c r="F313" s="20" t="n"/>
+      <c r="G313" s="53" t="n"/>
+    </row>
+    <row r="314" ht="19.8" customHeight="1">
+      <c r="A314" s="43" t="n"/>
+      <c r="B314" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C314" s="18" t="n"/>
+      <c r="D314" s="19" t="n"/>
+      <c r="E314" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F314" s="80" t="n"/>
+      <c r="G314" s="53" t="n"/>
+    </row>
+    <row r="315" ht="19.8" customHeight="1">
+      <c r="A315" s="50" t="n"/>
+      <c r="B315" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C315" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D312" s="19" t="n">
+      <c r="D315" s="24" t="n">
         <v>14.17</v>
       </c>
-      <c r="E312" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F312" s="80" t="n">
-        <v>283.4</v>
-      </c>
-      <c r="G312" s="53" t="n"/>
-    </row>
-    <row r="313" ht="19.8" customHeight="1">
-      <c r="A313" s="50" t="n"/>
-      <c r="B313" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C313" s="18" t="n"/>
-      <c r="D313" s="19" t="n"/>
-      <c r="E313" s="59" t="n">
+      <c r="E315" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F313" s="80" t="n"/>
-      <c r="G313" s="53" t="n"/>
-    </row>
-    <row r="314" ht="19.8" customHeight="1">
-      <c r="A314" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B314" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C314" s="47" t="n"/>
-      <c r="D314" s="18" t="n"/>
-      <c r="E314" s="18" t="n"/>
-      <c r="F314" s="20" t="n"/>
-      <c r="G314" s="53" t="n"/>
-    </row>
-    <row r="315" ht="19.8" customHeight="1">
-      <c r="A315" s="43" t="n"/>
-      <c r="B315" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C315" s="18" t="n"/>
-      <c r="D315" s="19" t="n"/>
-      <c r="E315" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F315" s="80" t="n"/>
+      <c r="F315" s="80" t="n">
+        <v>212.6</v>
+      </c>
       <c r="G315" s="53" t="n"/>
     </row>
     <row r="316" ht="19.8" customHeight="1">
-      <c r="A316" s="50" t="n"/>
-      <c r="B316" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C316" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D316" s="24" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="E316" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F316" s="80" t="n">
-        <v>212.6</v>
-      </c>
+      <c r="A316" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B316" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C316" s="83" t="n"/>
+      <c r="D316" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E316" s="47" t="n"/>
+      <c r="F316" s="20" t="n"/>
       <c r="G316" s="53" t="n"/>
     </row>
     <row r="317" ht="19.8" customHeight="1">
-      <c r="A317" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B317" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C317" s="83" t="n"/>
-      <c r="D317" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E317" s="47" t="n"/>
-      <c r="F317" s="20" t="n"/>
+      <c r="A317" s="43" t="n"/>
+      <c r="B317" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C317" s="18" t="n"/>
+      <c r="D317" s="22" t="n"/>
+      <c r="E317" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F317" s="80" t="n"/>
       <c r="G317" s="53" t="n"/>
     </row>
     <row r="318" ht="19.8" customHeight="1">
-      <c r="A318" s="43" t="n"/>
-      <c r="B318" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C318" s="18" t="n"/>
-      <c r="D318" s="22" t="n"/>
+      <c r="A318" s="47" t="n"/>
+      <c r="B318" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C318" s="18" t="inlineStr">
+        <is>
+          <t>14.17 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D318" s="19" t="n">
+        <v>42.51</v>
+      </c>
       <c r="E318" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F318" s="80" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="F318" s="80" t="n">
+        <v>382.6</v>
+      </c>
       <c r="G318" s="53" t="n"/>
     </row>
     <row r="319" ht="19.8" customHeight="1">
-      <c r="A319" s="47" t="n"/>
-      <c r="B319" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C319" s="18" t="inlineStr">
-        <is>
-          <t>14.17 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D319" s="19" t="n">
-        <v>42.51</v>
-      </c>
+      <c r="A319" s="50" t="n"/>
+      <c r="B319" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C319" s="18" t="n"/>
+      <c r="D319" s="19" t="n"/>
       <c r="E319" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F319" s="80" t="n">
-        <v>382.6</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F319" s="84" t="n"/>
       <c r="G319" s="53" t="n"/>
     </row>
     <row r="320" ht="19.8" customHeight="1">
-      <c r="A320" s="50" t="n"/>
-      <c r="B320" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C320" s="18" t="n"/>
-      <c r="D320" s="19" t="n"/>
-      <c r="E320" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F320" s="84" t="n"/>
+      <c r="A320" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B320" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C320" s="47" t="n"/>
+      <c r="D320" s="18" t="n"/>
+      <c r="E320" s="20" t="n"/>
+      <c r="F320" s="85" t="n">
+        <v>2268.7</v>
+      </c>
       <c r="G320" s="53" t="n"/>
     </row>
     <row r="321" ht="19.8" customHeight="1">
       <c r="A321" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B321" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C321" s="47" t="n"/>
-      <c r="D321" s="18" t="n"/>
-      <c r="E321" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C321" s="47" t="inlineStr">
+        <is>
+          <t>2268.70  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D321" s="12" t="n"/>
+      <c r="E321" s="14" t="n"/>
       <c r="F321" s="85" t="n">
-        <v>2268.7</v>
+        <v>2427.5</v>
       </c>
       <c r="G321" s="53" t="n"/>
     </row>
     <row r="322" ht="19.8" customHeight="1">
-      <c r="A322" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B322" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C322" s="47" t="inlineStr">
-        <is>
-          <t>2268.70  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A322" s="43" t="n"/>
+      <c r="B322" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C322" s="18" t="n"/>
       <c r="D322" s="12" t="n"/>
-      <c r="E322" s="14" t="n"/>
-      <c r="F322" s="85" t="n">
+      <c r="E322" s="39" t="n"/>
+      <c r="F322" s="87" t="n"/>
+      <c r="G322" s="53" t="n"/>
+    </row>
+    <row r="323" ht="19.8" customHeight="1">
+      <c r="A323" s="83" t="n"/>
+      <c r="B323" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C323" s="47" t="n"/>
+      <c r="D323" s="12" t="n"/>
+      <c r="E323" s="14" t="n"/>
+      <c r="F323" s="85" t="n">
         <v>2427.5</v>
       </c>
-      <c r="G322" s="53" t="n"/>
-    </row>
-    <row r="323" ht="19.8" customHeight="1">
-      <c r="A323" s="43" t="n"/>
-      <c r="B323" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C323" s="18" t="n"/>
-      <c r="D323" s="12" t="n"/>
-      <c r="E323" s="39" t="n"/>
-      <c r="F323" s="87" t="n"/>
       <c r="G323" s="53" t="n"/>
     </row>
     <row r="324" ht="19.8" customHeight="1">
-      <c r="A324" s="83" t="n"/>
-      <c r="B324" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C324" s="47" t="n"/>
+      <c r="A324" s="47" t="n"/>
+      <c r="B324" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C324" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D324" s="12" t="n"/>
-      <c r="E324" s="14" t="n"/>
-      <c r="F324" s="85" t="n">
-        <v>2427.5</v>
-      </c>
+      <c r="E324" s="39" t="n"/>
+      <c r="F324" s="61" t="n"/>
       <c r="G324" s="53" t="n"/>
     </row>
     <row r="325" ht="19.8" customHeight="1">
       <c r="A325" s="47" t="n"/>
-      <c r="B325" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C325" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B325" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C325" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D325" s="12" t="n"/>
       <c r="E325" s="39" t="n"/>
-      <c r="F325" s="61" t="n"/>
+      <c r="F325" s="20" t="n"/>
       <c r="G325" s="53" t="n"/>
     </row>
     <row r="326" ht="19.8" customHeight="1">
       <c r="A326" s="47" t="n"/>
       <c r="B326" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C326" s="19" t="n">
-        <v>274.4</v>
+          <t>Elementos necesarios</t>
+        </is>
+      </c>
+      <c r="C326" s="59" t="n">
+        <v>9</v>
       </c>
       <c r="D326" s="12" t="n"/>
       <c r="E326" s="39" t="n"/>
@@ -25853,11 +25845,11 @@
       <c r="A327" s="47" t="n"/>
       <c r="B327" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
+          <t>Ancho del radiador (cm)</t>
         </is>
       </c>
       <c r="C327" s="59" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="D327" s="12" t="n"/>
       <c r="E327" s="39" t="n"/>
@@ -25865,14 +25857,16 @@
       <c r="G327" s="53" t="n"/>
     </row>
     <row r="328" ht="19.8" customHeight="1">
-      <c r="A328" s="47" t="n"/>
+      <c r="A328" s="50" t="n"/>
       <c r="B328" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
-        </is>
-      </c>
-      <c r="C328" s="59" t="n">
-        <v>72</v>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C328" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
       </c>
       <c r="D328" s="12" t="n"/>
       <c r="E328" s="39" t="n"/>
@@ -25880,145 +25874,151 @@
       <c r="G328" s="53" t="n"/>
     </row>
     <row r="329" ht="19.8" customHeight="1">
-      <c r="A329" s="50" t="n"/>
-      <c r="B329" s="60" t="inlineStr">
-        <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C329" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
-      </c>
-      <c r="D329" s="12" t="n"/>
-      <c r="E329" s="39" t="n"/>
-      <c r="F329" s="20" t="n"/>
+      <c r="A329" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  17 - Bano   (PA)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B329" s="11" t="n"/>
+      <c r="C329" s="11" t="n"/>
+      <c r="D329" s="11" t="n"/>
+      <c r="E329" s="11" t="n"/>
+      <c r="F329" s="42" t="n"/>
       <c r="G329" s="53" t="n"/>
     </row>
-    <row r="330" ht="19.8" customHeight="1">
-      <c r="A330" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  17 - Bano   (PA)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B330" s="11" t="n"/>
-      <c r="C330" s="11" t="n"/>
-      <c r="D330" s="11" t="n"/>
-      <c r="E330" s="11" t="n"/>
-      <c r="F330" s="42" t="n"/>
+    <row r="330" ht="32" customHeight="1">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G330" s="53" t="n"/>
     </row>
-    <row r="331" ht="32" customHeight="1">
-      <c r="A331" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B331" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C331" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D331" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E331" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F331" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="331" ht="19.8" customHeight="1">
+      <c r="A331" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B331" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C331" s="43" t="n"/>
+      <c r="D331" s="58" t="n"/>
+      <c r="E331" s="58" t="n"/>
+      <c r="F331" s="61" t="n"/>
       <c r="G331" s="53" t="n"/>
     </row>
     <row r="332" ht="19.8" customHeight="1">
-      <c r="A332" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B332" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C332" s="43" t="n"/>
-      <c r="D332" s="58" t="n"/>
-      <c r="E332" s="58" t="n"/>
-      <c r="F332" s="61" t="n"/>
+      <c r="A332" s="90" t="n"/>
+      <c r="B332" s="91" t="inlineStr">
+        <is>
+          <t>VA03</t>
+        </is>
+      </c>
+      <c r="C332" s="18" t="inlineStr">
+        <is>
+          <t>0.75 x 2.52</t>
+        </is>
+      </c>
+      <c r="D332" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E332" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F332" s="80" t="n">
+        <v>113.4</v>
+      </c>
       <c r="G332" s="53" t="n"/>
     </row>
     <row r="333" ht="19.8" customHeight="1">
-      <c r="A333" s="90" t="n"/>
-      <c r="B333" s="91" t="inlineStr">
-        <is>
-          <t>VA03</t>
-        </is>
-      </c>
-      <c r="C333" s="18" t="inlineStr">
-        <is>
-          <t>0.75 x 2.52</t>
-        </is>
-      </c>
-      <c r="D333" s="19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="E333" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F333" s="80" t="n">
-        <v>113.4</v>
-      </c>
+      <c r="A333" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B333" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C333" s="47" t="n"/>
+      <c r="D333" s="18" t="n"/>
+      <c r="E333" s="18" t="n"/>
+      <c r="F333" s="20" t="n"/>
       <c r="G333" s="53" t="n"/>
     </row>
     <row r="334" ht="19.8" customHeight="1">
-      <c r="A334" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B334" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C334" s="47" t="n"/>
-      <c r="D334" s="18" t="n"/>
-      <c r="E334" s="18" t="n"/>
-      <c r="F334" s="20" t="n"/>
+      <c r="A334" s="43" t="n"/>
+      <c r="B334" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS (NE)</t>
+        </is>
+      </c>
+      <c r="C334" s="18" t="inlineStr">
+        <is>
+          <t>2.20 x 3.00</t>
+        </is>
+      </c>
+      <c r="D334" s="19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E334" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F334" s="80" t="n">
+        <v>132</v>
+      </c>
       <c r="G334" s="53" t="n"/>
     </row>
     <row r="335" ht="19.8" customHeight="1">
-      <c r="A335" s="43" t="n"/>
-      <c r="B335" s="79" t="inlineStr">
-        <is>
-          <t>AISLADAS (NE)</t>
+      <c r="A335" s="47" t="n"/>
+      <c r="B335" s="81" t="inlineStr">
+        <is>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C335" s="18" t="inlineStr">
         <is>
-          <t>2.20 x 3.00</t>
+          <t>1.60 x 3.00</t>
         </is>
       </c>
       <c r="D335" s="19" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="E335" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F335" s="80" t="n">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="G335" s="53" t="n"/>
     </row>
@@ -26026,366 +26026,358 @@
       <c r="A336" s="47" t="n"/>
       <c r="B336" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>INTERIORES (SO)</t>
         </is>
       </c>
       <c r="C336" s="18" t="inlineStr">
         <is>
+          <t>2.20 x 3.00</t>
+        </is>
+      </c>
+      <c r="D336" s="19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E336" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F336" s="80" t="n">
+        <v>165</v>
+      </c>
+      <c r="G336" s="53" t="n"/>
+    </row>
+    <row r="337" ht="19.8" customHeight="1">
+      <c r="A337" s="50" t="n"/>
+      <c r="B337" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C337" s="18" t="inlineStr">
+        <is>
           <t>1.60 x 3.00</t>
         </is>
       </c>
-      <c r="D336" s="19" t="n">
+      <c r="D337" s="19" t="n">
         <v>4.8</v>
-      </c>
-      <c r="E336" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F336" s="80" t="n">
-        <v>96</v>
-      </c>
-      <c r="G336" s="53" t="n"/>
-    </row>
-    <row r="337" ht="19.8" customHeight="1">
-      <c r="A337" s="47" t="n"/>
-      <c r="B337" s="81" t="inlineStr">
-        <is>
-          <t>INTERIORES (SO)</t>
-        </is>
-      </c>
-      <c r="C337" s="18" t="inlineStr">
-        <is>
-          <t>2.20 x 3.00</t>
-        </is>
-      </c>
-      <c r="D337" s="19" t="n">
-        <v>6.6</v>
       </c>
       <c r="E337" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F337" s="80" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="G337" s="53" t="n"/>
     </row>
     <row r="338" ht="19.8" customHeight="1">
-      <c r="A338" s="50" t="n"/>
-      <c r="B338" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C338" s="18" t="inlineStr">
-        <is>
-          <t>1.60 x 3.00</t>
-        </is>
-      </c>
-      <c r="D338" s="19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E338" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F338" s="80" t="n">
-        <v>120</v>
-      </c>
+      <c r="A338" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B338" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C338" s="47" t="n"/>
+      <c r="D338" s="18" t="n"/>
+      <c r="E338" s="18" t="n"/>
+      <c r="F338" s="20" t="n"/>
       <c r="G338" s="53" t="n"/>
     </row>
     <row r="339" ht="19.8" customHeight="1">
-      <c r="A339" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B339" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C339" s="47" t="n"/>
-      <c r="D339" s="18" t="n"/>
-      <c r="E339" s="18" t="n"/>
-      <c r="F339" s="20" t="n"/>
+      <c r="A339" s="43" t="n"/>
+      <c r="B339" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C339" s="18" t="n"/>
+      <c r="D339" s="19" t="n"/>
+      <c r="E339" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F339" s="80" t="n"/>
       <c r="G339" s="53" t="n"/>
     </row>
     <row r="340" ht="19.8" customHeight="1">
-      <c r="A340" s="43" t="n"/>
-      <c r="B340" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C340" s="18" t="n"/>
-      <c r="D340" s="19" t="n"/>
+      <c r="A340" s="47" t="n"/>
+      <c r="B340" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C340" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D340" s="19" t="n">
+        <v>3.52</v>
+      </c>
       <c r="E340" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F340" s="80" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F340" s="80" t="n">
+        <v>70.40000000000001</v>
+      </c>
       <c r="G340" s="53" t="n"/>
     </row>
     <row r="341" ht="19.8" customHeight="1">
-      <c r="A341" s="47" t="n"/>
-      <c r="B341" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C341" s="18" t="inlineStr">
+      <c r="A341" s="50" t="n"/>
+      <c r="B341" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C341" s="18" t="n"/>
+      <c r="D341" s="19" t="n"/>
+      <c r="E341" s="59" t="n">
+        <v>15</v>
+      </c>
+      <c r="F341" s="80" t="n"/>
+      <c r="G341" s="53" t="n"/>
+    </row>
+    <row r="342" ht="19.8" customHeight="1">
+      <c r="A342" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B342" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C342" s="47" t="n"/>
+      <c r="D342" s="18" t="n"/>
+      <c r="E342" s="18" t="n"/>
+      <c r="F342" s="20" t="n"/>
+      <c r="G342" s="53" t="n"/>
+    </row>
+    <row r="343" ht="19.8" customHeight="1">
+      <c r="A343" s="43" t="n"/>
+      <c r="B343" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C343" s="18" t="n"/>
+      <c r="D343" s="19" t="n"/>
+      <c r="E343" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F343" s="80" t="n"/>
+      <c r="G343" s="53" t="n"/>
+    </row>
+    <row r="344" ht="19.8" customHeight="1">
+      <c r="A344" s="50" t="n"/>
+      <c r="B344" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C344" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D341" s="19" t="n">
+      <c r="D344" s="24" t="n">
         <v>3.52</v>
       </c>
-      <c r="E341" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F341" s="80" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="G341" s="53" t="n"/>
-    </row>
-    <row r="342" ht="19.8" customHeight="1">
-      <c r="A342" s="50" t="n"/>
-      <c r="B342" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C342" s="18" t="n"/>
-      <c r="D342" s="19" t="n"/>
-      <c r="E342" s="59" t="n">
+      <c r="E344" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F342" s="80" t="n"/>
-      <c r="G342" s="53" t="n"/>
-    </row>
-    <row r="343" ht="19.8" customHeight="1">
-      <c r="A343" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B343" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C343" s="47" t="n"/>
-      <c r="D343" s="18" t="n"/>
-      <c r="E343" s="18" t="n"/>
-      <c r="F343" s="20" t="n"/>
-      <c r="G343" s="53" t="n"/>
-    </row>
-    <row r="344" ht="19.8" customHeight="1">
-      <c r="A344" s="43" t="n"/>
-      <c r="B344" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C344" s="18" t="n"/>
-      <c r="D344" s="19" t="n"/>
-      <c r="E344" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F344" s="80" t="n"/>
+      <c r="F344" s="80" t="n">
+        <v>52.8</v>
+      </c>
       <c r="G344" s="53" t="n"/>
     </row>
     <row r="345" ht="19.8" customHeight="1">
-      <c r="A345" s="50" t="n"/>
-      <c r="B345" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C345" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D345" s="24" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="E345" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F345" s="80" t="n">
-        <v>52.8</v>
-      </c>
+      <c r="A345" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B345" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C345" s="83" t="n"/>
+      <c r="D345" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E345" s="47" t="n"/>
+      <c r="F345" s="20" t="n"/>
       <c r="G345" s="53" t="n"/>
     </row>
     <row r="346" ht="19.8" customHeight="1">
-      <c r="A346" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B346" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C346" s="83" t="n"/>
-      <c r="D346" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E346" s="47" t="n"/>
-      <c r="F346" s="20" t="n"/>
+      <c r="A346" s="43" t="n"/>
+      <c r="B346" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C346" s="18" t="n"/>
+      <c r="D346" s="22" t="n"/>
+      <c r="E346" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F346" s="80" t="n"/>
       <c r="G346" s="53" t="n"/>
     </row>
     <row r="347" ht="19.8" customHeight="1">
-      <c r="A347" s="43" t="n"/>
-      <c r="B347" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C347" s="18" t="n"/>
-      <c r="D347" s="22" t="n"/>
+      <c r="A347" s="47" t="n"/>
+      <c r="B347" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C347" s="18" t="inlineStr">
+        <is>
+          <t>3.52 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D347" s="19" t="n">
+        <v>10.56</v>
+      </c>
       <c r="E347" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F347" s="80" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="F347" s="80" t="n">
+        <v>95</v>
+      </c>
       <c r="G347" s="53" t="n"/>
     </row>
     <row r="348" ht="19.8" customHeight="1">
-      <c r="A348" s="47" t="n"/>
-      <c r="B348" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C348" s="18" t="inlineStr">
-        <is>
-          <t>3.52 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D348" s="19" t="n">
-        <v>10.56</v>
-      </c>
+      <c r="A348" s="50" t="n"/>
+      <c r="B348" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C348" s="18" t="n"/>
+      <c r="D348" s="19" t="n"/>
       <c r="E348" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F348" s="80" t="n">
-        <v>95</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F348" s="84" t="n"/>
       <c r="G348" s="53" t="n"/>
     </row>
     <row r="349" ht="19.8" customHeight="1">
-      <c r="A349" s="50" t="n"/>
-      <c r="B349" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C349" s="18" t="n"/>
-      <c r="D349" s="19" t="n"/>
-      <c r="E349" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F349" s="84" t="n"/>
+      <c r="A349" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B349" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C349" s="47" t="n"/>
+      <c r="D349" s="18" t="n"/>
+      <c r="E349" s="20" t="n"/>
+      <c r="F349" s="85" t="n">
+        <v>844.6</v>
+      </c>
       <c r="G349" s="53" t="n"/>
     </row>
     <row r="350" ht="19.8" customHeight="1">
       <c r="A350" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B350" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C350" s="47" t="n"/>
-      <c r="D350" s="18" t="n"/>
-      <c r="E350" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C350" s="47" t="inlineStr">
+        <is>
+          <t>844.60  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D350" s="12" t="n"/>
+      <c r="E350" s="14" t="n"/>
       <c r="F350" s="85" t="n">
-        <v>844.6</v>
+        <v>903.7</v>
       </c>
       <c r="G350" s="53" t="n"/>
     </row>
     <row r="351" ht="19.8" customHeight="1">
-      <c r="A351" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B351" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C351" s="47" t="inlineStr">
-        <is>
-          <t>844.60  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A351" s="43" t="n"/>
+      <c r="B351" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C351" s="18" t="n"/>
       <c r="D351" s="12" t="n"/>
-      <c r="E351" s="14" t="n"/>
-      <c r="F351" s="85" t="n">
+      <c r="E351" s="39" t="n"/>
+      <c r="F351" s="87" t="n"/>
+      <c r="G351" s="53" t="n"/>
+    </row>
+    <row r="352" ht="19.8" customHeight="1">
+      <c r="A352" s="83" t="n"/>
+      <c r="B352" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C352" s="47" t="n"/>
+      <c r="D352" s="12" t="n"/>
+      <c r="E352" s="14" t="n"/>
+      <c r="F352" s="85" t="n">
         <v>903.7</v>
       </c>
-      <c r="G351" s="53" t="n"/>
-    </row>
-    <row r="352" ht="19.8" customHeight="1">
-      <c r="A352" s="43" t="n"/>
-      <c r="B352" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C352" s="18" t="n"/>
-      <c r="D352" s="12" t="n"/>
-      <c r="E352" s="39" t="n"/>
-      <c r="F352" s="87" t="n"/>
       <c r="G352" s="53" t="n"/>
     </row>
     <row r="353" ht="19.8" customHeight="1">
-      <c r="A353" s="83" t="n"/>
-      <c r="B353" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C353" s="47" t="n"/>
+      <c r="A353" s="47" t="n"/>
+      <c r="B353" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C353" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D353" s="12" t="n"/>
-      <c r="E353" s="14" t="n"/>
-      <c r="F353" s="85" t="n">
-        <v>903.7</v>
-      </c>
+      <c r="E353" s="39" t="n"/>
+      <c r="F353" s="61" t="n"/>
       <c r="G353" s="53" t="n"/>
     </row>
     <row r="354" ht="19.8" customHeight="1">
       <c r="A354" s="47" t="n"/>
-      <c r="B354" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C354" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B354" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
+        </is>
+      </c>
+      <c r="C354" s="59" t="n">
+        <v>708</v>
       </c>
       <c r="D354" s="12" t="n"/>
       <c r="E354" s="39" t="n"/>
-      <c r="F354" s="61" t="n"/>
+      <c r="F354" s="20" t="n"/>
       <c r="G354" s="53" t="n"/>
     </row>
     <row r="355" ht="19.8" customHeight="1">
       <c r="A355" s="47" t="n"/>
       <c r="B355" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 80</t>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
         </is>
       </c>
       <c r="C355" s="59" t="n">
-        <v>708</v>
+        <v>1315</v>
       </c>
       <c r="D355" s="12" t="n"/>
       <c r="E355" s="39" t="n"/>
@@ -26396,11 +26388,11 @@
       <c r="A356" s="47" t="n"/>
       <c r="B356" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 150</t>
+          <t>Toalleros necesarios</t>
         </is>
       </c>
       <c r="C356" s="59" t="n">
-        <v>1315</v>
+        <v>1</v>
       </c>
       <c r="D356" s="12" t="n"/>
       <c r="E356" s="39" t="n"/>
@@ -26408,51 +26400,37 @@
       <c r="G356" s="53" t="n"/>
     </row>
     <row r="357" ht="19.8" customHeight="1">
-      <c r="A357" s="47" t="n"/>
-      <c r="B357" s="60" t="inlineStr">
-        <is>
-          <t>Toalleros necesarios</t>
-        </is>
-      </c>
-      <c r="C357" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D357" s="12" t="n"/>
-      <c r="E357" s="39" t="n"/>
-      <c r="F357" s="20" t="n"/>
+      <c r="A357" s="50" t="n"/>
+      <c r="B357" s="72" t="inlineStr">
+        <is>
+          <t>Toallero adoptado</t>
+        </is>
+      </c>
+      <c r="C357" s="30" t="inlineStr">
+        <is>
+          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
+        </is>
+      </c>
+      <c r="D357" s="11" t="n"/>
+      <c r="E357" s="92" t="n"/>
+      <c r="F357" s="31" t="n"/>
       <c r="G357" s="53" t="n"/>
-    </row>
-    <row r="358" ht="19.8" customHeight="1">
-      <c r="A358" s="50" t="n"/>
-      <c r="B358" s="72" t="inlineStr">
-        <is>
-          <t>Toallero adoptado</t>
-        </is>
-      </c>
-      <c r="C358" s="30" t="inlineStr">
-        <is>
-          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
-        </is>
-      </c>
-      <c r="D358" s="11" t="n"/>
-      <c r="E358" s="92" t="n"/>
-      <c r="F358" s="31" t="n"/>
-      <c r="G358" s="53" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="101">
+    <mergeCell ref="C321:E321"/>
     <mergeCell ref="C202:E202"/>
     <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C329:E329"/>
-    <mergeCell ref="A301:F301"/>
     <mergeCell ref="C297:E297"/>
     <mergeCell ref="C60:E60"/>
     <mergeCell ref="C123:E123"/>
     <mergeCell ref="C268:E268"/>
     <mergeCell ref="C299:E299"/>
+    <mergeCell ref="C292:E292"/>
     <mergeCell ref="C57:E57"/>
     <mergeCell ref="C355:E355"/>
     <mergeCell ref="C293:E293"/>
+    <mergeCell ref="A329:F329"/>
     <mergeCell ref="C204:E204"/>
     <mergeCell ref="C357:E357"/>
     <mergeCell ref="C325:E325"/>
@@ -26493,12 +26471,11 @@
     <mergeCell ref="C324:E324"/>
     <mergeCell ref="C63:E63"/>
     <mergeCell ref="C121:E121"/>
-    <mergeCell ref="A330:F330"/>
     <mergeCell ref="C117:E117"/>
     <mergeCell ref="C173:E173"/>
     <mergeCell ref="C236:E236"/>
     <mergeCell ref="A210:F210"/>
-    <mergeCell ref="C300:E300"/>
+    <mergeCell ref="C350:E350"/>
     <mergeCell ref="C207:E207"/>
     <mergeCell ref="C328:E328"/>
     <mergeCell ref="C122:E122"/>
@@ -26513,6 +26490,7 @@
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="C235:E235"/>
     <mergeCell ref="C62:E62"/>
+    <mergeCell ref="A300:F300"/>
     <mergeCell ref="C234:E234"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C172:E172"/>
@@ -26531,7 +26509,6 @@
     <mergeCell ref="C119:E119"/>
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="C174:E174"/>
-    <mergeCell ref="C358:E358"/>
     <mergeCell ref="C327:E327"/>
     <mergeCell ref="C237:E237"/>
     <mergeCell ref="C351:E351"/>

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -20496,7 +20496,7 @@
       <c r="A42" s="47" t="n"/>
       <c r="B42" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (cocina)</t>
+          <t>INTERIORES (NE, cocina)</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
@@ -20542,7 +20542,7 @@
       <c r="A44" s="50" t="n"/>
       <c r="B44" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (escalera)</t>
+          <t>INTERIORES (SO, escalera)</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -22145,7 +22145,7 @@
       <c r="A129" s="43" t="n"/>
       <c r="B129" s="79" t="inlineStr">
         <is>
-          <t>AISLADAS (NE)</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
@@ -22168,7 +22168,7 @@
       <c r="A130" s="47" t="n"/>
       <c r="B130" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>AISLADAS (SO)</t>
         </is>
       </c>
       <c r="C130" s="18" t="inlineStr">
@@ -22191,7 +22191,7 @@
       <c r="A131" s="47" t="n"/>
       <c r="B131" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (SO)</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C131" s="18" t="inlineStr">
@@ -22214,7 +22214,7 @@
       <c r="A132" s="50" t="n"/>
       <c r="B132" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (NE)</t>
         </is>
       </c>
       <c r="C132" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -20519,7 +20519,7 @@
       <c r="A43" s="47" t="n"/>
       <c r="B43" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (NO, galeria, con la PV01)</t>
+          <t>INTERIORES (NO, galeria)</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
@@ -21556,7 +21556,7 @@
       <c r="A98" s="47" t="n"/>
       <c r="B98" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (resto del lado largo)</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C98" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -20542,7 +20542,7 @@
       <c r="A44" s="50" t="n"/>
       <c r="B44" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (SO, escalera)</t>
+          <t>INTERIORES (SO, escalera y bano exterior)</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -22672,7 +22672,7 @@
       <c r="A156" s="47" t="n"/>
       <c r="B156" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (SO)</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C156" s="18" t="inlineStr">
@@ -22718,7 +22718,7 @@
       <c r="A158" s="47" t="n"/>
       <c r="B158" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (SO)</t>
         </is>
       </c>
       <c r="C158" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -22672,7 +22672,7 @@
       <c r="A156" s="47" t="n"/>
       <c r="B156" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>AISLADAS (SO)</t>
         </is>
       </c>
       <c r="C156" s="18" t="inlineStr">
@@ -22695,7 +22695,7 @@
       <c r="A157" s="47" t="n"/>
       <c r="B157" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>AISLADAS (NO)</t>
         </is>
       </c>
       <c r="C157" s="18" t="inlineStr">
@@ -22718,7 +22718,7 @@
       <c r="A158" s="47" t="n"/>
       <c r="B158" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (SO)</t>
+          <t>INTERIORES (SE)</t>
         </is>
       </c>
       <c r="C158" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -23245,7 +23245,7 @@
       <c r="A187" s="47" t="n"/>
       <c r="B187" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (NO)</t>
         </is>
       </c>
       <c r="C187" s="18" t="inlineStr">
@@ -23291,7 +23291,7 @@
       <c r="A189" s="50" t="n"/>
       <c r="B189" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (SE)</t>
         </is>
       </c>
       <c r="C189" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -23245,7 +23245,7 @@
       <c r="A187" s="47" t="n"/>
       <c r="B187" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (NO)</t>
+          <t>INTERIORES (NO, dormitorio suite)</t>
         </is>
       </c>
       <c r="C187" s="18" t="inlineStr">
@@ -23291,7 +23291,7 @@
       <c r="A189" s="50" t="n"/>
       <c r="B189" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (SE)</t>
+          <t>INTERIORES (SE, bano visitas)</t>
         </is>
       </c>
       <c r="C189" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -23245,7 +23245,7 @@
       <c r="A187" s="47" t="n"/>
       <c r="B187" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (NO, dormitorio suite)</t>
+          <t>INTERIORES (NO, bano visitas)</t>
         </is>
       </c>
       <c r="C187" s="18" t="inlineStr">
@@ -23291,7 +23291,7 @@
       <c r="A189" s="50" t="n"/>
       <c r="B189" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (SE, bano visitas)</t>
+          <t>INTERIORES (SE, dormitorio suite)</t>
         </is>
       </c>
       <c r="C189" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -22695,7 +22695,7 @@
       <c r="A157" s="47" t="n"/>
       <c r="B157" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (NO)</t>
+          <t>AISLADAS (SE)</t>
         </is>
       </c>
       <c r="C157" s="18" t="inlineStr">
@@ -22718,7 +22718,7 @@
       <c r="A158" s="47" t="n"/>
       <c r="B158" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (SE)</t>
+          <t>INTERIORES (NO)</t>
         </is>
       </c>
       <c r="C158" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -19691,7 +19691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G357"/>
+  <dimension ref="A1:G356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.1" customWidth="1" min="1" max="1"/>
@@ -21523,17 +21523,17 @@
       </c>
       <c r="C96" s="18" t="inlineStr">
         <is>
-          <t>1.70 x 3.00</t>
+          <t>4.87 x 3.00</t>
         </is>
       </c>
       <c r="D96" s="19" t="n">
-        <v>5.1</v>
+        <v>14.61</v>
       </c>
       <c r="E96" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F96" s="80" t="n">
-        <v>102</v>
+        <v>292.2</v>
       </c>
       <c r="G96" s="53" t="n"/>
     </row>
@@ -21561,17 +21561,17 @@
       </c>
       <c r="C98" s="18" t="inlineStr">
         <is>
-          <t>3.17 x 3.00</t>
+          <t>3.38 x 3.00</t>
         </is>
       </c>
       <c r="D98" s="19" t="n">
-        <v>9.51</v>
+        <v>10.14</v>
       </c>
       <c r="E98" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F98" s="80" t="n">
-        <v>237.8</v>
+        <v>253.5</v>
       </c>
       <c r="G98" s="53" t="n"/>
     </row>
@@ -21584,17 +21584,17 @@
       </c>
       <c r="C99" s="18" t="inlineStr">
         <is>
-          <t>3.38 x 3.00</t>
+          <t>0.57 x 3.00</t>
         </is>
       </c>
       <c r="D99" s="19" t="n">
-        <v>10.14</v>
+        <v>1.71</v>
       </c>
       <c r="E99" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F99" s="80" t="n">
-        <v>253.5</v>
+        <v>42.8</v>
       </c>
       <c r="G99" s="53" t="n"/>
     </row>
@@ -21607,17 +21607,17 @@
       </c>
       <c r="C100" s="18" t="inlineStr">
         <is>
-          <t>1.66 x 3.00</t>
+          <t>1.49 x 3.00</t>
         </is>
       </c>
       <c r="D100" s="19" t="n">
-        <v>4.98</v>
+        <v>4.47</v>
       </c>
       <c r="E100" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F100" s="80" t="n">
-        <v>124.5</v>
+        <v>111.8</v>
       </c>
       <c r="G100" s="53" t="n"/>
     </row>
@@ -21630,23 +21630,23 @@
       </c>
       <c r="C101" s="18" t="inlineStr">
         <is>
-          <t>1.49 x 3.00</t>
+          <t>1.66 x 3.00</t>
         </is>
       </c>
       <c r="D101" s="19" t="n">
-        <v>4.47</v>
+        <v>4.98</v>
       </c>
       <c r="E101" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F101" s="80" t="n">
-        <v>111.8</v>
+        <v>124.5</v>
       </c>
       <c r="G101" s="53" t="n"/>
     </row>
     <row r="102" ht="19.8" customHeight="1">
-      <c r="A102" s="47" t="n"/>
-      <c r="B102" s="81" t="inlineStr">
+      <c r="A102" s="50" t="n"/>
+      <c r="B102" s="82" t="inlineStr">
         <is>
           <t>INTERIORES</t>
         </is>
@@ -21668,323 +21668,315 @@
       <c r="G102" s="53" t="n"/>
     </row>
     <row r="103" ht="19.8" customHeight="1">
-      <c r="A103" s="50" t="n"/>
-      <c r="B103" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C103" s="18" t="inlineStr">
-        <is>
-          <t>0.57 x 3.00</t>
-        </is>
-      </c>
-      <c r="D103" s="19" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="E103" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F103" s="80" t="n">
-        <v>42.8</v>
-      </c>
+      <c r="A103" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B103" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C103" s="47" t="n"/>
+      <c r="D103" s="18" t="n"/>
+      <c r="E103" s="18" t="n"/>
+      <c r="F103" s="20" t="n"/>
       <c r="G103" s="53" t="n"/>
     </row>
     <row r="104" ht="19.8" customHeight="1">
-      <c r="A104" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B104" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C104" s="47" t="n"/>
-      <c r="D104" s="18" t="n"/>
-      <c r="E104" s="18" t="n"/>
-      <c r="F104" s="20" t="n"/>
+      <c r="A104" s="43" t="n"/>
+      <c r="B104" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="n"/>
+      <c r="D104" s="19" t="n"/>
+      <c r="E104" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F104" s="80" t="n"/>
       <c r="G104" s="53" t="n"/>
     </row>
     <row r="105" ht="19.8" customHeight="1">
-      <c r="A105" s="43" t="n"/>
-      <c r="B105" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
+      <c r="A105" s="47" t="n"/>
+      <c r="B105" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C105" s="18" t="n"/>
       <c r="D105" s="19" t="n"/>
       <c r="E105" s="59" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F105" s="80" t="n"/>
       <c r="G105" s="53" t="n"/>
     </row>
     <row r="106" ht="19.8" customHeight="1">
-      <c r="A106" s="47" t="n"/>
-      <c r="B106" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C106" s="18" t="n"/>
-      <c r="D106" s="19" t="n"/>
+      <c r="A106" s="50" t="n"/>
+      <c r="B106" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D106" s="19" t="n">
+        <v>7.23</v>
+      </c>
       <c r="E106" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F106" s="80" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="F106" s="80" t="n">
+        <v>108.5</v>
+      </c>
       <c r="G106" s="53" t="n"/>
     </row>
     <row r="107" ht="19.8" customHeight="1">
-      <c r="A107" s="50" t="n"/>
-      <c r="B107" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C107" s="18" t="inlineStr">
+      <c r="A107" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B107" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C107" s="47" t="n"/>
+      <c r="D107" s="18" t="n"/>
+      <c r="E107" s="18" t="n"/>
+      <c r="F107" s="20" t="n"/>
+      <c r="G107" s="53" t="n"/>
+    </row>
+    <row r="108" ht="19.8" customHeight="1">
+      <c r="A108" s="43" t="n"/>
+      <c r="B108" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D107" s="19" t="n">
+      <c r="D108" s="19" t="n">
         <v>7.23</v>
       </c>
-      <c r="E107" s="59" t="n">
+      <c r="E108" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F108" s="80" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="G108" s="53" t="n"/>
+    </row>
+    <row r="109" ht="19.8" customHeight="1">
+      <c r="A109" s="50" t="n"/>
+      <c r="B109" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="n"/>
+      <c r="D109" s="24" t="n"/>
+      <c r="E109" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F107" s="80" t="n">
-        <v>108.5</v>
-      </c>
-      <c r="G107" s="53" t="n"/>
-    </row>
-    <row r="108" ht="19.8" customHeight="1">
-      <c r="A108" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B108" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C108" s="47" t="n"/>
-      <c r="D108" s="18" t="n"/>
-      <c r="E108" s="18" t="n"/>
-      <c r="F108" s="20" t="n"/>
-      <c r="G108" s="53" t="n"/>
-    </row>
-    <row r="109" ht="19.8" customHeight="1">
-      <c r="A109" s="43" t="n"/>
-      <c r="B109" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C109" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D109" s="19" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="E109" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F109" s="80" t="n">
-        <v>72.3</v>
-      </c>
+      <c r="F109" s="80" t="n"/>
       <c r="G109" s="53" t="n"/>
     </row>
     <row r="110" ht="19.8" customHeight="1">
-      <c r="A110" s="50" t="n"/>
-      <c r="B110" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C110" s="18" t="n"/>
-      <c r="D110" s="24" t="n"/>
-      <c r="E110" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F110" s="80" t="n"/>
+      <c r="A110" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B110" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C110" s="83" t="n"/>
+      <c r="D110" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E110" s="47" t="n"/>
+      <c r="F110" s="20" t="n"/>
       <c r="G110" s="53" t="n"/>
     </row>
     <row r="111" ht="19.8" customHeight="1">
-      <c r="A111" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B111" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C111" s="83" t="n"/>
-      <c r="D111" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E111" s="47" t="n"/>
-      <c r="F111" s="20" t="n"/>
+      <c r="A111" s="43" t="n"/>
+      <c r="B111" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C111" s="18" t="inlineStr">
+        <is>
+          <t>7.23 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D111" s="22" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="E111" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F111" s="80" t="n">
+        <v>130.1</v>
+      </c>
       <c r="G111" s="53" t="n"/>
     </row>
     <row r="112" ht="19.8" customHeight="1">
-      <c r="A112" s="43" t="n"/>
-      <c r="B112" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C112" s="18" t="inlineStr">
-        <is>
-          <t>7.23 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D112" s="22" t="n">
-        <v>21.69</v>
-      </c>
+      <c r="A112" s="47" t="n"/>
+      <c r="B112" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="n"/>
+      <c r="D112" s="19" t="n"/>
       <c r="E112" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F112" s="80" t="n">
-        <v>130.1</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F112" s="80" t="n"/>
       <c r="G112" s="53" t="n"/>
     </row>
     <row r="113" ht="19.8" customHeight="1">
-      <c r="A113" s="47" t="n"/>
-      <c r="B113" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
+      <c r="A113" s="50" t="n"/>
+      <c r="B113" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C113" s="18" t="n"/>
       <c r="D113" s="19" t="n"/>
       <c r="E113" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F113" s="80" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="F113" s="84" t="n"/>
       <c r="G113" s="53" t="n"/>
     </row>
     <row r="114" ht="19.8" customHeight="1">
-      <c r="A114" s="50" t="n"/>
-      <c r="B114" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C114" s="18" t="n"/>
-      <c r="D114" s="19" t="n"/>
-      <c r="E114" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F114" s="84" t="n"/>
+      <c r="A114" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B114" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C114" s="47" t="n"/>
+      <c r="D114" s="18" t="n"/>
+      <c r="E114" s="20" t="n"/>
+      <c r="F114" s="85" t="n">
+        <v>1217.5</v>
+      </c>
       <c r="G114" s="53" t="n"/>
     </row>
     <row r="115" ht="19.8" customHeight="1">
       <c r="A115" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B115" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C115" s="47" t="n"/>
-      <c r="D115" s="18" t="n"/>
-      <c r="E115" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C115" s="47" t="inlineStr">
+        <is>
+          <t>1217.50  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="n"/>
+      <c r="E115" s="14" t="n"/>
       <c r="F115" s="85" t="n">
-        <v>1265.1</v>
+        <v>1302.7</v>
       </c>
       <c r="G115" s="53" t="n"/>
     </row>
     <row r="116" ht="19.8" customHeight="1">
-      <c r="A116" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B116" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C116" s="47" t="inlineStr">
-        <is>
-          <t>1265.10  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A116" s="43" t="n"/>
+      <c r="B116" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="n"/>
       <c r="D116" s="12" t="n"/>
-      <c r="E116" s="14" t="n"/>
-      <c r="F116" s="85" t="n">
-        <v>1353.7</v>
-      </c>
+      <c r="E116" s="39" t="n"/>
+      <c r="F116" s="87" t="n"/>
       <c r="G116" s="53" t="n"/>
     </row>
     <row r="117" ht="19.8" customHeight="1">
-      <c r="A117" s="43" t="n"/>
-      <c r="B117" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C117" s="18" t="n"/>
+      <c r="A117" s="83" t="n"/>
+      <c r="B117" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C117" s="47" t="n"/>
       <c r="D117" s="12" t="n"/>
-      <c r="E117" s="39" t="n"/>
-      <c r="F117" s="87" t="n"/>
+      <c r="E117" s="14" t="n"/>
+      <c r="F117" s="85" t="n">
+        <v>1302.7</v>
+      </c>
       <c r="G117" s="53" t="n"/>
     </row>
     <row r="118" ht="19.8" customHeight="1">
-      <c r="A118" s="83" t="n"/>
-      <c r="B118" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C118" s="47" t="n"/>
+      <c r="A118" s="47" t="n"/>
+      <c r="B118" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D118" s="12" t="n"/>
-      <c r="E118" s="14" t="n"/>
-      <c r="F118" s="85" t="n">
-        <v>1353.7</v>
-      </c>
+      <c r="E118" s="39" t="n"/>
+      <c r="F118" s="61" t="n"/>
       <c r="G118" s="53" t="n"/>
     </row>
     <row r="119" ht="19.8" customHeight="1">
       <c r="A119" s="47" t="n"/>
-      <c r="B119" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C119" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B119" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C119" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D119" s="12" t="n"/>
       <c r="E119" s="39" t="n"/>
-      <c r="F119" s="61" t="n"/>
+      <c r="F119" s="20" t="n"/>
       <c r="G119" s="53" t="n"/>
     </row>
     <row r="120" ht="19.8" customHeight="1">
       <c r="A120" s="47" t="n"/>
       <c r="B120" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C120" s="19" t="n">
-        <v>274.4</v>
+          <t>Elementos necesarios</t>
+        </is>
+      </c>
+      <c r="C120" s="59" t="n">
+        <v>5</v>
       </c>
       <c r="D120" s="12" t="n"/>
       <c r="E120" s="39" t="n"/>
@@ -21995,11 +21987,11 @@
       <c r="A121" s="47" t="n"/>
       <c r="B121" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
+          <t>Ancho del radiador (cm)</t>
         </is>
       </c>
       <c r="C121" s="59" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D121" s="12" t="n"/>
       <c r="E121" s="39" t="n"/>
@@ -22007,14 +21999,16 @@
       <c r="G121" s="53" t="n"/>
     </row>
     <row r="122" ht="19.8" customHeight="1">
-      <c r="A122" s="47" t="n"/>
+      <c r="A122" s="50" t="n"/>
       <c r="B122" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
-        </is>
-      </c>
-      <c r="C122" s="59" t="n">
-        <v>40</v>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
       </c>
       <c r="D122" s="12" t="n"/>
       <c r="E122" s="39" t="n"/>
@@ -22022,145 +22016,151 @@
       <c r="G122" s="53" t="n"/>
     </row>
     <row r="123" ht="19.8" customHeight="1">
-      <c r="A123" s="50" t="n"/>
-      <c r="B123" s="60" t="inlineStr">
-        <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C123" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
-      </c>
-      <c r="D123" s="12" t="n"/>
-      <c r="E123" s="39" t="n"/>
-      <c r="F123" s="20" t="n"/>
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  Escalera   (PB)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="n"/>
+      <c r="C123" s="11" t="n"/>
+      <c r="D123" s="11" t="n"/>
+      <c r="E123" s="11" t="n"/>
+      <c r="F123" s="42" t="n"/>
       <c r="G123" s="53" t="n"/>
     </row>
-    <row r="124" ht="19.8" customHeight="1">
-      <c r="A124" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  Escalera   (PB)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B124" s="11" t="n"/>
-      <c r="C124" s="11" t="n"/>
-      <c r="D124" s="11" t="n"/>
-      <c r="E124" s="11" t="n"/>
-      <c r="F124" s="42" t="n"/>
+    <row r="124" ht="32" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G124" s="53" t="n"/>
     </row>
-    <row r="125" ht="32" customHeight="1">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="125" ht="19.8" customHeight="1">
+      <c r="A125" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B125" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C125" s="43" t="n"/>
+      <c r="D125" s="58" t="n"/>
+      <c r="E125" s="58" t="n"/>
+      <c r="F125" s="61" t="n"/>
       <c r="G125" s="53" t="n"/>
     </row>
     <row r="126" ht="19.8" customHeight="1">
-      <c r="A126" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B126" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C126" s="43" t="n"/>
-      <c r="D126" s="58" t="n"/>
-      <c r="E126" s="58" t="n"/>
-      <c r="F126" s="61" t="n"/>
+      <c r="A126" s="90" t="n"/>
+      <c r="B126" s="91" t="inlineStr">
+        <is>
+          <t>PF05</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="inlineStr">
+        <is>
+          <t>0.75 x 2.52</t>
+        </is>
+      </c>
+      <c r="D126" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E126" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F126" s="80" t="n">
+        <v>113.4</v>
+      </c>
       <c r="G126" s="53" t="n"/>
     </row>
     <row r="127" ht="19.8" customHeight="1">
-      <c r="A127" s="90" t="n"/>
-      <c r="B127" s="91" t="inlineStr">
-        <is>
-          <t>PF05</t>
-        </is>
-      </c>
-      <c r="C127" s="18" t="inlineStr">
-        <is>
-          <t>0.75 x 2.52</t>
-        </is>
-      </c>
-      <c r="D127" s="19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="E127" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F127" s="80" t="n">
-        <v>113.4</v>
-      </c>
+      <c r="A127" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B127" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C127" s="47" t="n"/>
+      <c r="D127" s="18" t="n"/>
+      <c r="E127" s="18" t="n"/>
+      <c r="F127" s="20" t="n"/>
       <c r="G127" s="53" t="n"/>
     </row>
     <row r="128" ht="19.8" customHeight="1">
-      <c r="A128" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B128" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C128" s="47" t="n"/>
-      <c r="D128" s="18" t="n"/>
-      <c r="E128" s="18" t="n"/>
-      <c r="F128" s="20" t="n"/>
+      <c r="A128" s="43" t="n"/>
+      <c r="B128" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C128" s="18" t="inlineStr">
+        <is>
+          <t>4.06 x 3.00</t>
+        </is>
+      </c>
+      <c r="D128" s="19" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="E128" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F128" s="80" t="n">
+        <v>243.6</v>
+      </c>
       <c r="G128" s="53" t="n"/>
     </row>
     <row r="129" ht="19.8" customHeight="1">
-      <c r="A129" s="43" t="n"/>
-      <c r="B129" s="79" t="inlineStr">
-        <is>
-          <t>AISLADAS</t>
+      <c r="A129" s="47" t="n"/>
+      <c r="B129" s="81" t="inlineStr">
+        <is>
+          <t>AISLADAS (SO)</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>4.06 x 3.00</t>
+          <t>1.73 x 3.00</t>
         </is>
       </c>
       <c r="D129" s="19" t="n">
-        <v>12.18</v>
+        <v>5.19</v>
       </c>
       <c r="E129" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F129" s="80" t="n">
-        <v>243.6</v>
+        <v>103.8</v>
       </c>
       <c r="G129" s="53" t="n"/>
     </row>
@@ -22168,488 +22168,488 @@
       <c r="A130" s="47" t="n"/>
       <c r="B130" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (SO)</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C130" s="18" t="inlineStr">
         <is>
+          <t>4.06 x 3.00</t>
+        </is>
+      </c>
+      <c r="D130" s="19" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="E130" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F130" s="80" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="G130" s="53" t="n"/>
+    </row>
+    <row r="131" ht="19.8" customHeight="1">
+      <c r="A131" s="50" t="n"/>
+      <c r="B131" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES (NE)</t>
+        </is>
+      </c>
+      <c r="C131" s="18" t="inlineStr">
+        <is>
           <t>1.73 x 3.00</t>
         </is>
       </c>
-      <c r="D130" s="19" t="n">
+      <c r="D131" s="19" t="n">
         <v>5.19</v>
-      </c>
-      <c r="E130" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F130" s="80" t="n">
-        <v>103.8</v>
-      </c>
-      <c r="G130" s="53" t="n"/>
-    </row>
-    <row r="131" ht="19.8" customHeight="1">
-      <c r="A131" s="47" t="n"/>
-      <c r="B131" s="81" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C131" s="18" t="inlineStr">
-        <is>
-          <t>4.06 x 3.00</t>
-        </is>
-      </c>
-      <c r="D131" s="19" t="n">
-        <v>12.18</v>
       </c>
       <c r="E131" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F131" s="80" t="n">
-        <v>304.5</v>
+        <v>129.8</v>
       </c>
       <c r="G131" s="53" t="n"/>
     </row>
     <row r="132" ht="19.8" customHeight="1">
-      <c r="A132" s="50" t="n"/>
-      <c r="B132" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES (NE)</t>
-        </is>
-      </c>
-      <c r="C132" s="18" t="inlineStr">
-        <is>
-          <t>1.73 x 3.00</t>
-        </is>
-      </c>
-      <c r="D132" s="19" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="E132" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F132" s="80" t="n">
-        <v>129.8</v>
-      </c>
+      <c r="A132" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B132" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C132" s="47" t="n"/>
+      <c r="D132" s="18" t="n"/>
+      <c r="E132" s="18" t="n"/>
+      <c r="F132" s="20" t="n"/>
       <c r="G132" s="53" t="n"/>
     </row>
     <row r="133" ht="19.8" customHeight="1">
-      <c r="A133" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B133" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C133" s="47" t="n"/>
-      <c r="D133" s="18" t="n"/>
-      <c r="E133" s="18" t="n"/>
-      <c r="F133" s="20" t="n"/>
+      <c r="A133" s="43" t="n"/>
+      <c r="B133" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C133" s="18" t="n"/>
+      <c r="D133" s="19" t="n"/>
+      <c r="E133" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F133" s="80" t="n"/>
       <c r="G133" s="53" t="n"/>
     </row>
     <row r="134" ht="19.8" customHeight="1">
-      <c r="A134" s="43" t="n"/>
-      <c r="B134" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
+      <c r="A134" s="47" t="n"/>
+      <c r="B134" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C134" s="18" t="n"/>
       <c r="D134" s="19" t="n"/>
       <c r="E134" s="59" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F134" s="80" t="n"/>
       <c r="G134" s="53" t="n"/>
     </row>
     <row r="135" ht="19.8" customHeight="1">
-      <c r="A135" s="47" t="n"/>
-      <c r="B135" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C135" s="18" t="n"/>
-      <c r="D135" s="19" t="n"/>
+      <c r="A135" s="50" t="n"/>
+      <c r="B135" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C135" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D135" s="19" t="n">
+        <v>7.02</v>
+      </c>
       <c r="E135" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F135" s="80" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="F135" s="80" t="n">
+        <v>105.3</v>
+      </c>
       <c r="G135" s="53" t="n"/>
     </row>
     <row r="136" ht="19.8" customHeight="1">
-      <c r="A136" s="50" t="n"/>
-      <c r="B136" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C136" s="18" t="inlineStr">
+      <c r="A136" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B136" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C136" s="47" t="n"/>
+      <c r="D136" s="18" t="n"/>
+      <c r="E136" s="18" t="n"/>
+      <c r="F136" s="20" t="n"/>
+      <c r="G136" s="53" t="n"/>
+    </row>
+    <row r="137" ht="19.8" customHeight="1">
+      <c r="A137" s="43" t="n"/>
+      <c r="B137" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C137" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D136" s="19" t="n">
+      <c r="D137" s="19" t="n">
         <v>7.02</v>
       </c>
-      <c r="E136" s="59" t="n">
+      <c r="E137" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F137" s="80" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="G137" s="53" t="n"/>
+    </row>
+    <row r="138" ht="19.8" customHeight="1">
+      <c r="A138" s="50" t="n"/>
+      <c r="B138" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="n"/>
+      <c r="D138" s="24" t="n"/>
+      <c r="E138" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F136" s="80" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="G136" s="53" t="n"/>
-    </row>
-    <row r="137" ht="19.8" customHeight="1">
-      <c r="A137" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B137" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C137" s="47" t="n"/>
-      <c r="D137" s="18" t="n"/>
-      <c r="E137" s="18" t="n"/>
-      <c r="F137" s="20" t="n"/>
-      <c r="G137" s="53" t="n"/>
-    </row>
-    <row r="138" ht="19.8" customHeight="1">
-      <c r="A138" s="43" t="n"/>
-      <c r="B138" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C138" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D138" s="19" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="E138" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F138" s="80" t="n">
-        <v>70.2</v>
-      </c>
+      <c r="F138" s="80" t="n"/>
       <c r="G138" s="53" t="n"/>
     </row>
     <row r="139" ht="19.8" customHeight="1">
-      <c r="A139" s="50" t="n"/>
-      <c r="B139" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C139" s="18" t="n"/>
-      <c r="D139" s="24" t="n"/>
-      <c r="E139" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F139" s="80" t="n"/>
+      <c r="A139" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B139" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C139" s="83" t="n"/>
+      <c r="D139" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E139" s="47" t="n"/>
+      <c r="F139" s="20" t="n"/>
       <c r="G139" s="53" t="n"/>
     </row>
     <row r="140" ht="19.8" customHeight="1">
-      <c r="A140" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B140" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C140" s="83" t="n"/>
-      <c r="D140" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E140" s="47" t="n"/>
-      <c r="F140" s="20" t="n"/>
+      <c r="A140" s="43" t="n"/>
+      <c r="B140" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C140" s="18" t="n"/>
+      <c r="D140" s="22" t="n"/>
+      <c r="E140" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F140" s="80" t="n"/>
       <c r="G140" s="53" t="n"/>
     </row>
     <row r="141" ht="19.8" customHeight="1">
-      <c r="A141" s="43" t="n"/>
-      <c r="B141" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C141" s="18" t="n"/>
-      <c r="D141" s="22" t="n"/>
+      <c r="A141" s="47" t="n"/>
+      <c r="B141" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C141" s="18" t="inlineStr">
+        <is>
+          <t>7.02 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D141" s="19" t="n">
+        <v>21.06</v>
+      </c>
       <c r="E141" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F141" s="80" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="F141" s="80" t="n">
+        <v>189.5</v>
+      </c>
       <c r="G141" s="53" t="n"/>
     </row>
     <row r="142" ht="19.8" customHeight="1">
-      <c r="A142" s="47" t="n"/>
-      <c r="B142" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C142" s="18" t="inlineStr">
-        <is>
-          <t>7.02 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D142" s="19" t="n">
-        <v>21.06</v>
-      </c>
+      <c r="A142" s="50" t="n"/>
+      <c r="B142" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="n"/>
+      <c r="D142" s="19" t="n"/>
       <c r="E142" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F142" s="80" t="n">
-        <v>189.5</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F142" s="84" t="n"/>
       <c r="G142" s="53" t="n"/>
     </row>
     <row r="143" ht="19.8" customHeight="1">
-      <c r="A143" s="50" t="n"/>
-      <c r="B143" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C143" s="18" t="n"/>
-      <c r="D143" s="19" t="n"/>
-      <c r="E143" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F143" s="84" t="n"/>
+      <c r="A143" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B143" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C143" s="47" t="n"/>
+      <c r="D143" s="18" t="n"/>
+      <c r="E143" s="20" t="n"/>
+      <c r="F143" s="85" t="n">
+        <v>1260.1</v>
+      </c>
       <c r="G143" s="53" t="n"/>
     </row>
     <row r="144" ht="19.8" customHeight="1">
       <c r="A144" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B144" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C144" s="47" t="n"/>
-      <c r="D144" s="18" t="n"/>
-      <c r="E144" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C144" s="47" t="inlineStr">
+        <is>
+          <t>1260.10  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D144" s="12" t="n"/>
+      <c r="E144" s="14" t="n"/>
       <c r="F144" s="85" t="n">
-        <v>1260.1</v>
+        <v>1348.3</v>
       </c>
       <c r="G144" s="53" t="n"/>
     </row>
     <row r="145" ht="19.8" customHeight="1">
-      <c r="A145" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B145" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C145" s="47" t="inlineStr">
-        <is>
-          <t>1260.10  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A145" s="43" t="n"/>
+      <c r="B145" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C145" s="18" t="n"/>
       <c r="D145" s="12" t="n"/>
-      <c r="E145" s="14" t="n"/>
-      <c r="F145" s="85" t="n">
+      <c r="E145" s="39" t="n"/>
+      <c r="F145" s="87" t="n"/>
+      <c r="G145" s="53" t="n"/>
+    </row>
+    <row r="146" ht="19.8" customHeight="1">
+      <c r="A146" s="83" t="n"/>
+      <c r="B146" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C146" s="47" t="n"/>
+      <c r="D146" s="12" t="n"/>
+      <c r="E146" s="14" t="n"/>
+      <c r="F146" s="85" t="n">
         <v>1348.3</v>
       </c>
-      <c r="G145" s="53" t="n"/>
-    </row>
-    <row r="146" ht="19.8" customHeight="1">
-      <c r="A146" s="43" t="n"/>
-      <c r="B146" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C146" s="18" t="n"/>
-      <c r="D146" s="12" t="n"/>
-      <c r="E146" s="39" t="n"/>
-      <c r="F146" s="87" t="n"/>
       <c r="G146" s="53" t="n"/>
     </row>
     <row r="147" ht="19.8" customHeight="1">
-      <c r="A147" s="83" t="n"/>
+      <c r="A147" s="89" t="n"/>
       <c r="B147" s="78" t="inlineStr">
         <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C147" s="47" t="n"/>
+          <t>SIN EMISOR</t>
+        </is>
+      </c>
+      <c r="C147" s="47" t="inlineStr">
+        <is>
+          <t>la cubre el radiador de 14 - Play room</t>
+        </is>
+      </c>
       <c r="D147" s="12" t="n"/>
-      <c r="E147" s="14" t="n"/>
-      <c r="F147" s="85" t="n">
-        <v>1348.3</v>
-      </c>
+      <c r="E147" s="39" t="n"/>
+      <c r="F147" s="61" t="n"/>
       <c r="G147" s="53" t="n"/>
     </row>
     <row r="148" ht="19.8" customHeight="1">
-      <c r="A148" s="89" t="n"/>
-      <c r="B148" s="78" t="inlineStr">
-        <is>
-          <t>SIN EMISOR</t>
-        </is>
-      </c>
-      <c r="C148" s="47" t="inlineStr">
-        <is>
-          <t>la cubre el radiador de 14 - Play room</t>
-        </is>
-      </c>
-      <c r="D148" s="12" t="n"/>
-      <c r="E148" s="39" t="n"/>
-      <c r="F148" s="61" t="n"/>
+      <c r="A148" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  09 - Dormitorio suite   (PB)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="n"/>
+      <c r="C148" s="11" t="n"/>
+      <c r="D148" s="11" t="n"/>
+      <c r="E148" s="11" t="n"/>
+      <c r="F148" s="42" t="n"/>
       <c r="G148" s="53" t="n"/>
     </row>
-    <row r="149" ht="19.8" customHeight="1">
-      <c r="A149" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  09 - Dormitorio suite   (PB)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="n"/>
-      <c r="C149" s="11" t="n"/>
-      <c r="D149" s="11" t="n"/>
-      <c r="E149" s="11" t="n"/>
-      <c r="F149" s="42" t="n"/>
+    <row r="149" ht="32" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G149" s="53" t="n"/>
     </row>
-    <row r="150" ht="32" customHeight="1">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="150" ht="19.8" customHeight="1">
+      <c r="A150" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B150" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C150" s="43" t="n"/>
+      <c r="D150" s="58" t="n"/>
+      <c r="E150" s="58" t="n"/>
+      <c r="F150" s="61" t="n"/>
       <c r="G150" s="53" t="n"/>
     </row>
     <row r="151" ht="19.8" customHeight="1">
-      <c r="A151" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B151" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C151" s="43" t="n"/>
-      <c r="D151" s="58" t="n"/>
-      <c r="E151" s="58" t="n"/>
-      <c r="F151" s="61" t="n"/>
+      <c r="A151" s="43" t="n"/>
+      <c r="B151" s="79" t="inlineStr">
+        <is>
+          <t>VA01</t>
+        </is>
+      </c>
+      <c r="C151" s="18" t="inlineStr">
+        <is>
+          <t>0.75 x 3.00</t>
+        </is>
+      </c>
+      <c r="D151" s="19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E151" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F151" s="80" t="n">
+        <v>135</v>
+      </c>
       <c r="G151" s="53" t="n"/>
     </row>
     <row r="152" ht="19.8" customHeight="1">
-      <c r="A152" s="43" t="n"/>
-      <c r="B152" s="79" t="inlineStr">
-        <is>
-          <t>VA01</t>
+      <c r="A152" s="50" t="n"/>
+      <c r="B152" s="82" t="inlineStr">
+        <is>
+          <t>PV03</t>
         </is>
       </c>
       <c r="C152" s="18" t="inlineStr">
         <is>
-          <t>0.75 x 3.00</t>
+          <t>1.76 x 3.00</t>
         </is>
       </c>
       <c r="D152" s="19" t="n">
-        <v>2.25</v>
+        <v>5.28</v>
       </c>
       <c r="E152" s="59" t="n">
         <v>60</v>
       </c>
       <c r="F152" s="80" t="n">
-        <v>135</v>
+        <v>316.8</v>
       </c>
       <c r="G152" s="53" t="n"/>
     </row>
     <row r="153" ht="19.8" customHeight="1">
-      <c r="A153" s="50" t="n"/>
-      <c r="B153" s="82" t="inlineStr">
-        <is>
-          <t>PV03</t>
-        </is>
-      </c>
-      <c r="C153" s="18" t="inlineStr">
-        <is>
-          <t>1.76 x 3.00</t>
-        </is>
-      </c>
-      <c r="D153" s="19" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="E153" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F153" s="80" t="n">
-        <v>316.8</v>
-      </c>
+      <c r="A153" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B153" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C153" s="47" t="n"/>
+      <c r="D153" s="18" t="n"/>
+      <c r="E153" s="18" t="n"/>
+      <c r="F153" s="20" t="n"/>
       <c r="G153" s="53" t="n"/>
     </row>
     <row r="154" ht="19.8" customHeight="1">
-      <c r="A154" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B154" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C154" s="47" t="n"/>
-      <c r="D154" s="18" t="n"/>
-      <c r="E154" s="18" t="n"/>
-      <c r="F154" s="20" t="n"/>
+      <c r="A154" s="43" t="n"/>
+      <c r="B154" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS (NE)</t>
+        </is>
+      </c>
+      <c r="C154" s="18" t="inlineStr">
+        <is>
+          <t>3.50 x 3.00</t>
+        </is>
+      </c>
+      <c r="D154" s="19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E154" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F154" s="80" t="n">
+        <v>210</v>
+      </c>
       <c r="G154" s="53" t="n"/>
     </row>
     <row r="155" ht="19.8" customHeight="1">
-      <c r="A155" s="43" t="n"/>
-      <c r="B155" s="79" t="inlineStr">
-        <is>
-          <t>AISLADAS (NE)</t>
+      <c r="A155" s="47" t="n"/>
+      <c r="B155" s="81" t="inlineStr">
+        <is>
+          <t>AISLADAS (SO)</t>
         </is>
       </c>
       <c r="C155" s="18" t="inlineStr">
@@ -22672,7 +22672,7 @@
       <c r="A156" s="47" t="n"/>
       <c r="B156" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (SO)</t>
+          <t>AISLADAS (SE)</t>
         </is>
       </c>
       <c r="C156" s="18" t="inlineStr">
@@ -22695,7 +22695,7 @@
       <c r="A157" s="47" t="n"/>
       <c r="B157" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (SE)</t>
+          <t>INTERIORES (NO)</t>
         </is>
       </c>
       <c r="C157" s="18" t="inlineStr">
@@ -22707,346 +22707,338 @@
         <v>10.5</v>
       </c>
       <c r="E157" s="59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F157" s="80" t="n">
-        <v>210</v>
+        <v>262.5</v>
       </c>
       <c r="G157" s="53" t="n"/>
     </row>
     <row r="158" ht="19.8" customHeight="1">
-      <c r="A158" s="47" t="n"/>
-      <c r="B158" s="81" t="inlineStr">
-        <is>
-          <t>INTERIORES (NO)</t>
-        </is>
-      </c>
-      <c r="C158" s="18" t="inlineStr">
-        <is>
-          <t>3.50 x 3.00</t>
-        </is>
-      </c>
-      <c r="D158" s="19" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="A158" s="50" t="n"/>
+      <c r="B158" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C158" s="18" t="n"/>
+      <c r="D158" s="19" t="n"/>
       <c r="E158" s="59" t="n">
         <v>25</v>
       </c>
-      <c r="F158" s="80" t="n">
-        <v>262.5</v>
-      </c>
+      <c r="F158" s="80" t="n"/>
       <c r="G158" s="53" t="n"/>
     </row>
     <row r="159" ht="19.8" customHeight="1">
-      <c r="A159" s="50" t="n"/>
-      <c r="B159" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C159" s="18" t="n"/>
-      <c r="D159" s="19" t="n"/>
-      <c r="E159" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F159" s="80" t="n"/>
+      <c r="A159" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B159" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C159" s="47" t="n"/>
+      <c r="D159" s="18" t="n"/>
+      <c r="E159" s="18" t="n"/>
+      <c r="F159" s="20" t="n"/>
       <c r="G159" s="53" t="n"/>
     </row>
     <row r="160" ht="19.8" customHeight="1">
-      <c r="A160" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B160" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C160" s="47" t="n"/>
-      <c r="D160" s="18" t="n"/>
-      <c r="E160" s="18" t="n"/>
-      <c r="F160" s="20" t="n"/>
+      <c r="A160" s="43" t="n"/>
+      <c r="B160" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C160" s="18" t="n"/>
+      <c r="D160" s="19" t="n"/>
+      <c r="E160" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F160" s="80" t="n"/>
       <c r="G160" s="53" t="n"/>
     </row>
     <row r="161" ht="19.8" customHeight="1">
-      <c r="A161" s="43" t="n"/>
-      <c r="B161" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
+      <c r="A161" s="47" t="n"/>
+      <c r="B161" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C161" s="18" t="n"/>
       <c r="D161" s="19" t="n"/>
       <c r="E161" s="59" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F161" s="80" t="n"/>
       <c r="G161" s="53" t="n"/>
     </row>
     <row r="162" ht="19.8" customHeight="1">
-      <c r="A162" s="47" t="n"/>
-      <c r="B162" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C162" s="18" t="n"/>
-      <c r="D162" s="19" t="n"/>
+      <c r="A162" s="50" t="n"/>
+      <c r="B162" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C162" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D162" s="19" t="n">
+        <v>12.25</v>
+      </c>
       <c r="E162" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F162" s="80" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="F162" s="80" t="n">
+        <v>183.8</v>
+      </c>
       <c r="G162" s="53" t="n"/>
     </row>
     <row r="163" ht="19.8" customHeight="1">
-      <c r="A163" s="50" t="n"/>
-      <c r="B163" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C163" s="18" t="inlineStr">
+      <c r="A163" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B163" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C163" s="47" t="n"/>
+      <c r="D163" s="18" t="n"/>
+      <c r="E163" s="18" t="n"/>
+      <c r="F163" s="20" t="n"/>
+      <c r="G163" s="53" t="n"/>
+    </row>
+    <row r="164" ht="19.8" customHeight="1">
+      <c r="A164" s="43" t="n"/>
+      <c r="B164" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C164" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D163" s="19" t="n">
+      <c r="D164" s="19" t="n">
         <v>12.25</v>
       </c>
-      <c r="E163" s="59" t="n">
+      <c r="E164" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F164" s="80" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="G164" s="53" t="n"/>
+    </row>
+    <row r="165" ht="19.8" customHeight="1">
+      <c r="A165" s="50" t="n"/>
+      <c r="B165" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C165" s="18" t="n"/>
+      <c r="D165" s="24" t="n"/>
+      <c r="E165" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F163" s="80" t="n">
-        <v>183.8</v>
-      </c>
-      <c r="G163" s="53" t="n"/>
-    </row>
-    <row r="164" ht="19.8" customHeight="1">
-      <c r="A164" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B164" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C164" s="47" t="n"/>
-      <c r="D164" s="18" t="n"/>
-      <c r="E164" s="18" t="n"/>
-      <c r="F164" s="20" t="n"/>
-      <c r="G164" s="53" t="n"/>
-    </row>
-    <row r="165" ht="19.8" customHeight="1">
-      <c r="A165" s="43" t="n"/>
-      <c r="B165" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C165" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D165" s="19" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="E165" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F165" s="80" t="n">
-        <v>122.5</v>
-      </c>
+      <c r="F165" s="80" t="n"/>
       <c r="G165" s="53" t="n"/>
     </row>
     <row r="166" ht="19.8" customHeight="1">
-      <c r="A166" s="50" t="n"/>
-      <c r="B166" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C166" s="18" t="n"/>
-      <c r="D166" s="24" t="n"/>
-      <c r="E166" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F166" s="80" t="n"/>
+      <c r="A166" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B166" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C166" s="83" t="n"/>
+      <c r="D166" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E166" s="47" t="n"/>
+      <c r="F166" s="20" t="n"/>
       <c r="G166" s="53" t="n"/>
     </row>
     <row r="167" ht="19.8" customHeight="1">
-      <c r="A167" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B167" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C167" s="83" t="n"/>
-      <c r="D167" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E167" s="47" t="n"/>
-      <c r="F167" s="20" t="n"/>
+      <c r="A167" s="43" t="n"/>
+      <c r="B167" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C167" s="18" t="n"/>
+      <c r="D167" s="22" t="n"/>
+      <c r="E167" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F167" s="80" t="n"/>
       <c r="G167" s="53" t="n"/>
     </row>
     <row r="168" ht="19.8" customHeight="1">
-      <c r="A168" s="43" t="n"/>
-      <c r="B168" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
+      <c r="A168" s="47" t="n"/>
+      <c r="B168" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C168" s="18" t="n"/>
-      <c r="D168" s="22" t="n"/>
+      <c r="D168" s="19" t="n"/>
       <c r="E168" s="59" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F168" s="80" t="n"/>
       <c r="G168" s="53" t="n"/>
     </row>
     <row r="169" ht="19.8" customHeight="1">
-      <c r="A169" s="47" t="n"/>
-      <c r="B169" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C169" s="18" t="n"/>
-      <c r="D169" s="19" t="n"/>
+      <c r="A169" s="50" t="n"/>
+      <c r="B169" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C169" s="18" t="inlineStr">
+        <is>
+          <t>12.25 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D169" s="19" t="n">
+        <v>36.75</v>
+      </c>
       <c r="E169" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F169" s="80" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="F169" s="84" t="n">
+        <v>441</v>
+      </c>
       <c r="G169" s="53" t="n"/>
     </row>
     <row r="170" ht="19.8" customHeight="1">
-      <c r="A170" s="50" t="n"/>
-      <c r="B170" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C170" s="18" t="inlineStr">
-        <is>
-          <t>12.25 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D170" s="19" t="n">
-        <v>36.75</v>
-      </c>
-      <c r="E170" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F170" s="84" t="n">
-        <v>441</v>
+      <c r="A170" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B170" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C170" s="47" t="n"/>
+      <c r="D170" s="18" t="n"/>
+      <c r="E170" s="20" t="n"/>
+      <c r="F170" s="85" t="n">
+        <v>2091.6</v>
       </c>
       <c r="G170" s="53" t="n"/>
     </row>
     <row r="171" ht="19.8" customHeight="1">
       <c r="A171" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B171" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C171" s="47" t="n"/>
-      <c r="D171" s="18" t="n"/>
-      <c r="E171" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C171" s="47" t="inlineStr">
+        <is>
+          <t>2091.60  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D171" s="12" t="n"/>
+      <c r="E171" s="14" t="n"/>
       <c r="F171" s="85" t="n">
-        <v>2091.6</v>
+        <v>2238</v>
       </c>
       <c r="G171" s="53" t="n"/>
     </row>
     <row r="172" ht="19.8" customHeight="1">
-      <c r="A172" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B172" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C172" s="47" t="inlineStr">
-        <is>
-          <t>2091.60  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A172" s="43" t="n"/>
+      <c r="B172" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C172" s="18" t="n"/>
       <c r="D172" s="12" t="n"/>
-      <c r="E172" s="14" t="n"/>
-      <c r="F172" s="85" t="n">
+      <c r="E172" s="39" t="n"/>
+      <c r="F172" s="87" t="n"/>
+      <c r="G172" s="53" t="n"/>
+    </row>
+    <row r="173" ht="19.8" customHeight="1">
+      <c r="A173" s="83" t="n"/>
+      <c r="B173" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C173" s="47" t="n"/>
+      <c r="D173" s="12" t="n"/>
+      <c r="E173" s="14" t="n"/>
+      <c r="F173" s="85" t="n">
         <v>2238</v>
       </c>
-      <c r="G172" s="53" t="n"/>
-    </row>
-    <row r="173" ht="19.8" customHeight="1">
-      <c r="A173" s="43" t="n"/>
-      <c r="B173" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C173" s="18" t="n"/>
-      <c r="D173" s="12" t="n"/>
-      <c r="E173" s="39" t="n"/>
-      <c r="F173" s="87" t="n"/>
       <c r="G173" s="53" t="n"/>
     </row>
     <row r="174" ht="19.8" customHeight="1">
-      <c r="A174" s="83" t="n"/>
-      <c r="B174" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C174" s="47" t="n"/>
+      <c r="A174" s="47" t="n"/>
+      <c r="B174" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C174" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D174" s="12" t="n"/>
-      <c r="E174" s="14" t="n"/>
-      <c r="F174" s="85" t="n">
-        <v>2238</v>
-      </c>
+      <c r="E174" s="39" t="n"/>
+      <c r="F174" s="61" t="n"/>
       <c r="G174" s="53" t="n"/>
     </row>
     <row r="175" ht="19.8" customHeight="1">
       <c r="A175" s="47" t="n"/>
-      <c r="B175" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C175" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B175" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C175" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D175" s="12" t="n"/>
       <c r="E175" s="39" t="n"/>
-      <c r="F175" s="61" t="n"/>
+      <c r="F175" s="20" t="n"/>
       <c r="G175" s="53" t="n"/>
     </row>
     <row r="176" ht="19.8" customHeight="1">
       <c r="A176" s="47" t="n"/>
       <c r="B176" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C176" s="19" t="n">
-        <v>274.4</v>
+          <t>Elementos necesarios</t>
+        </is>
+      </c>
+      <c r="C176" s="59" t="n">
+        <v>9</v>
       </c>
       <c r="D176" s="12" t="n"/>
       <c r="E176" s="39" t="n"/>
@@ -23057,11 +23049,11 @@
       <c r="A177" s="47" t="n"/>
       <c r="B177" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
+          <t>Ancho del radiador (cm)</t>
         </is>
       </c>
       <c r="C177" s="59" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="D177" s="12" t="n"/>
       <c r="E177" s="39" t="n"/>
@@ -23069,14 +23061,16 @@
       <c r="G177" s="53" t="n"/>
     </row>
     <row r="178" ht="19.8" customHeight="1">
-      <c r="A178" s="47" t="n"/>
+      <c r="A178" s="50" t="n"/>
       <c r="B178" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
-        </is>
-      </c>
-      <c r="C178" s="59" t="n">
-        <v>72</v>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C178" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
       </c>
       <c r="D178" s="12" t="n"/>
       <c r="E178" s="39" t="n"/>
@@ -23084,527 +23078,525 @@
       <c r="G178" s="53" t="n"/>
     </row>
     <row r="179" ht="19.8" customHeight="1">
-      <c r="A179" s="50" t="n"/>
-      <c r="B179" s="60" t="inlineStr">
-        <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C179" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
-      </c>
-      <c r="D179" s="12" t="n"/>
-      <c r="E179" s="39" t="n"/>
-      <c r="F179" s="20" t="n"/>
+      <c r="A179" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  10 - Bano suite   (PB)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B179" s="11" t="n"/>
+      <c r="C179" s="11" t="n"/>
+      <c r="D179" s="11" t="n"/>
+      <c r="E179" s="11" t="n"/>
+      <c r="F179" s="42" t="n"/>
       <c r="G179" s="53" t="n"/>
     </row>
-    <row r="180" ht="19.8" customHeight="1">
-      <c r="A180" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  10 - Bano suite   (PB)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B180" s="11" t="n"/>
-      <c r="C180" s="11" t="n"/>
-      <c r="D180" s="11" t="n"/>
-      <c r="E180" s="11" t="n"/>
-      <c r="F180" s="42" t="n"/>
+    <row r="180" ht="32" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G180" s="53" t="n"/>
     </row>
-    <row r="181" ht="32" customHeight="1">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E181" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F181" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="181" ht="19.8" customHeight="1">
+      <c r="A181" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B181" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C181" s="43" t="n"/>
+      <c r="D181" s="58" t="n"/>
+      <c r="E181" s="58" t="n"/>
+      <c r="F181" s="61" t="n"/>
       <c r="G181" s="53" t="n"/>
     </row>
     <row r="182" ht="19.8" customHeight="1">
-      <c r="A182" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B182" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C182" s="43" t="n"/>
-      <c r="D182" s="58" t="n"/>
-      <c r="E182" s="58" t="n"/>
-      <c r="F182" s="61" t="n"/>
+      <c r="A182" s="90" t="n"/>
+      <c r="B182" s="91" t="inlineStr">
+        <is>
+          <t>VA02</t>
+        </is>
+      </c>
+      <c r="C182" s="18" t="inlineStr">
+        <is>
+          <t>0.75 x 2.15</t>
+        </is>
+      </c>
+      <c r="D182" s="19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="E182" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F182" s="80" t="n">
+        <v>96.59999999999999</v>
+      </c>
       <c r="G182" s="53" t="n"/>
     </row>
     <row r="183" ht="19.8" customHeight="1">
-      <c r="A183" s="90" t="n"/>
-      <c r="B183" s="91" t="inlineStr">
-        <is>
-          <t>VA02</t>
-        </is>
-      </c>
-      <c r="C183" s="18" t="inlineStr">
-        <is>
-          <t>0.75 x 2.15</t>
-        </is>
-      </c>
-      <c r="D183" s="19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="E183" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F183" s="80" t="n">
-        <v>96.59999999999999</v>
-      </c>
+      <c r="A183" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B183" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C183" s="47" t="n"/>
+      <c r="D183" s="18" t="n"/>
+      <c r="E183" s="18" t="n"/>
+      <c r="F183" s="20" t="n"/>
       <c r="G183" s="53" t="n"/>
     </row>
     <row r="184" ht="19.8" customHeight="1">
-      <c r="A184" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B184" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C184" s="47" t="n"/>
-      <c r="D184" s="18" t="n"/>
-      <c r="E184" s="18" t="n"/>
-      <c r="F184" s="20" t="n"/>
+      <c r="A184" s="43" t="n"/>
+      <c r="B184" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS (NE)</t>
+        </is>
+      </c>
+      <c r="C184" s="18" t="inlineStr">
+        <is>
+          <t>3.38 x 3.00</t>
+        </is>
+      </c>
+      <c r="D184" s="19" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="E184" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F184" s="80" t="n">
+        <v>202.8</v>
+      </c>
       <c r="G184" s="53" t="n"/>
     </row>
     <row r="185" ht="19.8" customHeight="1">
-      <c r="A185" s="43" t="n"/>
-      <c r="B185" s="79" t="inlineStr">
-        <is>
-          <t>AISLADAS (NE)</t>
-        </is>
-      </c>
-      <c r="C185" s="18" t="inlineStr">
-        <is>
-          <t>3.38 x 3.00</t>
-        </is>
-      </c>
-      <c r="D185" s="19" t="n">
-        <v>10.14</v>
-      </c>
+      <c r="A185" s="47" t="n"/>
+      <c r="B185" s="81" t="inlineStr">
+        <is>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C185" s="18" t="n"/>
+      <c r="D185" s="19" t="n"/>
       <c r="E185" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F185" s="80" t="n">
-        <v>202.8</v>
-      </c>
+      <c r="F185" s="80" t="n"/>
       <c r="G185" s="53" t="n"/>
     </row>
     <row r="186" ht="19.8" customHeight="1">
       <c r="A186" s="47" t="n"/>
       <c r="B186" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C186" s="18" t="n"/>
-      <c r="D186" s="19" t="n"/>
+          <t>INTERIORES (NO, bano visitas)</t>
+        </is>
+      </c>
+      <c r="C186" s="18" t="inlineStr">
+        <is>
+          <t>1.72 x 3.00</t>
+        </is>
+      </c>
+      <c r="D186" s="19" t="n">
+        <v>5.16</v>
+      </c>
       <c r="E186" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F186" s="80" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="F186" s="80" t="n">
+        <v>129</v>
+      </c>
       <c r="G186" s="53" t="n"/>
     </row>
     <row r="187" ht="19.8" customHeight="1">
       <c r="A187" s="47" t="n"/>
       <c r="B187" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (NO, bano visitas)</t>
+          <t>INTERIORES (SO)</t>
         </is>
       </c>
       <c r="C187" s="18" t="inlineStr">
         <is>
-          <t>1.72 x 3.00</t>
+          <t>3.38 x 3.00</t>
         </is>
       </c>
       <c r="D187" s="19" t="n">
-        <v>5.16</v>
+        <v>10.14</v>
       </c>
       <c r="E187" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F187" s="80" t="n">
-        <v>129</v>
+        <v>253.5</v>
       </c>
       <c r="G187" s="53" t="n"/>
     </row>
     <row r="188" ht="19.8" customHeight="1">
-      <c r="A188" s="47" t="n"/>
-      <c r="B188" s="81" t="inlineStr">
-        <is>
-          <t>INTERIORES (SO)</t>
+      <c r="A188" s="50" t="n"/>
+      <c r="B188" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES (SE, dormitorio suite)</t>
         </is>
       </c>
       <c r="C188" s="18" t="inlineStr">
         <is>
-          <t>3.38 x 3.00</t>
+          <t>1.72 x 3.00</t>
         </is>
       </c>
       <c r="D188" s="19" t="n">
-        <v>10.14</v>
+        <v>5.16</v>
       </c>
       <c r="E188" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F188" s="80" t="n">
-        <v>253.5</v>
+        <v>129</v>
       </c>
       <c r="G188" s="53" t="n"/>
     </row>
     <row r="189" ht="19.8" customHeight="1">
-      <c r="A189" s="50" t="n"/>
-      <c r="B189" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES (SE, dormitorio suite)</t>
-        </is>
-      </c>
-      <c r="C189" s="18" t="inlineStr">
-        <is>
-          <t>1.72 x 3.00</t>
-        </is>
-      </c>
-      <c r="D189" s="19" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="E189" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F189" s="80" t="n">
-        <v>129</v>
-      </c>
+      <c r="A189" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B189" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C189" s="47" t="n"/>
+      <c r="D189" s="18" t="n"/>
+      <c r="E189" s="18" t="n"/>
+      <c r="F189" s="20" t="n"/>
       <c r="G189" s="53" t="n"/>
     </row>
     <row r="190" ht="19.8" customHeight="1">
-      <c r="A190" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B190" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C190" s="47" t="n"/>
-      <c r="D190" s="18" t="n"/>
-      <c r="E190" s="18" t="n"/>
-      <c r="F190" s="20" t="n"/>
+      <c r="A190" s="43" t="n"/>
+      <c r="B190" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C190" s="18" t="n"/>
+      <c r="D190" s="19" t="n"/>
+      <c r="E190" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F190" s="80" t="n"/>
       <c r="G190" s="53" t="n"/>
     </row>
     <row r="191" ht="19.8" customHeight="1">
-      <c r="A191" s="43" t="n"/>
-      <c r="B191" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
+      <c r="A191" s="47" t="n"/>
+      <c r="B191" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C191" s="18" t="n"/>
       <c r="D191" s="19" t="n"/>
       <c r="E191" s="59" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F191" s="80" t="n"/>
       <c r="G191" s="53" t="n"/>
     </row>
     <row r="192" ht="19.8" customHeight="1">
-      <c r="A192" s="47" t="n"/>
-      <c r="B192" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C192" s="18" t="n"/>
-      <c r="D192" s="19" t="n"/>
+      <c r="A192" s="50" t="n"/>
+      <c r="B192" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C192" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D192" s="19" t="n">
+        <v>5.81</v>
+      </c>
       <c r="E192" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F192" s="80" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="F192" s="80" t="n">
+        <v>87.2</v>
+      </c>
       <c r="G192" s="53" t="n"/>
     </row>
     <row r="193" ht="19.8" customHeight="1">
-      <c r="A193" s="50" t="n"/>
-      <c r="B193" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C193" s="18" t="inlineStr">
+      <c r="A193" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B193" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C193" s="47" t="n"/>
+      <c r="D193" s="18" t="n"/>
+      <c r="E193" s="18" t="n"/>
+      <c r="F193" s="20" t="n"/>
+      <c r="G193" s="53" t="n"/>
+    </row>
+    <row r="194" ht="19.8" customHeight="1">
+      <c r="A194" s="43" t="n"/>
+      <c r="B194" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C194" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D193" s="19" t="n">
+      <c r="D194" s="19" t="n">
         <v>5.81</v>
       </c>
-      <c r="E193" s="59" t="n">
+      <c r="E194" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F194" s="80" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="G194" s="53" t="n"/>
+    </row>
+    <row r="195" ht="19.8" customHeight="1">
+      <c r="A195" s="50" t="n"/>
+      <c r="B195" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C195" s="18" t="n"/>
+      <c r="D195" s="24" t="n"/>
+      <c r="E195" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F193" s="80" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="G193" s="53" t="n"/>
-    </row>
-    <row r="194" ht="19.8" customHeight="1">
-      <c r="A194" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B194" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C194" s="47" t="n"/>
-      <c r="D194" s="18" t="n"/>
-      <c r="E194" s="18" t="n"/>
-      <c r="F194" s="20" t="n"/>
-      <c r="G194" s="53" t="n"/>
-    </row>
-    <row r="195" ht="19.8" customHeight="1">
-      <c r="A195" s="43" t="n"/>
-      <c r="B195" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C195" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D195" s="19" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="E195" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F195" s="80" t="n">
-        <v>58.1</v>
-      </c>
+      <c r="F195" s="80" t="n"/>
       <c r="G195" s="53" t="n"/>
     </row>
     <row r="196" ht="19.8" customHeight="1">
-      <c r="A196" s="50" t="n"/>
-      <c r="B196" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C196" s="18" t="n"/>
-      <c r="D196" s="24" t="n"/>
-      <c r="E196" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F196" s="80" t="n"/>
+      <c r="A196" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B196" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C196" s="83" t="n"/>
+      <c r="D196" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E196" s="47" t="n"/>
+      <c r="F196" s="20" t="n"/>
       <c r="G196" s="53" t="n"/>
     </row>
     <row r="197" ht="19.8" customHeight="1">
-      <c r="A197" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B197" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C197" s="83" t="n"/>
-      <c r="D197" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E197" s="47" t="n"/>
-      <c r="F197" s="20" t="n"/>
+      <c r="A197" s="43" t="n"/>
+      <c r="B197" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C197" s="18" t="inlineStr">
+        <is>
+          <t>5.81 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D197" s="22" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="E197" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F197" s="80" t="n">
+        <v>104.6</v>
+      </c>
       <c r="G197" s="53" t="n"/>
     </row>
     <row r="198" ht="19.8" customHeight="1">
-      <c r="A198" s="43" t="n"/>
-      <c r="B198" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C198" s="18" t="inlineStr">
-        <is>
-          <t>5.81 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D198" s="22" t="n">
-        <v>17.43</v>
-      </c>
+      <c r="A198" s="47" t="n"/>
+      <c r="B198" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C198" s="18" t="n"/>
+      <c r="D198" s="19" t="n"/>
       <c r="E198" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F198" s="80" t="n">
-        <v>104.6</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F198" s="80" t="n"/>
       <c r="G198" s="53" t="n"/>
     </row>
     <row r="199" ht="19.8" customHeight="1">
-      <c r="A199" s="47" t="n"/>
-      <c r="B199" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
+      <c r="A199" s="50" t="n"/>
+      <c r="B199" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C199" s="18" t="n"/>
       <c r="D199" s="19" t="n"/>
       <c r="E199" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F199" s="80" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="F199" s="84" t="n"/>
       <c r="G199" s="53" t="n"/>
     </row>
     <row r="200" ht="19.8" customHeight="1">
-      <c r="A200" s="50" t="n"/>
-      <c r="B200" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C200" s="18" t="n"/>
-      <c r="D200" s="19" t="n"/>
-      <c r="E200" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F200" s="84" t="n"/>
+      <c r="A200" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B200" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C200" s="47" t="n"/>
+      <c r="D200" s="18" t="n"/>
+      <c r="E200" s="20" t="n"/>
+      <c r="F200" s="85" t="n">
+        <v>1060.8</v>
+      </c>
       <c r="G200" s="53" t="n"/>
     </row>
     <row r="201" ht="19.8" customHeight="1">
       <c r="A201" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B201" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C201" s="47" t="n"/>
-      <c r="D201" s="18" t="n"/>
-      <c r="E201" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C201" s="47" t="inlineStr">
+        <is>
+          <t>1060.80  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D201" s="12" t="n"/>
+      <c r="E201" s="14" t="n"/>
       <c r="F201" s="85" t="n">
-        <v>1060.8</v>
+        <v>1135.1</v>
       </c>
       <c r="G201" s="53" t="n"/>
     </row>
     <row r="202" ht="19.8" customHeight="1">
-      <c r="A202" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B202" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C202" s="47" t="inlineStr">
-        <is>
-          <t>1060.80  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A202" s="43" t="n"/>
+      <c r="B202" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C202" s="18" t="n"/>
       <c r="D202" s="12" t="n"/>
-      <c r="E202" s="14" t="n"/>
-      <c r="F202" s="85" t="n">
+      <c r="E202" s="39" t="n"/>
+      <c r="F202" s="87" t="n"/>
+      <c r="G202" s="53" t="n"/>
+    </row>
+    <row r="203" ht="19.8" customHeight="1">
+      <c r="A203" s="83" t="n"/>
+      <c r="B203" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C203" s="47" t="n"/>
+      <c r="D203" s="12" t="n"/>
+      <c r="E203" s="14" t="n"/>
+      <c r="F203" s="85" t="n">
         <v>1135.1</v>
       </c>
-      <c r="G202" s="53" t="n"/>
-    </row>
-    <row r="203" ht="19.8" customHeight="1">
-      <c r="A203" s="43" t="n"/>
-      <c r="B203" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C203" s="18" t="n"/>
-      <c r="D203" s="12" t="n"/>
-      <c r="E203" s="39" t="n"/>
-      <c r="F203" s="87" t="n"/>
       <c r="G203" s="53" t="n"/>
     </row>
     <row r="204" ht="19.8" customHeight="1">
-      <c r="A204" s="83" t="n"/>
-      <c r="B204" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C204" s="47" t="n"/>
+      <c r="A204" s="47" t="n"/>
+      <c r="B204" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C204" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D204" s="12" t="n"/>
-      <c r="E204" s="14" t="n"/>
-      <c r="F204" s="85" t="n">
-        <v>1135.1</v>
-      </c>
+      <c r="E204" s="39" t="n"/>
+      <c r="F204" s="61" t="n"/>
       <c r="G204" s="53" t="n"/>
     </row>
     <row r="205" ht="19.8" customHeight="1">
       <c r="A205" s="47" t="n"/>
-      <c r="B205" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C205" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B205" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
+        </is>
+      </c>
+      <c r="C205" s="59" t="n">
+        <v>708</v>
       </c>
       <c r="D205" s="12" t="n"/>
       <c r="E205" s="39" t="n"/>
-      <c r="F205" s="61" t="n"/>
+      <c r="F205" s="20" t="n"/>
       <c r="G205" s="53" t="n"/>
     </row>
     <row r="206" ht="19.8" customHeight="1">
       <c r="A206" s="47" t="n"/>
       <c r="B206" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 80</t>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
         </is>
       </c>
       <c r="C206" s="59" t="n">
-        <v>708</v>
+        <v>1315</v>
       </c>
       <c r="D206" s="12" t="n"/>
       <c r="E206" s="39" t="n"/>
@@ -23615,11 +23607,11 @@
       <c r="A207" s="47" t="n"/>
       <c r="B207" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 150</t>
+          <t>Toalleros necesarios</t>
         </is>
       </c>
       <c r="C207" s="59" t="n">
-        <v>1315</v>
+        <v>1</v>
       </c>
       <c r="D207" s="12" t="n"/>
       <c r="E207" s="39" t="n"/>
@@ -23627,14 +23619,16 @@
       <c r="G207" s="53" t="n"/>
     </row>
     <row r="208" ht="19.8" customHeight="1">
-      <c r="A208" s="47" t="n"/>
+      <c r="A208" s="50" t="n"/>
       <c r="B208" s="60" t="inlineStr">
         <is>
-          <t>Toalleros necesarios</t>
-        </is>
-      </c>
-      <c r="C208" s="59" t="n">
-        <v>1</v>
+          <t>Toallero adoptado</t>
+        </is>
+      </c>
+      <c r="C208" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
+        </is>
       </c>
       <c r="D208" s="12" t="n"/>
       <c r="E208" s="39" t="n"/>
@@ -23642,153 +23636,159 @@
       <c r="G208" s="53" t="n"/>
     </row>
     <row r="209" ht="19.8" customHeight="1">
-      <c r="A209" s="50" t="n"/>
-      <c r="B209" s="60" t="inlineStr">
-        <is>
-          <t>Toallero adoptado</t>
-        </is>
-      </c>
-      <c r="C209" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
-        </is>
-      </c>
-      <c r="D209" s="12" t="n"/>
-      <c r="E209" s="39" t="n"/>
-      <c r="F209" s="20" t="n"/>
+      <c r="A209" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  11 - Bano visitas   (PB)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B209" s="11" t="n"/>
+      <c r="C209" s="11" t="n"/>
+      <c r="D209" s="11" t="n"/>
+      <c r="E209" s="11" t="n"/>
+      <c r="F209" s="42" t="n"/>
       <c r="G209" s="53" t="n"/>
     </row>
-    <row r="210" ht="19.8" customHeight="1">
-      <c r="A210" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  11 - Bano visitas   (PB)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B210" s="11" t="n"/>
-      <c r="C210" s="11" t="n"/>
-      <c r="D210" s="11" t="n"/>
-      <c r="E210" s="11" t="n"/>
-      <c r="F210" s="42" t="n"/>
+    <row r="210" ht="32" customHeight="1">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G210" s="53" t="n"/>
     </row>
-    <row r="211" ht="32" customHeight="1">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F211" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="211" ht="19.8" customHeight="1">
+      <c r="A211" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B211" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C211" s="43" t="n"/>
+      <c r="D211" s="58" t="n"/>
+      <c r="E211" s="58" t="n"/>
+      <c r="F211" s="61" t="n"/>
       <c r="G211" s="53" t="n"/>
     </row>
     <row r="212" ht="19.8" customHeight="1">
-      <c r="A212" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B212" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C212" s="43" t="n"/>
-      <c r="D212" s="58" t="n"/>
-      <c r="E212" s="58" t="n"/>
-      <c r="F212" s="61" t="n"/>
+      <c r="A212" s="90" t="n"/>
+      <c r="B212" s="91" t="inlineStr">
+        <is>
+          <t>(sin aberturas)</t>
+        </is>
+      </c>
+      <c r="C212" s="18" t="n"/>
+      <c r="D212" s="19" t="n"/>
+      <c r="E212" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F212" s="80" t="n"/>
       <c r="G212" s="53" t="n"/>
     </row>
     <row r="213" ht="19.8" customHeight="1">
-      <c r="A213" s="90" t="n"/>
-      <c r="B213" s="91" t="inlineStr">
-        <is>
-          <t>(sin aberturas)</t>
-        </is>
-      </c>
-      <c r="C213" s="18" t="n"/>
-      <c r="D213" s="19" t="n"/>
-      <c r="E213" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F213" s="80" t="n"/>
+      <c r="A213" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B213" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C213" s="47" t="n"/>
+      <c r="D213" s="18" t="n"/>
+      <c r="E213" s="18" t="n"/>
+      <c r="F213" s="20" t="n"/>
       <c r="G213" s="53" t="n"/>
     </row>
     <row r="214" ht="19.8" customHeight="1">
-      <c r="A214" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B214" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C214" s="47" t="n"/>
-      <c r="D214" s="18" t="n"/>
-      <c r="E214" s="18" t="n"/>
-      <c r="F214" s="20" t="n"/>
+      <c r="A214" s="43" t="n"/>
+      <c r="B214" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C214" s="18" t="inlineStr">
+        <is>
+          <t>1.30 x 3.00</t>
+        </is>
+      </c>
+      <c r="D214" s="19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E214" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F214" s="80" t="n">
+        <v>78</v>
+      </c>
       <c r="G214" s="53" t="n"/>
     </row>
     <row r="215" ht="19.8" customHeight="1">
-      <c r="A215" s="43" t="n"/>
-      <c r="B215" s="79" t="inlineStr">
+      <c r="A215" s="47" t="n"/>
+      <c r="B215" s="81" t="inlineStr">
         <is>
           <t>AISLADAS</t>
         </is>
       </c>
-      <c r="C215" s="18" t="inlineStr">
-        <is>
-          <t>1.30 x 3.00</t>
-        </is>
-      </c>
-      <c r="D215" s="19" t="n">
-        <v>3.9</v>
-      </c>
+      <c r="C215" s="18" t="n"/>
+      <c r="D215" s="19" t="n"/>
       <c r="E215" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F215" s="80" t="n">
-        <v>78</v>
-      </c>
+      <c r="F215" s="80" t="n"/>
       <c r="G215" s="53" t="n"/>
     </row>
     <row r="216" ht="19.8" customHeight="1">
       <c r="A216" s="47" t="n"/>
       <c r="B216" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C216" s="18" t="n"/>
-      <c r="D216" s="19" t="n"/>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C216" s="18" t="inlineStr">
+        <is>
+          <t>2.40 x 3.00</t>
+        </is>
+      </c>
+      <c r="D216" s="19" t="n">
+        <v>7.2</v>
+      </c>
       <c r="E216" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F216" s="80" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="F216" s="80" t="n">
+        <v>180</v>
+      </c>
       <c r="G216" s="53" t="n"/>
     </row>
     <row r="217" ht="19.8" customHeight="1">
@@ -23815,346 +23815,338 @@
       <c r="G217" s="53" t="n"/>
     </row>
     <row r="218" ht="19.8" customHeight="1">
-      <c r="A218" s="47" t="n"/>
-      <c r="B218" s="81" t="inlineStr">
+      <c r="A218" s="50" t="n"/>
+      <c r="B218" s="82" t="inlineStr">
         <is>
           <t>INTERIORES</t>
         </is>
       </c>
       <c r="C218" s="18" t="inlineStr">
         <is>
-          <t>2.40 x 3.00</t>
+          <t>1.30 x 3.00</t>
         </is>
       </c>
       <c r="D218" s="19" t="n">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="E218" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F218" s="80" t="n">
-        <v>180</v>
+        <v>97.5</v>
       </c>
       <c r="G218" s="53" t="n"/>
     </row>
     <row r="219" ht="19.8" customHeight="1">
-      <c r="A219" s="50" t="n"/>
-      <c r="B219" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C219" s="18" t="inlineStr">
-        <is>
-          <t>1.30 x 3.00</t>
-        </is>
-      </c>
-      <c r="D219" s="19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E219" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F219" s="80" t="n">
-        <v>97.5</v>
-      </c>
+      <c r="A219" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B219" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C219" s="47" t="n"/>
+      <c r="D219" s="18" t="n"/>
+      <c r="E219" s="18" t="n"/>
+      <c r="F219" s="20" t="n"/>
       <c r="G219" s="53" t="n"/>
     </row>
     <row r="220" ht="19.8" customHeight="1">
-      <c r="A220" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B220" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C220" s="47" t="n"/>
-      <c r="D220" s="18" t="n"/>
-      <c r="E220" s="18" t="n"/>
-      <c r="F220" s="20" t="n"/>
+      <c r="A220" s="43" t="n"/>
+      <c r="B220" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C220" s="18" t="n"/>
+      <c r="D220" s="19" t="n"/>
+      <c r="E220" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F220" s="80" t="n"/>
       <c r="G220" s="53" t="n"/>
     </row>
     <row r="221" ht="19.8" customHeight="1">
-      <c r="A221" s="43" t="n"/>
-      <c r="B221" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
+      <c r="A221" s="47" t="n"/>
+      <c r="B221" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C221" s="18" t="n"/>
       <c r="D221" s="19" t="n"/>
       <c r="E221" s="59" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F221" s="80" t="n"/>
       <c r="G221" s="53" t="n"/>
     </row>
     <row r="222" ht="19.8" customHeight="1">
-      <c r="A222" s="47" t="n"/>
-      <c r="B222" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C222" s="18" t="n"/>
-      <c r="D222" s="19" t="n"/>
+      <c r="A222" s="50" t="n"/>
+      <c r="B222" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C222" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D222" s="19" t="n">
+        <v>3.12</v>
+      </c>
       <c r="E222" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F222" s="80" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="F222" s="80" t="n">
+        <v>46.8</v>
+      </c>
       <c r="G222" s="53" t="n"/>
     </row>
     <row r="223" ht="19.8" customHeight="1">
-      <c r="A223" s="50" t="n"/>
-      <c r="B223" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C223" s="18" t="inlineStr">
+      <c r="A223" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B223" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C223" s="47" t="n"/>
+      <c r="D223" s="18" t="n"/>
+      <c r="E223" s="18" t="n"/>
+      <c r="F223" s="20" t="n"/>
+      <c r="G223" s="53" t="n"/>
+    </row>
+    <row r="224" ht="19.8" customHeight="1">
+      <c r="A224" s="43" t="n"/>
+      <c r="B224" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C224" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D223" s="19" t="n">
+      <c r="D224" s="19" t="n">
         <v>3.12</v>
       </c>
-      <c r="E223" s="59" t="n">
+      <c r="E224" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F224" s="80" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="G224" s="53" t="n"/>
+    </row>
+    <row r="225" ht="19.8" customHeight="1">
+      <c r="A225" s="50" t="n"/>
+      <c r="B225" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C225" s="18" t="n"/>
+      <c r="D225" s="24" t="n"/>
+      <c r="E225" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F223" s="80" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="G223" s="53" t="n"/>
-    </row>
-    <row r="224" ht="19.8" customHeight="1">
-      <c r="A224" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B224" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C224" s="47" t="n"/>
-      <c r="D224" s="18" t="n"/>
-      <c r="E224" s="18" t="n"/>
-      <c r="F224" s="20" t="n"/>
-      <c r="G224" s="53" t="n"/>
-    </row>
-    <row r="225" ht="19.8" customHeight="1">
-      <c r="A225" s="43" t="n"/>
-      <c r="B225" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C225" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D225" s="19" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E225" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F225" s="80" t="n">
-        <v>31.2</v>
-      </c>
+      <c r="F225" s="80" t="n"/>
       <c r="G225" s="53" t="n"/>
     </row>
     <row r="226" ht="19.8" customHeight="1">
-      <c r="A226" s="50" t="n"/>
-      <c r="B226" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C226" s="18" t="n"/>
-      <c r="D226" s="24" t="n"/>
-      <c r="E226" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F226" s="80" t="n"/>
+      <c r="A226" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B226" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C226" s="83" t="n"/>
+      <c r="D226" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E226" s="47" t="n"/>
+      <c r="F226" s="20" t="n"/>
       <c r="G226" s="53" t="n"/>
     </row>
     <row r="227" ht="19.8" customHeight="1">
-      <c r="A227" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B227" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C227" s="83" t="n"/>
-      <c r="D227" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E227" s="47" t="n"/>
-      <c r="F227" s="20" t="n"/>
+      <c r="A227" s="43" t="n"/>
+      <c r="B227" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C227" s="18" t="inlineStr">
+        <is>
+          <t>3.12 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D227" s="22" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="E227" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F227" s="80" t="n">
+        <v>56.2</v>
+      </c>
       <c r="G227" s="53" t="n"/>
     </row>
     <row r="228" ht="19.8" customHeight="1">
-      <c r="A228" s="43" t="n"/>
-      <c r="B228" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C228" s="18" t="inlineStr">
-        <is>
-          <t>3.12 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D228" s="22" t="n">
-        <v>9.359999999999999</v>
-      </c>
+      <c r="A228" s="47" t="n"/>
+      <c r="B228" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C228" s="18" t="n"/>
+      <c r="D228" s="19" t="n"/>
       <c r="E228" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F228" s="80" t="n">
-        <v>56.2</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F228" s="80" t="n"/>
       <c r="G228" s="53" t="n"/>
     </row>
     <row r="229" ht="19.8" customHeight="1">
-      <c r="A229" s="47" t="n"/>
-      <c r="B229" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
+      <c r="A229" s="50" t="n"/>
+      <c r="B229" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C229" s="18" t="n"/>
       <c r="D229" s="19" t="n"/>
       <c r="E229" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F229" s="80" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="F229" s="84" t="n"/>
       <c r="G229" s="53" t="n"/>
     </row>
     <row r="230" ht="19.8" customHeight="1">
-      <c r="A230" s="50" t="n"/>
-      <c r="B230" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C230" s="18" t="n"/>
-      <c r="D230" s="19" t="n"/>
-      <c r="E230" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F230" s="84" t="n"/>
+      <c r="A230" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B230" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C230" s="47" t="n"/>
+      <c r="D230" s="18" t="n"/>
+      <c r="E230" s="20" t="n"/>
+      <c r="F230" s="85" t="n">
+        <v>669.7</v>
+      </c>
       <c r="G230" s="53" t="n"/>
     </row>
     <row r="231" ht="19.8" customHeight="1">
       <c r="A231" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B231" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C231" s="47" t="n"/>
-      <c r="D231" s="18" t="n"/>
-      <c r="E231" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C231" s="47" t="inlineStr">
+        <is>
+          <t>669.70  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D231" s="12" t="n"/>
+      <c r="E231" s="14" t="n"/>
       <c r="F231" s="85" t="n">
-        <v>669.7</v>
+        <v>716.6</v>
       </c>
       <c r="G231" s="53" t="n"/>
     </row>
     <row r="232" ht="19.8" customHeight="1">
-      <c r="A232" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B232" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C232" s="47" t="inlineStr">
-        <is>
-          <t>669.70  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A232" s="43" t="n"/>
+      <c r="B232" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C232" s="18" t="n"/>
       <c r="D232" s="12" t="n"/>
-      <c r="E232" s="14" t="n"/>
-      <c r="F232" s="85" t="n">
+      <c r="E232" s="39" t="n"/>
+      <c r="F232" s="87" t="n"/>
+      <c r="G232" s="53" t="n"/>
+    </row>
+    <row r="233" ht="19.8" customHeight="1">
+      <c r="A233" s="83" t="n"/>
+      <c r="B233" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C233" s="47" t="n"/>
+      <c r="D233" s="12" t="n"/>
+      <c r="E233" s="14" t="n"/>
+      <c r="F233" s="85" t="n">
         <v>716.6</v>
       </c>
-      <c r="G232" s="53" t="n"/>
-    </row>
-    <row r="233" ht="19.8" customHeight="1">
-      <c r="A233" s="43" t="n"/>
-      <c r="B233" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C233" s="18" t="n"/>
-      <c r="D233" s="12" t="n"/>
-      <c r="E233" s="39" t="n"/>
-      <c r="F233" s="87" t="n"/>
       <c r="G233" s="53" t="n"/>
     </row>
     <row r="234" ht="19.8" customHeight="1">
-      <c r="A234" s="83" t="n"/>
-      <c r="B234" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C234" s="47" t="n"/>
+      <c r="A234" s="47" t="n"/>
+      <c r="B234" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C234" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D234" s="12" t="n"/>
-      <c r="E234" s="14" t="n"/>
-      <c r="F234" s="85" t="n">
-        <v>716.6</v>
-      </c>
+      <c r="E234" s="39" t="n"/>
+      <c r="F234" s="61" t="n"/>
       <c r="G234" s="53" t="n"/>
     </row>
     <row r="235" ht="19.8" customHeight="1">
       <c r="A235" s="47" t="n"/>
-      <c r="B235" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C235" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B235" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
+        </is>
+      </c>
+      <c r="C235" s="59" t="n">
+        <v>708</v>
       </c>
       <c r="D235" s="12" t="n"/>
       <c r="E235" s="39" t="n"/>
-      <c r="F235" s="61" t="n"/>
+      <c r="F235" s="20" t="n"/>
       <c r="G235" s="53" t="n"/>
     </row>
     <row r="236" ht="19.8" customHeight="1">
       <c r="A236" s="47" t="n"/>
       <c r="B236" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 80</t>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
         </is>
       </c>
       <c r="C236" s="59" t="n">
-        <v>708</v>
+        <v>1315</v>
       </c>
       <c r="D236" s="12" t="n"/>
       <c r="E236" s="39" t="n"/>
@@ -24165,11 +24157,11 @@
       <c r="A237" s="47" t="n"/>
       <c r="B237" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 150</t>
+          <t>Toalleros necesarios</t>
         </is>
       </c>
       <c r="C237" s="59" t="n">
-        <v>1315</v>
+        <v>1</v>
       </c>
       <c r="D237" s="12" t="n"/>
       <c r="E237" s="39" t="n"/>
@@ -24177,14 +24169,16 @@
       <c r="G237" s="53" t="n"/>
     </row>
     <row r="238" ht="19.8" customHeight="1">
-      <c r="A238" s="47" t="n"/>
+      <c r="A238" s="50" t="n"/>
       <c r="B238" s="60" t="inlineStr">
         <is>
-          <t>Toalleros necesarios</t>
-        </is>
-      </c>
-      <c r="C238" s="59" t="n">
-        <v>1</v>
+          <t>Toallero adoptado</t>
+        </is>
+      </c>
+      <c r="C238" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
+        </is>
       </c>
       <c r="D238" s="12" t="n"/>
       <c r="E238" s="39" t="n"/>
@@ -24192,153 +24186,159 @@
       <c r="G238" s="53" t="n"/>
     </row>
     <row r="239" ht="19.8" customHeight="1">
-      <c r="A239" s="50" t="n"/>
-      <c r="B239" s="60" t="inlineStr">
-        <is>
-          <t>Toallero adoptado</t>
-        </is>
-      </c>
-      <c r="C239" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
-        </is>
-      </c>
-      <c r="D239" s="12" t="n"/>
-      <c r="E239" s="39" t="n"/>
-      <c r="F239" s="20" t="n"/>
+      <c r="A239" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  13 - Dormitorio Norte   (PA)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B239" s="11" t="n"/>
+      <c r="C239" s="11" t="n"/>
+      <c r="D239" s="11" t="n"/>
+      <c r="E239" s="11" t="n"/>
+      <c r="F239" s="42" t="n"/>
       <c r="G239" s="53" t="n"/>
     </row>
-    <row r="240" ht="19.8" customHeight="1">
-      <c r="A240" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  13 - Dormitorio Norte   (PA)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B240" s="11" t="n"/>
-      <c r="C240" s="11" t="n"/>
-      <c r="D240" s="11" t="n"/>
-      <c r="E240" s="11" t="n"/>
-      <c r="F240" s="42" t="n"/>
+    <row r="240" ht="32" customHeight="1">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G240" s="53" t="n"/>
     </row>
-    <row r="241" ht="32" customHeight="1">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E241" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F241" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="241" ht="19.8" customHeight="1">
+      <c r="A241" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B241" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C241" s="43" t="n"/>
+      <c r="D241" s="58" t="n"/>
+      <c r="E241" s="58" t="n"/>
+      <c r="F241" s="61" t="n"/>
       <c r="G241" s="53" t="n"/>
     </row>
     <row r="242" ht="19.8" customHeight="1">
-      <c r="A242" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B242" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C242" s="43" t="n"/>
-      <c r="D242" s="58" t="n"/>
-      <c r="E242" s="58" t="n"/>
-      <c r="F242" s="61" t="n"/>
+      <c r="A242" s="43" t="n"/>
+      <c r="B242" s="79" t="inlineStr">
+        <is>
+          <t>VA04</t>
+        </is>
+      </c>
+      <c r="C242" s="18" t="inlineStr">
+        <is>
+          <t>2.00 x 2.52</t>
+        </is>
+      </c>
+      <c r="D242" s="19" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="E242" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F242" s="80" t="n">
+        <v>302.4</v>
+      </c>
       <c r="G242" s="53" t="n"/>
     </row>
     <row r="243" ht="19.8" customHeight="1">
-      <c r="A243" s="43" t="n"/>
-      <c r="B243" s="79" t="inlineStr">
-        <is>
-          <t>VA04</t>
+      <c r="A243" s="50" t="n"/>
+      <c r="B243" s="82" t="inlineStr">
+        <is>
+          <t>VA05</t>
         </is>
       </c>
       <c r="C243" s="18" t="inlineStr">
         <is>
-          <t>2.00 x 2.52</t>
+          <t>1.40 x 2.52</t>
         </is>
       </c>
       <c r="D243" s="19" t="n">
-        <v>5.04</v>
+        <v>3.53</v>
       </c>
       <c r="E243" s="59" t="n">
         <v>60</v>
       </c>
       <c r="F243" s="80" t="n">
-        <v>302.4</v>
+        <v>211.8</v>
       </c>
       <c r="G243" s="53" t="n"/>
     </row>
     <row r="244" ht="19.8" customHeight="1">
-      <c r="A244" s="50" t="n"/>
-      <c r="B244" s="82" t="inlineStr">
-        <is>
-          <t>VA05</t>
-        </is>
-      </c>
-      <c r="C244" s="18" t="inlineStr">
-        <is>
-          <t>1.40 x 2.52</t>
-        </is>
-      </c>
-      <c r="D244" s="19" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="E244" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F244" s="80" t="n">
-        <v>211.8</v>
-      </c>
+      <c r="A244" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B244" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C244" s="47" t="n"/>
+      <c r="D244" s="18" t="n"/>
+      <c r="E244" s="18" t="n"/>
+      <c r="F244" s="20" t="n"/>
       <c r="G244" s="53" t="n"/>
     </row>
     <row r="245" ht="19.8" customHeight="1">
-      <c r="A245" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B245" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C245" s="47" t="n"/>
-      <c r="D245" s="18" t="n"/>
-      <c r="E245" s="18" t="n"/>
-      <c r="F245" s="20" t="n"/>
+      <c r="A245" s="43" t="n"/>
+      <c r="B245" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS (NO)</t>
+        </is>
+      </c>
+      <c r="C245" s="18" t="inlineStr">
+        <is>
+          <t>4.25 x 3.00</t>
+        </is>
+      </c>
+      <c r="D245" s="19" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="E245" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F245" s="80" t="n">
+        <v>255</v>
+      </c>
       <c r="G245" s="53" t="n"/>
     </row>
     <row r="246" ht="19.8" customHeight="1">
-      <c r="A246" s="43" t="n"/>
-      <c r="B246" s="79" t="inlineStr">
-        <is>
-          <t>AISLADAS (NO)</t>
+      <c r="A246" s="47" t="n"/>
+      <c r="B246" s="81" t="inlineStr">
+        <is>
+          <t>AISLADAS (SE)</t>
         </is>
       </c>
       <c r="C246" s="18" t="inlineStr">
@@ -24361,22 +24361,22 @@
       <c r="A247" s="47" t="n"/>
       <c r="B247" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (SE)</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C247" s="18" t="inlineStr">
         <is>
-          <t>4.25 x 3.00</t>
+          <t>4.00 x 3.00</t>
         </is>
       </c>
       <c r="D247" s="19" t="n">
-        <v>12.75</v>
+        <v>12</v>
       </c>
       <c r="E247" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F247" s="80" t="n">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="G247" s="53" t="n"/>
     </row>
@@ -24384,7 +24384,7 @@
       <c r="A248" s="47" t="n"/>
       <c r="B248" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C248" s="18" t="inlineStr">
@@ -24396,346 +24396,338 @@
         <v>12</v>
       </c>
       <c r="E248" s="59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F248" s="80" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="G248" s="53" t="n"/>
     </row>
     <row r="249" ht="19.8" customHeight="1">
-      <c r="A249" s="47" t="n"/>
-      <c r="B249" s="81" t="inlineStr">
+      <c r="A249" s="50" t="n"/>
+      <c r="B249" s="82" t="inlineStr">
         <is>
           <t>INTERIORES</t>
         </is>
       </c>
-      <c r="C249" s="18" t="inlineStr">
-        <is>
-          <t>4.00 x 3.00</t>
-        </is>
-      </c>
-      <c r="D249" s="19" t="n">
-        <v>12</v>
-      </c>
+      <c r="C249" s="18" t="n"/>
+      <c r="D249" s="19" t="n"/>
       <c r="E249" s="59" t="n">
         <v>25</v>
       </c>
-      <c r="F249" s="80" t="n">
-        <v>300</v>
-      </c>
+      <c r="F249" s="80" t="n"/>
       <c r="G249" s="53" t="n"/>
     </row>
     <row r="250" ht="19.8" customHeight="1">
-      <c r="A250" s="50" t="n"/>
-      <c r="B250" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C250" s="18" t="n"/>
-      <c r="D250" s="19" t="n"/>
-      <c r="E250" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F250" s="80" t="n"/>
+      <c r="A250" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B250" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C250" s="47" t="n"/>
+      <c r="D250" s="18" t="n"/>
+      <c r="E250" s="18" t="n"/>
+      <c r="F250" s="20" t="n"/>
       <c r="G250" s="53" t="n"/>
     </row>
     <row r="251" ht="19.8" customHeight="1">
-      <c r="A251" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B251" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C251" s="47" t="n"/>
-      <c r="D251" s="18" t="n"/>
-      <c r="E251" s="18" t="n"/>
-      <c r="F251" s="20" t="n"/>
+      <c r="A251" s="43" t="n"/>
+      <c r="B251" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C251" s="18" t="n"/>
+      <c r="D251" s="19" t="n"/>
+      <c r="E251" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F251" s="80" t="n"/>
       <c r="G251" s="53" t="n"/>
     </row>
     <row r="252" ht="19.8" customHeight="1">
-      <c r="A252" s="43" t="n"/>
-      <c r="B252" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C252" s="18" t="n"/>
-      <c r="D252" s="19" t="n"/>
+      <c r="A252" s="47" t="n"/>
+      <c r="B252" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C252" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D252" s="19" t="n">
+        <v>17</v>
+      </c>
       <c r="E252" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F252" s="80" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F252" s="80" t="n">
+        <v>340</v>
+      </c>
       <c r="G252" s="53" t="n"/>
     </row>
     <row r="253" ht="19.8" customHeight="1">
-      <c r="A253" s="47" t="n"/>
-      <c r="B253" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C253" s="18" t="inlineStr">
+      <c r="A253" s="50" t="n"/>
+      <c r="B253" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C253" s="18" t="n"/>
+      <c r="D253" s="19" t="n"/>
+      <c r="E253" s="59" t="n">
+        <v>15</v>
+      </c>
+      <c r="F253" s="80" t="n"/>
+      <c r="G253" s="53" t="n"/>
+    </row>
+    <row r="254" ht="19.8" customHeight="1">
+      <c r="A254" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B254" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C254" s="47" t="n"/>
+      <c r="D254" s="18" t="n"/>
+      <c r="E254" s="18" t="n"/>
+      <c r="F254" s="20" t="n"/>
+      <c r="G254" s="53" t="n"/>
+    </row>
+    <row r="255" ht="19.8" customHeight="1">
+      <c r="A255" s="43" t="n"/>
+      <c r="B255" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C255" s="18" t="n"/>
+      <c r="D255" s="19" t="n"/>
+      <c r="E255" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F255" s="80" t="n"/>
+      <c r="G255" s="53" t="n"/>
+    </row>
+    <row r="256" ht="19.8" customHeight="1">
+      <c r="A256" s="50" t="n"/>
+      <c r="B256" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C256" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D253" s="19" t="n">
+      <c r="D256" s="24" t="n">
         <v>17</v>
       </c>
-      <c r="E253" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F253" s="80" t="n">
-        <v>340</v>
-      </c>
-      <c r="G253" s="53" t="n"/>
-    </row>
-    <row r="254" ht="19.8" customHeight="1">
-      <c r="A254" s="50" t="n"/>
-      <c r="B254" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C254" s="18" t="n"/>
-      <c r="D254" s="19" t="n"/>
-      <c r="E254" s="59" t="n">
+      <c r="E256" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F254" s="80" t="n"/>
-      <c r="G254" s="53" t="n"/>
-    </row>
-    <row r="255" ht="19.8" customHeight="1">
-      <c r="A255" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B255" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C255" s="47" t="n"/>
-      <c r="D255" s="18" t="n"/>
-      <c r="E255" s="18" t="n"/>
-      <c r="F255" s="20" t="n"/>
-      <c r="G255" s="53" t="n"/>
-    </row>
-    <row r="256" ht="19.8" customHeight="1">
-      <c r="A256" s="43" t="n"/>
-      <c r="B256" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C256" s="18" t="n"/>
-      <c r="D256" s="19" t="n"/>
-      <c r="E256" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F256" s="80" t="n"/>
+      <c r="F256" s="80" t="n">
+        <v>255</v>
+      </c>
       <c r="G256" s="53" t="n"/>
     </row>
     <row r="257" ht="19.8" customHeight="1">
-      <c r="A257" s="50" t="n"/>
-      <c r="B257" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C257" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D257" s="24" t="n">
-        <v>17</v>
-      </c>
-      <c r="E257" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F257" s="80" t="n">
-        <v>255</v>
-      </c>
+      <c r="A257" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B257" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C257" s="83" t="n"/>
+      <c r="D257" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E257" s="47" t="n"/>
+      <c r="F257" s="20" t="n"/>
       <c r="G257" s="53" t="n"/>
     </row>
     <row r="258" ht="19.8" customHeight="1">
-      <c r="A258" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B258" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C258" s="83" t="n"/>
-      <c r="D258" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E258" s="47" t="n"/>
-      <c r="F258" s="20" t="n"/>
+      <c r="A258" s="43" t="n"/>
+      <c r="B258" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C258" s="18" t="n"/>
+      <c r="D258" s="22" t="n"/>
+      <c r="E258" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F258" s="80" t="n"/>
       <c r="G258" s="53" t="n"/>
     </row>
     <row r="259" ht="19.8" customHeight="1">
-      <c r="A259" s="43" t="n"/>
-      <c r="B259" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
+      <c r="A259" s="47" t="n"/>
+      <c r="B259" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C259" s="18" t="n"/>
-      <c r="D259" s="22" t="n"/>
+      <c r="D259" s="19" t="n"/>
       <c r="E259" s="59" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F259" s="80" t="n"/>
       <c r="G259" s="53" t="n"/>
     </row>
     <row r="260" ht="19.8" customHeight="1">
-      <c r="A260" s="47" t="n"/>
-      <c r="B260" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C260" s="18" t="n"/>
-      <c r="D260" s="19" t="n"/>
+      <c r="A260" s="50" t="n"/>
+      <c r="B260" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C260" s="18" t="inlineStr">
+        <is>
+          <t>17.00 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D260" s="19" t="n">
+        <v>51</v>
+      </c>
       <c r="E260" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F260" s="80" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="F260" s="84" t="n">
+        <v>612</v>
+      </c>
       <c r="G260" s="53" t="n"/>
     </row>
     <row r="261" ht="19.8" customHeight="1">
-      <c r="A261" s="50" t="n"/>
-      <c r="B261" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C261" s="18" t="inlineStr">
-        <is>
-          <t>17.00 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D261" s="19" t="n">
-        <v>51</v>
-      </c>
-      <c r="E261" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F261" s="84" t="n">
-        <v>612</v>
+      <c r="A261" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B261" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C261" s="47" t="n"/>
+      <c r="D261" s="18" t="n"/>
+      <c r="E261" s="20" t="n"/>
+      <c r="F261" s="85" t="n">
+        <v>2771.2</v>
       </c>
       <c r="G261" s="53" t="n"/>
     </row>
     <row r="262" ht="19.8" customHeight="1">
       <c r="A262" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B262" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C262" s="47" t="n"/>
-      <c r="D262" s="18" t="n"/>
-      <c r="E262" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C262" s="47" t="inlineStr">
+        <is>
+          <t>2771.20  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D262" s="12" t="n"/>
+      <c r="E262" s="14" t="n"/>
       <c r="F262" s="85" t="n">
-        <v>2771.2</v>
+        <v>2965.2</v>
       </c>
       <c r="G262" s="53" t="n"/>
     </row>
     <row r="263" ht="19.8" customHeight="1">
-      <c r="A263" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B263" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C263" s="47" t="inlineStr">
-        <is>
-          <t>2771.20  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A263" s="43" t="n"/>
+      <c r="B263" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C263" s="18" t="n"/>
       <c r="D263" s="12" t="n"/>
-      <c r="E263" s="14" t="n"/>
-      <c r="F263" s="85" t="n">
+      <c r="E263" s="39" t="n"/>
+      <c r="F263" s="87" t="n"/>
+      <c r="G263" s="53" t="n"/>
+    </row>
+    <row r="264" ht="19.8" customHeight="1">
+      <c r="A264" s="83" t="n"/>
+      <c r="B264" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C264" s="47" t="n"/>
+      <c r="D264" s="12" t="n"/>
+      <c r="E264" s="14" t="n"/>
+      <c r="F264" s="85" t="n">
         <v>2965.2</v>
       </c>
-      <c r="G263" s="53" t="n"/>
-    </row>
-    <row r="264" ht="19.8" customHeight="1">
-      <c r="A264" s="43" t="n"/>
-      <c r="B264" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C264" s="18" t="n"/>
-      <c r="D264" s="12" t="n"/>
-      <c r="E264" s="39" t="n"/>
-      <c r="F264" s="87" t="n"/>
       <c r="G264" s="53" t="n"/>
     </row>
     <row r="265" ht="19.8" customHeight="1">
-      <c r="A265" s="83" t="n"/>
-      <c r="B265" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C265" s="47" t="n"/>
+      <c r="A265" s="47" t="n"/>
+      <c r="B265" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C265" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D265" s="12" t="n"/>
-      <c r="E265" s="14" t="n"/>
-      <c r="F265" s="85" t="n">
-        <v>2965.2</v>
-      </c>
+      <c r="E265" s="39" t="n"/>
+      <c r="F265" s="61" t="n"/>
       <c r="G265" s="53" t="n"/>
     </row>
     <row r="266" ht="19.8" customHeight="1">
       <c r="A266" s="47" t="n"/>
-      <c r="B266" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C266" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B266" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C266" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D266" s="12" t="n"/>
       <c r="E266" s="39" t="n"/>
-      <c r="F266" s="61" t="n"/>
+      <c r="F266" s="20" t="n"/>
       <c r="G266" s="53" t="n"/>
     </row>
     <row r="267" ht="19.8" customHeight="1">
       <c r="A267" s="47" t="n"/>
       <c r="B267" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C267" s="19" t="n">
-        <v>274.4</v>
+          <t>Elementos necesarios</t>
+        </is>
+      </c>
+      <c r="C267" s="59" t="n">
+        <v>11</v>
       </c>
       <c r="D267" s="12" t="n"/>
       <c r="E267" s="39" t="n"/>
@@ -24746,11 +24738,11 @@
       <c r="A268" s="47" t="n"/>
       <c r="B268" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
+          <t>Ancho del radiador (cm)</t>
         </is>
       </c>
       <c r="C268" s="59" t="n">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="D268" s="12" t="n"/>
       <c r="E268" s="39" t="n"/>
@@ -24758,14 +24750,16 @@
       <c r="G268" s="53" t="n"/>
     </row>
     <row r="269" ht="19.8" customHeight="1">
-      <c r="A269" s="47" t="n"/>
+      <c r="A269" s="50" t="n"/>
       <c r="B269" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
-        </is>
-      </c>
-      <c r="C269" s="59" t="n">
-        <v>88</v>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C269" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
       </c>
       <c r="D269" s="12" t="n"/>
       <c r="E269" s="39" t="n"/>
@@ -24773,510 +24767,508 @@
       <c r="G269" s="53" t="n"/>
     </row>
     <row r="270" ht="19.8" customHeight="1">
-      <c r="A270" s="50" t="n"/>
-      <c r="B270" s="60" t="inlineStr">
-        <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C270" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
-      </c>
-      <c r="D270" s="12" t="n"/>
-      <c r="E270" s="39" t="n"/>
-      <c r="F270" s="20" t="n"/>
+      <c r="A270" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  14 - Play room   (PA)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B270" s="11" t="n"/>
+      <c r="C270" s="11" t="n"/>
+      <c r="D270" s="11" t="n"/>
+      <c r="E270" s="11" t="n"/>
+      <c r="F270" s="42" t="n"/>
       <c r="G270" s="53" t="n"/>
     </row>
-    <row r="271" ht="19.8" customHeight="1">
-      <c r="A271" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  14 - Play room   (PA)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B271" s="11" t="n"/>
-      <c r="C271" s="11" t="n"/>
-      <c r="D271" s="11" t="n"/>
-      <c r="E271" s="11" t="n"/>
-      <c r="F271" s="42" t="n"/>
+    <row r="271" ht="32" customHeight="1">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G271" s="53" t="n"/>
     </row>
-    <row r="272" ht="32" customHeight="1">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B272" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D272" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E272" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F272" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="272" ht="19.8" customHeight="1">
+      <c r="A272" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B272" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C272" s="43" t="n"/>
+      <c r="D272" s="58" t="n"/>
+      <c r="E272" s="58" t="n"/>
+      <c r="F272" s="61" t="n"/>
       <c r="G272" s="53" t="n"/>
     </row>
     <row r="273" ht="19.8" customHeight="1">
-      <c r="A273" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B273" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C273" s="43" t="n"/>
-      <c r="D273" s="58" t="n"/>
-      <c r="E273" s="58" t="n"/>
-      <c r="F273" s="61" t="n"/>
+      <c r="A273" s="90" t="n"/>
+      <c r="B273" s="91" t="inlineStr">
+        <is>
+          <t>VA04</t>
+        </is>
+      </c>
+      <c r="C273" s="18" t="inlineStr">
+        <is>
+          <t>2.00 x 2.52</t>
+        </is>
+      </c>
+      <c r="D273" s="19" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="E273" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F273" s="80" t="n">
+        <v>302.4</v>
+      </c>
       <c r="G273" s="53" t="n"/>
     </row>
     <row r="274" ht="19.8" customHeight="1">
-      <c r="A274" s="90" t="n"/>
-      <c r="B274" s="91" t="inlineStr">
-        <is>
-          <t>VA04</t>
-        </is>
-      </c>
-      <c r="C274" s="18" t="inlineStr">
-        <is>
-          <t>2.00 x 2.52</t>
-        </is>
-      </c>
-      <c r="D274" s="19" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="E274" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F274" s="80" t="n">
-        <v>302.4</v>
-      </c>
+      <c r="A274" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B274" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C274" s="47" t="n"/>
+      <c r="D274" s="18" t="n"/>
+      <c r="E274" s="18" t="n"/>
+      <c r="F274" s="20" t="n"/>
       <c r="G274" s="53" t="n"/>
     </row>
     <row r="275" ht="19.8" customHeight="1">
-      <c r="A275" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B275" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C275" s="47" t="n"/>
-      <c r="D275" s="18" t="n"/>
-      <c r="E275" s="18" t="n"/>
-      <c r="F275" s="20" t="n"/>
+      <c r="A275" s="43" t="n"/>
+      <c r="B275" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS (NO)</t>
+        </is>
+      </c>
+      <c r="C275" s="18" t="inlineStr">
+        <is>
+          <t>4.13 x 3.00</t>
+        </is>
+      </c>
+      <c r="D275" s="19" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="E275" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F275" s="80" t="n">
+        <v>247.8</v>
+      </c>
       <c r="G275" s="53" t="n"/>
     </row>
     <row r="276" ht="19.8" customHeight="1">
-      <c r="A276" s="43" t="n"/>
-      <c r="B276" s="79" t="inlineStr">
-        <is>
-          <t>AISLADAS (NO)</t>
-        </is>
-      </c>
-      <c r="C276" s="18" t="inlineStr">
-        <is>
-          <t>4.13 x 3.00</t>
-        </is>
-      </c>
-      <c r="D276" s="19" t="n">
-        <v>12.39</v>
-      </c>
+      <c r="A276" s="47" t="n"/>
+      <c r="B276" s="81" t="inlineStr">
+        <is>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C276" s="18" t="n"/>
+      <c r="D276" s="19" t="n"/>
       <c r="E276" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F276" s="80" t="n">
-        <v>247.8</v>
-      </c>
+      <c r="F276" s="80" t="n"/>
       <c r="G276" s="53" t="n"/>
     </row>
     <row r="277" ht="19.8" customHeight="1">
       <c r="A277" s="47" t="n"/>
       <c r="B277" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C277" s="18" t="n"/>
-      <c r="D277" s="19" t="n"/>
+          <t>INTERIORES (NE)</t>
+        </is>
+      </c>
+      <c r="C277" s="18" t="inlineStr">
+        <is>
+          <t>4.08 x 3.00</t>
+        </is>
+      </c>
+      <c r="D277" s="19" t="n">
+        <v>12.24</v>
+      </c>
       <c r="E277" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F277" s="80" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="F277" s="80" t="n">
+        <v>306</v>
+      </c>
       <c r="G277" s="53" t="n"/>
     </row>
     <row r="278" ht="19.8" customHeight="1">
-      <c r="A278" s="47" t="n"/>
-      <c r="B278" s="81" t="inlineStr">
-        <is>
-          <t>INTERIORES (NE)</t>
+      <c r="A278" s="50" t="n"/>
+      <c r="B278" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES (SE)</t>
         </is>
       </c>
       <c r="C278" s="18" t="inlineStr">
         <is>
-          <t>4.08 x 3.00</t>
+          <t>4.13 x 3.00</t>
         </is>
       </c>
       <c r="D278" s="19" t="n">
-        <v>12.24</v>
+        <v>12.39</v>
       </c>
       <c r="E278" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F278" s="80" t="n">
-        <v>306</v>
+        <v>309.8</v>
       </c>
       <c r="G278" s="53" t="n"/>
     </row>
     <row r="279" ht="19.8" customHeight="1">
-      <c r="A279" s="50" t="n"/>
-      <c r="B279" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES (SE)</t>
-        </is>
-      </c>
-      <c r="C279" s="18" t="inlineStr">
-        <is>
-          <t>4.13 x 3.00</t>
-        </is>
-      </c>
-      <c r="D279" s="19" t="n">
-        <v>12.39</v>
-      </c>
-      <c r="E279" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F279" s="80" t="n">
-        <v>309.8</v>
-      </c>
+      <c r="A279" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B279" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C279" s="47" t="n"/>
+      <c r="D279" s="18" t="n"/>
+      <c r="E279" s="18" t="n"/>
+      <c r="F279" s="20" t="n"/>
       <c r="G279" s="53" t="n"/>
     </row>
     <row r="280" ht="19.8" customHeight="1">
-      <c r="A280" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B280" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C280" s="47" t="n"/>
-      <c r="D280" s="18" t="n"/>
-      <c r="E280" s="18" t="n"/>
-      <c r="F280" s="20" t="n"/>
+      <c r="A280" s="43" t="n"/>
+      <c r="B280" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C280" s="18" t="n"/>
+      <c r="D280" s="19" t="n"/>
+      <c r="E280" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F280" s="80" t="n"/>
       <c r="G280" s="53" t="n"/>
     </row>
     <row r="281" ht="19.8" customHeight="1">
-      <c r="A281" s="43" t="n"/>
-      <c r="B281" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C281" s="18" t="n"/>
-      <c r="D281" s="19" t="n"/>
+      <c r="A281" s="47" t="n"/>
+      <c r="B281" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C281" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D281" s="19" t="n">
+        <v>16.85</v>
+      </c>
       <c r="E281" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F281" s="80" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F281" s="80" t="n">
+        <v>337</v>
+      </c>
       <c r="G281" s="53" t="n"/>
     </row>
     <row r="282" ht="19.8" customHeight="1">
-      <c r="A282" s="47" t="n"/>
-      <c r="B282" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C282" s="18" t="inlineStr">
+      <c r="A282" s="50" t="n"/>
+      <c r="B282" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C282" s="18" t="n"/>
+      <c r="D282" s="19" t="n"/>
+      <c r="E282" s="59" t="n">
+        <v>15</v>
+      </c>
+      <c r="F282" s="80" t="n"/>
+      <c r="G282" s="53" t="n"/>
+    </row>
+    <row r="283" ht="19.8" customHeight="1">
+      <c r="A283" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B283" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C283" s="47" t="n"/>
+      <c r="D283" s="18" t="n"/>
+      <c r="E283" s="18" t="n"/>
+      <c r="F283" s="20" t="n"/>
+      <c r="G283" s="53" t="n"/>
+    </row>
+    <row r="284" ht="19.8" customHeight="1">
+      <c r="A284" s="43" t="n"/>
+      <c r="B284" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C284" s="18" t="n"/>
+      <c r="D284" s="19" t="n"/>
+      <c r="E284" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F284" s="80" t="n"/>
+      <c r="G284" s="53" t="n"/>
+    </row>
+    <row r="285" ht="19.8" customHeight="1">
+      <c r="A285" s="50" t="n"/>
+      <c r="B285" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C285" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D282" s="19" t="n">
+      <c r="D285" s="24" t="n">
         <v>16.85</v>
       </c>
-      <c r="E282" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F282" s="80" t="n">
-        <v>337</v>
-      </c>
-      <c r="G282" s="53" t="n"/>
-    </row>
-    <row r="283" ht="19.8" customHeight="1">
-      <c r="A283" s="50" t="n"/>
-      <c r="B283" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C283" s="18" t="n"/>
-      <c r="D283" s="19" t="n"/>
-      <c r="E283" s="59" t="n">
+      <c r="E285" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F283" s="80" t="n"/>
-      <c r="G283" s="53" t="n"/>
-    </row>
-    <row r="284" ht="19.8" customHeight="1">
-      <c r="A284" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B284" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C284" s="47" t="n"/>
-      <c r="D284" s="18" t="n"/>
-      <c r="E284" s="18" t="n"/>
-      <c r="F284" s="20" t="n"/>
-      <c r="G284" s="53" t="n"/>
-    </row>
-    <row r="285" ht="19.8" customHeight="1">
-      <c r="A285" s="43" t="n"/>
-      <c r="B285" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C285" s="18" t="n"/>
-      <c r="D285" s="19" t="n"/>
-      <c r="E285" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F285" s="80" t="n"/>
+      <c r="F285" s="80" t="n">
+        <v>252.8</v>
+      </c>
       <c r="G285" s="53" t="n"/>
     </row>
     <row r="286" ht="19.8" customHeight="1">
-      <c r="A286" s="50" t="n"/>
-      <c r="B286" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C286" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D286" s="24" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="E286" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F286" s="80" t="n">
-        <v>252.8</v>
-      </c>
+      <c r="A286" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B286" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C286" s="83" t="n"/>
+      <c r="D286" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E286" s="47" t="n"/>
+      <c r="F286" s="20" t="n"/>
       <c r="G286" s="53" t="n"/>
     </row>
     <row r="287" ht="19.8" customHeight="1">
-      <c r="A287" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B287" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C287" s="83" t="n"/>
-      <c r="D287" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E287" s="47" t="n"/>
-      <c r="F287" s="20" t="n"/>
+      <c r="A287" s="43" t="n"/>
+      <c r="B287" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C287" s="18" t="inlineStr">
+        <is>
+          <t>16.85 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D287" s="22" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="E287" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F287" s="80" t="n">
+        <v>303.3</v>
+      </c>
       <c r="G287" s="53" t="n"/>
     </row>
     <row r="288" ht="19.8" customHeight="1">
-      <c r="A288" s="43" t="n"/>
-      <c r="B288" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C288" s="18" t="inlineStr">
-        <is>
-          <t>16.85 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D288" s="22" t="n">
-        <v>50.55</v>
-      </c>
+      <c r="A288" s="47" t="n"/>
+      <c r="B288" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C288" s="18" t="n"/>
+      <c r="D288" s="19" t="n"/>
       <c r="E288" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F288" s="80" t="n">
-        <v>303.3</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F288" s="80" t="n"/>
       <c r="G288" s="53" t="n"/>
     </row>
     <row r="289" ht="19.8" customHeight="1">
-      <c r="A289" s="47" t="n"/>
-      <c r="B289" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
+      <c r="A289" s="50" t="n"/>
+      <c r="B289" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C289" s="18" t="n"/>
       <c r="D289" s="19" t="n"/>
       <c r="E289" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F289" s="80" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="F289" s="84" t="n"/>
       <c r="G289" s="53" t="n"/>
     </row>
     <row r="290" ht="19.8" customHeight="1">
-      <c r="A290" s="50" t="n"/>
-      <c r="B290" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C290" s="18" t="n"/>
-      <c r="D290" s="19" t="n"/>
-      <c r="E290" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F290" s="84" t="n"/>
+      <c r="A290" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B290" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C290" s="47" t="n"/>
+      <c r="D290" s="18" t="n"/>
+      <c r="E290" s="20" t="n"/>
+      <c r="F290" s="85" t="n">
+        <v>2059.1</v>
+      </c>
       <c r="G290" s="53" t="n"/>
     </row>
     <row r="291" ht="19.8" customHeight="1">
       <c r="A291" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B291" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C291" s="47" t="n"/>
-      <c r="D291" s="18" t="n"/>
-      <c r="E291" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C291" s="47" t="inlineStr">
+        <is>
+          <t>2059.10  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D291" s="12" t="n"/>
+      <c r="E291" s="14" t="n"/>
       <c r="F291" s="85" t="n">
-        <v>2059.1</v>
+        <v>2203.2</v>
       </c>
       <c r="G291" s="53" t="n"/>
     </row>
     <row r="292" ht="19.8" customHeight="1">
-      <c r="A292" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B292" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C292" s="47" t="inlineStr">
-        <is>
-          <t>2059.10  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+      <c r="A292" s="43" t="n"/>
+      <c r="B292" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C292" s="18" t="inlineStr">
+        <is>
+          <t>Escalera</t>
         </is>
       </c>
       <c r="D292" s="12" t="n"/>
-      <c r="E292" s="14" t="n"/>
-      <c r="F292" s="85" t="n">
-        <v>2203.2</v>
+      <c r="E292" s="39" t="n"/>
+      <c r="F292" s="87" t="n">
+        <v>1348.3</v>
       </c>
       <c r="G292" s="53" t="n"/>
     </row>
     <row r="293" ht="19.8" customHeight="1">
-      <c r="A293" s="43" t="n"/>
-      <c r="B293" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C293" s="18" t="inlineStr">
-        <is>
-          <t>Escalera</t>
-        </is>
-      </c>
+      <c r="A293" s="83" t="n"/>
+      <c r="B293" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C293" s="47" t="n"/>
       <c r="D293" s="12" t="n"/>
-      <c r="E293" s="39" t="n"/>
-      <c r="F293" s="87" t="n">
-        <v>1348.3</v>
+      <c r="E293" s="14" t="n"/>
+      <c r="F293" s="85" t="n">
+        <v>3551.5</v>
       </c>
       <c r="G293" s="53" t="n"/>
     </row>
     <row r="294" ht="19.8" customHeight="1">
-      <c r="A294" s="83" t="n"/>
-      <c r="B294" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C294" s="47" t="n"/>
+      <c r="A294" s="47" t="n"/>
+      <c r="B294" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C294" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D294" s="12" t="n"/>
-      <c r="E294" s="14" t="n"/>
-      <c r="F294" s="85" t="n">
-        <v>3551.5</v>
-      </c>
+      <c r="E294" s="39" t="n"/>
+      <c r="F294" s="61" t="n"/>
       <c r="G294" s="53" t="n"/>
     </row>
     <row r="295" ht="19.8" customHeight="1">
       <c r="A295" s="47" t="n"/>
-      <c r="B295" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C295" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B295" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C295" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D295" s="12" t="n"/>
       <c r="E295" s="39" t="n"/>
-      <c r="F295" s="61" t="n"/>
+      <c r="F295" s="20" t="n"/>
       <c r="G295" s="53" t="n"/>
     </row>
     <row r="296" ht="19.8" customHeight="1">
       <c r="A296" s="47" t="n"/>
       <c r="B296" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C296" s="19" t="n">
-        <v>274.4</v>
+          <t>Elementos necesarios</t>
+        </is>
+      </c>
+      <c r="C296" s="59" t="n">
+        <v>13</v>
       </c>
       <c r="D296" s="12" t="n"/>
       <c r="E296" s="39" t="n"/>
@@ -25287,11 +25279,11 @@
       <c r="A297" s="47" t="n"/>
       <c r="B297" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
+          <t>Ancho del radiador (cm)</t>
         </is>
       </c>
       <c r="C297" s="59" t="n">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="D297" s="12" t="n"/>
       <c r="E297" s="39" t="n"/>
@@ -25299,14 +25291,16 @@
       <c r="G297" s="53" t="n"/>
     </row>
     <row r="298" ht="19.8" customHeight="1">
-      <c r="A298" s="47" t="n"/>
+      <c r="A298" s="50" t="n"/>
       <c r="B298" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
-        </is>
-      </c>
-      <c r="C298" s="59" t="n">
-        <v>104</v>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C298" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
       </c>
       <c r="D298" s="12" t="n"/>
       <c r="E298" s="39" t="n"/>
@@ -25314,145 +25308,151 @@
       <c r="G298" s="53" t="n"/>
     </row>
     <row r="299" ht="19.8" customHeight="1">
-      <c r="A299" s="50" t="n"/>
-      <c r="B299" s="60" t="inlineStr">
-        <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C299" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
-      </c>
-      <c r="D299" s="12" t="n"/>
-      <c r="E299" s="39" t="n"/>
-      <c r="F299" s="20" t="n"/>
+      <c r="A299" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  15 - Dormitorio Sur   (PA)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B299" s="11" t="n"/>
+      <c r="C299" s="11" t="n"/>
+      <c r="D299" s="11" t="n"/>
+      <c r="E299" s="11" t="n"/>
+      <c r="F299" s="42" t="n"/>
       <c r="G299" s="53" t="n"/>
     </row>
-    <row r="300" ht="19.8" customHeight="1">
-      <c r="A300" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  15 - Dormitorio Sur   (PA)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B300" s="11" t="n"/>
-      <c r="C300" s="11" t="n"/>
-      <c r="D300" s="11" t="n"/>
-      <c r="E300" s="11" t="n"/>
-      <c r="F300" s="42" t="n"/>
+    <row r="300" ht="32" customHeight="1">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G300" s="53" t="n"/>
     </row>
-    <row r="301" ht="32" customHeight="1">
-      <c r="A301" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B301" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C301" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D301" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E301" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F301" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="301" ht="19.8" customHeight="1">
+      <c r="A301" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B301" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C301" s="43" t="n"/>
+      <c r="D301" s="58" t="n"/>
+      <c r="E301" s="58" t="n"/>
+      <c r="F301" s="61" t="n"/>
       <c r="G301" s="53" t="n"/>
     </row>
     <row r="302" ht="19.8" customHeight="1">
-      <c r="A302" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B302" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C302" s="43" t="n"/>
-      <c r="D302" s="58" t="n"/>
-      <c r="E302" s="58" t="n"/>
-      <c r="F302" s="61" t="n"/>
+      <c r="A302" s="90" t="n"/>
+      <c r="B302" s="91" t="inlineStr">
+        <is>
+          <t>PV04</t>
+        </is>
+      </c>
+      <c r="C302" s="18" t="inlineStr">
+        <is>
+          <t>2.06 x 3.00</t>
+        </is>
+      </c>
+      <c r="D302" s="19" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="E302" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F302" s="80" t="n">
+        <v>370.8</v>
+      </c>
       <c r="G302" s="53" t="n"/>
     </row>
     <row r="303" ht="19.8" customHeight="1">
-      <c r="A303" s="90" t="n"/>
-      <c r="B303" s="91" t="inlineStr">
-        <is>
-          <t>PV04</t>
-        </is>
-      </c>
-      <c r="C303" s="18" t="inlineStr">
-        <is>
-          <t>2.06 x 3.00</t>
-        </is>
-      </c>
-      <c r="D303" s="19" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="E303" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F303" s="80" t="n">
-        <v>370.8</v>
-      </c>
+      <c r="A303" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B303" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C303" s="47" t="n"/>
+      <c r="D303" s="18" t="n"/>
+      <c r="E303" s="18" t="n"/>
+      <c r="F303" s="20" t="n"/>
       <c r="G303" s="53" t="n"/>
     </row>
     <row r="304" ht="19.8" customHeight="1">
-      <c r="A304" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B304" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C304" s="47" t="n"/>
-      <c r="D304" s="18" t="n"/>
-      <c r="E304" s="18" t="n"/>
-      <c r="F304" s="20" t="n"/>
+      <c r="A304" s="43" t="n"/>
+      <c r="B304" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS (SE)</t>
+        </is>
+      </c>
+      <c r="C304" s="18" t="inlineStr">
+        <is>
+          <t>4.05 x 3.00</t>
+        </is>
+      </c>
+      <c r="D304" s="19" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="E304" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F304" s="80" t="n">
+        <v>243</v>
+      </c>
       <c r="G304" s="53" t="n"/>
     </row>
     <row r="305" ht="19.8" customHeight="1">
-      <c r="A305" s="43" t="n"/>
-      <c r="B305" s="79" t="inlineStr">
-        <is>
-          <t>AISLADAS (SE)</t>
+      <c r="A305" s="47" t="n"/>
+      <c r="B305" s="81" t="inlineStr">
+        <is>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C305" s="18" t="inlineStr">
         <is>
-          <t>4.05 x 3.00</t>
+          <t>3.50 x 3.00</t>
         </is>
       </c>
       <c r="D305" s="19" t="n">
-        <v>12.15</v>
+        <v>10.5</v>
       </c>
       <c r="E305" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F305" s="80" t="n">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="G305" s="53" t="n"/>
     </row>
@@ -25460,366 +25460,358 @@
       <c r="A306" s="47" t="n"/>
       <c r="B306" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>INTERIORES (NO)</t>
         </is>
       </c>
       <c r="C306" s="18" t="inlineStr">
         <is>
+          <t>4.05 x 3.00</t>
+        </is>
+      </c>
+      <c r="D306" s="19" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="E306" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F306" s="80" t="n">
+        <v>303.8</v>
+      </c>
+      <c r="G306" s="53" t="n"/>
+    </row>
+    <row r="307" ht="19.8" customHeight="1">
+      <c r="A307" s="50" t="n"/>
+      <c r="B307" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C307" s="18" t="inlineStr">
+        <is>
           <t>3.50 x 3.00</t>
         </is>
       </c>
-      <c r="D306" s="19" t="n">
+      <c r="D307" s="19" t="n">
         <v>10.5</v>
-      </c>
-      <c r="E306" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F306" s="80" t="n">
-        <v>210</v>
-      </c>
-      <c r="G306" s="53" t="n"/>
-    </row>
-    <row r="307" ht="19.8" customHeight="1">
-      <c r="A307" s="47" t="n"/>
-      <c r="B307" s="81" t="inlineStr">
-        <is>
-          <t>INTERIORES (NO)</t>
-        </is>
-      </c>
-      <c r="C307" s="18" t="inlineStr">
-        <is>
-          <t>4.05 x 3.00</t>
-        </is>
-      </c>
-      <c r="D307" s="19" t="n">
-        <v>12.15</v>
       </c>
       <c r="E307" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F307" s="80" t="n">
-        <v>303.8</v>
+        <v>262.5</v>
       </c>
       <c r="G307" s="53" t="n"/>
     </row>
     <row r="308" ht="19.8" customHeight="1">
-      <c r="A308" s="50" t="n"/>
-      <c r="B308" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C308" s="18" t="inlineStr">
-        <is>
-          <t>3.50 x 3.00</t>
-        </is>
-      </c>
-      <c r="D308" s="19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="E308" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F308" s="80" t="n">
-        <v>262.5</v>
-      </c>
+      <c r="A308" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B308" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C308" s="47" t="n"/>
+      <c r="D308" s="18" t="n"/>
+      <c r="E308" s="18" t="n"/>
+      <c r="F308" s="20" t="n"/>
       <c r="G308" s="53" t="n"/>
     </row>
     <row r="309" ht="19.8" customHeight="1">
-      <c r="A309" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B309" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C309" s="47" t="n"/>
-      <c r="D309" s="18" t="n"/>
-      <c r="E309" s="18" t="n"/>
-      <c r="F309" s="20" t="n"/>
+      <c r="A309" s="43" t="n"/>
+      <c r="B309" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C309" s="18" t="n"/>
+      <c r="D309" s="19" t="n"/>
+      <c r="E309" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F309" s="80" t="n"/>
       <c r="G309" s="53" t="n"/>
     </row>
     <row r="310" ht="19.8" customHeight="1">
-      <c r="A310" s="43" t="n"/>
-      <c r="B310" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C310" s="18" t="n"/>
-      <c r="D310" s="19" t="n"/>
+      <c r="A310" s="47" t="n"/>
+      <c r="B310" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C310" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D310" s="19" t="n">
+        <v>14.17</v>
+      </c>
       <c r="E310" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F310" s="80" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F310" s="80" t="n">
+        <v>283.4</v>
+      </c>
       <c r="G310" s="53" t="n"/>
     </row>
     <row r="311" ht="19.8" customHeight="1">
-      <c r="A311" s="47" t="n"/>
-      <c r="B311" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C311" s="18" t="inlineStr">
+      <c r="A311" s="50" t="n"/>
+      <c r="B311" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C311" s="18" t="n"/>
+      <c r="D311" s="19" t="n"/>
+      <c r="E311" s="59" t="n">
+        <v>15</v>
+      </c>
+      <c r="F311" s="80" t="n"/>
+      <c r="G311" s="53" t="n"/>
+    </row>
+    <row r="312" ht="19.8" customHeight="1">
+      <c r="A312" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B312" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C312" s="47" t="n"/>
+      <c r="D312" s="18" t="n"/>
+      <c r="E312" s="18" t="n"/>
+      <c r="F312" s="20" t="n"/>
+      <c r="G312" s="53" t="n"/>
+    </row>
+    <row r="313" ht="19.8" customHeight="1">
+      <c r="A313" s="43" t="n"/>
+      <c r="B313" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C313" s="18" t="n"/>
+      <c r="D313" s="19" t="n"/>
+      <c r="E313" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F313" s="80" t="n"/>
+      <c r="G313" s="53" t="n"/>
+    </row>
+    <row r="314" ht="19.8" customHeight="1">
+      <c r="A314" s="50" t="n"/>
+      <c r="B314" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C314" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D311" s="19" t="n">
+      <c r="D314" s="24" t="n">
         <v>14.17</v>
       </c>
-      <c r="E311" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F311" s="80" t="n">
-        <v>283.4</v>
-      </c>
-      <c r="G311" s="53" t="n"/>
-    </row>
-    <row r="312" ht="19.8" customHeight="1">
-      <c r="A312" s="50" t="n"/>
-      <c r="B312" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C312" s="18" t="n"/>
-      <c r="D312" s="19" t="n"/>
-      <c r="E312" s="59" t="n">
+      <c r="E314" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F312" s="80" t="n"/>
-      <c r="G312" s="53" t="n"/>
-    </row>
-    <row r="313" ht="19.8" customHeight="1">
-      <c r="A313" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B313" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C313" s="47" t="n"/>
-      <c r="D313" s="18" t="n"/>
-      <c r="E313" s="18" t="n"/>
-      <c r="F313" s="20" t="n"/>
-      <c r="G313" s="53" t="n"/>
-    </row>
-    <row r="314" ht="19.8" customHeight="1">
-      <c r="A314" s="43" t="n"/>
-      <c r="B314" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C314" s="18" t="n"/>
-      <c r="D314" s="19" t="n"/>
-      <c r="E314" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F314" s="80" t="n"/>
+      <c r="F314" s="80" t="n">
+        <v>212.6</v>
+      </c>
       <c r="G314" s="53" t="n"/>
     </row>
     <row r="315" ht="19.8" customHeight="1">
-      <c r="A315" s="50" t="n"/>
-      <c r="B315" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C315" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D315" s="24" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="E315" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F315" s="80" t="n">
-        <v>212.6</v>
-      </c>
+      <c r="A315" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B315" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C315" s="83" t="n"/>
+      <c r="D315" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E315" s="47" t="n"/>
+      <c r="F315" s="20" t="n"/>
       <c r="G315" s="53" t="n"/>
     </row>
     <row r="316" ht="19.8" customHeight="1">
-      <c r="A316" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B316" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C316" s="83" t="n"/>
-      <c r="D316" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E316" s="47" t="n"/>
-      <c r="F316" s="20" t="n"/>
+      <c r="A316" s="43" t="n"/>
+      <c r="B316" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C316" s="18" t="n"/>
+      <c r="D316" s="22" t="n"/>
+      <c r="E316" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F316" s="80" t="n"/>
       <c r="G316" s="53" t="n"/>
     </row>
     <row r="317" ht="19.8" customHeight="1">
-      <c r="A317" s="43" t="n"/>
-      <c r="B317" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C317" s="18" t="n"/>
-      <c r="D317" s="22" t="n"/>
+      <c r="A317" s="47" t="n"/>
+      <c r="B317" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C317" s="18" t="inlineStr">
+        <is>
+          <t>14.17 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D317" s="19" t="n">
+        <v>42.51</v>
+      </c>
       <c r="E317" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F317" s="80" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="F317" s="80" t="n">
+        <v>382.6</v>
+      </c>
       <c r="G317" s="53" t="n"/>
     </row>
     <row r="318" ht="19.8" customHeight="1">
-      <c r="A318" s="47" t="n"/>
-      <c r="B318" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C318" s="18" t="inlineStr">
-        <is>
-          <t>14.17 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D318" s="19" t="n">
-        <v>42.51</v>
-      </c>
+      <c r="A318" s="50" t="n"/>
+      <c r="B318" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C318" s="18" t="n"/>
+      <c r="D318" s="19" t="n"/>
       <c r="E318" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F318" s="80" t="n">
-        <v>382.6</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F318" s="84" t="n"/>
       <c r="G318" s="53" t="n"/>
     </row>
     <row r="319" ht="19.8" customHeight="1">
-      <c r="A319" s="50" t="n"/>
-      <c r="B319" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C319" s="18" t="n"/>
-      <c r="D319" s="19" t="n"/>
-      <c r="E319" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F319" s="84" t="n"/>
+      <c r="A319" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B319" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C319" s="47" t="n"/>
+      <c r="D319" s="18" t="n"/>
+      <c r="E319" s="20" t="n"/>
+      <c r="F319" s="85" t="n">
+        <v>2268.7</v>
+      </c>
       <c r="G319" s="53" t="n"/>
     </row>
     <row r="320" ht="19.8" customHeight="1">
       <c r="A320" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B320" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C320" s="47" t="n"/>
-      <c r="D320" s="18" t="n"/>
-      <c r="E320" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C320" s="47" t="inlineStr">
+        <is>
+          <t>2268.70  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D320" s="12" t="n"/>
+      <c r="E320" s="14" t="n"/>
       <c r="F320" s="85" t="n">
-        <v>2268.7</v>
+        <v>2427.5</v>
       </c>
       <c r="G320" s="53" t="n"/>
     </row>
     <row r="321" ht="19.8" customHeight="1">
-      <c r="A321" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B321" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C321" s="47" t="inlineStr">
-        <is>
-          <t>2268.70  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A321" s="43" t="n"/>
+      <c r="B321" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C321" s="18" t="n"/>
       <c r="D321" s="12" t="n"/>
-      <c r="E321" s="14" t="n"/>
-      <c r="F321" s="85" t="n">
+      <c r="E321" s="39" t="n"/>
+      <c r="F321" s="87" t="n"/>
+      <c r="G321" s="53" t="n"/>
+    </row>
+    <row r="322" ht="19.8" customHeight="1">
+      <c r="A322" s="83" t="n"/>
+      <c r="B322" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C322" s="47" t="n"/>
+      <c r="D322" s="12" t="n"/>
+      <c r="E322" s="14" t="n"/>
+      <c r="F322" s="85" t="n">
         <v>2427.5</v>
       </c>
-      <c r="G321" s="53" t="n"/>
-    </row>
-    <row r="322" ht="19.8" customHeight="1">
-      <c r="A322" s="43" t="n"/>
-      <c r="B322" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C322" s="18" t="n"/>
-      <c r="D322" s="12" t="n"/>
-      <c r="E322" s="39" t="n"/>
-      <c r="F322" s="87" t="n"/>
       <c r="G322" s="53" t="n"/>
     </row>
     <row r="323" ht="19.8" customHeight="1">
-      <c r="A323" s="83" t="n"/>
-      <c r="B323" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C323" s="47" t="n"/>
+      <c r="A323" s="47" t="n"/>
+      <c r="B323" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C323" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D323" s="12" t="n"/>
-      <c r="E323" s="14" t="n"/>
-      <c r="F323" s="85" t="n">
-        <v>2427.5</v>
-      </c>
+      <c r="E323" s="39" t="n"/>
+      <c r="F323" s="61" t="n"/>
       <c r="G323" s="53" t="n"/>
     </row>
     <row r="324" ht="19.8" customHeight="1">
       <c r="A324" s="47" t="n"/>
-      <c r="B324" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C324" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B324" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C324" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D324" s="12" t="n"/>
       <c r="E324" s="39" t="n"/>
-      <c r="F324" s="61" t="n"/>
+      <c r="F324" s="20" t="n"/>
       <c r="G324" s="53" t="n"/>
     </row>
     <row r="325" ht="19.8" customHeight="1">
       <c r="A325" s="47" t="n"/>
       <c r="B325" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C325" s="19" t="n">
-        <v>274.4</v>
+          <t>Elementos necesarios</t>
+        </is>
+      </c>
+      <c r="C325" s="59" t="n">
+        <v>9</v>
       </c>
       <c r="D325" s="12" t="n"/>
       <c r="E325" s="39" t="n"/>
@@ -25830,11 +25822,11 @@
       <c r="A326" s="47" t="n"/>
       <c r="B326" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
+          <t>Ancho del radiador (cm)</t>
         </is>
       </c>
       <c r="C326" s="59" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="D326" s="12" t="n"/>
       <c r="E326" s="39" t="n"/>
@@ -25842,14 +25834,16 @@
       <c r="G326" s="53" t="n"/>
     </row>
     <row r="327" ht="19.8" customHeight="1">
-      <c r="A327" s="47" t="n"/>
+      <c r="A327" s="50" t="n"/>
       <c r="B327" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
-        </is>
-      </c>
-      <c r="C327" s="59" t="n">
-        <v>72</v>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C327" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
       </c>
       <c r="D327" s="12" t="n"/>
       <c r="E327" s="39" t="n"/>
@@ -25857,145 +25851,151 @@
       <c r="G327" s="53" t="n"/>
     </row>
     <row r="328" ht="19.8" customHeight="1">
-      <c r="A328" s="50" t="n"/>
-      <c r="B328" s="60" t="inlineStr">
-        <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C328" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
-      </c>
-      <c r="D328" s="12" t="n"/>
-      <c r="E328" s="39" t="n"/>
-      <c r="F328" s="20" t="n"/>
+      <c r="A328" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  17 - Bano   (PA)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B328" s="11" t="n"/>
+      <c r="C328" s="11" t="n"/>
+      <c r="D328" s="11" t="n"/>
+      <c r="E328" s="11" t="n"/>
+      <c r="F328" s="42" t="n"/>
       <c r="G328" s="53" t="n"/>
     </row>
-    <row r="329" ht="19.8" customHeight="1">
-      <c r="A329" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  17 - Bano   (PA)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B329" s="11" t="n"/>
-      <c r="C329" s="11" t="n"/>
-      <c r="D329" s="11" t="n"/>
-      <c r="E329" s="11" t="n"/>
-      <c r="F329" s="42" t="n"/>
+    <row r="329" ht="32" customHeight="1">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G329" s="53" t="n"/>
     </row>
-    <row r="330" ht="32" customHeight="1">
-      <c r="A330" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B330" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C330" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D330" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E330" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F330" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="330" ht="19.8" customHeight="1">
+      <c r="A330" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B330" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C330" s="43" t="n"/>
+      <c r="D330" s="58" t="n"/>
+      <c r="E330" s="58" t="n"/>
+      <c r="F330" s="61" t="n"/>
       <c r="G330" s="53" t="n"/>
     </row>
     <row r="331" ht="19.8" customHeight="1">
-      <c r="A331" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B331" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C331" s="43" t="n"/>
-      <c r="D331" s="58" t="n"/>
-      <c r="E331" s="58" t="n"/>
-      <c r="F331" s="61" t="n"/>
+      <c r="A331" s="90" t="n"/>
+      <c r="B331" s="91" t="inlineStr">
+        <is>
+          <t>VA03</t>
+        </is>
+      </c>
+      <c r="C331" s="18" t="inlineStr">
+        <is>
+          <t>0.75 x 2.52</t>
+        </is>
+      </c>
+      <c r="D331" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E331" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F331" s="80" t="n">
+        <v>113.4</v>
+      </c>
       <c r="G331" s="53" t="n"/>
     </row>
     <row r="332" ht="19.8" customHeight="1">
-      <c r="A332" s="90" t="n"/>
-      <c r="B332" s="91" t="inlineStr">
-        <is>
-          <t>VA03</t>
-        </is>
-      </c>
-      <c r="C332" s="18" t="inlineStr">
-        <is>
-          <t>0.75 x 2.52</t>
-        </is>
-      </c>
-      <c r="D332" s="19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="E332" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F332" s="80" t="n">
-        <v>113.4</v>
-      </c>
+      <c r="A332" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B332" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C332" s="47" t="n"/>
+      <c r="D332" s="18" t="n"/>
+      <c r="E332" s="18" t="n"/>
+      <c r="F332" s="20" t="n"/>
       <c r="G332" s="53" t="n"/>
     </row>
     <row r="333" ht="19.8" customHeight="1">
-      <c r="A333" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B333" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C333" s="47" t="n"/>
-      <c r="D333" s="18" t="n"/>
-      <c r="E333" s="18" t="n"/>
-      <c r="F333" s="20" t="n"/>
+      <c r="A333" s="43" t="n"/>
+      <c r="B333" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS (NE)</t>
+        </is>
+      </c>
+      <c r="C333" s="18" t="inlineStr">
+        <is>
+          <t>2.20 x 3.00</t>
+        </is>
+      </c>
+      <c r="D333" s="19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E333" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F333" s="80" t="n">
+        <v>132</v>
+      </c>
       <c r="G333" s="53" t="n"/>
     </row>
     <row r="334" ht="19.8" customHeight="1">
-      <c r="A334" s="43" t="n"/>
-      <c r="B334" s="79" t="inlineStr">
-        <is>
-          <t>AISLADAS (NE)</t>
+      <c r="A334" s="47" t="n"/>
+      <c r="B334" s="81" t="inlineStr">
+        <is>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C334" s="18" t="inlineStr">
         <is>
-          <t>2.20 x 3.00</t>
+          <t>1.60 x 3.00</t>
         </is>
       </c>
       <c r="D334" s="19" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="E334" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F334" s="80" t="n">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="G334" s="53" t="n"/>
     </row>
@@ -26003,366 +26003,358 @@
       <c r="A335" s="47" t="n"/>
       <c r="B335" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>INTERIORES (SO)</t>
         </is>
       </c>
       <c r="C335" s="18" t="inlineStr">
         <is>
+          <t>2.20 x 3.00</t>
+        </is>
+      </c>
+      <c r="D335" s="19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E335" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F335" s="80" t="n">
+        <v>165</v>
+      </c>
+      <c r="G335" s="53" t="n"/>
+    </row>
+    <row r="336" ht="19.8" customHeight="1">
+      <c r="A336" s="50" t="n"/>
+      <c r="B336" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C336" s="18" t="inlineStr">
+        <is>
           <t>1.60 x 3.00</t>
         </is>
       </c>
-      <c r="D335" s="19" t="n">
+      <c r="D336" s="19" t="n">
         <v>4.8</v>
-      </c>
-      <c r="E335" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F335" s="80" t="n">
-        <v>96</v>
-      </c>
-      <c r="G335" s="53" t="n"/>
-    </row>
-    <row r="336" ht="19.8" customHeight="1">
-      <c r="A336" s="47" t="n"/>
-      <c r="B336" s="81" t="inlineStr">
-        <is>
-          <t>INTERIORES (SO)</t>
-        </is>
-      </c>
-      <c r="C336" s="18" t="inlineStr">
-        <is>
-          <t>2.20 x 3.00</t>
-        </is>
-      </c>
-      <c r="D336" s="19" t="n">
-        <v>6.6</v>
       </c>
       <c r="E336" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F336" s="80" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="G336" s="53" t="n"/>
     </row>
     <row r="337" ht="19.8" customHeight="1">
-      <c r="A337" s="50" t="n"/>
-      <c r="B337" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C337" s="18" t="inlineStr">
-        <is>
-          <t>1.60 x 3.00</t>
-        </is>
-      </c>
-      <c r="D337" s="19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E337" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F337" s="80" t="n">
-        <v>120</v>
-      </c>
+      <c r="A337" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B337" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C337" s="47" t="n"/>
+      <c r="D337" s="18" t="n"/>
+      <c r="E337" s="18" t="n"/>
+      <c r="F337" s="20" t="n"/>
       <c r="G337" s="53" t="n"/>
     </row>
     <row r="338" ht="19.8" customHeight="1">
-      <c r="A338" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B338" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C338" s="47" t="n"/>
-      <c r="D338" s="18" t="n"/>
-      <c r="E338" s="18" t="n"/>
-      <c r="F338" s="20" t="n"/>
+      <c r="A338" s="43" t="n"/>
+      <c r="B338" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C338" s="18" t="n"/>
+      <c r="D338" s="19" t="n"/>
+      <c r="E338" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F338" s="80" t="n"/>
       <c r="G338" s="53" t="n"/>
     </row>
     <row r="339" ht="19.8" customHeight="1">
-      <c r="A339" s="43" t="n"/>
-      <c r="B339" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C339" s="18" t="n"/>
-      <c r="D339" s="19" t="n"/>
+      <c r="A339" s="47" t="n"/>
+      <c r="B339" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C339" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D339" s="19" t="n">
+        <v>3.52</v>
+      </c>
       <c r="E339" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F339" s="80" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F339" s="80" t="n">
+        <v>70.40000000000001</v>
+      </c>
       <c r="G339" s="53" t="n"/>
     </row>
     <row r="340" ht="19.8" customHeight="1">
-      <c r="A340" s="47" t="n"/>
-      <c r="B340" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C340" s="18" t="inlineStr">
+      <c r="A340" s="50" t="n"/>
+      <c r="B340" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C340" s="18" t="n"/>
+      <c r="D340" s="19" t="n"/>
+      <c r="E340" s="59" t="n">
+        <v>15</v>
+      </c>
+      <c r="F340" s="80" t="n"/>
+      <c r="G340" s="53" t="n"/>
+    </row>
+    <row r="341" ht="19.8" customHeight="1">
+      <c r="A341" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B341" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C341" s="47" t="n"/>
+      <c r="D341" s="18" t="n"/>
+      <c r="E341" s="18" t="n"/>
+      <c r="F341" s="20" t="n"/>
+      <c r="G341" s="53" t="n"/>
+    </row>
+    <row r="342" ht="19.8" customHeight="1">
+      <c r="A342" s="43" t="n"/>
+      <c r="B342" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C342" s="18" t="n"/>
+      <c r="D342" s="19" t="n"/>
+      <c r="E342" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F342" s="80" t="n"/>
+      <c r="G342" s="53" t="n"/>
+    </row>
+    <row r="343" ht="19.8" customHeight="1">
+      <c r="A343" s="50" t="n"/>
+      <c r="B343" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C343" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D340" s="19" t="n">
+      <c r="D343" s="24" t="n">
         <v>3.52</v>
       </c>
-      <c r="E340" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F340" s="80" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="G340" s="53" t="n"/>
-    </row>
-    <row r="341" ht="19.8" customHeight="1">
-      <c r="A341" s="50" t="n"/>
-      <c r="B341" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C341" s="18" t="n"/>
-      <c r="D341" s="19" t="n"/>
-      <c r="E341" s="59" t="n">
+      <c r="E343" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F341" s="80" t="n"/>
-      <c r="G341" s="53" t="n"/>
-    </row>
-    <row r="342" ht="19.8" customHeight="1">
-      <c r="A342" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B342" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C342" s="47" t="n"/>
-      <c r="D342" s="18" t="n"/>
-      <c r="E342" s="18" t="n"/>
-      <c r="F342" s="20" t="n"/>
-      <c r="G342" s="53" t="n"/>
-    </row>
-    <row r="343" ht="19.8" customHeight="1">
-      <c r="A343" s="43" t="n"/>
-      <c r="B343" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C343" s="18" t="n"/>
-      <c r="D343" s="19" t="n"/>
-      <c r="E343" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F343" s="80" t="n"/>
+      <c r="F343" s="80" t="n">
+        <v>52.8</v>
+      </c>
       <c r="G343" s="53" t="n"/>
     </row>
     <row r="344" ht="19.8" customHeight="1">
-      <c r="A344" s="50" t="n"/>
-      <c r="B344" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C344" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D344" s="24" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="E344" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F344" s="80" t="n">
-        <v>52.8</v>
-      </c>
+      <c r="A344" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B344" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C344" s="83" t="n"/>
+      <c r="D344" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E344" s="47" t="n"/>
+      <c r="F344" s="20" t="n"/>
       <c r="G344" s="53" t="n"/>
     </row>
     <row r="345" ht="19.8" customHeight="1">
-      <c r="A345" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B345" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C345" s="83" t="n"/>
-      <c r="D345" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E345" s="47" t="n"/>
-      <c r="F345" s="20" t="n"/>
+      <c r="A345" s="43" t="n"/>
+      <c r="B345" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C345" s="18" t="n"/>
+      <c r="D345" s="22" t="n"/>
+      <c r="E345" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F345" s="80" t="n"/>
       <c r="G345" s="53" t="n"/>
     </row>
     <row r="346" ht="19.8" customHeight="1">
-      <c r="A346" s="43" t="n"/>
-      <c r="B346" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C346" s="18" t="n"/>
-      <c r="D346" s="22" t="n"/>
+      <c r="A346" s="47" t="n"/>
+      <c r="B346" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C346" s="18" t="inlineStr">
+        <is>
+          <t>3.52 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D346" s="19" t="n">
+        <v>10.56</v>
+      </c>
       <c r="E346" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F346" s="80" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="F346" s="80" t="n">
+        <v>95</v>
+      </c>
       <c r="G346" s="53" t="n"/>
     </row>
     <row r="347" ht="19.8" customHeight="1">
-      <c r="A347" s="47" t="n"/>
-      <c r="B347" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C347" s="18" t="inlineStr">
-        <is>
-          <t>3.52 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D347" s="19" t="n">
-        <v>10.56</v>
-      </c>
+      <c r="A347" s="50" t="n"/>
+      <c r="B347" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C347" s="18" t="n"/>
+      <c r="D347" s="19" t="n"/>
       <c r="E347" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F347" s="80" t="n">
-        <v>95</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F347" s="84" t="n"/>
       <c r="G347" s="53" t="n"/>
     </row>
     <row r="348" ht="19.8" customHeight="1">
-      <c r="A348" s="50" t="n"/>
-      <c r="B348" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C348" s="18" t="n"/>
-      <c r="D348" s="19" t="n"/>
-      <c r="E348" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F348" s="84" t="n"/>
+      <c r="A348" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B348" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C348" s="47" t="n"/>
+      <c r="D348" s="18" t="n"/>
+      <c r="E348" s="20" t="n"/>
+      <c r="F348" s="85" t="n">
+        <v>844.6</v>
+      </c>
       <c r="G348" s="53" t="n"/>
     </row>
     <row r="349" ht="19.8" customHeight="1">
       <c r="A349" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B349" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C349" s="47" t="n"/>
-      <c r="D349" s="18" t="n"/>
-      <c r="E349" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C349" s="47" t="inlineStr">
+        <is>
+          <t>844.60  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D349" s="12" t="n"/>
+      <c r="E349" s="14" t="n"/>
       <c r="F349" s="85" t="n">
-        <v>844.6</v>
+        <v>903.7</v>
       </c>
       <c r="G349" s="53" t="n"/>
     </row>
     <row r="350" ht="19.8" customHeight="1">
-      <c r="A350" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B350" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C350" s="47" t="inlineStr">
-        <is>
-          <t>844.60  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A350" s="43" t="n"/>
+      <c r="B350" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C350" s="18" t="n"/>
       <c r="D350" s="12" t="n"/>
-      <c r="E350" s="14" t="n"/>
-      <c r="F350" s="85" t="n">
+      <c r="E350" s="39" t="n"/>
+      <c r="F350" s="87" t="n"/>
+      <c r="G350" s="53" t="n"/>
+    </row>
+    <row r="351" ht="19.8" customHeight="1">
+      <c r="A351" s="83" t="n"/>
+      <c r="B351" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C351" s="47" t="n"/>
+      <c r="D351" s="12" t="n"/>
+      <c r="E351" s="14" t="n"/>
+      <c r="F351" s="85" t="n">
         <v>903.7</v>
       </c>
-      <c r="G350" s="53" t="n"/>
-    </row>
-    <row r="351" ht="19.8" customHeight="1">
-      <c r="A351" s="43" t="n"/>
-      <c r="B351" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C351" s="18" t="n"/>
-      <c r="D351" s="12" t="n"/>
-      <c r="E351" s="39" t="n"/>
-      <c r="F351" s="87" t="n"/>
       <c r="G351" s="53" t="n"/>
     </row>
     <row r="352" ht="19.8" customHeight="1">
-      <c r="A352" s="83" t="n"/>
-      <c r="B352" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C352" s="47" t="n"/>
+      <c r="A352" s="47" t="n"/>
+      <c r="B352" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C352" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D352" s="12" t="n"/>
-      <c r="E352" s="14" t="n"/>
-      <c r="F352" s="85" t="n">
-        <v>903.7</v>
-      </c>
+      <c r="E352" s="39" t="n"/>
+      <c r="F352" s="61" t="n"/>
       <c r="G352" s="53" t="n"/>
     </row>
     <row r="353" ht="19.8" customHeight="1">
       <c r="A353" s="47" t="n"/>
-      <c r="B353" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C353" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B353" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
+        </is>
+      </c>
+      <c r="C353" s="59" t="n">
+        <v>708</v>
       </c>
       <c r="D353" s="12" t="n"/>
       <c r="E353" s="39" t="n"/>
-      <c r="F353" s="61" t="n"/>
+      <c r="F353" s="20" t="n"/>
       <c r="G353" s="53" t="n"/>
     </row>
     <row r="354" ht="19.8" customHeight="1">
       <c r="A354" s="47" t="n"/>
       <c r="B354" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 80</t>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
         </is>
       </c>
       <c r="C354" s="59" t="n">
-        <v>708</v>
+        <v>1315</v>
       </c>
       <c r="D354" s="12" t="n"/>
       <c r="E354" s="39" t="n"/>
@@ -26373,11 +26365,11 @@
       <c r="A355" s="47" t="n"/>
       <c r="B355" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 150</t>
+          <t>Toalleros necesarios</t>
         </is>
       </c>
       <c r="C355" s="59" t="n">
-        <v>1315</v>
+        <v>1</v>
       </c>
       <c r="D355" s="12" t="n"/>
       <c r="E355" s="39" t="n"/>
@@ -26385,36 +26377,21 @@
       <c r="G355" s="53" t="n"/>
     </row>
     <row r="356" ht="19.8" customHeight="1">
-      <c r="A356" s="47" t="n"/>
-      <c r="B356" s="60" t="inlineStr">
-        <is>
-          <t>Toalleros necesarios</t>
-        </is>
-      </c>
-      <c r="C356" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D356" s="12" t="n"/>
-      <c r="E356" s="39" t="n"/>
-      <c r="F356" s="20" t="n"/>
+      <c r="A356" s="50" t="n"/>
+      <c r="B356" s="72" t="inlineStr">
+        <is>
+          <t>Toallero adoptado</t>
+        </is>
+      </c>
+      <c r="C356" s="30" t="inlineStr">
+        <is>
+          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
+        </is>
+      </c>
+      <c r="D356" s="11" t="n"/>
+      <c r="E356" s="92" t="n"/>
+      <c r="F356" s="31" t="n"/>
       <c r="G356" s="53" t="n"/>
-    </row>
-    <row r="357" ht="19.8" customHeight="1">
-      <c r="A357" s="50" t="n"/>
-      <c r="B357" s="72" t="inlineStr">
-        <is>
-          <t>Toallero adoptado</t>
-        </is>
-      </c>
-      <c r="C357" s="30" t="inlineStr">
-        <is>
-          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
-        </is>
-      </c>
-      <c r="D357" s="11" t="n"/>
-      <c r="E357" s="92" t="n"/>
-      <c r="F357" s="31" t="n"/>
-      <c r="G357" s="53" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="101">
@@ -26422,27 +26399,22 @@
     <mergeCell ref="C202:E202"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C297:E297"/>
+    <mergeCell ref="A239:F239"/>
     <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C123:E123"/>
     <mergeCell ref="C268:E268"/>
-    <mergeCell ref="C299:E299"/>
     <mergeCell ref="C292:E292"/>
     <mergeCell ref="C57:E57"/>
     <mergeCell ref="C355:E355"/>
     <mergeCell ref="C293:E293"/>
-    <mergeCell ref="A329:F329"/>
     <mergeCell ref="C204:E204"/>
-    <mergeCell ref="C357:E357"/>
     <mergeCell ref="C325:E325"/>
     <mergeCell ref="C206:E206"/>
-    <mergeCell ref="A124:F124"/>
     <mergeCell ref="C205:E205"/>
-    <mergeCell ref="C270:E270"/>
     <mergeCell ref="C118:E118"/>
+    <mergeCell ref="C320:E320"/>
     <mergeCell ref="C238:E238"/>
     <mergeCell ref="C176:E176"/>
     <mergeCell ref="C232:E232"/>
-    <mergeCell ref="A149:F149"/>
     <mergeCell ref="C356:E356"/>
     <mergeCell ref="C59:E59"/>
     <mergeCell ref="C295:E295"/>
@@ -26450,11 +26422,9 @@
     <mergeCell ref="C178:E178"/>
     <mergeCell ref="C61:E61"/>
     <mergeCell ref="C233:E233"/>
-    <mergeCell ref="A240:F240"/>
+    <mergeCell ref="C296:E296"/>
+    <mergeCell ref="C352:E352"/>
     <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C296:E296"/>
-    <mergeCell ref="C209:E209"/>
-    <mergeCell ref="C352:E352"/>
     <mergeCell ref="C145:E145"/>
     <mergeCell ref="C323:E323"/>
     <mergeCell ref="C298:E298"/>
@@ -26469,17 +26439,20 @@
     <mergeCell ref="C88:E88"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C324:E324"/>
+    <mergeCell ref="C231:E231"/>
+    <mergeCell ref="C121:E121"/>
     <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C121:E121"/>
     <mergeCell ref="C117:E117"/>
     <mergeCell ref="C173:E173"/>
     <mergeCell ref="C236:E236"/>
-    <mergeCell ref="A210:F210"/>
     <mergeCell ref="C350:E350"/>
+    <mergeCell ref="A179:F179"/>
+    <mergeCell ref="C115:E115"/>
     <mergeCell ref="C207:E207"/>
-    <mergeCell ref="C328:E328"/>
+    <mergeCell ref="C262:E262"/>
+    <mergeCell ref="C144:E144"/>
     <mergeCell ref="C122:E122"/>
-    <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A299:F299"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="C264:E264"/>
     <mergeCell ref="C326:E326"/>
@@ -26488,35 +26461,39 @@
     <mergeCell ref="C263:E263"/>
     <mergeCell ref="C354:E354"/>
     <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A328:F328"/>
     <mergeCell ref="C235:E235"/>
+    <mergeCell ref="A270:F270"/>
     <mergeCell ref="C62:E62"/>
-    <mergeCell ref="A300:F300"/>
     <mergeCell ref="C234:E234"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C172:E172"/>
     <mergeCell ref="C353:E353"/>
     <mergeCell ref="C64:E64"/>
     <mergeCell ref="C147:E147"/>
-    <mergeCell ref="A271:F271"/>
+    <mergeCell ref="C171:E171"/>
+    <mergeCell ref="C349:E349"/>
     <mergeCell ref="A65:F65"/>
     <mergeCell ref="C177:E177"/>
     <mergeCell ref="C146:E146"/>
-    <mergeCell ref="C148:E148"/>
+    <mergeCell ref="C291:E291"/>
+    <mergeCell ref="C201:E201"/>
     <mergeCell ref="C90:E90"/>
     <mergeCell ref="C120:E120"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="C203:E203"/>
     <mergeCell ref="C119:E119"/>
+    <mergeCell ref="A209:F209"/>
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="C174:E174"/>
     <mergeCell ref="C327:E327"/>
     <mergeCell ref="C237:E237"/>
     <mergeCell ref="C351:E351"/>
-    <mergeCell ref="C179:E179"/>
-    <mergeCell ref="C239:E239"/>
+    <mergeCell ref="A148:F148"/>
     <mergeCell ref="C175:E175"/>
     <mergeCell ref="C58:E58"/>
     <mergeCell ref="C294:E294"/>
+    <mergeCell ref="A123:F123"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="C265:E265"/>
   </mergeCells>

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -21518,7 +21518,7 @@
       <c r="A96" s="43" t="n"/>
       <c r="B96" s="79" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>AISLADAS (SO)</t>
         </is>
       </c>
       <c r="C96" s="18" t="inlineStr">
@@ -21556,7 +21556,7 @@
       <c r="A98" s="47" t="n"/>
       <c r="B98" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (NE)</t>
         </is>
       </c>
       <c r="C98" s="18" t="inlineStr">
@@ -21602,7 +21602,7 @@
       <c r="A100" s="47" t="n"/>
       <c r="B100" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (NE)</t>
         </is>
       </c>
       <c r="C100" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -19691,7 +19691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G356"/>
+  <dimension ref="A1:G355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.1" customWidth="1" min="1" max="1"/>
@@ -21579,7 +21579,7 @@
       <c r="A99" s="47" t="n"/>
       <c r="B99" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (NO)</t>
         </is>
       </c>
       <c r="C99" s="18" t="inlineStr">
@@ -21622,10 +21622,10 @@
       <c r="G100" s="53" t="n"/>
     </row>
     <row r="101" ht="19.8" customHeight="1">
-      <c r="A101" s="47" t="n"/>
-      <c r="B101" s="81" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
+      <c r="A101" s="50" t="n"/>
+      <c r="B101" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES (SE)</t>
         </is>
       </c>
       <c r="C101" s="18" t="inlineStr">
@@ -21645,323 +21645,315 @@
       <c r="G101" s="53" t="n"/>
     </row>
     <row r="102" ht="19.8" customHeight="1">
-      <c r="A102" s="50" t="n"/>
-      <c r="B102" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C102" s="18" t="inlineStr">
-        <is>
-          <t>1.09 x 3.00</t>
-        </is>
-      </c>
-      <c r="D102" s="19" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="E102" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F102" s="80" t="n">
-        <v>81.8</v>
-      </c>
+      <c r="A102" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B102" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C102" s="47" t="n"/>
+      <c r="D102" s="18" t="n"/>
+      <c r="E102" s="18" t="n"/>
+      <c r="F102" s="20" t="n"/>
       <c r="G102" s="53" t="n"/>
     </row>
     <row r="103" ht="19.8" customHeight="1">
-      <c r="A103" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B103" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C103" s="47" t="n"/>
-      <c r="D103" s="18" t="n"/>
-      <c r="E103" s="18" t="n"/>
-      <c r="F103" s="20" t="n"/>
+      <c r="A103" s="43" t="n"/>
+      <c r="B103" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="n"/>
+      <c r="D103" s="19" t="n"/>
+      <c r="E103" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F103" s="80" t="n"/>
       <c r="G103" s="53" t="n"/>
     </row>
     <row r="104" ht="19.8" customHeight="1">
-      <c r="A104" s="43" t="n"/>
-      <c r="B104" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
+      <c r="A104" s="47" t="n"/>
+      <c r="B104" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C104" s="18" t="n"/>
       <c r="D104" s="19" t="n"/>
       <c r="E104" s="59" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F104" s="80" t="n"/>
       <c r="G104" s="53" t="n"/>
     </row>
     <row r="105" ht="19.8" customHeight="1">
-      <c r="A105" s="47" t="n"/>
-      <c r="B105" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C105" s="18" t="n"/>
-      <c r="D105" s="19" t="n"/>
+      <c r="A105" s="50" t="n"/>
+      <c r="B105" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D105" s="19" t="n">
+        <v>7.23</v>
+      </c>
       <c r="E105" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F105" s="80" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="F105" s="80" t="n">
+        <v>108.5</v>
+      </c>
       <c r="G105" s="53" t="n"/>
     </row>
     <row r="106" ht="19.8" customHeight="1">
-      <c r="A106" s="50" t="n"/>
-      <c r="B106" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C106" s="18" t="inlineStr">
+      <c r="A106" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B106" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C106" s="47" t="n"/>
+      <c r="D106" s="18" t="n"/>
+      <c r="E106" s="18" t="n"/>
+      <c r="F106" s="20" t="n"/>
+      <c r="G106" s="53" t="n"/>
+    </row>
+    <row r="107" ht="19.8" customHeight="1">
+      <c r="A107" s="43" t="n"/>
+      <c r="B107" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D106" s="19" t="n">
+      <c r="D107" s="19" t="n">
         <v>7.23</v>
       </c>
-      <c r="E106" s="59" t="n">
+      <c r="E107" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F107" s="80" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="G107" s="53" t="n"/>
+    </row>
+    <row r="108" ht="19.8" customHeight="1">
+      <c r="A108" s="50" t="n"/>
+      <c r="B108" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="n"/>
+      <c r="D108" s="24" t="n"/>
+      <c r="E108" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F106" s="80" t="n">
-        <v>108.5</v>
-      </c>
-      <c r="G106" s="53" t="n"/>
-    </row>
-    <row r="107" ht="19.8" customHeight="1">
-      <c r="A107" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B107" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C107" s="47" t="n"/>
-      <c r="D107" s="18" t="n"/>
-      <c r="E107" s="18" t="n"/>
-      <c r="F107" s="20" t="n"/>
-      <c r="G107" s="53" t="n"/>
-    </row>
-    <row r="108" ht="19.8" customHeight="1">
-      <c r="A108" s="43" t="n"/>
-      <c r="B108" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C108" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D108" s="19" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="E108" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F108" s="80" t="n">
-        <v>72.3</v>
-      </c>
+      <c r="F108" s="80" t="n"/>
       <c r="G108" s="53" t="n"/>
     </row>
     <row r="109" ht="19.8" customHeight="1">
-      <c r="A109" s="50" t="n"/>
-      <c r="B109" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C109" s="18" t="n"/>
-      <c r="D109" s="24" t="n"/>
-      <c r="E109" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F109" s="80" t="n"/>
+      <c r="A109" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B109" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C109" s="83" t="n"/>
+      <c r="D109" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E109" s="47" t="n"/>
+      <c r="F109" s="20" t="n"/>
       <c r="G109" s="53" t="n"/>
     </row>
     <row r="110" ht="19.8" customHeight="1">
-      <c r="A110" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B110" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C110" s="83" t="n"/>
-      <c r="D110" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E110" s="47" t="n"/>
-      <c r="F110" s="20" t="n"/>
+      <c r="A110" s="43" t="n"/>
+      <c r="B110" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="inlineStr">
+        <is>
+          <t>7.23 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D110" s="22" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="E110" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F110" s="80" t="n">
+        <v>130.1</v>
+      </c>
       <c r="G110" s="53" t="n"/>
     </row>
     <row r="111" ht="19.8" customHeight="1">
-      <c r="A111" s="43" t="n"/>
-      <c r="B111" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C111" s="18" t="inlineStr">
-        <is>
-          <t>7.23 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D111" s="22" t="n">
-        <v>21.69</v>
-      </c>
+      <c r="A111" s="47" t="n"/>
+      <c r="B111" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C111" s="18" t="n"/>
+      <c r="D111" s="19" t="n"/>
       <c r="E111" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F111" s="80" t="n">
-        <v>130.1</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F111" s="80" t="n"/>
       <c r="G111" s="53" t="n"/>
     </row>
     <row r="112" ht="19.8" customHeight="1">
-      <c r="A112" s="47" t="n"/>
-      <c r="B112" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
+      <c r="A112" s="50" t="n"/>
+      <c r="B112" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C112" s="18" t="n"/>
       <c r="D112" s="19" t="n"/>
       <c r="E112" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F112" s="80" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="F112" s="84" t="n"/>
       <c r="G112" s="53" t="n"/>
     </row>
     <row r="113" ht="19.8" customHeight="1">
-      <c r="A113" s="50" t="n"/>
-      <c r="B113" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C113" s="18" t="n"/>
-      <c r="D113" s="19" t="n"/>
-      <c r="E113" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F113" s="84" t="n"/>
+      <c r="A113" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B113" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C113" s="47" t="n"/>
+      <c r="D113" s="18" t="n"/>
+      <c r="E113" s="20" t="n"/>
+      <c r="F113" s="85" t="n">
+        <v>1135.7</v>
+      </c>
       <c r="G113" s="53" t="n"/>
     </row>
     <row r="114" ht="19.8" customHeight="1">
       <c r="A114" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B114" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C114" s="47" t="n"/>
-      <c r="D114" s="18" t="n"/>
-      <c r="E114" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C114" s="47" t="inlineStr">
+        <is>
+          <t>1135.70  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="n"/>
+      <c r="E114" s="14" t="n"/>
       <c r="F114" s="85" t="n">
-        <v>1217.5</v>
+        <v>1215.2</v>
       </c>
       <c r="G114" s="53" t="n"/>
     </row>
     <row r="115" ht="19.8" customHeight="1">
-      <c r="A115" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B115" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C115" s="47" t="inlineStr">
-        <is>
-          <t>1217.50  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A115" s="43" t="n"/>
+      <c r="B115" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="n"/>
       <c r="D115" s="12" t="n"/>
-      <c r="E115" s="14" t="n"/>
-      <c r="F115" s="85" t="n">
-        <v>1302.7</v>
-      </c>
+      <c r="E115" s="39" t="n"/>
+      <c r="F115" s="87" t="n"/>
       <c r="G115" s="53" t="n"/>
     </row>
     <row r="116" ht="19.8" customHeight="1">
-      <c r="A116" s="43" t="n"/>
-      <c r="B116" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C116" s="18" t="n"/>
+      <c r="A116" s="83" t="n"/>
+      <c r="B116" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C116" s="47" t="n"/>
       <c r="D116" s="12" t="n"/>
-      <c r="E116" s="39" t="n"/>
-      <c r="F116" s="87" t="n"/>
+      <c r="E116" s="14" t="n"/>
+      <c r="F116" s="85" t="n">
+        <v>1215.2</v>
+      </c>
       <c r="G116" s="53" t="n"/>
     </row>
     <row r="117" ht="19.8" customHeight="1">
-      <c r="A117" s="83" t="n"/>
-      <c r="B117" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C117" s="47" t="n"/>
+      <c r="A117" s="47" t="n"/>
+      <c r="B117" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C117" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D117" s="12" t="n"/>
-      <c r="E117" s="14" t="n"/>
-      <c r="F117" s="85" t="n">
-        <v>1302.7</v>
-      </c>
+      <c r="E117" s="39" t="n"/>
+      <c r="F117" s="61" t="n"/>
       <c r="G117" s="53" t="n"/>
     </row>
     <row r="118" ht="19.8" customHeight="1">
       <c r="A118" s="47" t="n"/>
-      <c r="B118" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C118" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B118" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C118" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D118" s="12" t="n"/>
       <c r="E118" s="39" t="n"/>
-      <c r="F118" s="61" t="n"/>
+      <c r="F118" s="20" t="n"/>
       <c r="G118" s="53" t="n"/>
     </row>
     <row r="119" ht="19.8" customHeight="1">
       <c r="A119" s="47" t="n"/>
       <c r="B119" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C119" s="19" t="n">
-        <v>274.4</v>
+          <t>Elementos necesarios</t>
+        </is>
+      </c>
+      <c r="C119" s="59" t="n">
+        <v>5</v>
       </c>
       <c r="D119" s="12" t="n"/>
       <c r="E119" s="39" t="n"/>
@@ -21972,11 +21964,11 @@
       <c r="A120" s="47" t="n"/>
       <c r="B120" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
+          <t>Ancho del radiador (cm)</t>
         </is>
       </c>
       <c r="C120" s="59" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D120" s="12" t="n"/>
       <c r="E120" s="39" t="n"/>
@@ -21984,14 +21976,16 @@
       <c r="G120" s="53" t="n"/>
     </row>
     <row r="121" ht="19.8" customHeight="1">
-      <c r="A121" s="47" t="n"/>
+      <c r="A121" s="50" t="n"/>
       <c r="B121" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
-        </is>
-      </c>
-      <c r="C121" s="59" t="n">
-        <v>40</v>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C121" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
       </c>
       <c r="D121" s="12" t="n"/>
       <c r="E121" s="39" t="n"/>
@@ -21999,145 +21993,151 @@
       <c r="G121" s="53" t="n"/>
     </row>
     <row r="122" ht="19.8" customHeight="1">
-      <c r="A122" s="50" t="n"/>
-      <c r="B122" s="60" t="inlineStr">
-        <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C122" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
-      </c>
-      <c r="D122" s="12" t="n"/>
-      <c r="E122" s="39" t="n"/>
-      <c r="F122" s="20" t="n"/>
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  Escalera   (PB)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="n"/>
+      <c r="C122" s="11" t="n"/>
+      <c r="D122" s="11" t="n"/>
+      <c r="E122" s="11" t="n"/>
+      <c r="F122" s="42" t="n"/>
       <c r="G122" s="53" t="n"/>
     </row>
-    <row r="123" ht="19.8" customHeight="1">
-      <c r="A123" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  Escalera   (PB)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B123" s="11" t="n"/>
-      <c r="C123" s="11" t="n"/>
-      <c r="D123" s="11" t="n"/>
-      <c r="E123" s="11" t="n"/>
-      <c r="F123" s="42" t="n"/>
+    <row r="123" ht="32" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G123" s="53" t="n"/>
     </row>
-    <row r="124" ht="32" customHeight="1">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="124" ht="19.8" customHeight="1">
+      <c r="A124" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B124" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C124" s="43" t="n"/>
+      <c r="D124" s="58" t="n"/>
+      <c r="E124" s="58" t="n"/>
+      <c r="F124" s="61" t="n"/>
       <c r="G124" s="53" t="n"/>
     </row>
     <row r="125" ht="19.8" customHeight="1">
-      <c r="A125" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B125" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C125" s="43" t="n"/>
-      <c r="D125" s="58" t="n"/>
-      <c r="E125" s="58" t="n"/>
-      <c r="F125" s="61" t="n"/>
+      <c r="A125" s="90" t="n"/>
+      <c r="B125" s="91" t="inlineStr">
+        <is>
+          <t>PF05</t>
+        </is>
+      </c>
+      <c r="C125" s="18" t="inlineStr">
+        <is>
+          <t>0.75 x 2.52</t>
+        </is>
+      </c>
+      <c r="D125" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E125" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F125" s="80" t="n">
+        <v>113.4</v>
+      </c>
       <c r="G125" s="53" t="n"/>
     </row>
     <row r="126" ht="19.8" customHeight="1">
-      <c r="A126" s="90" t="n"/>
-      <c r="B126" s="91" t="inlineStr">
-        <is>
-          <t>PF05</t>
-        </is>
-      </c>
-      <c r="C126" s="18" t="inlineStr">
-        <is>
-          <t>0.75 x 2.52</t>
-        </is>
-      </c>
-      <c r="D126" s="19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="E126" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F126" s="80" t="n">
-        <v>113.4</v>
-      </c>
+      <c r="A126" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B126" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C126" s="47" t="n"/>
+      <c r="D126" s="18" t="n"/>
+      <c r="E126" s="18" t="n"/>
+      <c r="F126" s="20" t="n"/>
       <c r="G126" s="53" t="n"/>
     </row>
     <row r="127" ht="19.8" customHeight="1">
-      <c r="A127" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B127" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C127" s="47" t="n"/>
-      <c r="D127" s="18" t="n"/>
-      <c r="E127" s="18" t="n"/>
-      <c r="F127" s="20" t="n"/>
+      <c r="A127" s="43" t="n"/>
+      <c r="B127" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C127" s="18" t="inlineStr">
+        <is>
+          <t>4.06 x 3.00</t>
+        </is>
+      </c>
+      <c r="D127" s="19" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="E127" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F127" s="80" t="n">
+        <v>243.6</v>
+      </c>
       <c r="G127" s="53" t="n"/>
     </row>
     <row r="128" ht="19.8" customHeight="1">
-      <c r="A128" s="43" t="n"/>
-      <c r="B128" s="79" t="inlineStr">
-        <is>
-          <t>AISLADAS</t>
+      <c r="A128" s="47" t="n"/>
+      <c r="B128" s="81" t="inlineStr">
+        <is>
+          <t>AISLADAS (SO)</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
         <is>
-          <t>4.06 x 3.00</t>
+          <t>1.73 x 3.00</t>
         </is>
       </c>
       <c r="D128" s="19" t="n">
-        <v>12.18</v>
+        <v>5.19</v>
       </c>
       <c r="E128" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F128" s="80" t="n">
-        <v>243.6</v>
+        <v>103.8</v>
       </c>
       <c r="G128" s="53" t="n"/>
     </row>
@@ -22145,488 +22145,488 @@
       <c r="A129" s="47" t="n"/>
       <c r="B129" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (SO)</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
+          <t>4.06 x 3.00</t>
+        </is>
+      </c>
+      <c r="D129" s="19" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="E129" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F129" s="80" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="G129" s="53" t="n"/>
+    </row>
+    <row r="130" ht="19.8" customHeight="1">
+      <c r="A130" s="50" t="n"/>
+      <c r="B130" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES (NE)</t>
+        </is>
+      </c>
+      <c r="C130" s="18" t="inlineStr">
+        <is>
           <t>1.73 x 3.00</t>
         </is>
       </c>
-      <c r="D129" s="19" t="n">
+      <c r="D130" s="19" t="n">
         <v>5.19</v>
-      </c>
-      <c r="E129" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F129" s="80" t="n">
-        <v>103.8</v>
-      </c>
-      <c r="G129" s="53" t="n"/>
-    </row>
-    <row r="130" ht="19.8" customHeight="1">
-      <c r="A130" s="47" t="n"/>
-      <c r="B130" s="81" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C130" s="18" t="inlineStr">
-        <is>
-          <t>4.06 x 3.00</t>
-        </is>
-      </c>
-      <c r="D130" s="19" t="n">
-        <v>12.18</v>
       </c>
       <c r="E130" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F130" s="80" t="n">
-        <v>304.5</v>
+        <v>129.8</v>
       </c>
       <c r="G130" s="53" t="n"/>
     </row>
     <row r="131" ht="19.8" customHeight="1">
-      <c r="A131" s="50" t="n"/>
-      <c r="B131" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES (NE)</t>
-        </is>
-      </c>
-      <c r="C131" s="18" t="inlineStr">
-        <is>
-          <t>1.73 x 3.00</t>
-        </is>
-      </c>
-      <c r="D131" s="19" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="E131" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F131" s="80" t="n">
-        <v>129.8</v>
-      </c>
+      <c r="A131" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B131" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C131" s="47" t="n"/>
+      <c r="D131" s="18" t="n"/>
+      <c r="E131" s="18" t="n"/>
+      <c r="F131" s="20" t="n"/>
       <c r="G131" s="53" t="n"/>
     </row>
     <row r="132" ht="19.8" customHeight="1">
-      <c r="A132" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B132" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C132" s="47" t="n"/>
-      <c r="D132" s="18" t="n"/>
-      <c r="E132" s="18" t="n"/>
-      <c r="F132" s="20" t="n"/>
+      <c r="A132" s="43" t="n"/>
+      <c r="B132" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="n"/>
+      <c r="D132" s="19" t="n"/>
+      <c r="E132" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F132" s="80" t="n"/>
       <c r="G132" s="53" t="n"/>
     </row>
     <row r="133" ht="19.8" customHeight="1">
-      <c r="A133" s="43" t="n"/>
-      <c r="B133" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
+      <c r="A133" s="47" t="n"/>
+      <c r="B133" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C133" s="18" t="n"/>
       <c r="D133" s="19" t="n"/>
       <c r="E133" s="59" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F133" s="80" t="n"/>
       <c r="G133" s="53" t="n"/>
     </row>
     <row r="134" ht="19.8" customHeight="1">
-      <c r="A134" s="47" t="n"/>
-      <c r="B134" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C134" s="18" t="n"/>
-      <c r="D134" s="19" t="n"/>
+      <c r="A134" s="50" t="n"/>
+      <c r="B134" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D134" s="19" t="n">
+        <v>7.02</v>
+      </c>
       <c r="E134" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F134" s="80" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="F134" s="80" t="n">
+        <v>105.3</v>
+      </c>
       <c r="G134" s="53" t="n"/>
     </row>
     <row r="135" ht="19.8" customHeight="1">
-      <c r="A135" s="50" t="n"/>
-      <c r="B135" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C135" s="18" t="inlineStr">
+      <c r="A135" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B135" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C135" s="47" t="n"/>
+      <c r="D135" s="18" t="n"/>
+      <c r="E135" s="18" t="n"/>
+      <c r="F135" s="20" t="n"/>
+      <c r="G135" s="53" t="n"/>
+    </row>
+    <row r="136" ht="19.8" customHeight="1">
+      <c r="A136" s="43" t="n"/>
+      <c r="B136" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C136" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D135" s="19" t="n">
+      <c r="D136" s="19" t="n">
         <v>7.02</v>
       </c>
-      <c r="E135" s="59" t="n">
+      <c r="E136" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F136" s="80" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="G136" s="53" t="n"/>
+    </row>
+    <row r="137" ht="19.8" customHeight="1">
+      <c r="A137" s="50" t="n"/>
+      <c r="B137" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C137" s="18" t="n"/>
+      <c r="D137" s="24" t="n"/>
+      <c r="E137" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F135" s="80" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="G135" s="53" t="n"/>
-    </row>
-    <row r="136" ht="19.8" customHeight="1">
-      <c r="A136" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B136" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C136" s="47" t="n"/>
-      <c r="D136" s="18" t="n"/>
-      <c r="E136" s="18" t="n"/>
-      <c r="F136" s="20" t="n"/>
-      <c r="G136" s="53" t="n"/>
-    </row>
-    <row r="137" ht="19.8" customHeight="1">
-      <c r="A137" s="43" t="n"/>
-      <c r="B137" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C137" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D137" s="19" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="E137" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F137" s="80" t="n">
-        <v>70.2</v>
-      </c>
+      <c r="F137" s="80" t="n"/>
       <c r="G137" s="53" t="n"/>
     </row>
     <row r="138" ht="19.8" customHeight="1">
-      <c r="A138" s="50" t="n"/>
-      <c r="B138" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C138" s="18" t="n"/>
-      <c r="D138" s="24" t="n"/>
-      <c r="E138" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F138" s="80" t="n"/>
+      <c r="A138" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B138" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C138" s="83" t="n"/>
+      <c r="D138" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E138" s="47" t="n"/>
+      <c r="F138" s="20" t="n"/>
       <c r="G138" s="53" t="n"/>
     </row>
     <row r="139" ht="19.8" customHeight="1">
-      <c r="A139" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B139" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C139" s="83" t="n"/>
-      <c r="D139" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E139" s="47" t="n"/>
-      <c r="F139" s="20" t="n"/>
+      <c r="A139" s="43" t="n"/>
+      <c r="B139" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C139" s="18" t="n"/>
+      <c r="D139" s="22" t="n"/>
+      <c r="E139" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F139" s="80" t="n"/>
       <c r="G139" s="53" t="n"/>
     </row>
     <row r="140" ht="19.8" customHeight="1">
-      <c r="A140" s="43" t="n"/>
-      <c r="B140" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C140" s="18" t="n"/>
-      <c r="D140" s="22" t="n"/>
+      <c r="A140" s="47" t="n"/>
+      <c r="B140" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C140" s="18" t="inlineStr">
+        <is>
+          <t>7.02 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D140" s="19" t="n">
+        <v>21.06</v>
+      </c>
       <c r="E140" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F140" s="80" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="F140" s="80" t="n">
+        <v>189.5</v>
+      </c>
       <c r="G140" s="53" t="n"/>
     </row>
     <row r="141" ht="19.8" customHeight="1">
-      <c r="A141" s="47" t="n"/>
-      <c r="B141" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C141" s="18" t="inlineStr">
-        <is>
-          <t>7.02 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D141" s="19" t="n">
-        <v>21.06</v>
-      </c>
+      <c r="A141" s="50" t="n"/>
+      <c r="B141" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C141" s="18" t="n"/>
+      <c r="D141" s="19" t="n"/>
       <c r="E141" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F141" s="80" t="n">
-        <v>189.5</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F141" s="84" t="n"/>
       <c r="G141" s="53" t="n"/>
     </row>
     <row r="142" ht="19.8" customHeight="1">
-      <c r="A142" s="50" t="n"/>
-      <c r="B142" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C142" s="18" t="n"/>
-      <c r="D142" s="19" t="n"/>
-      <c r="E142" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F142" s="84" t="n"/>
+      <c r="A142" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B142" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C142" s="47" t="n"/>
+      <c r="D142" s="18" t="n"/>
+      <c r="E142" s="20" t="n"/>
+      <c r="F142" s="85" t="n">
+        <v>1260.1</v>
+      </c>
       <c r="G142" s="53" t="n"/>
     </row>
     <row r="143" ht="19.8" customHeight="1">
       <c r="A143" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B143" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C143" s="47" t="n"/>
-      <c r="D143" s="18" t="n"/>
-      <c r="E143" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C143" s="47" t="inlineStr">
+        <is>
+          <t>1260.10  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="n"/>
+      <c r="E143" s="14" t="n"/>
       <c r="F143" s="85" t="n">
-        <v>1260.1</v>
+        <v>1348.3</v>
       </c>
       <c r="G143" s="53" t="n"/>
     </row>
     <row r="144" ht="19.8" customHeight="1">
-      <c r="A144" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B144" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C144" s="47" t="inlineStr">
-        <is>
-          <t>1260.10  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A144" s="43" t="n"/>
+      <c r="B144" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="n"/>
       <c r="D144" s="12" t="n"/>
-      <c r="E144" s="14" t="n"/>
-      <c r="F144" s="85" t="n">
+      <c r="E144" s="39" t="n"/>
+      <c r="F144" s="87" t="n"/>
+      <c r="G144" s="53" t="n"/>
+    </row>
+    <row r="145" ht="19.8" customHeight="1">
+      <c r="A145" s="83" t="n"/>
+      <c r="B145" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C145" s="47" t="n"/>
+      <c r="D145" s="12" t="n"/>
+      <c r="E145" s="14" t="n"/>
+      <c r="F145" s="85" t="n">
         <v>1348.3</v>
       </c>
-      <c r="G144" s="53" t="n"/>
-    </row>
-    <row r="145" ht="19.8" customHeight="1">
-      <c r="A145" s="43" t="n"/>
-      <c r="B145" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C145" s="18" t="n"/>
-      <c r="D145" s="12" t="n"/>
-      <c r="E145" s="39" t="n"/>
-      <c r="F145" s="87" t="n"/>
       <c r="G145" s="53" t="n"/>
     </row>
     <row r="146" ht="19.8" customHeight="1">
-      <c r="A146" s="83" t="n"/>
+      <c r="A146" s="89" t="n"/>
       <c r="B146" s="78" t="inlineStr">
         <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C146" s="47" t="n"/>
+          <t>SIN EMISOR</t>
+        </is>
+      </c>
+      <c r="C146" s="47" t="inlineStr">
+        <is>
+          <t>la cubre el radiador de 14 - Play room</t>
+        </is>
+      </c>
       <c r="D146" s="12" t="n"/>
-      <c r="E146" s="14" t="n"/>
-      <c r="F146" s="85" t="n">
-        <v>1348.3</v>
-      </c>
+      <c r="E146" s="39" t="n"/>
+      <c r="F146" s="61" t="n"/>
       <c r="G146" s="53" t="n"/>
     </row>
     <row r="147" ht="19.8" customHeight="1">
-      <c r="A147" s="89" t="n"/>
-      <c r="B147" s="78" t="inlineStr">
-        <is>
-          <t>SIN EMISOR</t>
-        </is>
-      </c>
-      <c r="C147" s="47" t="inlineStr">
-        <is>
-          <t>la cubre el radiador de 14 - Play room</t>
-        </is>
-      </c>
-      <c r="D147" s="12" t="n"/>
-      <c r="E147" s="39" t="n"/>
-      <c r="F147" s="61" t="n"/>
+      <c r="A147" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  09 - Dormitorio suite   (PB)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="n"/>
+      <c r="C147" s="11" t="n"/>
+      <c r="D147" s="11" t="n"/>
+      <c r="E147" s="11" t="n"/>
+      <c r="F147" s="42" t="n"/>
       <c r="G147" s="53" t="n"/>
     </row>
-    <row r="148" ht="19.8" customHeight="1">
-      <c r="A148" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  09 - Dormitorio suite   (PB)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="n"/>
-      <c r="C148" s="11" t="n"/>
-      <c r="D148" s="11" t="n"/>
-      <c r="E148" s="11" t="n"/>
-      <c r="F148" s="42" t="n"/>
+    <row r="148" ht="32" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G148" s="53" t="n"/>
     </row>
-    <row r="149" ht="32" customHeight="1">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="149" ht="19.8" customHeight="1">
+      <c r="A149" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B149" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C149" s="43" t="n"/>
+      <c r="D149" s="58" t="n"/>
+      <c r="E149" s="58" t="n"/>
+      <c r="F149" s="61" t="n"/>
       <c r="G149" s="53" t="n"/>
     </row>
     <row r="150" ht="19.8" customHeight="1">
-      <c r="A150" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B150" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C150" s="43" t="n"/>
-      <c r="D150" s="58" t="n"/>
-      <c r="E150" s="58" t="n"/>
-      <c r="F150" s="61" t="n"/>
+      <c r="A150" s="43" t="n"/>
+      <c r="B150" s="79" t="inlineStr">
+        <is>
+          <t>VA01</t>
+        </is>
+      </c>
+      <c r="C150" s="18" t="inlineStr">
+        <is>
+          <t>0.75 x 3.00</t>
+        </is>
+      </c>
+      <c r="D150" s="19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E150" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F150" s="80" t="n">
+        <v>135</v>
+      </c>
       <c r="G150" s="53" t="n"/>
     </row>
     <row r="151" ht="19.8" customHeight="1">
-      <c r="A151" s="43" t="n"/>
-      <c r="B151" s="79" t="inlineStr">
-        <is>
-          <t>VA01</t>
+      <c r="A151" s="50" t="n"/>
+      <c r="B151" s="82" t="inlineStr">
+        <is>
+          <t>PV03</t>
         </is>
       </c>
       <c r="C151" s="18" t="inlineStr">
         <is>
-          <t>0.75 x 3.00</t>
+          <t>1.76 x 3.00</t>
         </is>
       </c>
       <c r="D151" s="19" t="n">
-        <v>2.25</v>
+        <v>5.28</v>
       </c>
       <c r="E151" s="59" t="n">
         <v>60</v>
       </c>
       <c r="F151" s="80" t="n">
-        <v>135</v>
+        <v>316.8</v>
       </c>
       <c r="G151" s="53" t="n"/>
     </row>
     <row r="152" ht="19.8" customHeight="1">
-      <c r="A152" s="50" t="n"/>
-      <c r="B152" s="82" t="inlineStr">
-        <is>
-          <t>PV03</t>
-        </is>
-      </c>
-      <c r="C152" s="18" t="inlineStr">
-        <is>
-          <t>1.76 x 3.00</t>
-        </is>
-      </c>
-      <c r="D152" s="19" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="E152" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F152" s="80" t="n">
-        <v>316.8</v>
-      </c>
+      <c r="A152" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B152" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C152" s="47" t="n"/>
+      <c r="D152" s="18" t="n"/>
+      <c r="E152" s="18" t="n"/>
+      <c r="F152" s="20" t="n"/>
       <c r="G152" s="53" t="n"/>
     </row>
     <row r="153" ht="19.8" customHeight="1">
-      <c r="A153" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B153" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C153" s="47" t="n"/>
-      <c r="D153" s="18" t="n"/>
-      <c r="E153" s="18" t="n"/>
-      <c r="F153" s="20" t="n"/>
+      <c r="A153" s="43" t="n"/>
+      <c r="B153" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS (NE)</t>
+        </is>
+      </c>
+      <c r="C153" s="18" t="inlineStr">
+        <is>
+          <t>3.50 x 3.00</t>
+        </is>
+      </c>
+      <c r="D153" s="19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E153" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F153" s="80" t="n">
+        <v>210</v>
+      </c>
       <c r="G153" s="53" t="n"/>
     </row>
     <row r="154" ht="19.8" customHeight="1">
-      <c r="A154" s="43" t="n"/>
-      <c r="B154" s="79" t="inlineStr">
-        <is>
-          <t>AISLADAS (NE)</t>
+      <c r="A154" s="47" t="n"/>
+      <c r="B154" s="81" t="inlineStr">
+        <is>
+          <t>AISLADAS (SO)</t>
         </is>
       </c>
       <c r="C154" s="18" t="inlineStr">
@@ -22649,7 +22649,7 @@
       <c r="A155" s="47" t="n"/>
       <c r="B155" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (SO)</t>
+          <t>AISLADAS (SE)</t>
         </is>
       </c>
       <c r="C155" s="18" t="inlineStr">
@@ -22672,7 +22672,7 @@
       <c r="A156" s="47" t="n"/>
       <c r="B156" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (SE)</t>
+          <t>INTERIORES (NO)</t>
         </is>
       </c>
       <c r="C156" s="18" t="inlineStr">
@@ -22684,346 +22684,338 @@
         <v>10.5</v>
       </c>
       <c r="E156" s="59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F156" s="80" t="n">
-        <v>210</v>
+        <v>262.5</v>
       </c>
       <c r="G156" s="53" t="n"/>
     </row>
     <row r="157" ht="19.8" customHeight="1">
-      <c r="A157" s="47" t="n"/>
-      <c r="B157" s="81" t="inlineStr">
-        <is>
-          <t>INTERIORES (NO)</t>
-        </is>
-      </c>
-      <c r="C157" s="18" t="inlineStr">
-        <is>
-          <t>3.50 x 3.00</t>
-        </is>
-      </c>
-      <c r="D157" s="19" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="A157" s="50" t="n"/>
+      <c r="B157" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C157" s="18" t="n"/>
+      <c r="D157" s="19" t="n"/>
       <c r="E157" s="59" t="n">
         <v>25</v>
       </c>
-      <c r="F157" s="80" t="n">
-        <v>262.5</v>
-      </c>
+      <c r="F157" s="80" t="n"/>
       <c r="G157" s="53" t="n"/>
     </row>
     <row r="158" ht="19.8" customHeight="1">
-      <c r="A158" s="50" t="n"/>
-      <c r="B158" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C158" s="18" t="n"/>
-      <c r="D158" s="19" t="n"/>
-      <c r="E158" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F158" s="80" t="n"/>
+      <c r="A158" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B158" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C158" s="47" t="n"/>
+      <c r="D158" s="18" t="n"/>
+      <c r="E158" s="18" t="n"/>
+      <c r="F158" s="20" t="n"/>
       <c r="G158" s="53" t="n"/>
     </row>
     <row r="159" ht="19.8" customHeight="1">
-      <c r="A159" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B159" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C159" s="47" t="n"/>
-      <c r="D159" s="18" t="n"/>
-      <c r="E159" s="18" t="n"/>
-      <c r="F159" s="20" t="n"/>
+      <c r="A159" s="43" t="n"/>
+      <c r="B159" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="n"/>
+      <c r="D159" s="19" t="n"/>
+      <c r="E159" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F159" s="80" t="n"/>
       <c r="G159" s="53" t="n"/>
     </row>
     <row r="160" ht="19.8" customHeight="1">
-      <c r="A160" s="43" t="n"/>
-      <c r="B160" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
+      <c r="A160" s="47" t="n"/>
+      <c r="B160" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C160" s="18" t="n"/>
       <c r="D160" s="19" t="n"/>
       <c r="E160" s="59" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F160" s="80" t="n"/>
       <c r="G160" s="53" t="n"/>
     </row>
     <row r="161" ht="19.8" customHeight="1">
-      <c r="A161" s="47" t="n"/>
-      <c r="B161" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C161" s="18" t="n"/>
-      <c r="D161" s="19" t="n"/>
+      <c r="A161" s="50" t="n"/>
+      <c r="B161" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C161" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D161" s="19" t="n">
+        <v>12.25</v>
+      </c>
       <c r="E161" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F161" s="80" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="F161" s="80" t="n">
+        <v>183.8</v>
+      </c>
       <c r="G161" s="53" t="n"/>
     </row>
     <row r="162" ht="19.8" customHeight="1">
-      <c r="A162" s="50" t="n"/>
-      <c r="B162" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C162" s="18" t="inlineStr">
+      <c r="A162" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B162" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C162" s="47" t="n"/>
+      <c r="D162" s="18" t="n"/>
+      <c r="E162" s="18" t="n"/>
+      <c r="F162" s="20" t="n"/>
+      <c r="G162" s="53" t="n"/>
+    </row>
+    <row r="163" ht="19.8" customHeight="1">
+      <c r="A163" s="43" t="n"/>
+      <c r="B163" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C163" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D162" s="19" t="n">
+      <c r="D163" s="19" t="n">
         <v>12.25</v>
       </c>
-      <c r="E162" s="59" t="n">
+      <c r="E163" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F163" s="80" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="G163" s="53" t="n"/>
+    </row>
+    <row r="164" ht="19.8" customHeight="1">
+      <c r="A164" s="50" t="n"/>
+      <c r="B164" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C164" s="18" t="n"/>
+      <c r="D164" s="24" t="n"/>
+      <c r="E164" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F162" s="80" t="n">
-        <v>183.8</v>
-      </c>
-      <c r="G162" s="53" t="n"/>
-    </row>
-    <row r="163" ht="19.8" customHeight="1">
-      <c r="A163" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B163" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C163" s="47" t="n"/>
-      <c r="D163" s="18" t="n"/>
-      <c r="E163" s="18" t="n"/>
-      <c r="F163" s="20" t="n"/>
-      <c r="G163" s="53" t="n"/>
-    </row>
-    <row r="164" ht="19.8" customHeight="1">
-      <c r="A164" s="43" t="n"/>
-      <c r="B164" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C164" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D164" s="19" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="E164" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F164" s="80" t="n">
-        <v>122.5</v>
-      </c>
+      <c r="F164" s="80" t="n"/>
       <c r="G164" s="53" t="n"/>
     </row>
     <row r="165" ht="19.8" customHeight="1">
-      <c r="A165" s="50" t="n"/>
-      <c r="B165" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C165" s="18" t="n"/>
-      <c r="D165" s="24" t="n"/>
-      <c r="E165" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F165" s="80" t="n"/>
+      <c r="A165" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B165" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C165" s="83" t="n"/>
+      <c r="D165" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E165" s="47" t="n"/>
+      <c r="F165" s="20" t="n"/>
       <c r="G165" s="53" t="n"/>
     </row>
     <row r="166" ht="19.8" customHeight="1">
-      <c r="A166" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B166" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C166" s="83" t="n"/>
-      <c r="D166" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E166" s="47" t="n"/>
-      <c r="F166" s="20" t="n"/>
+      <c r="A166" s="43" t="n"/>
+      <c r="B166" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C166" s="18" t="n"/>
+      <c r="D166" s="22" t="n"/>
+      <c r="E166" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F166" s="80" t="n"/>
       <c r="G166" s="53" t="n"/>
     </row>
     <row r="167" ht="19.8" customHeight="1">
-      <c r="A167" s="43" t="n"/>
-      <c r="B167" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
+      <c r="A167" s="47" t="n"/>
+      <c r="B167" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C167" s="18" t="n"/>
-      <c r="D167" s="22" t="n"/>
+      <c r="D167" s="19" t="n"/>
       <c r="E167" s="59" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F167" s="80" t="n"/>
       <c r="G167" s="53" t="n"/>
     </row>
     <row r="168" ht="19.8" customHeight="1">
-      <c r="A168" s="47" t="n"/>
-      <c r="B168" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C168" s="18" t="n"/>
-      <c r="D168" s="19" t="n"/>
+      <c r="A168" s="50" t="n"/>
+      <c r="B168" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C168" s="18" t="inlineStr">
+        <is>
+          <t>12.25 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D168" s="19" t="n">
+        <v>36.75</v>
+      </c>
       <c r="E168" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F168" s="80" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="F168" s="84" t="n">
+        <v>441</v>
+      </c>
       <c r="G168" s="53" t="n"/>
     </row>
     <row r="169" ht="19.8" customHeight="1">
-      <c r="A169" s="50" t="n"/>
-      <c r="B169" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C169" s="18" t="inlineStr">
-        <is>
-          <t>12.25 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D169" s="19" t="n">
-        <v>36.75</v>
-      </c>
-      <c r="E169" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F169" s="84" t="n">
-        <v>441</v>
+      <c r="A169" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B169" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C169" s="47" t="n"/>
+      <c r="D169" s="18" t="n"/>
+      <c r="E169" s="20" t="n"/>
+      <c r="F169" s="85" t="n">
+        <v>2091.6</v>
       </c>
       <c r="G169" s="53" t="n"/>
     </row>
     <row r="170" ht="19.8" customHeight="1">
       <c r="A170" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B170" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C170" s="47" t="n"/>
-      <c r="D170" s="18" t="n"/>
-      <c r="E170" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C170" s="47" t="inlineStr">
+        <is>
+          <t>2091.60  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D170" s="12" t="n"/>
+      <c r="E170" s="14" t="n"/>
       <c r="F170" s="85" t="n">
-        <v>2091.6</v>
+        <v>2238</v>
       </c>
       <c r="G170" s="53" t="n"/>
     </row>
     <row r="171" ht="19.8" customHeight="1">
-      <c r="A171" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B171" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C171" s="47" t="inlineStr">
-        <is>
-          <t>2091.60  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A171" s="43" t="n"/>
+      <c r="B171" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="n"/>
       <c r="D171" s="12" t="n"/>
-      <c r="E171" s="14" t="n"/>
-      <c r="F171" s="85" t="n">
+      <c r="E171" s="39" t="n"/>
+      <c r="F171" s="87" t="n"/>
+      <c r="G171" s="53" t="n"/>
+    </row>
+    <row r="172" ht="19.8" customHeight="1">
+      <c r="A172" s="83" t="n"/>
+      <c r="B172" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C172" s="47" t="n"/>
+      <c r="D172" s="12" t="n"/>
+      <c r="E172" s="14" t="n"/>
+      <c r="F172" s="85" t="n">
         <v>2238</v>
       </c>
-      <c r="G171" s="53" t="n"/>
-    </row>
-    <row r="172" ht="19.8" customHeight="1">
-      <c r="A172" s="43" t="n"/>
-      <c r="B172" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C172" s="18" t="n"/>
-      <c r="D172" s="12" t="n"/>
-      <c r="E172" s="39" t="n"/>
-      <c r="F172" s="87" t="n"/>
       <c r="G172" s="53" t="n"/>
     </row>
     <row r="173" ht="19.8" customHeight="1">
-      <c r="A173" s="83" t="n"/>
-      <c r="B173" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C173" s="47" t="n"/>
+      <c r="A173" s="47" t="n"/>
+      <c r="B173" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C173" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D173" s="12" t="n"/>
-      <c r="E173" s="14" t="n"/>
-      <c r="F173" s="85" t="n">
-        <v>2238</v>
-      </c>
+      <c r="E173" s="39" t="n"/>
+      <c r="F173" s="61" t="n"/>
       <c r="G173" s="53" t="n"/>
     </row>
     <row r="174" ht="19.8" customHeight="1">
       <c r="A174" s="47" t="n"/>
-      <c r="B174" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C174" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B174" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C174" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D174" s="12" t="n"/>
       <c r="E174" s="39" t="n"/>
-      <c r="F174" s="61" t="n"/>
+      <c r="F174" s="20" t="n"/>
       <c r="G174" s="53" t="n"/>
     </row>
     <row r="175" ht="19.8" customHeight="1">
       <c r="A175" s="47" t="n"/>
       <c r="B175" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C175" s="19" t="n">
-        <v>274.4</v>
+          <t>Elementos necesarios</t>
+        </is>
+      </c>
+      <c r="C175" s="59" t="n">
+        <v>9</v>
       </c>
       <c r="D175" s="12" t="n"/>
       <c r="E175" s="39" t="n"/>
@@ -23034,11 +23026,11 @@
       <c r="A176" s="47" t="n"/>
       <c r="B176" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
+          <t>Ancho del radiador (cm)</t>
         </is>
       </c>
       <c r="C176" s="59" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="D176" s="12" t="n"/>
       <c r="E176" s="39" t="n"/>
@@ -23046,14 +23038,16 @@
       <c r="G176" s="53" t="n"/>
     </row>
     <row r="177" ht="19.8" customHeight="1">
-      <c r="A177" s="47" t="n"/>
+      <c r="A177" s="50" t="n"/>
       <c r="B177" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
-        </is>
-      </c>
-      <c r="C177" s="59" t="n">
-        <v>72</v>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C177" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
       </c>
       <c r="D177" s="12" t="n"/>
       <c r="E177" s="39" t="n"/>
@@ -23061,527 +23055,525 @@
       <c r="G177" s="53" t="n"/>
     </row>
     <row r="178" ht="19.8" customHeight="1">
-      <c r="A178" s="50" t="n"/>
-      <c r="B178" s="60" t="inlineStr">
-        <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C178" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
-      </c>
-      <c r="D178" s="12" t="n"/>
-      <c r="E178" s="39" t="n"/>
-      <c r="F178" s="20" t="n"/>
+      <c r="A178" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  10 - Bano suite   (PB)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B178" s="11" t="n"/>
+      <c r="C178" s="11" t="n"/>
+      <c r="D178" s="11" t="n"/>
+      <c r="E178" s="11" t="n"/>
+      <c r="F178" s="42" t="n"/>
       <c r="G178" s="53" t="n"/>
     </row>
-    <row r="179" ht="19.8" customHeight="1">
-      <c r="A179" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  10 - Bano suite   (PB)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B179" s="11" t="n"/>
-      <c r="C179" s="11" t="n"/>
-      <c r="D179" s="11" t="n"/>
-      <c r="E179" s="11" t="n"/>
-      <c r="F179" s="42" t="n"/>
+    <row r="179" ht="32" customHeight="1">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G179" s="53" t="n"/>
     </row>
-    <row r="180" ht="32" customHeight="1">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F180" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="180" ht="19.8" customHeight="1">
+      <c r="A180" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B180" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C180" s="43" t="n"/>
+      <c r="D180" s="58" t="n"/>
+      <c r="E180" s="58" t="n"/>
+      <c r="F180" s="61" t="n"/>
       <c r="G180" s="53" t="n"/>
     </row>
     <row r="181" ht="19.8" customHeight="1">
-      <c r="A181" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B181" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C181" s="43" t="n"/>
-      <c r="D181" s="58" t="n"/>
-      <c r="E181" s="58" t="n"/>
-      <c r="F181" s="61" t="n"/>
+      <c r="A181" s="90" t="n"/>
+      <c r="B181" s="91" t="inlineStr">
+        <is>
+          <t>VA02</t>
+        </is>
+      </c>
+      <c r="C181" s="18" t="inlineStr">
+        <is>
+          <t>0.75 x 2.15</t>
+        </is>
+      </c>
+      <c r="D181" s="19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="E181" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F181" s="80" t="n">
+        <v>96.59999999999999</v>
+      </c>
       <c r="G181" s="53" t="n"/>
     </row>
     <row r="182" ht="19.8" customHeight="1">
-      <c r="A182" s="90" t="n"/>
-      <c r="B182" s="91" t="inlineStr">
-        <is>
-          <t>VA02</t>
-        </is>
-      </c>
-      <c r="C182" s="18" t="inlineStr">
-        <is>
-          <t>0.75 x 2.15</t>
-        </is>
-      </c>
-      <c r="D182" s="19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="E182" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F182" s="80" t="n">
-        <v>96.59999999999999</v>
-      </c>
+      <c r="A182" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B182" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C182" s="47" t="n"/>
+      <c r="D182" s="18" t="n"/>
+      <c r="E182" s="18" t="n"/>
+      <c r="F182" s="20" t="n"/>
       <c r="G182" s="53" t="n"/>
     </row>
     <row r="183" ht="19.8" customHeight="1">
-      <c r="A183" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B183" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C183" s="47" t="n"/>
-      <c r="D183" s="18" t="n"/>
-      <c r="E183" s="18" t="n"/>
-      <c r="F183" s="20" t="n"/>
+      <c r="A183" s="43" t="n"/>
+      <c r="B183" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS (NE)</t>
+        </is>
+      </c>
+      <c r="C183" s="18" t="inlineStr">
+        <is>
+          <t>3.38 x 3.00</t>
+        </is>
+      </c>
+      <c r="D183" s="19" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="E183" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F183" s="80" t="n">
+        <v>202.8</v>
+      </c>
       <c r="G183" s="53" t="n"/>
     </row>
     <row r="184" ht="19.8" customHeight="1">
-      <c r="A184" s="43" t="n"/>
-      <c r="B184" s="79" t="inlineStr">
-        <is>
-          <t>AISLADAS (NE)</t>
-        </is>
-      </c>
-      <c r="C184" s="18" t="inlineStr">
-        <is>
-          <t>3.38 x 3.00</t>
-        </is>
-      </c>
-      <c r="D184" s="19" t="n">
-        <v>10.14</v>
-      </c>
+      <c r="A184" s="47" t="n"/>
+      <c r="B184" s="81" t="inlineStr">
+        <is>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C184" s="18" t="n"/>
+      <c r="D184" s="19" t="n"/>
       <c r="E184" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F184" s="80" t="n">
-        <v>202.8</v>
-      </c>
+      <c r="F184" s="80" t="n"/>
       <c r="G184" s="53" t="n"/>
     </row>
     <row r="185" ht="19.8" customHeight="1">
       <c r="A185" s="47" t="n"/>
       <c r="B185" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C185" s="18" t="n"/>
-      <c r="D185" s="19" t="n"/>
+          <t>INTERIORES (NO, bano visitas)</t>
+        </is>
+      </c>
+      <c r="C185" s="18" t="inlineStr">
+        <is>
+          <t>1.72 x 3.00</t>
+        </is>
+      </c>
+      <c r="D185" s="19" t="n">
+        <v>5.16</v>
+      </c>
       <c r="E185" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F185" s="80" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="F185" s="80" t="n">
+        <v>129</v>
+      </c>
       <c r="G185" s="53" t="n"/>
     </row>
     <row r="186" ht="19.8" customHeight="1">
       <c r="A186" s="47" t="n"/>
       <c r="B186" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (NO, bano visitas)</t>
+          <t>INTERIORES (SO)</t>
         </is>
       </c>
       <c r="C186" s="18" t="inlineStr">
         <is>
-          <t>1.72 x 3.00</t>
+          <t>3.38 x 3.00</t>
         </is>
       </c>
       <c r="D186" s="19" t="n">
-        <v>5.16</v>
+        <v>10.14</v>
       </c>
       <c r="E186" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F186" s="80" t="n">
-        <v>129</v>
+        <v>253.5</v>
       </c>
       <c r="G186" s="53" t="n"/>
     </row>
     <row r="187" ht="19.8" customHeight="1">
-      <c r="A187" s="47" t="n"/>
-      <c r="B187" s="81" t="inlineStr">
-        <is>
-          <t>INTERIORES (SO)</t>
+      <c r="A187" s="50" t="n"/>
+      <c r="B187" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES (SE, dormitorio suite)</t>
         </is>
       </c>
       <c r="C187" s="18" t="inlineStr">
         <is>
-          <t>3.38 x 3.00</t>
+          <t>1.72 x 3.00</t>
         </is>
       </c>
       <c r="D187" s="19" t="n">
-        <v>10.14</v>
+        <v>5.16</v>
       </c>
       <c r="E187" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F187" s="80" t="n">
-        <v>253.5</v>
+        <v>129</v>
       </c>
       <c r="G187" s="53" t="n"/>
     </row>
     <row r="188" ht="19.8" customHeight="1">
-      <c r="A188" s="50" t="n"/>
-      <c r="B188" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES (SE, dormitorio suite)</t>
-        </is>
-      </c>
-      <c r="C188" s="18" t="inlineStr">
-        <is>
-          <t>1.72 x 3.00</t>
-        </is>
-      </c>
-      <c r="D188" s="19" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="E188" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F188" s="80" t="n">
-        <v>129</v>
-      </c>
+      <c r="A188" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B188" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C188" s="47" t="n"/>
+      <c r="D188" s="18" t="n"/>
+      <c r="E188" s="18" t="n"/>
+      <c r="F188" s="20" t="n"/>
       <c r="G188" s="53" t="n"/>
     </row>
     <row r="189" ht="19.8" customHeight="1">
-      <c r="A189" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B189" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C189" s="47" t="n"/>
-      <c r="D189" s="18" t="n"/>
-      <c r="E189" s="18" t="n"/>
-      <c r="F189" s="20" t="n"/>
+      <c r="A189" s="43" t="n"/>
+      <c r="B189" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C189" s="18" t="n"/>
+      <c r="D189" s="19" t="n"/>
+      <c r="E189" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F189" s="80" t="n"/>
       <c r="G189" s="53" t="n"/>
     </row>
     <row r="190" ht="19.8" customHeight="1">
-      <c r="A190" s="43" t="n"/>
-      <c r="B190" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
+      <c r="A190" s="47" t="n"/>
+      <c r="B190" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C190" s="18" t="n"/>
       <c r="D190" s="19" t="n"/>
       <c r="E190" s="59" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F190" s="80" t="n"/>
       <c r="G190" s="53" t="n"/>
     </row>
     <row r="191" ht="19.8" customHeight="1">
-      <c r="A191" s="47" t="n"/>
-      <c r="B191" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C191" s="18" t="n"/>
-      <c r="D191" s="19" t="n"/>
+      <c r="A191" s="50" t="n"/>
+      <c r="B191" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C191" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D191" s="19" t="n">
+        <v>5.81</v>
+      </c>
       <c r="E191" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F191" s="80" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="F191" s="80" t="n">
+        <v>87.2</v>
+      </c>
       <c r="G191" s="53" t="n"/>
     </row>
     <row r="192" ht="19.8" customHeight="1">
-      <c r="A192" s="50" t="n"/>
-      <c r="B192" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C192" s="18" t="inlineStr">
+      <c r="A192" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B192" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C192" s="47" t="n"/>
+      <c r="D192" s="18" t="n"/>
+      <c r="E192" s="18" t="n"/>
+      <c r="F192" s="20" t="n"/>
+      <c r="G192" s="53" t="n"/>
+    </row>
+    <row r="193" ht="19.8" customHeight="1">
+      <c r="A193" s="43" t="n"/>
+      <c r="B193" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C193" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D192" s="19" t="n">
+      <c r="D193" s="19" t="n">
         <v>5.81</v>
       </c>
-      <c r="E192" s="59" t="n">
+      <c r="E193" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F193" s="80" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="G193" s="53" t="n"/>
+    </row>
+    <row r="194" ht="19.8" customHeight="1">
+      <c r="A194" s="50" t="n"/>
+      <c r="B194" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C194" s="18" t="n"/>
+      <c r="D194" s="24" t="n"/>
+      <c r="E194" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F192" s="80" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="G192" s="53" t="n"/>
-    </row>
-    <row r="193" ht="19.8" customHeight="1">
-      <c r="A193" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B193" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C193" s="47" t="n"/>
-      <c r="D193" s="18" t="n"/>
-      <c r="E193" s="18" t="n"/>
-      <c r="F193" s="20" t="n"/>
-      <c r="G193" s="53" t="n"/>
-    </row>
-    <row r="194" ht="19.8" customHeight="1">
-      <c r="A194" s="43" t="n"/>
-      <c r="B194" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C194" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D194" s="19" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="E194" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F194" s="80" t="n">
-        <v>58.1</v>
-      </c>
+      <c r="F194" s="80" t="n"/>
       <c r="G194" s="53" t="n"/>
     </row>
     <row r="195" ht="19.8" customHeight="1">
-      <c r="A195" s="50" t="n"/>
-      <c r="B195" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C195" s="18" t="n"/>
-      <c r="D195" s="24" t="n"/>
-      <c r="E195" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F195" s="80" t="n"/>
+      <c r="A195" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B195" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C195" s="83" t="n"/>
+      <c r="D195" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E195" s="47" t="n"/>
+      <c r="F195" s="20" t="n"/>
       <c r="G195" s="53" t="n"/>
     </row>
     <row r="196" ht="19.8" customHeight="1">
-      <c r="A196" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B196" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C196" s="83" t="n"/>
-      <c r="D196" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E196" s="47" t="n"/>
-      <c r="F196" s="20" t="n"/>
+      <c r="A196" s="43" t="n"/>
+      <c r="B196" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C196" s="18" t="inlineStr">
+        <is>
+          <t>5.81 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D196" s="22" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="E196" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F196" s="80" t="n">
+        <v>104.6</v>
+      </c>
       <c r="G196" s="53" t="n"/>
     </row>
     <row r="197" ht="19.8" customHeight="1">
-      <c r="A197" s="43" t="n"/>
-      <c r="B197" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C197" s="18" t="inlineStr">
-        <is>
-          <t>5.81 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D197" s="22" t="n">
-        <v>17.43</v>
-      </c>
+      <c r="A197" s="47" t="n"/>
+      <c r="B197" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C197" s="18" t="n"/>
+      <c r="D197" s="19" t="n"/>
       <c r="E197" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F197" s="80" t="n">
-        <v>104.6</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F197" s="80" t="n"/>
       <c r="G197" s="53" t="n"/>
     </row>
     <row r="198" ht="19.8" customHeight="1">
-      <c r="A198" s="47" t="n"/>
-      <c r="B198" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
+      <c r="A198" s="50" t="n"/>
+      <c r="B198" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C198" s="18" t="n"/>
       <c r="D198" s="19" t="n"/>
       <c r="E198" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F198" s="80" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="F198" s="84" t="n"/>
       <c r="G198" s="53" t="n"/>
     </row>
     <row r="199" ht="19.8" customHeight="1">
-      <c r="A199" s="50" t="n"/>
-      <c r="B199" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C199" s="18" t="n"/>
-      <c r="D199" s="19" t="n"/>
-      <c r="E199" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F199" s="84" t="n"/>
+      <c r="A199" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B199" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C199" s="47" t="n"/>
+      <c r="D199" s="18" t="n"/>
+      <c r="E199" s="20" t="n"/>
+      <c r="F199" s="85" t="n">
+        <v>1060.8</v>
+      </c>
       <c r="G199" s="53" t="n"/>
     </row>
     <row r="200" ht="19.8" customHeight="1">
       <c r="A200" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B200" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C200" s="47" t="n"/>
-      <c r="D200" s="18" t="n"/>
-      <c r="E200" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C200" s="47" t="inlineStr">
+        <is>
+          <t>1060.80  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D200" s="12" t="n"/>
+      <c r="E200" s="14" t="n"/>
       <c r="F200" s="85" t="n">
-        <v>1060.8</v>
+        <v>1135.1</v>
       </c>
       <c r="G200" s="53" t="n"/>
     </row>
     <row r="201" ht="19.8" customHeight="1">
-      <c r="A201" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B201" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C201" s="47" t="inlineStr">
-        <is>
-          <t>1060.80  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A201" s="43" t="n"/>
+      <c r="B201" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C201" s="18" t="n"/>
       <c r="D201" s="12" t="n"/>
-      <c r="E201" s="14" t="n"/>
-      <c r="F201" s="85" t="n">
+      <c r="E201" s="39" t="n"/>
+      <c r="F201" s="87" t="n"/>
+      <c r="G201" s="53" t="n"/>
+    </row>
+    <row r="202" ht="19.8" customHeight="1">
+      <c r="A202" s="83" t="n"/>
+      <c r="B202" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C202" s="47" t="n"/>
+      <c r="D202" s="12" t="n"/>
+      <c r="E202" s="14" t="n"/>
+      <c r="F202" s="85" t="n">
         <v>1135.1</v>
       </c>
-      <c r="G201" s="53" t="n"/>
-    </row>
-    <row r="202" ht="19.8" customHeight="1">
-      <c r="A202" s="43" t="n"/>
-      <c r="B202" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C202" s="18" t="n"/>
-      <c r="D202" s="12" t="n"/>
-      <c r="E202" s="39" t="n"/>
-      <c r="F202" s="87" t="n"/>
       <c r="G202" s="53" t="n"/>
     </row>
     <row r="203" ht="19.8" customHeight="1">
-      <c r="A203" s="83" t="n"/>
-      <c r="B203" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C203" s="47" t="n"/>
+      <c r="A203" s="47" t="n"/>
+      <c r="B203" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C203" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D203" s="12" t="n"/>
-      <c r="E203" s="14" t="n"/>
-      <c r="F203" s="85" t="n">
-        <v>1135.1</v>
-      </c>
+      <c r="E203" s="39" t="n"/>
+      <c r="F203" s="61" t="n"/>
       <c r="G203" s="53" t="n"/>
     </row>
     <row r="204" ht="19.8" customHeight="1">
       <c r="A204" s="47" t="n"/>
-      <c r="B204" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C204" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B204" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
+        </is>
+      </c>
+      <c r="C204" s="59" t="n">
+        <v>708</v>
       </c>
       <c r="D204" s="12" t="n"/>
       <c r="E204" s="39" t="n"/>
-      <c r="F204" s="61" t="n"/>
+      <c r="F204" s="20" t="n"/>
       <c r="G204" s="53" t="n"/>
     </row>
     <row r="205" ht="19.8" customHeight="1">
       <c r="A205" s="47" t="n"/>
       <c r="B205" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 80</t>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
         </is>
       </c>
       <c r="C205" s="59" t="n">
-        <v>708</v>
+        <v>1315</v>
       </c>
       <c r="D205" s="12" t="n"/>
       <c r="E205" s="39" t="n"/>
@@ -23592,11 +23584,11 @@
       <c r="A206" s="47" t="n"/>
       <c r="B206" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 150</t>
+          <t>Toalleros necesarios</t>
         </is>
       </c>
       <c r="C206" s="59" t="n">
-        <v>1315</v>
+        <v>1</v>
       </c>
       <c r="D206" s="12" t="n"/>
       <c r="E206" s="39" t="n"/>
@@ -23604,14 +23596,16 @@
       <c r="G206" s="53" t="n"/>
     </row>
     <row r="207" ht="19.8" customHeight="1">
-      <c r="A207" s="47" t="n"/>
+      <c r="A207" s="50" t="n"/>
       <c r="B207" s="60" t="inlineStr">
         <is>
-          <t>Toalleros necesarios</t>
-        </is>
-      </c>
-      <c r="C207" s="59" t="n">
-        <v>1</v>
+          <t>Toallero adoptado</t>
+        </is>
+      </c>
+      <c r="C207" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
+        </is>
       </c>
       <c r="D207" s="12" t="n"/>
       <c r="E207" s="39" t="n"/>
@@ -23619,153 +23613,159 @@
       <c r="G207" s="53" t="n"/>
     </row>
     <row r="208" ht="19.8" customHeight="1">
-      <c r="A208" s="50" t="n"/>
-      <c r="B208" s="60" t="inlineStr">
-        <is>
-          <t>Toallero adoptado</t>
-        </is>
-      </c>
-      <c r="C208" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
-        </is>
-      </c>
-      <c r="D208" s="12" t="n"/>
-      <c r="E208" s="39" t="n"/>
-      <c r="F208" s="20" t="n"/>
+      <c r="A208" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  11 - Bano visitas   (PB)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B208" s="11" t="n"/>
+      <c r="C208" s="11" t="n"/>
+      <c r="D208" s="11" t="n"/>
+      <c r="E208" s="11" t="n"/>
+      <c r="F208" s="42" t="n"/>
       <c r="G208" s="53" t="n"/>
     </row>
-    <row r="209" ht="19.8" customHeight="1">
-      <c r="A209" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  11 - Bano visitas   (PB)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B209" s="11" t="n"/>
-      <c r="C209" s="11" t="n"/>
-      <c r="D209" s="11" t="n"/>
-      <c r="E209" s="11" t="n"/>
-      <c r="F209" s="42" t="n"/>
+    <row r="209" ht="32" customHeight="1">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G209" s="53" t="n"/>
     </row>
-    <row r="210" ht="32" customHeight="1">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E210" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F210" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="210" ht="19.8" customHeight="1">
+      <c r="A210" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B210" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C210" s="43" t="n"/>
+      <c r="D210" s="58" t="n"/>
+      <c r="E210" s="58" t="n"/>
+      <c r="F210" s="61" t="n"/>
       <c r="G210" s="53" t="n"/>
     </row>
     <row r="211" ht="19.8" customHeight="1">
-      <c r="A211" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B211" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C211" s="43" t="n"/>
-      <c r="D211" s="58" t="n"/>
-      <c r="E211" s="58" t="n"/>
-      <c r="F211" s="61" t="n"/>
+      <c r="A211" s="90" t="n"/>
+      <c r="B211" s="91" t="inlineStr">
+        <is>
+          <t>(sin aberturas)</t>
+        </is>
+      </c>
+      <c r="C211" s="18" t="n"/>
+      <c r="D211" s="19" t="n"/>
+      <c r="E211" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F211" s="80" t="n"/>
       <c r="G211" s="53" t="n"/>
     </row>
     <row r="212" ht="19.8" customHeight="1">
-      <c r="A212" s="90" t="n"/>
-      <c r="B212" s="91" t="inlineStr">
-        <is>
-          <t>(sin aberturas)</t>
-        </is>
-      </c>
-      <c r="C212" s="18" t="n"/>
-      <c r="D212" s="19" t="n"/>
-      <c r="E212" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F212" s="80" t="n"/>
+      <c r="A212" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B212" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C212" s="47" t="n"/>
+      <c r="D212" s="18" t="n"/>
+      <c r="E212" s="18" t="n"/>
+      <c r="F212" s="20" t="n"/>
       <c r="G212" s="53" t="n"/>
     </row>
     <row r="213" ht="19.8" customHeight="1">
-      <c r="A213" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B213" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C213" s="47" t="n"/>
-      <c r="D213" s="18" t="n"/>
-      <c r="E213" s="18" t="n"/>
-      <c r="F213" s="20" t="n"/>
+      <c r="A213" s="43" t="n"/>
+      <c r="B213" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C213" s="18" t="inlineStr">
+        <is>
+          <t>1.30 x 3.00</t>
+        </is>
+      </c>
+      <c r="D213" s="19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E213" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F213" s="80" t="n">
+        <v>78</v>
+      </c>
       <c r="G213" s="53" t="n"/>
     </row>
     <row r="214" ht="19.8" customHeight="1">
-      <c r="A214" s="43" t="n"/>
-      <c r="B214" s="79" t="inlineStr">
+      <c r="A214" s="47" t="n"/>
+      <c r="B214" s="81" t="inlineStr">
         <is>
           <t>AISLADAS</t>
         </is>
       </c>
-      <c r="C214" s="18" t="inlineStr">
-        <is>
-          <t>1.30 x 3.00</t>
-        </is>
-      </c>
-      <c r="D214" s="19" t="n">
-        <v>3.9</v>
-      </c>
+      <c r="C214" s="18" t="n"/>
+      <c r="D214" s="19" t="n"/>
       <c r="E214" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F214" s="80" t="n">
-        <v>78</v>
-      </c>
+      <c r="F214" s="80" t="n"/>
       <c r="G214" s="53" t="n"/>
     </row>
     <row r="215" ht="19.8" customHeight="1">
       <c r="A215" s="47" t="n"/>
       <c r="B215" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C215" s="18" t="n"/>
-      <c r="D215" s="19" t="n"/>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C215" s="18" t="inlineStr">
+        <is>
+          <t>2.40 x 3.00</t>
+        </is>
+      </c>
+      <c r="D215" s="19" t="n">
+        <v>7.2</v>
+      </c>
       <c r="E215" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F215" s="80" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="F215" s="80" t="n">
+        <v>180</v>
+      </c>
       <c r="G215" s="53" t="n"/>
     </row>
     <row r="216" ht="19.8" customHeight="1">
@@ -23792,346 +23792,338 @@
       <c r="G216" s="53" t="n"/>
     </row>
     <row r="217" ht="19.8" customHeight="1">
-      <c r="A217" s="47" t="n"/>
-      <c r="B217" s="81" t="inlineStr">
+      <c r="A217" s="50" t="n"/>
+      <c r="B217" s="82" t="inlineStr">
         <is>
           <t>INTERIORES</t>
         </is>
       </c>
       <c r="C217" s="18" t="inlineStr">
         <is>
-          <t>2.40 x 3.00</t>
+          <t>1.30 x 3.00</t>
         </is>
       </c>
       <c r="D217" s="19" t="n">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="E217" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F217" s="80" t="n">
-        <v>180</v>
+        <v>97.5</v>
       </c>
       <c r="G217" s="53" t="n"/>
     </row>
     <row r="218" ht="19.8" customHeight="1">
-      <c r="A218" s="50" t="n"/>
-      <c r="B218" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C218" s="18" t="inlineStr">
-        <is>
-          <t>1.30 x 3.00</t>
-        </is>
-      </c>
-      <c r="D218" s="19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E218" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F218" s="80" t="n">
-        <v>97.5</v>
-      </c>
+      <c r="A218" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B218" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C218" s="47" t="n"/>
+      <c r="D218" s="18" t="n"/>
+      <c r="E218" s="18" t="n"/>
+      <c r="F218" s="20" t="n"/>
       <c r="G218" s="53" t="n"/>
     </row>
     <row r="219" ht="19.8" customHeight="1">
-      <c r="A219" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B219" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C219" s="47" t="n"/>
-      <c r="D219" s="18" t="n"/>
-      <c r="E219" s="18" t="n"/>
-      <c r="F219" s="20" t="n"/>
+      <c r="A219" s="43" t="n"/>
+      <c r="B219" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C219" s="18" t="n"/>
+      <c r="D219" s="19" t="n"/>
+      <c r="E219" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F219" s="80" t="n"/>
       <c r="G219" s="53" t="n"/>
     </row>
     <row r="220" ht="19.8" customHeight="1">
-      <c r="A220" s="43" t="n"/>
-      <c r="B220" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
+      <c r="A220" s="47" t="n"/>
+      <c r="B220" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C220" s="18" t="n"/>
       <c r="D220" s="19" t="n"/>
       <c r="E220" s="59" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F220" s="80" t="n"/>
       <c r="G220" s="53" t="n"/>
     </row>
     <row r="221" ht="19.8" customHeight="1">
-      <c r="A221" s="47" t="n"/>
-      <c r="B221" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C221" s="18" t="n"/>
-      <c r="D221" s="19" t="n"/>
+      <c r="A221" s="50" t="n"/>
+      <c r="B221" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C221" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D221" s="19" t="n">
+        <v>3.12</v>
+      </c>
       <c r="E221" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F221" s="80" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="F221" s="80" t="n">
+        <v>46.8</v>
+      </c>
       <c r="G221" s="53" t="n"/>
     </row>
     <row r="222" ht="19.8" customHeight="1">
-      <c r="A222" s="50" t="n"/>
-      <c r="B222" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C222" s="18" t="inlineStr">
+      <c r="A222" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B222" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C222" s="47" t="n"/>
+      <c r="D222" s="18" t="n"/>
+      <c r="E222" s="18" t="n"/>
+      <c r="F222" s="20" t="n"/>
+      <c r="G222" s="53" t="n"/>
+    </row>
+    <row r="223" ht="19.8" customHeight="1">
+      <c r="A223" s="43" t="n"/>
+      <c r="B223" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C223" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D222" s="19" t="n">
+      <c r="D223" s="19" t="n">
         <v>3.12</v>
       </c>
-      <c r="E222" s="59" t="n">
+      <c r="E223" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F223" s="80" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="G223" s="53" t="n"/>
+    </row>
+    <row r="224" ht="19.8" customHeight="1">
+      <c r="A224" s="50" t="n"/>
+      <c r="B224" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C224" s="18" t="n"/>
+      <c r="D224" s="24" t="n"/>
+      <c r="E224" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F222" s="80" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="G222" s="53" t="n"/>
-    </row>
-    <row r="223" ht="19.8" customHeight="1">
-      <c r="A223" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B223" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C223" s="47" t="n"/>
-      <c r="D223" s="18" t="n"/>
-      <c r="E223" s="18" t="n"/>
-      <c r="F223" s="20" t="n"/>
-      <c r="G223" s="53" t="n"/>
-    </row>
-    <row r="224" ht="19.8" customHeight="1">
-      <c r="A224" s="43" t="n"/>
-      <c r="B224" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C224" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D224" s="19" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E224" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F224" s="80" t="n">
-        <v>31.2</v>
-      </c>
+      <c r="F224" s="80" t="n"/>
       <c r="G224" s="53" t="n"/>
     </row>
     <row r="225" ht="19.8" customHeight="1">
-      <c r="A225" s="50" t="n"/>
-      <c r="B225" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C225" s="18" t="n"/>
-      <c r="D225" s="24" t="n"/>
-      <c r="E225" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F225" s="80" t="n"/>
+      <c r="A225" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B225" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C225" s="83" t="n"/>
+      <c r="D225" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E225" s="47" t="n"/>
+      <c r="F225" s="20" t="n"/>
       <c r="G225" s="53" t="n"/>
     </row>
     <row r="226" ht="19.8" customHeight="1">
-      <c r="A226" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B226" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C226" s="83" t="n"/>
-      <c r="D226" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E226" s="47" t="n"/>
-      <c r="F226" s="20" t="n"/>
+      <c r="A226" s="43" t="n"/>
+      <c r="B226" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C226" s="18" t="inlineStr">
+        <is>
+          <t>3.12 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D226" s="22" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="E226" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F226" s="80" t="n">
+        <v>56.2</v>
+      </c>
       <c r="G226" s="53" t="n"/>
     </row>
     <row r="227" ht="19.8" customHeight="1">
-      <c r="A227" s="43" t="n"/>
-      <c r="B227" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C227" s="18" t="inlineStr">
-        <is>
-          <t>3.12 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D227" s="22" t="n">
-        <v>9.359999999999999</v>
-      </c>
+      <c r="A227" s="47" t="n"/>
+      <c r="B227" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C227" s="18" t="n"/>
+      <c r="D227" s="19" t="n"/>
       <c r="E227" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F227" s="80" t="n">
-        <v>56.2</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F227" s="80" t="n"/>
       <c r="G227" s="53" t="n"/>
     </row>
     <row r="228" ht="19.8" customHeight="1">
-      <c r="A228" s="47" t="n"/>
-      <c r="B228" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
+      <c r="A228" s="50" t="n"/>
+      <c r="B228" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C228" s="18" t="n"/>
       <c r="D228" s="19" t="n"/>
       <c r="E228" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F228" s="80" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="F228" s="84" t="n"/>
       <c r="G228" s="53" t="n"/>
     </row>
     <row r="229" ht="19.8" customHeight="1">
-      <c r="A229" s="50" t="n"/>
-      <c r="B229" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C229" s="18" t="n"/>
-      <c r="D229" s="19" t="n"/>
-      <c r="E229" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F229" s="84" t="n"/>
+      <c r="A229" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B229" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C229" s="47" t="n"/>
+      <c r="D229" s="18" t="n"/>
+      <c r="E229" s="20" t="n"/>
+      <c r="F229" s="85" t="n">
+        <v>669.7</v>
+      </c>
       <c r="G229" s="53" t="n"/>
     </row>
     <row r="230" ht="19.8" customHeight="1">
       <c r="A230" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B230" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C230" s="47" t="n"/>
-      <c r="D230" s="18" t="n"/>
-      <c r="E230" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C230" s="47" t="inlineStr">
+        <is>
+          <t>669.70  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D230" s="12" t="n"/>
+      <c r="E230" s="14" t="n"/>
       <c r="F230" s="85" t="n">
-        <v>669.7</v>
+        <v>716.6</v>
       </c>
       <c r="G230" s="53" t="n"/>
     </row>
     <row r="231" ht="19.8" customHeight="1">
-      <c r="A231" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B231" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C231" s="47" t="inlineStr">
-        <is>
-          <t>669.70  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A231" s="43" t="n"/>
+      <c r="B231" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C231" s="18" t="n"/>
       <c r="D231" s="12" t="n"/>
-      <c r="E231" s="14" t="n"/>
-      <c r="F231" s="85" t="n">
+      <c r="E231" s="39" t="n"/>
+      <c r="F231" s="87" t="n"/>
+      <c r="G231" s="53" t="n"/>
+    </row>
+    <row r="232" ht="19.8" customHeight="1">
+      <c r="A232" s="83" t="n"/>
+      <c r="B232" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C232" s="47" t="n"/>
+      <c r="D232" s="12" t="n"/>
+      <c r="E232" s="14" t="n"/>
+      <c r="F232" s="85" t="n">
         <v>716.6</v>
       </c>
-      <c r="G231" s="53" t="n"/>
-    </row>
-    <row r="232" ht="19.8" customHeight="1">
-      <c r="A232" s="43" t="n"/>
-      <c r="B232" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C232" s="18" t="n"/>
-      <c r="D232" s="12" t="n"/>
-      <c r="E232" s="39" t="n"/>
-      <c r="F232" s="87" t="n"/>
       <c r="G232" s="53" t="n"/>
     </row>
     <row r="233" ht="19.8" customHeight="1">
-      <c r="A233" s="83" t="n"/>
-      <c r="B233" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C233" s="47" t="n"/>
+      <c r="A233" s="47" t="n"/>
+      <c r="B233" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C233" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D233" s="12" t="n"/>
-      <c r="E233" s="14" t="n"/>
-      <c r="F233" s="85" t="n">
-        <v>716.6</v>
-      </c>
+      <c r="E233" s="39" t="n"/>
+      <c r="F233" s="61" t="n"/>
       <c r="G233" s="53" t="n"/>
     </row>
     <row r="234" ht="19.8" customHeight="1">
       <c r="A234" s="47" t="n"/>
-      <c r="B234" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C234" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B234" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
+        </is>
+      </c>
+      <c r="C234" s="59" t="n">
+        <v>708</v>
       </c>
       <c r="D234" s="12" t="n"/>
       <c r="E234" s="39" t="n"/>
-      <c r="F234" s="61" t="n"/>
+      <c r="F234" s="20" t="n"/>
       <c r="G234" s="53" t="n"/>
     </row>
     <row r="235" ht="19.8" customHeight="1">
       <c r="A235" s="47" t="n"/>
       <c r="B235" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 80</t>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
         </is>
       </c>
       <c r="C235" s="59" t="n">
-        <v>708</v>
+        <v>1315</v>
       </c>
       <c r="D235" s="12" t="n"/>
       <c r="E235" s="39" t="n"/>
@@ -24142,11 +24134,11 @@
       <c r="A236" s="47" t="n"/>
       <c r="B236" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 150</t>
+          <t>Toalleros necesarios</t>
         </is>
       </c>
       <c r="C236" s="59" t="n">
-        <v>1315</v>
+        <v>1</v>
       </c>
       <c r="D236" s="12" t="n"/>
       <c r="E236" s="39" t="n"/>
@@ -24154,14 +24146,16 @@
       <c r="G236" s="53" t="n"/>
     </row>
     <row r="237" ht="19.8" customHeight="1">
-      <c r="A237" s="47" t="n"/>
+      <c r="A237" s="50" t="n"/>
       <c r="B237" s="60" t="inlineStr">
         <is>
-          <t>Toalleros necesarios</t>
-        </is>
-      </c>
-      <c r="C237" s="59" t="n">
-        <v>1</v>
+          <t>Toallero adoptado</t>
+        </is>
+      </c>
+      <c r="C237" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
+        </is>
       </c>
       <c r="D237" s="12" t="n"/>
       <c r="E237" s="39" t="n"/>
@@ -24169,153 +24163,159 @@
       <c r="G237" s="53" t="n"/>
     </row>
     <row r="238" ht="19.8" customHeight="1">
-      <c r="A238" s="50" t="n"/>
-      <c r="B238" s="60" t="inlineStr">
-        <is>
-          <t>Toallero adoptado</t>
-        </is>
-      </c>
-      <c r="C238" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
-        </is>
-      </c>
-      <c r="D238" s="12" t="n"/>
-      <c r="E238" s="39" t="n"/>
-      <c r="F238" s="20" t="n"/>
+      <c r="A238" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  13 - Dormitorio Norte   (PA)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B238" s="11" t="n"/>
+      <c r="C238" s="11" t="n"/>
+      <c r="D238" s="11" t="n"/>
+      <c r="E238" s="11" t="n"/>
+      <c r="F238" s="42" t="n"/>
       <c r="G238" s="53" t="n"/>
     </row>
-    <row r="239" ht="19.8" customHeight="1">
-      <c r="A239" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  13 - Dormitorio Norte   (PA)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B239" s="11" t="n"/>
-      <c r="C239" s="11" t="n"/>
-      <c r="D239" s="11" t="n"/>
-      <c r="E239" s="11" t="n"/>
-      <c r="F239" s="42" t="n"/>
+    <row r="239" ht="32" customHeight="1">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G239" s="53" t="n"/>
     </row>
-    <row r="240" ht="32" customHeight="1">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E240" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F240" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="240" ht="19.8" customHeight="1">
+      <c r="A240" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B240" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C240" s="43" t="n"/>
+      <c r="D240" s="58" t="n"/>
+      <c r="E240" s="58" t="n"/>
+      <c r="F240" s="61" t="n"/>
       <c r="G240" s="53" t="n"/>
     </row>
     <row r="241" ht="19.8" customHeight="1">
-      <c r="A241" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B241" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C241" s="43" t="n"/>
-      <c r="D241" s="58" t="n"/>
-      <c r="E241" s="58" t="n"/>
-      <c r="F241" s="61" t="n"/>
+      <c r="A241" s="43" t="n"/>
+      <c r="B241" s="79" t="inlineStr">
+        <is>
+          <t>VA04</t>
+        </is>
+      </c>
+      <c r="C241" s="18" t="inlineStr">
+        <is>
+          <t>2.00 x 2.52</t>
+        </is>
+      </c>
+      <c r="D241" s="19" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="E241" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F241" s="80" t="n">
+        <v>302.4</v>
+      </c>
       <c r="G241" s="53" t="n"/>
     </row>
     <row r="242" ht="19.8" customHeight="1">
-      <c r="A242" s="43" t="n"/>
-      <c r="B242" s="79" t="inlineStr">
-        <is>
-          <t>VA04</t>
+      <c r="A242" s="50" t="n"/>
+      <c r="B242" s="82" t="inlineStr">
+        <is>
+          <t>VA05</t>
         </is>
       </c>
       <c r="C242" s="18" t="inlineStr">
         <is>
-          <t>2.00 x 2.52</t>
+          <t>1.40 x 2.52</t>
         </is>
       </c>
       <c r="D242" s="19" t="n">
-        <v>5.04</v>
+        <v>3.53</v>
       </c>
       <c r="E242" s="59" t="n">
         <v>60</v>
       </c>
       <c r="F242" s="80" t="n">
-        <v>302.4</v>
+        <v>211.8</v>
       </c>
       <c r="G242" s="53" t="n"/>
     </row>
     <row r="243" ht="19.8" customHeight="1">
-      <c r="A243" s="50" t="n"/>
-      <c r="B243" s="82" t="inlineStr">
-        <is>
-          <t>VA05</t>
-        </is>
-      </c>
-      <c r="C243" s="18" t="inlineStr">
-        <is>
-          <t>1.40 x 2.52</t>
-        </is>
-      </c>
-      <c r="D243" s="19" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="E243" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F243" s="80" t="n">
-        <v>211.8</v>
-      </c>
+      <c r="A243" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B243" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C243" s="47" t="n"/>
+      <c r="D243" s="18" t="n"/>
+      <c r="E243" s="18" t="n"/>
+      <c r="F243" s="20" t="n"/>
       <c r="G243" s="53" t="n"/>
     </row>
     <row r="244" ht="19.8" customHeight="1">
-      <c r="A244" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B244" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C244" s="47" t="n"/>
-      <c r="D244" s="18" t="n"/>
-      <c r="E244" s="18" t="n"/>
-      <c r="F244" s="20" t="n"/>
+      <c r="A244" s="43" t="n"/>
+      <c r="B244" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS (NO)</t>
+        </is>
+      </c>
+      <c r="C244" s="18" t="inlineStr">
+        <is>
+          <t>4.25 x 3.00</t>
+        </is>
+      </c>
+      <c r="D244" s="19" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="E244" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F244" s="80" t="n">
+        <v>255</v>
+      </c>
       <c r="G244" s="53" t="n"/>
     </row>
     <row r="245" ht="19.8" customHeight="1">
-      <c r="A245" s="43" t="n"/>
-      <c r="B245" s="79" t="inlineStr">
-        <is>
-          <t>AISLADAS (NO)</t>
+      <c r="A245" s="47" t="n"/>
+      <c r="B245" s="81" t="inlineStr">
+        <is>
+          <t>AISLADAS (SE)</t>
         </is>
       </c>
       <c r="C245" s="18" t="inlineStr">
@@ -24338,22 +24338,22 @@
       <c r="A246" s="47" t="n"/>
       <c r="B246" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (SE)</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C246" s="18" t="inlineStr">
         <is>
-          <t>4.25 x 3.00</t>
+          <t>4.00 x 3.00</t>
         </is>
       </c>
       <c r="D246" s="19" t="n">
-        <v>12.75</v>
+        <v>12</v>
       </c>
       <c r="E246" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F246" s="80" t="n">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="G246" s="53" t="n"/>
     </row>
@@ -24361,7 +24361,7 @@
       <c r="A247" s="47" t="n"/>
       <c r="B247" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C247" s="18" t="inlineStr">
@@ -24373,346 +24373,338 @@
         <v>12</v>
       </c>
       <c r="E247" s="59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F247" s="80" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="G247" s="53" t="n"/>
     </row>
     <row r="248" ht="19.8" customHeight="1">
-      <c r="A248" s="47" t="n"/>
-      <c r="B248" s="81" t="inlineStr">
+      <c r="A248" s="50" t="n"/>
+      <c r="B248" s="82" t="inlineStr">
         <is>
           <t>INTERIORES</t>
         </is>
       </c>
-      <c r="C248" s="18" t="inlineStr">
-        <is>
-          <t>4.00 x 3.00</t>
-        </is>
-      </c>
-      <c r="D248" s="19" t="n">
-        <v>12</v>
-      </c>
+      <c r="C248" s="18" t="n"/>
+      <c r="D248" s="19" t="n"/>
       <c r="E248" s="59" t="n">
         <v>25</v>
       </c>
-      <c r="F248" s="80" t="n">
-        <v>300</v>
-      </c>
+      <c r="F248" s="80" t="n"/>
       <c r="G248" s="53" t="n"/>
     </row>
     <row r="249" ht="19.8" customHeight="1">
-      <c r="A249" s="50" t="n"/>
-      <c r="B249" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C249" s="18" t="n"/>
-      <c r="D249" s="19" t="n"/>
-      <c r="E249" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F249" s="80" t="n"/>
+      <c r="A249" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B249" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C249" s="47" t="n"/>
+      <c r="D249" s="18" t="n"/>
+      <c r="E249" s="18" t="n"/>
+      <c r="F249" s="20" t="n"/>
       <c r="G249" s="53" t="n"/>
     </row>
     <row r="250" ht="19.8" customHeight="1">
-      <c r="A250" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B250" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C250" s="47" t="n"/>
-      <c r="D250" s="18" t="n"/>
-      <c r="E250" s="18" t="n"/>
-      <c r="F250" s="20" t="n"/>
+      <c r="A250" s="43" t="n"/>
+      <c r="B250" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C250" s="18" t="n"/>
+      <c r="D250" s="19" t="n"/>
+      <c r="E250" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F250" s="80" t="n"/>
       <c r="G250" s="53" t="n"/>
     </row>
     <row r="251" ht="19.8" customHeight="1">
-      <c r="A251" s="43" t="n"/>
-      <c r="B251" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C251" s="18" t="n"/>
-      <c r="D251" s="19" t="n"/>
+      <c r="A251" s="47" t="n"/>
+      <c r="B251" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C251" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D251" s="19" t="n">
+        <v>17</v>
+      </c>
       <c r="E251" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F251" s="80" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F251" s="80" t="n">
+        <v>340</v>
+      </c>
       <c r="G251" s="53" t="n"/>
     </row>
     <row r="252" ht="19.8" customHeight="1">
-      <c r="A252" s="47" t="n"/>
-      <c r="B252" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C252" s="18" t="inlineStr">
+      <c r="A252" s="50" t="n"/>
+      <c r="B252" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C252" s="18" t="n"/>
+      <c r="D252" s="19" t="n"/>
+      <c r="E252" s="59" t="n">
+        <v>15</v>
+      </c>
+      <c r="F252" s="80" t="n"/>
+      <c r="G252" s="53" t="n"/>
+    </row>
+    <row r="253" ht="19.8" customHeight="1">
+      <c r="A253" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B253" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C253" s="47" t="n"/>
+      <c r="D253" s="18" t="n"/>
+      <c r="E253" s="18" t="n"/>
+      <c r="F253" s="20" t="n"/>
+      <c r="G253" s="53" t="n"/>
+    </row>
+    <row r="254" ht="19.8" customHeight="1">
+      <c r="A254" s="43" t="n"/>
+      <c r="B254" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C254" s="18" t="n"/>
+      <c r="D254" s="19" t="n"/>
+      <c r="E254" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F254" s="80" t="n"/>
+      <c r="G254" s="53" t="n"/>
+    </row>
+    <row r="255" ht="19.8" customHeight="1">
+      <c r="A255" s="50" t="n"/>
+      <c r="B255" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C255" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D252" s="19" t="n">
+      <c r="D255" s="24" t="n">
         <v>17</v>
       </c>
-      <c r="E252" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F252" s="80" t="n">
-        <v>340</v>
-      </c>
-      <c r="G252" s="53" t="n"/>
-    </row>
-    <row r="253" ht="19.8" customHeight="1">
-      <c r="A253" s="50" t="n"/>
-      <c r="B253" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C253" s="18" t="n"/>
-      <c r="D253" s="19" t="n"/>
-      <c r="E253" s="59" t="n">
+      <c r="E255" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F253" s="80" t="n"/>
-      <c r="G253" s="53" t="n"/>
-    </row>
-    <row r="254" ht="19.8" customHeight="1">
-      <c r="A254" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B254" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C254" s="47" t="n"/>
-      <c r="D254" s="18" t="n"/>
-      <c r="E254" s="18" t="n"/>
-      <c r="F254" s="20" t="n"/>
-      <c r="G254" s="53" t="n"/>
-    </row>
-    <row r="255" ht="19.8" customHeight="1">
-      <c r="A255" s="43" t="n"/>
-      <c r="B255" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C255" s="18" t="n"/>
-      <c r="D255" s="19" t="n"/>
-      <c r="E255" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F255" s="80" t="n"/>
+      <c r="F255" s="80" t="n">
+        <v>255</v>
+      </c>
       <c r="G255" s="53" t="n"/>
     </row>
     <row r="256" ht="19.8" customHeight="1">
-      <c r="A256" s="50" t="n"/>
-      <c r="B256" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C256" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D256" s="24" t="n">
-        <v>17</v>
-      </c>
-      <c r="E256" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F256" s="80" t="n">
-        <v>255</v>
-      </c>
+      <c r="A256" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B256" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C256" s="83" t="n"/>
+      <c r="D256" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E256" s="47" t="n"/>
+      <c r="F256" s="20" t="n"/>
       <c r="G256" s="53" t="n"/>
     </row>
     <row r="257" ht="19.8" customHeight="1">
-      <c r="A257" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B257" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C257" s="83" t="n"/>
-      <c r="D257" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E257" s="47" t="n"/>
-      <c r="F257" s="20" t="n"/>
+      <c r="A257" s="43" t="n"/>
+      <c r="B257" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C257" s="18" t="n"/>
+      <c r="D257" s="22" t="n"/>
+      <c r="E257" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F257" s="80" t="n"/>
       <c r="G257" s="53" t="n"/>
     </row>
     <row r="258" ht="19.8" customHeight="1">
-      <c r="A258" s="43" t="n"/>
-      <c r="B258" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
+      <c r="A258" s="47" t="n"/>
+      <c r="B258" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C258" s="18" t="n"/>
-      <c r="D258" s="22" t="n"/>
+      <c r="D258" s="19" t="n"/>
       <c r="E258" s="59" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F258" s="80" t="n"/>
       <c r="G258" s="53" t="n"/>
     </row>
     <row r="259" ht="19.8" customHeight="1">
-      <c r="A259" s="47" t="n"/>
-      <c r="B259" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C259" s="18" t="n"/>
-      <c r="D259" s="19" t="n"/>
+      <c r="A259" s="50" t="n"/>
+      <c r="B259" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C259" s="18" t="inlineStr">
+        <is>
+          <t>17.00 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D259" s="19" t="n">
+        <v>51</v>
+      </c>
       <c r="E259" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F259" s="80" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="F259" s="84" t="n">
+        <v>612</v>
+      </c>
       <c r="G259" s="53" t="n"/>
     </row>
     <row r="260" ht="19.8" customHeight="1">
-      <c r="A260" s="50" t="n"/>
-      <c r="B260" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C260" s="18" t="inlineStr">
-        <is>
-          <t>17.00 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D260" s="19" t="n">
-        <v>51</v>
-      </c>
-      <c r="E260" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F260" s="84" t="n">
-        <v>612</v>
+      <c r="A260" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B260" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C260" s="47" t="n"/>
+      <c r="D260" s="18" t="n"/>
+      <c r="E260" s="20" t="n"/>
+      <c r="F260" s="85" t="n">
+        <v>2771.2</v>
       </c>
       <c r="G260" s="53" t="n"/>
     </row>
     <row r="261" ht="19.8" customHeight="1">
       <c r="A261" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B261" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C261" s="47" t="n"/>
-      <c r="D261" s="18" t="n"/>
-      <c r="E261" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C261" s="47" t="inlineStr">
+        <is>
+          <t>2771.20  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D261" s="12" t="n"/>
+      <c r="E261" s="14" t="n"/>
       <c r="F261" s="85" t="n">
-        <v>2771.2</v>
+        <v>2965.2</v>
       </c>
       <c r="G261" s="53" t="n"/>
     </row>
     <row r="262" ht="19.8" customHeight="1">
-      <c r="A262" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B262" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C262" s="47" t="inlineStr">
-        <is>
-          <t>2771.20  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A262" s="43" t="n"/>
+      <c r="B262" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C262" s="18" t="n"/>
       <c r="D262" s="12" t="n"/>
-      <c r="E262" s="14" t="n"/>
-      <c r="F262" s="85" t="n">
+      <c r="E262" s="39" t="n"/>
+      <c r="F262" s="87" t="n"/>
+      <c r="G262" s="53" t="n"/>
+    </row>
+    <row r="263" ht="19.8" customHeight="1">
+      <c r="A263" s="83" t="n"/>
+      <c r="B263" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C263" s="47" t="n"/>
+      <c r="D263" s="12" t="n"/>
+      <c r="E263" s="14" t="n"/>
+      <c r="F263" s="85" t="n">
         <v>2965.2</v>
       </c>
-      <c r="G262" s="53" t="n"/>
-    </row>
-    <row r="263" ht="19.8" customHeight="1">
-      <c r="A263" s="43" t="n"/>
-      <c r="B263" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C263" s="18" t="n"/>
-      <c r="D263" s="12" t="n"/>
-      <c r="E263" s="39" t="n"/>
-      <c r="F263" s="87" t="n"/>
       <c r="G263" s="53" t="n"/>
     </row>
     <row r="264" ht="19.8" customHeight="1">
-      <c r="A264" s="83" t="n"/>
-      <c r="B264" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C264" s="47" t="n"/>
+      <c r="A264" s="47" t="n"/>
+      <c r="B264" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C264" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D264" s="12" t="n"/>
-      <c r="E264" s="14" t="n"/>
-      <c r="F264" s="85" t="n">
-        <v>2965.2</v>
-      </c>
+      <c r="E264" s="39" t="n"/>
+      <c r="F264" s="61" t="n"/>
       <c r="G264" s="53" t="n"/>
     </row>
     <row r="265" ht="19.8" customHeight="1">
       <c r="A265" s="47" t="n"/>
-      <c r="B265" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C265" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B265" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C265" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D265" s="12" t="n"/>
       <c r="E265" s="39" t="n"/>
-      <c r="F265" s="61" t="n"/>
+      <c r="F265" s="20" t="n"/>
       <c r="G265" s="53" t="n"/>
     </row>
     <row r="266" ht="19.8" customHeight="1">
       <c r="A266" s="47" t="n"/>
       <c r="B266" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C266" s="19" t="n">
-        <v>274.4</v>
+          <t>Elementos necesarios</t>
+        </is>
+      </c>
+      <c r="C266" s="59" t="n">
+        <v>11</v>
       </c>
       <c r="D266" s="12" t="n"/>
       <c r="E266" s="39" t="n"/>
@@ -24723,11 +24715,11 @@
       <c r="A267" s="47" t="n"/>
       <c r="B267" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
+          <t>Ancho del radiador (cm)</t>
         </is>
       </c>
       <c r="C267" s="59" t="n">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="D267" s="12" t="n"/>
       <c r="E267" s="39" t="n"/>
@@ -24735,14 +24727,16 @@
       <c r="G267" s="53" t="n"/>
     </row>
     <row r="268" ht="19.8" customHeight="1">
-      <c r="A268" s="47" t="n"/>
+      <c r="A268" s="50" t="n"/>
       <c r="B268" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
-        </is>
-      </c>
-      <c r="C268" s="59" t="n">
-        <v>88</v>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C268" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
       </c>
       <c r="D268" s="12" t="n"/>
       <c r="E268" s="39" t="n"/>
@@ -24750,510 +24744,508 @@
       <c r="G268" s="53" t="n"/>
     </row>
     <row r="269" ht="19.8" customHeight="1">
-      <c r="A269" s="50" t="n"/>
-      <c r="B269" s="60" t="inlineStr">
-        <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C269" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
-      </c>
-      <c r="D269" s="12" t="n"/>
-      <c r="E269" s="39" t="n"/>
-      <c r="F269" s="20" t="n"/>
+      <c r="A269" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  14 - Play room   (PA)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B269" s="11" t="n"/>
+      <c r="C269" s="11" t="n"/>
+      <c r="D269" s="11" t="n"/>
+      <c r="E269" s="11" t="n"/>
+      <c r="F269" s="42" t="n"/>
       <c r="G269" s="53" t="n"/>
     </row>
-    <row r="270" ht="19.8" customHeight="1">
-      <c r="A270" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  14 - Play room   (PA)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B270" s="11" t="n"/>
-      <c r="C270" s="11" t="n"/>
-      <c r="D270" s="11" t="n"/>
-      <c r="E270" s="11" t="n"/>
-      <c r="F270" s="42" t="n"/>
+    <row r="270" ht="32" customHeight="1">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G270" s="53" t="n"/>
     </row>
-    <row r="271" ht="32" customHeight="1">
-      <c r="A271" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B271" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D271" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E271" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F271" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="271" ht="19.8" customHeight="1">
+      <c r="A271" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B271" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C271" s="43" t="n"/>
+      <c r="D271" s="58" t="n"/>
+      <c r="E271" s="58" t="n"/>
+      <c r="F271" s="61" t="n"/>
       <c r="G271" s="53" t="n"/>
     </row>
     <row r="272" ht="19.8" customHeight="1">
-      <c r="A272" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B272" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C272" s="43" t="n"/>
-      <c r="D272" s="58" t="n"/>
-      <c r="E272" s="58" t="n"/>
-      <c r="F272" s="61" t="n"/>
+      <c r="A272" s="90" t="n"/>
+      <c r="B272" s="91" t="inlineStr">
+        <is>
+          <t>VA04</t>
+        </is>
+      </c>
+      <c r="C272" s="18" t="inlineStr">
+        <is>
+          <t>2.00 x 2.52</t>
+        </is>
+      </c>
+      <c r="D272" s="19" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="E272" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F272" s="80" t="n">
+        <v>302.4</v>
+      </c>
       <c r="G272" s="53" t="n"/>
     </row>
     <row r="273" ht="19.8" customHeight="1">
-      <c r="A273" s="90" t="n"/>
-      <c r="B273" s="91" t="inlineStr">
-        <is>
-          <t>VA04</t>
-        </is>
-      </c>
-      <c r="C273" s="18" t="inlineStr">
-        <is>
-          <t>2.00 x 2.52</t>
-        </is>
-      </c>
-      <c r="D273" s="19" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="E273" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F273" s="80" t="n">
-        <v>302.4</v>
-      </c>
+      <c r="A273" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B273" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C273" s="47" t="n"/>
+      <c r="D273" s="18" t="n"/>
+      <c r="E273" s="18" t="n"/>
+      <c r="F273" s="20" t="n"/>
       <c r="G273" s="53" t="n"/>
     </row>
     <row r="274" ht="19.8" customHeight="1">
-      <c r="A274" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B274" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C274" s="47" t="n"/>
-      <c r="D274" s="18" t="n"/>
-      <c r="E274" s="18" t="n"/>
-      <c r="F274" s="20" t="n"/>
+      <c r="A274" s="43" t="n"/>
+      <c r="B274" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS (NO)</t>
+        </is>
+      </c>
+      <c r="C274" s="18" t="inlineStr">
+        <is>
+          <t>4.13 x 3.00</t>
+        </is>
+      </c>
+      <c r="D274" s="19" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="E274" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F274" s="80" t="n">
+        <v>247.8</v>
+      </c>
       <c r="G274" s="53" t="n"/>
     </row>
     <row r="275" ht="19.8" customHeight="1">
-      <c r="A275" s="43" t="n"/>
-      <c r="B275" s="79" t="inlineStr">
-        <is>
-          <t>AISLADAS (NO)</t>
-        </is>
-      </c>
-      <c r="C275" s="18" t="inlineStr">
-        <is>
-          <t>4.13 x 3.00</t>
-        </is>
-      </c>
-      <c r="D275" s="19" t="n">
-        <v>12.39</v>
-      </c>
+      <c r="A275" s="47" t="n"/>
+      <c r="B275" s="81" t="inlineStr">
+        <is>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C275" s="18" t="n"/>
+      <c r="D275" s="19" t="n"/>
       <c r="E275" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F275" s="80" t="n">
-        <v>247.8</v>
-      </c>
+      <c r="F275" s="80" t="n"/>
       <c r="G275" s="53" t="n"/>
     </row>
     <row r="276" ht="19.8" customHeight="1">
       <c r="A276" s="47" t="n"/>
       <c r="B276" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C276" s="18" t="n"/>
-      <c r="D276" s="19" t="n"/>
+          <t>INTERIORES (NE)</t>
+        </is>
+      </c>
+      <c r="C276" s="18" t="inlineStr">
+        <is>
+          <t>4.08 x 3.00</t>
+        </is>
+      </c>
+      <c r="D276" s="19" t="n">
+        <v>12.24</v>
+      </c>
       <c r="E276" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F276" s="80" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="F276" s="80" t="n">
+        <v>306</v>
+      </c>
       <c r="G276" s="53" t="n"/>
     </row>
     <row r="277" ht="19.8" customHeight="1">
-      <c r="A277" s="47" t="n"/>
-      <c r="B277" s="81" t="inlineStr">
-        <is>
-          <t>INTERIORES (NE)</t>
+      <c r="A277" s="50" t="n"/>
+      <c r="B277" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES (SE)</t>
         </is>
       </c>
       <c r="C277" s="18" t="inlineStr">
         <is>
-          <t>4.08 x 3.00</t>
+          <t>4.13 x 3.00</t>
         </is>
       </c>
       <c r="D277" s="19" t="n">
-        <v>12.24</v>
+        <v>12.39</v>
       </c>
       <c r="E277" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F277" s="80" t="n">
-        <v>306</v>
+        <v>309.8</v>
       </c>
       <c r="G277" s="53" t="n"/>
     </row>
     <row r="278" ht="19.8" customHeight="1">
-      <c r="A278" s="50" t="n"/>
-      <c r="B278" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES (SE)</t>
-        </is>
-      </c>
-      <c r="C278" s="18" t="inlineStr">
-        <is>
-          <t>4.13 x 3.00</t>
-        </is>
-      </c>
-      <c r="D278" s="19" t="n">
-        <v>12.39</v>
-      </c>
-      <c r="E278" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F278" s="80" t="n">
-        <v>309.8</v>
-      </c>
+      <c r="A278" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B278" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C278" s="47" t="n"/>
+      <c r="D278" s="18" t="n"/>
+      <c r="E278" s="18" t="n"/>
+      <c r="F278" s="20" t="n"/>
       <c r="G278" s="53" t="n"/>
     </row>
     <row r="279" ht="19.8" customHeight="1">
-      <c r="A279" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B279" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C279" s="47" t="n"/>
-      <c r="D279" s="18" t="n"/>
-      <c r="E279" s="18" t="n"/>
-      <c r="F279" s="20" t="n"/>
+      <c r="A279" s="43" t="n"/>
+      <c r="B279" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C279" s="18" t="n"/>
+      <c r="D279" s="19" t="n"/>
+      <c r="E279" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F279" s="80" t="n"/>
       <c r="G279" s="53" t="n"/>
     </row>
     <row r="280" ht="19.8" customHeight="1">
-      <c r="A280" s="43" t="n"/>
-      <c r="B280" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C280" s="18" t="n"/>
-      <c r="D280" s="19" t="n"/>
+      <c r="A280" s="47" t="n"/>
+      <c r="B280" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C280" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D280" s="19" t="n">
+        <v>16.85</v>
+      </c>
       <c r="E280" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F280" s="80" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F280" s="80" t="n">
+        <v>337</v>
+      </c>
       <c r="G280" s="53" t="n"/>
     </row>
     <row r="281" ht="19.8" customHeight="1">
-      <c r="A281" s="47" t="n"/>
-      <c r="B281" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C281" s="18" t="inlineStr">
+      <c r="A281" s="50" t="n"/>
+      <c r="B281" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C281" s="18" t="n"/>
+      <c r="D281" s="19" t="n"/>
+      <c r="E281" s="59" t="n">
+        <v>15</v>
+      </c>
+      <c r="F281" s="80" t="n"/>
+      <c r="G281" s="53" t="n"/>
+    </row>
+    <row r="282" ht="19.8" customHeight="1">
+      <c r="A282" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B282" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C282" s="47" t="n"/>
+      <c r="D282" s="18" t="n"/>
+      <c r="E282" s="18" t="n"/>
+      <c r="F282" s="20" t="n"/>
+      <c r="G282" s="53" t="n"/>
+    </row>
+    <row r="283" ht="19.8" customHeight="1">
+      <c r="A283" s="43" t="n"/>
+      <c r="B283" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C283" s="18" t="n"/>
+      <c r="D283" s="19" t="n"/>
+      <c r="E283" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F283" s="80" t="n"/>
+      <c r="G283" s="53" t="n"/>
+    </row>
+    <row r="284" ht="19.8" customHeight="1">
+      <c r="A284" s="50" t="n"/>
+      <c r="B284" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C284" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D281" s="19" t="n">
+      <c r="D284" s="24" t="n">
         <v>16.85</v>
       </c>
-      <c r="E281" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F281" s="80" t="n">
-        <v>337</v>
-      </c>
-      <c r="G281" s="53" t="n"/>
-    </row>
-    <row r="282" ht="19.8" customHeight="1">
-      <c r="A282" s="50" t="n"/>
-      <c r="B282" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C282" s="18" t="n"/>
-      <c r="D282" s="19" t="n"/>
-      <c r="E282" s="59" t="n">
+      <c r="E284" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F282" s="80" t="n"/>
-      <c r="G282" s="53" t="n"/>
-    </row>
-    <row r="283" ht="19.8" customHeight="1">
-      <c r="A283" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B283" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C283" s="47" t="n"/>
-      <c r="D283" s="18" t="n"/>
-      <c r="E283" s="18" t="n"/>
-      <c r="F283" s="20" t="n"/>
-      <c r="G283" s="53" t="n"/>
-    </row>
-    <row r="284" ht="19.8" customHeight="1">
-      <c r="A284" s="43" t="n"/>
-      <c r="B284" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C284" s="18" t="n"/>
-      <c r="D284" s="19" t="n"/>
-      <c r="E284" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F284" s="80" t="n"/>
+      <c r="F284" s="80" t="n">
+        <v>252.8</v>
+      </c>
       <c r="G284" s="53" t="n"/>
     </row>
     <row r="285" ht="19.8" customHeight="1">
-      <c r="A285" s="50" t="n"/>
-      <c r="B285" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C285" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D285" s="24" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="E285" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F285" s="80" t="n">
-        <v>252.8</v>
-      </c>
+      <c r="A285" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B285" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C285" s="83" t="n"/>
+      <c r="D285" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E285" s="47" t="n"/>
+      <c r="F285" s="20" t="n"/>
       <c r="G285" s="53" t="n"/>
     </row>
     <row r="286" ht="19.8" customHeight="1">
-      <c r="A286" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B286" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C286" s="83" t="n"/>
-      <c r="D286" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E286" s="47" t="n"/>
-      <c r="F286" s="20" t="n"/>
+      <c r="A286" s="43" t="n"/>
+      <c r="B286" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C286" s="18" t="inlineStr">
+        <is>
+          <t>16.85 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D286" s="22" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="E286" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F286" s="80" t="n">
+        <v>303.3</v>
+      </c>
       <c r="G286" s="53" t="n"/>
     </row>
     <row r="287" ht="19.8" customHeight="1">
-      <c r="A287" s="43" t="n"/>
-      <c r="B287" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C287" s="18" t="inlineStr">
-        <is>
-          <t>16.85 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D287" s="22" t="n">
-        <v>50.55</v>
-      </c>
+      <c r="A287" s="47" t="n"/>
+      <c r="B287" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C287" s="18" t="n"/>
+      <c r="D287" s="19" t="n"/>
       <c r="E287" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F287" s="80" t="n">
-        <v>303.3</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F287" s="80" t="n"/>
       <c r="G287" s="53" t="n"/>
     </row>
     <row r="288" ht="19.8" customHeight="1">
-      <c r="A288" s="47" t="n"/>
-      <c r="B288" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
+      <c r="A288" s="50" t="n"/>
+      <c r="B288" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C288" s="18" t="n"/>
       <c r="D288" s="19" t="n"/>
       <c r="E288" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F288" s="80" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="F288" s="84" t="n"/>
       <c r="G288" s="53" t="n"/>
     </row>
     <row r="289" ht="19.8" customHeight="1">
-      <c r="A289" s="50" t="n"/>
-      <c r="B289" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C289" s="18" t="n"/>
-      <c r="D289" s="19" t="n"/>
-      <c r="E289" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F289" s="84" t="n"/>
+      <c r="A289" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B289" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C289" s="47" t="n"/>
+      <c r="D289" s="18" t="n"/>
+      <c r="E289" s="20" t="n"/>
+      <c r="F289" s="85" t="n">
+        <v>2059.1</v>
+      </c>
       <c r="G289" s="53" t="n"/>
     </row>
     <row r="290" ht="19.8" customHeight="1">
       <c r="A290" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B290" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C290" s="47" t="n"/>
-      <c r="D290" s="18" t="n"/>
-      <c r="E290" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C290" s="47" t="inlineStr">
+        <is>
+          <t>2059.10  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D290" s="12" t="n"/>
+      <c r="E290" s="14" t="n"/>
       <c r="F290" s="85" t="n">
-        <v>2059.1</v>
+        <v>2203.2</v>
       </c>
       <c r="G290" s="53" t="n"/>
     </row>
     <row r="291" ht="19.8" customHeight="1">
-      <c r="A291" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B291" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C291" s="47" t="inlineStr">
-        <is>
-          <t>2059.10  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+      <c r="A291" s="43" t="n"/>
+      <c r="B291" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C291" s="18" t="inlineStr">
+        <is>
+          <t>Escalera</t>
         </is>
       </c>
       <c r="D291" s="12" t="n"/>
-      <c r="E291" s="14" t="n"/>
-      <c r="F291" s="85" t="n">
-        <v>2203.2</v>
+      <c r="E291" s="39" t="n"/>
+      <c r="F291" s="87" t="n">
+        <v>1348.3</v>
       </c>
       <c r="G291" s="53" t="n"/>
     </row>
     <row r="292" ht="19.8" customHeight="1">
-      <c r="A292" s="43" t="n"/>
-      <c r="B292" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C292" s="18" t="inlineStr">
-        <is>
-          <t>Escalera</t>
-        </is>
-      </c>
+      <c r="A292" s="83" t="n"/>
+      <c r="B292" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C292" s="47" t="n"/>
       <c r="D292" s="12" t="n"/>
-      <c r="E292" s="39" t="n"/>
-      <c r="F292" s="87" t="n">
-        <v>1348.3</v>
+      <c r="E292" s="14" t="n"/>
+      <c r="F292" s="85" t="n">
+        <v>3551.5</v>
       </c>
       <c r="G292" s="53" t="n"/>
     </row>
     <row r="293" ht="19.8" customHeight="1">
-      <c r="A293" s="83" t="n"/>
-      <c r="B293" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C293" s="47" t="n"/>
+      <c r="A293" s="47" t="n"/>
+      <c r="B293" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C293" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D293" s="12" t="n"/>
-      <c r="E293" s="14" t="n"/>
-      <c r="F293" s="85" t="n">
-        <v>3551.5</v>
-      </c>
+      <c r="E293" s="39" t="n"/>
+      <c r="F293" s="61" t="n"/>
       <c r="G293" s="53" t="n"/>
     </row>
     <row r="294" ht="19.8" customHeight="1">
       <c r="A294" s="47" t="n"/>
-      <c r="B294" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C294" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B294" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C294" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D294" s="12" t="n"/>
       <c r="E294" s="39" t="n"/>
-      <c r="F294" s="61" t="n"/>
+      <c r="F294" s="20" t="n"/>
       <c r="G294" s="53" t="n"/>
     </row>
     <row r="295" ht="19.8" customHeight="1">
       <c r="A295" s="47" t="n"/>
       <c r="B295" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C295" s="19" t="n">
-        <v>274.4</v>
+          <t>Elementos necesarios</t>
+        </is>
+      </c>
+      <c r="C295" s="59" t="n">
+        <v>13</v>
       </c>
       <c r="D295" s="12" t="n"/>
       <c r="E295" s="39" t="n"/>
@@ -25264,11 +25256,11 @@
       <c r="A296" s="47" t="n"/>
       <c r="B296" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
+          <t>Ancho del radiador (cm)</t>
         </is>
       </c>
       <c r="C296" s="59" t="n">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="D296" s="12" t="n"/>
       <c r="E296" s="39" t="n"/>
@@ -25276,14 +25268,16 @@
       <c r="G296" s="53" t="n"/>
     </row>
     <row r="297" ht="19.8" customHeight="1">
-      <c r="A297" s="47" t="n"/>
+      <c r="A297" s="50" t="n"/>
       <c r="B297" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
-        </is>
-      </c>
-      <c r="C297" s="59" t="n">
-        <v>104</v>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C297" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
       </c>
       <c r="D297" s="12" t="n"/>
       <c r="E297" s="39" t="n"/>
@@ -25291,145 +25285,151 @@
       <c r="G297" s="53" t="n"/>
     </row>
     <row r="298" ht="19.8" customHeight="1">
-      <c r="A298" s="50" t="n"/>
-      <c r="B298" s="60" t="inlineStr">
-        <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C298" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
-      </c>
-      <c r="D298" s="12" t="n"/>
-      <c r="E298" s="39" t="n"/>
-      <c r="F298" s="20" t="n"/>
+      <c r="A298" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  15 - Dormitorio Sur   (PA)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B298" s="11" t="n"/>
+      <c r="C298" s="11" t="n"/>
+      <c r="D298" s="11" t="n"/>
+      <c r="E298" s="11" t="n"/>
+      <c r="F298" s="42" t="n"/>
       <c r="G298" s="53" t="n"/>
     </row>
-    <row r="299" ht="19.8" customHeight="1">
-      <c r="A299" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  15 - Dormitorio Sur   (PA)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B299" s="11" t="n"/>
-      <c r="C299" s="11" t="n"/>
-      <c r="D299" s="11" t="n"/>
-      <c r="E299" s="11" t="n"/>
-      <c r="F299" s="42" t="n"/>
+    <row r="299" ht="32" customHeight="1">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G299" s="53" t="n"/>
     </row>
-    <row r="300" ht="32" customHeight="1">
-      <c r="A300" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B300" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C300" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D300" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E300" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F300" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="300" ht="19.8" customHeight="1">
+      <c r="A300" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B300" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C300" s="43" t="n"/>
+      <c r="D300" s="58" t="n"/>
+      <c r="E300" s="58" t="n"/>
+      <c r="F300" s="61" t="n"/>
       <c r="G300" s="53" t="n"/>
     </row>
     <row r="301" ht="19.8" customHeight="1">
-      <c r="A301" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B301" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C301" s="43" t="n"/>
-      <c r="D301" s="58" t="n"/>
-      <c r="E301" s="58" t="n"/>
-      <c r="F301" s="61" t="n"/>
+      <c r="A301" s="90" t="n"/>
+      <c r="B301" s="91" t="inlineStr">
+        <is>
+          <t>PV04</t>
+        </is>
+      </c>
+      <c r="C301" s="18" t="inlineStr">
+        <is>
+          <t>2.06 x 3.00</t>
+        </is>
+      </c>
+      <c r="D301" s="19" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="E301" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F301" s="80" t="n">
+        <v>370.8</v>
+      </c>
       <c r="G301" s="53" t="n"/>
     </row>
     <row r="302" ht="19.8" customHeight="1">
-      <c r="A302" s="90" t="n"/>
-      <c r="B302" s="91" t="inlineStr">
-        <is>
-          <t>PV04</t>
-        </is>
-      </c>
-      <c r="C302" s="18" t="inlineStr">
-        <is>
-          <t>2.06 x 3.00</t>
-        </is>
-      </c>
-      <c r="D302" s="19" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="E302" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F302" s="80" t="n">
-        <v>370.8</v>
-      </c>
+      <c r="A302" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B302" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C302" s="47" t="n"/>
+      <c r="D302" s="18" t="n"/>
+      <c r="E302" s="18" t="n"/>
+      <c r="F302" s="20" t="n"/>
       <c r="G302" s="53" t="n"/>
     </row>
     <row r="303" ht="19.8" customHeight="1">
-      <c r="A303" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B303" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C303" s="47" t="n"/>
-      <c r="D303" s="18" t="n"/>
-      <c r="E303" s="18" t="n"/>
-      <c r="F303" s="20" t="n"/>
+      <c r="A303" s="43" t="n"/>
+      <c r="B303" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS (SE)</t>
+        </is>
+      </c>
+      <c r="C303" s="18" t="inlineStr">
+        <is>
+          <t>4.05 x 3.00</t>
+        </is>
+      </c>
+      <c r="D303" s="19" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="E303" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F303" s="80" t="n">
+        <v>243</v>
+      </c>
       <c r="G303" s="53" t="n"/>
     </row>
     <row r="304" ht="19.8" customHeight="1">
-      <c r="A304" s="43" t="n"/>
-      <c r="B304" s="79" t="inlineStr">
-        <is>
-          <t>AISLADAS (SE)</t>
+      <c r="A304" s="47" t="n"/>
+      <c r="B304" s="81" t="inlineStr">
+        <is>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C304" s="18" t="inlineStr">
         <is>
-          <t>4.05 x 3.00</t>
+          <t>3.50 x 3.00</t>
         </is>
       </c>
       <c r="D304" s="19" t="n">
-        <v>12.15</v>
+        <v>10.5</v>
       </c>
       <c r="E304" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F304" s="80" t="n">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="G304" s="53" t="n"/>
     </row>
@@ -25437,366 +25437,358 @@
       <c r="A305" s="47" t="n"/>
       <c r="B305" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>INTERIORES (NO)</t>
         </is>
       </c>
       <c r="C305" s="18" t="inlineStr">
         <is>
+          <t>4.05 x 3.00</t>
+        </is>
+      </c>
+      <c r="D305" s="19" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="E305" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F305" s="80" t="n">
+        <v>303.8</v>
+      </c>
+      <c r="G305" s="53" t="n"/>
+    </row>
+    <row r="306" ht="19.8" customHeight="1">
+      <c r="A306" s="50" t="n"/>
+      <c r="B306" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C306" s="18" t="inlineStr">
+        <is>
           <t>3.50 x 3.00</t>
         </is>
       </c>
-      <c r="D305" s="19" t="n">
+      <c r="D306" s="19" t="n">
         <v>10.5</v>
-      </c>
-      <c r="E305" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F305" s="80" t="n">
-        <v>210</v>
-      </c>
-      <c r="G305" s="53" t="n"/>
-    </row>
-    <row r="306" ht="19.8" customHeight="1">
-      <c r="A306" s="47" t="n"/>
-      <c r="B306" s="81" t="inlineStr">
-        <is>
-          <t>INTERIORES (NO)</t>
-        </is>
-      </c>
-      <c r="C306" s="18" t="inlineStr">
-        <is>
-          <t>4.05 x 3.00</t>
-        </is>
-      </c>
-      <c r="D306" s="19" t="n">
-        <v>12.15</v>
       </c>
       <c r="E306" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F306" s="80" t="n">
-        <v>303.8</v>
+        <v>262.5</v>
       </c>
       <c r="G306" s="53" t="n"/>
     </row>
     <row r="307" ht="19.8" customHeight="1">
-      <c r="A307" s="50" t="n"/>
-      <c r="B307" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C307" s="18" t="inlineStr">
-        <is>
-          <t>3.50 x 3.00</t>
-        </is>
-      </c>
-      <c r="D307" s="19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="E307" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F307" s="80" t="n">
-        <v>262.5</v>
-      </c>
+      <c r="A307" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B307" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C307" s="47" t="n"/>
+      <c r="D307" s="18" t="n"/>
+      <c r="E307" s="18" t="n"/>
+      <c r="F307" s="20" t="n"/>
       <c r="G307" s="53" t="n"/>
     </row>
     <row r="308" ht="19.8" customHeight="1">
-      <c r="A308" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B308" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C308" s="47" t="n"/>
-      <c r="D308" s="18" t="n"/>
-      <c r="E308" s="18" t="n"/>
-      <c r="F308" s="20" t="n"/>
+      <c r="A308" s="43" t="n"/>
+      <c r="B308" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C308" s="18" t="n"/>
+      <c r="D308" s="19" t="n"/>
+      <c r="E308" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F308" s="80" t="n"/>
       <c r="G308" s="53" t="n"/>
     </row>
     <row r="309" ht="19.8" customHeight="1">
-      <c r="A309" s="43" t="n"/>
-      <c r="B309" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C309" s="18" t="n"/>
-      <c r="D309" s="19" t="n"/>
+      <c r="A309" s="47" t="n"/>
+      <c r="B309" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C309" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D309" s="19" t="n">
+        <v>14.17</v>
+      </c>
       <c r="E309" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F309" s="80" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F309" s="80" t="n">
+        <v>283.4</v>
+      </c>
       <c r="G309" s="53" t="n"/>
     </row>
     <row r="310" ht="19.8" customHeight="1">
-      <c r="A310" s="47" t="n"/>
-      <c r="B310" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C310" s="18" t="inlineStr">
+      <c r="A310" s="50" t="n"/>
+      <c r="B310" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C310" s="18" t="n"/>
+      <c r="D310" s="19" t="n"/>
+      <c r="E310" s="59" t="n">
+        <v>15</v>
+      </c>
+      <c r="F310" s="80" t="n"/>
+      <c r="G310" s="53" t="n"/>
+    </row>
+    <row r="311" ht="19.8" customHeight="1">
+      <c r="A311" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B311" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C311" s="47" t="n"/>
+      <c r="D311" s="18" t="n"/>
+      <c r="E311" s="18" t="n"/>
+      <c r="F311" s="20" t="n"/>
+      <c r="G311" s="53" t="n"/>
+    </row>
+    <row r="312" ht="19.8" customHeight="1">
+      <c r="A312" s="43" t="n"/>
+      <c r="B312" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C312" s="18" t="n"/>
+      <c r="D312" s="19" t="n"/>
+      <c r="E312" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F312" s="80" t="n"/>
+      <c r="G312" s="53" t="n"/>
+    </row>
+    <row r="313" ht="19.8" customHeight="1">
+      <c r="A313" s="50" t="n"/>
+      <c r="B313" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C313" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D310" s="19" t="n">
+      <c r="D313" s="24" t="n">
         <v>14.17</v>
       </c>
-      <c r="E310" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F310" s="80" t="n">
-        <v>283.4</v>
-      </c>
-      <c r="G310" s="53" t="n"/>
-    </row>
-    <row r="311" ht="19.8" customHeight="1">
-      <c r="A311" s="50" t="n"/>
-      <c r="B311" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C311" s="18" t="n"/>
-      <c r="D311" s="19" t="n"/>
-      <c r="E311" s="59" t="n">
+      <c r="E313" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F311" s="80" t="n"/>
-      <c r="G311" s="53" t="n"/>
-    </row>
-    <row r="312" ht="19.8" customHeight="1">
-      <c r="A312" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B312" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C312" s="47" t="n"/>
-      <c r="D312" s="18" t="n"/>
-      <c r="E312" s="18" t="n"/>
-      <c r="F312" s="20" t="n"/>
-      <c r="G312" s="53" t="n"/>
-    </row>
-    <row r="313" ht="19.8" customHeight="1">
-      <c r="A313" s="43" t="n"/>
-      <c r="B313" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C313" s="18" t="n"/>
-      <c r="D313" s="19" t="n"/>
-      <c r="E313" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F313" s="80" t="n"/>
+      <c r="F313" s="80" t="n">
+        <v>212.6</v>
+      </c>
       <c r="G313" s="53" t="n"/>
     </row>
     <row r="314" ht="19.8" customHeight="1">
-      <c r="A314" s="50" t="n"/>
-      <c r="B314" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C314" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D314" s="24" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="E314" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F314" s="80" t="n">
-        <v>212.6</v>
-      </c>
+      <c r="A314" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B314" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C314" s="83" t="n"/>
+      <c r="D314" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E314" s="47" t="n"/>
+      <c r="F314" s="20" t="n"/>
       <c r="G314" s="53" t="n"/>
     </row>
     <row r="315" ht="19.8" customHeight="1">
-      <c r="A315" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B315" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C315" s="83" t="n"/>
-      <c r="D315" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E315" s="47" t="n"/>
-      <c r="F315" s="20" t="n"/>
+      <c r="A315" s="43" t="n"/>
+      <c r="B315" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C315" s="18" t="n"/>
+      <c r="D315" s="22" t="n"/>
+      <c r="E315" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F315" s="80" t="n"/>
       <c r="G315" s="53" t="n"/>
     </row>
     <row r="316" ht="19.8" customHeight="1">
-      <c r="A316" s="43" t="n"/>
-      <c r="B316" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C316" s="18" t="n"/>
-      <c r="D316" s="22" t="n"/>
+      <c r="A316" s="47" t="n"/>
+      <c r="B316" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C316" s="18" t="inlineStr">
+        <is>
+          <t>14.17 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D316" s="19" t="n">
+        <v>42.51</v>
+      </c>
       <c r="E316" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F316" s="80" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="F316" s="80" t="n">
+        <v>382.6</v>
+      </c>
       <c r="G316" s="53" t="n"/>
     </row>
     <row r="317" ht="19.8" customHeight="1">
-      <c r="A317" s="47" t="n"/>
-      <c r="B317" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C317" s="18" t="inlineStr">
-        <is>
-          <t>14.17 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D317" s="19" t="n">
-        <v>42.51</v>
-      </c>
+      <c r="A317" s="50" t="n"/>
+      <c r="B317" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C317" s="18" t="n"/>
+      <c r="D317" s="19" t="n"/>
       <c r="E317" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F317" s="80" t="n">
-        <v>382.6</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F317" s="84" t="n"/>
       <c r="G317" s="53" t="n"/>
     </row>
     <row r="318" ht="19.8" customHeight="1">
-      <c r="A318" s="50" t="n"/>
-      <c r="B318" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C318" s="18" t="n"/>
-      <c r="D318" s="19" t="n"/>
-      <c r="E318" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F318" s="84" t="n"/>
+      <c r="A318" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B318" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C318" s="47" t="n"/>
+      <c r="D318" s="18" t="n"/>
+      <c r="E318" s="20" t="n"/>
+      <c r="F318" s="85" t="n">
+        <v>2268.7</v>
+      </c>
       <c r="G318" s="53" t="n"/>
     </row>
     <row r="319" ht="19.8" customHeight="1">
       <c r="A319" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B319" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C319" s="47" t="n"/>
-      <c r="D319" s="18" t="n"/>
-      <c r="E319" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C319" s="47" t="inlineStr">
+        <is>
+          <t>2268.70  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D319" s="12" t="n"/>
+      <c r="E319" s="14" t="n"/>
       <c r="F319" s="85" t="n">
-        <v>2268.7</v>
+        <v>2427.5</v>
       </c>
       <c r="G319" s="53" t="n"/>
     </row>
     <row r="320" ht="19.8" customHeight="1">
-      <c r="A320" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B320" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C320" s="47" t="inlineStr">
-        <is>
-          <t>2268.70  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A320" s="43" t="n"/>
+      <c r="B320" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C320" s="18" t="n"/>
       <c r="D320" s="12" t="n"/>
-      <c r="E320" s="14" t="n"/>
-      <c r="F320" s="85" t="n">
+      <c r="E320" s="39" t="n"/>
+      <c r="F320" s="87" t="n"/>
+      <c r="G320" s="53" t="n"/>
+    </row>
+    <row r="321" ht="19.8" customHeight="1">
+      <c r="A321" s="83" t="n"/>
+      <c r="B321" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C321" s="47" t="n"/>
+      <c r="D321" s="12" t="n"/>
+      <c r="E321" s="14" t="n"/>
+      <c r="F321" s="85" t="n">
         <v>2427.5</v>
       </c>
-      <c r="G320" s="53" t="n"/>
-    </row>
-    <row r="321" ht="19.8" customHeight="1">
-      <c r="A321" s="43" t="n"/>
-      <c r="B321" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C321" s="18" t="n"/>
-      <c r="D321" s="12" t="n"/>
-      <c r="E321" s="39" t="n"/>
-      <c r="F321" s="87" t="n"/>
       <c r="G321" s="53" t="n"/>
     </row>
     <row r="322" ht="19.8" customHeight="1">
-      <c r="A322" s="83" t="n"/>
-      <c r="B322" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C322" s="47" t="n"/>
+      <c r="A322" s="47" t="n"/>
+      <c r="B322" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C322" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D322" s="12" t="n"/>
-      <c r="E322" s="14" t="n"/>
-      <c r="F322" s="85" t="n">
-        <v>2427.5</v>
-      </c>
+      <c r="E322" s="39" t="n"/>
+      <c r="F322" s="61" t="n"/>
       <c r="G322" s="53" t="n"/>
     </row>
     <row r="323" ht="19.8" customHeight="1">
       <c r="A323" s="47" t="n"/>
-      <c r="B323" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C323" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B323" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C323" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D323" s="12" t="n"/>
       <c r="E323" s="39" t="n"/>
-      <c r="F323" s="61" t="n"/>
+      <c r="F323" s="20" t="n"/>
       <c r="G323" s="53" t="n"/>
     </row>
     <row r="324" ht="19.8" customHeight="1">
       <c r="A324" s="47" t="n"/>
       <c r="B324" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C324" s="19" t="n">
-        <v>274.4</v>
+          <t>Elementos necesarios</t>
+        </is>
+      </c>
+      <c r="C324" s="59" t="n">
+        <v>9</v>
       </c>
       <c r="D324" s="12" t="n"/>
       <c r="E324" s="39" t="n"/>
@@ -25807,11 +25799,11 @@
       <c r="A325" s="47" t="n"/>
       <c r="B325" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
+          <t>Ancho del radiador (cm)</t>
         </is>
       </c>
       <c r="C325" s="59" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="D325" s="12" t="n"/>
       <c r="E325" s="39" t="n"/>
@@ -25819,14 +25811,16 @@
       <c r="G325" s="53" t="n"/>
     </row>
     <row r="326" ht="19.8" customHeight="1">
-      <c r="A326" s="47" t="n"/>
+      <c r="A326" s="50" t="n"/>
       <c r="B326" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
-        </is>
-      </c>
-      <c r="C326" s="59" t="n">
-        <v>72</v>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C326" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
       </c>
       <c r="D326" s="12" t="n"/>
       <c r="E326" s="39" t="n"/>
@@ -25834,145 +25828,151 @@
       <c r="G326" s="53" t="n"/>
     </row>
     <row r="327" ht="19.8" customHeight="1">
-      <c r="A327" s="50" t="n"/>
-      <c r="B327" s="60" t="inlineStr">
-        <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C327" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
-      </c>
-      <c r="D327" s="12" t="n"/>
-      <c r="E327" s="39" t="n"/>
-      <c r="F327" s="20" t="n"/>
+      <c r="A327" s="8" t="inlineStr">
+        <is>
+          <t>LOCAL  17 - Bano   (PA)   -   altura 3.00 m</t>
+        </is>
+      </c>
+      <c r="B327" s="11" t="n"/>
+      <c r="C327" s="11" t="n"/>
+      <c r="D327" s="11" t="n"/>
+      <c r="E327" s="11" t="n"/>
+      <c r="F327" s="42" t="n"/>
       <c r="G327" s="53" t="n"/>
     </row>
-    <row r="328" ht="19.8" customHeight="1">
-      <c r="A328" s="8" t="inlineStr">
-        <is>
-          <t>LOCAL  17 - Bano   (PA)   -   altura 3.00 m</t>
-        </is>
-      </c>
-      <c r="B328" s="11" t="n"/>
-      <c r="C328" s="11" t="n"/>
-      <c r="D328" s="11" t="n"/>
-      <c r="E328" s="11" t="n"/>
-      <c r="F328" s="42" t="n"/>
+    <row r="328" ht="32" customHeight="1">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
       <c r="G328" s="53" t="n"/>
     </row>
-    <row r="329" ht="32" customHeight="1">
-      <c r="A329" s="2" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B329" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C329" s="2" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D329" s="2" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E329" s="2" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F329" s="2" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="329" ht="19.8" customHeight="1">
+      <c r="A329" s="36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B329" s="78" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C329" s="43" t="n"/>
+      <c r="D329" s="58" t="n"/>
+      <c r="E329" s="58" t="n"/>
+      <c r="F329" s="61" t="n"/>
       <c r="G329" s="53" t="n"/>
     </row>
     <row r="330" ht="19.8" customHeight="1">
-      <c r="A330" s="36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B330" s="78" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C330" s="43" t="n"/>
-      <c r="D330" s="58" t="n"/>
-      <c r="E330" s="58" t="n"/>
-      <c r="F330" s="61" t="n"/>
+      <c r="A330" s="90" t="n"/>
+      <c r="B330" s="91" t="inlineStr">
+        <is>
+          <t>VA03</t>
+        </is>
+      </c>
+      <c r="C330" s="18" t="inlineStr">
+        <is>
+          <t>0.75 x 2.52</t>
+        </is>
+      </c>
+      <c r="D330" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E330" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F330" s="80" t="n">
+        <v>113.4</v>
+      </c>
       <c r="G330" s="53" t="n"/>
     </row>
     <row r="331" ht="19.8" customHeight="1">
-      <c r="A331" s="90" t="n"/>
-      <c r="B331" s="91" t="inlineStr">
-        <is>
-          <t>VA03</t>
-        </is>
-      </c>
-      <c r="C331" s="18" t="inlineStr">
-        <is>
-          <t>0.75 x 2.52</t>
-        </is>
-      </c>
-      <c r="D331" s="19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="E331" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F331" s="80" t="n">
-        <v>113.4</v>
-      </c>
+      <c r="A331" s="36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B331" s="78" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C331" s="47" t="n"/>
+      <c r="D331" s="18" t="n"/>
+      <c r="E331" s="18" t="n"/>
+      <c r="F331" s="20" t="n"/>
       <c r="G331" s="53" t="n"/>
     </row>
     <row r="332" ht="19.8" customHeight="1">
-      <c r="A332" s="36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B332" s="78" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C332" s="47" t="n"/>
-      <c r="D332" s="18" t="n"/>
-      <c r="E332" s="18" t="n"/>
-      <c r="F332" s="20" t="n"/>
+      <c r="A332" s="43" t="n"/>
+      <c r="B332" s="79" t="inlineStr">
+        <is>
+          <t>AISLADAS (NE)</t>
+        </is>
+      </c>
+      <c r="C332" s="18" t="inlineStr">
+        <is>
+          <t>2.20 x 3.00</t>
+        </is>
+      </c>
+      <c r="D332" s="19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E332" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F332" s="80" t="n">
+        <v>132</v>
+      </c>
       <c r="G332" s="53" t="n"/>
     </row>
     <row r="333" ht="19.8" customHeight="1">
-      <c r="A333" s="43" t="n"/>
-      <c r="B333" s="79" t="inlineStr">
-        <is>
-          <t>AISLADAS (NE)</t>
+      <c r="A333" s="47" t="n"/>
+      <c r="B333" s="81" t="inlineStr">
+        <is>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C333" s="18" t="inlineStr">
         <is>
-          <t>2.20 x 3.00</t>
+          <t>1.60 x 3.00</t>
         </is>
       </c>
       <c r="D333" s="19" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="E333" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F333" s="80" t="n">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="G333" s="53" t="n"/>
     </row>
@@ -25980,366 +25980,358 @@
       <c r="A334" s="47" t="n"/>
       <c r="B334" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>INTERIORES (SO)</t>
         </is>
       </c>
       <c r="C334" s="18" t="inlineStr">
         <is>
+          <t>2.20 x 3.00</t>
+        </is>
+      </c>
+      <c r="D334" s="19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E334" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F334" s="80" t="n">
+        <v>165</v>
+      </c>
+      <c r="G334" s="53" t="n"/>
+    </row>
+    <row r="335" ht="19.8" customHeight="1">
+      <c r="A335" s="50" t="n"/>
+      <c r="B335" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C335" s="18" t="inlineStr">
+        <is>
           <t>1.60 x 3.00</t>
         </is>
       </c>
-      <c r="D334" s="19" t="n">
+      <c r="D335" s="19" t="n">
         <v>4.8</v>
-      </c>
-      <c r="E334" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F334" s="80" t="n">
-        <v>96</v>
-      </c>
-      <c r="G334" s="53" t="n"/>
-    </row>
-    <row r="335" ht="19.8" customHeight="1">
-      <c r="A335" s="47" t="n"/>
-      <c r="B335" s="81" t="inlineStr">
-        <is>
-          <t>INTERIORES (SO)</t>
-        </is>
-      </c>
-      <c r="C335" s="18" t="inlineStr">
-        <is>
-          <t>2.20 x 3.00</t>
-        </is>
-      </c>
-      <c r="D335" s="19" t="n">
-        <v>6.6</v>
       </c>
       <c r="E335" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F335" s="80" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="G335" s="53" t="n"/>
     </row>
     <row r="336" ht="19.8" customHeight="1">
-      <c r="A336" s="50" t="n"/>
-      <c r="B336" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C336" s="18" t="inlineStr">
-        <is>
-          <t>1.60 x 3.00</t>
-        </is>
-      </c>
-      <c r="D336" s="19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E336" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F336" s="80" t="n">
-        <v>120</v>
-      </c>
+      <c r="A336" s="36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B336" s="78" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C336" s="47" t="n"/>
+      <c r="D336" s="18" t="n"/>
+      <c r="E336" s="18" t="n"/>
+      <c r="F336" s="20" t="n"/>
       <c r="G336" s="53" t="n"/>
     </row>
     <row r="337" ht="19.8" customHeight="1">
-      <c r="A337" s="36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B337" s="78" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C337" s="47" t="n"/>
-      <c r="D337" s="18" t="n"/>
-      <c r="E337" s="18" t="n"/>
-      <c r="F337" s="20" t="n"/>
+      <c r="A337" s="43" t="n"/>
+      <c r="B337" s="79" t="inlineStr">
+        <is>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C337" s="18" t="n"/>
+      <c r="D337" s="19" t="n"/>
+      <c r="E337" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F337" s="80" t="n"/>
       <c r="G337" s="53" t="n"/>
     </row>
     <row r="338" ht="19.8" customHeight="1">
-      <c r="A338" s="43" t="n"/>
-      <c r="B338" s="79" t="inlineStr">
-        <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C338" s="18" t="n"/>
-      <c r="D338" s="19" t="n"/>
+      <c r="A338" s="47" t="n"/>
+      <c r="B338" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C338" s="18" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D338" s="19" t="n">
+        <v>3.52</v>
+      </c>
       <c r="E338" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F338" s="80" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F338" s="80" t="n">
+        <v>70.40000000000001</v>
+      </c>
       <c r="G338" s="53" t="n"/>
     </row>
     <row r="339" ht="19.8" customHeight="1">
-      <c r="A339" s="47" t="n"/>
-      <c r="B339" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C339" s="18" t="inlineStr">
+      <c r="A339" s="50" t="n"/>
+      <c r="B339" s="82" t="inlineStr">
+        <is>
+          <t>TECHO ENTREPISO</t>
+        </is>
+      </c>
+      <c r="C339" s="18" t="n"/>
+      <c r="D339" s="19" t="n"/>
+      <c r="E339" s="59" t="n">
+        <v>15</v>
+      </c>
+      <c r="F339" s="80" t="n"/>
+      <c r="G339" s="53" t="n"/>
+    </row>
+    <row r="340" ht="19.8" customHeight="1">
+      <c r="A340" s="36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B340" s="78" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C340" s="47" t="n"/>
+      <c r="D340" s="18" t="n"/>
+      <c r="E340" s="18" t="n"/>
+      <c r="F340" s="20" t="n"/>
+      <c r="G340" s="53" t="n"/>
+    </row>
+    <row r="341" ht="19.8" customHeight="1">
+      <c r="A341" s="43" t="n"/>
+      <c r="B341" s="79" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C341" s="18" t="n"/>
+      <c r="D341" s="19" t="n"/>
+      <c r="E341" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F341" s="80" t="n"/>
+      <c r="G341" s="53" t="n"/>
+    </row>
+    <row r="342" ht="19.8" customHeight="1">
+      <c r="A342" s="50" t="n"/>
+      <c r="B342" s="82" t="inlineStr">
+        <is>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C342" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D339" s="19" t="n">
+      <c r="D342" s="24" t="n">
         <v>3.52</v>
       </c>
-      <c r="E339" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F339" s="80" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="G339" s="53" t="n"/>
-    </row>
-    <row r="340" ht="19.8" customHeight="1">
-      <c r="A340" s="50" t="n"/>
-      <c r="B340" s="82" t="inlineStr">
-        <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C340" s="18" t="n"/>
-      <c r="D340" s="19" t="n"/>
-      <c r="E340" s="59" t="n">
+      <c r="E342" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F340" s="80" t="n"/>
-      <c r="G340" s="53" t="n"/>
-    </row>
-    <row r="341" ht="19.8" customHeight="1">
-      <c r="A341" s="36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B341" s="78" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C341" s="47" t="n"/>
-      <c r="D341" s="18" t="n"/>
-      <c r="E341" s="18" t="n"/>
-      <c r="F341" s="20" t="n"/>
-      <c r="G341" s="53" t="n"/>
-    </row>
-    <row r="342" ht="19.8" customHeight="1">
-      <c r="A342" s="43" t="n"/>
-      <c r="B342" s="79" t="inlineStr">
-        <is>
-          <t>SOBRE TIERRA</t>
-        </is>
-      </c>
-      <c r="C342" s="18" t="n"/>
-      <c r="D342" s="19" t="n"/>
-      <c r="E342" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="F342" s="80" t="n"/>
+      <c r="F342" s="80" t="n">
+        <v>52.8</v>
+      </c>
       <c r="G342" s="53" t="n"/>
     </row>
     <row r="343" ht="19.8" customHeight="1">
-      <c r="A343" s="50" t="n"/>
-      <c r="B343" s="82" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C343" s="18" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D343" s="24" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="E343" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F343" s="80" t="n">
-        <v>52.8</v>
-      </c>
+      <c r="A343" s="36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B343" s="78" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C343" s="83" t="n"/>
+      <c r="D343" s="36" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E343" s="47" t="n"/>
+      <c r="F343" s="20" t="n"/>
       <c r="G343" s="53" t="n"/>
     </row>
     <row r="344" ht="19.8" customHeight="1">
-      <c r="A344" s="36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B344" s="78" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C344" s="83" t="n"/>
-      <c r="D344" s="36" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E344" s="47" t="n"/>
-      <c r="F344" s="20" t="n"/>
+      <c r="A344" s="43" t="n"/>
+      <c r="B344" s="79" t="inlineStr">
+        <is>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C344" s="18" t="n"/>
+      <c r="D344" s="22" t="n"/>
+      <c r="E344" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F344" s="80" t="n"/>
       <c r="G344" s="53" t="n"/>
     </row>
     <row r="345" ht="19.8" customHeight="1">
-      <c r="A345" s="43" t="n"/>
-      <c r="B345" s="79" t="inlineStr">
-        <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C345" s="18" t="n"/>
-      <c r="D345" s="22" t="n"/>
+      <c r="A345" s="47" t="n"/>
+      <c r="B345" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C345" s="18" t="inlineStr">
+        <is>
+          <t>3.52 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D345" s="19" t="n">
+        <v>10.56</v>
+      </c>
       <c r="E345" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F345" s="80" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="F345" s="80" t="n">
+        <v>95</v>
+      </c>
       <c r="G345" s="53" t="n"/>
     </row>
     <row r="346" ht="19.8" customHeight="1">
-      <c r="A346" s="47" t="n"/>
-      <c r="B346" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C346" s="18" t="inlineStr">
-        <is>
-          <t>3.52 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D346" s="19" t="n">
-        <v>10.56</v>
-      </c>
+      <c r="A346" s="50" t="n"/>
+      <c r="B346" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C346" s="18" t="n"/>
+      <c r="D346" s="19" t="n"/>
       <c r="E346" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F346" s="80" t="n">
-        <v>95</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F346" s="84" t="n"/>
       <c r="G346" s="53" t="n"/>
     </row>
     <row r="347" ht="19.8" customHeight="1">
-      <c r="A347" s="50" t="n"/>
-      <c r="B347" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C347" s="18" t="n"/>
-      <c r="D347" s="19" t="n"/>
-      <c r="E347" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="F347" s="84" t="n"/>
+      <c r="A347" s="36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B347" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C347" s="47" t="n"/>
+      <c r="D347" s="18" t="n"/>
+      <c r="E347" s="20" t="n"/>
+      <c r="F347" s="85" t="n">
+        <v>844.6</v>
+      </c>
       <c r="G347" s="53" t="n"/>
     </row>
     <row r="348" ht="19.8" customHeight="1">
       <c r="A348" s="36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B348" s="78" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C348" s="47" t="n"/>
-      <c r="D348" s="18" t="n"/>
-      <c r="E348" s="20" t="n"/>
+          <t>PERDIDA TOTAL</t>
+        </is>
+      </c>
+      <c r="C348" s="47" t="inlineStr">
+        <is>
+          <t>844.60  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D348" s="12" t="n"/>
+      <c r="E348" s="14" t="n"/>
       <c r="F348" s="85" t="n">
-        <v>844.6</v>
+        <v>903.7</v>
       </c>
       <c r="G348" s="53" t="n"/>
     </row>
     <row r="349" ht="19.8" customHeight="1">
-      <c r="A349" s="36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B349" s="78" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C349" s="47" t="inlineStr">
-        <is>
-          <t>844.60  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
+      <c r="A349" s="43" t="n"/>
+      <c r="B349" s="86" t="inlineStr">
+        <is>
+          <t>Carga de locales sin emisor</t>
+        </is>
+      </c>
+      <c r="C349" s="18" t="n"/>
       <c r="D349" s="12" t="n"/>
-      <c r="E349" s="14" t="n"/>
-      <c r="F349" s="85" t="n">
+      <c r="E349" s="39" t="n"/>
+      <c r="F349" s="87" t="n"/>
+      <c r="G349" s="53" t="n"/>
+    </row>
+    <row r="350" ht="19.8" customHeight="1">
+      <c r="A350" s="83" t="n"/>
+      <c r="B350" s="78" t="inlineStr">
+        <is>
+          <t>CARGA TOTAL A CUBRIR</t>
+        </is>
+      </c>
+      <c r="C350" s="47" t="n"/>
+      <c r="D350" s="12" t="n"/>
+      <c r="E350" s="14" t="n"/>
+      <c r="F350" s="85" t="n">
         <v>903.7</v>
       </c>
-      <c r="G349" s="53" t="n"/>
-    </row>
-    <row r="350" ht="19.8" customHeight="1">
-      <c r="A350" s="43" t="n"/>
-      <c r="B350" s="86" t="inlineStr">
-        <is>
-          <t>Carga de locales sin emisor</t>
-        </is>
-      </c>
-      <c r="C350" s="18" t="n"/>
-      <c r="D350" s="12" t="n"/>
-      <c r="E350" s="39" t="n"/>
-      <c r="F350" s="87" t="n"/>
       <c r="G350" s="53" t="n"/>
     </row>
     <row r="351" ht="19.8" customHeight="1">
-      <c r="A351" s="83" t="n"/>
-      <c r="B351" s="78" t="inlineStr">
-        <is>
-          <t>CARGA TOTAL A CUBRIR</t>
-        </is>
-      </c>
-      <c r="C351" s="47" t="n"/>
+      <c r="A351" s="47" t="n"/>
+      <c r="B351" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C351" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
+      </c>
       <c r="D351" s="12" t="n"/>
-      <c r="E351" s="14" t="n"/>
-      <c r="F351" s="85" t="n">
-        <v>903.7</v>
-      </c>
+      <c r="E351" s="39" t="n"/>
+      <c r="F351" s="61" t="n"/>
       <c r="G351" s="53" t="n"/>
     </row>
     <row r="352" ht="19.8" customHeight="1">
       <c r="A352" s="47" t="n"/>
-      <c r="B352" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C352" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
+      <c r="B352" s="60" t="inlineStr">
+        <is>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
+        </is>
+      </c>
+      <c r="C352" s="59" t="n">
+        <v>708</v>
       </c>
       <c r="D352" s="12" t="n"/>
       <c r="E352" s="39" t="n"/>
-      <c r="F352" s="61" t="n"/>
+      <c r="F352" s="20" t="n"/>
       <c r="G352" s="53" t="n"/>
     </row>
     <row r="353" ht="19.8" customHeight="1">
       <c r="A353" s="47" t="n"/>
       <c r="B353" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 80</t>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
         </is>
       </c>
       <c r="C353" s="59" t="n">
-        <v>708</v>
+        <v>1315</v>
       </c>
       <c r="D353" s="12" t="n"/>
       <c r="E353" s="39" t="n"/>
@@ -26350,11 +26342,11 @@
       <c r="A354" s="47" t="n"/>
       <c r="B354" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 150</t>
+          <t>Toalleros necesarios</t>
         </is>
       </c>
       <c r="C354" s="59" t="n">
-        <v>1315</v>
+        <v>1</v>
       </c>
       <c r="D354" s="12" t="n"/>
       <c r="E354" s="39" t="n"/>
@@ -26362,44 +26354,29 @@
       <c r="G354" s="53" t="n"/>
     </row>
     <row r="355" ht="19.8" customHeight="1">
-      <c r="A355" s="47" t="n"/>
-      <c r="B355" s="60" t="inlineStr">
-        <is>
-          <t>Toalleros necesarios</t>
-        </is>
-      </c>
-      <c r="C355" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D355" s="12" t="n"/>
-      <c r="E355" s="39" t="n"/>
-      <c r="F355" s="20" t="n"/>
+      <c r="A355" s="50" t="n"/>
+      <c r="B355" s="72" t="inlineStr">
+        <is>
+          <t>Toallero adoptado</t>
+        </is>
+      </c>
+      <c r="C355" s="30" t="inlineStr">
+        <is>
+          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
+        </is>
+      </c>
+      <c r="D355" s="11" t="n"/>
+      <c r="E355" s="92" t="n"/>
+      <c r="F355" s="31" t="n"/>
       <c r="G355" s="53" t="n"/>
-    </row>
-    <row r="356" ht="19.8" customHeight="1">
-      <c r="A356" s="50" t="n"/>
-      <c r="B356" s="72" t="inlineStr">
-        <is>
-          <t>Toallero adoptado</t>
-        </is>
-      </c>
-      <c r="C356" s="30" t="inlineStr">
-        <is>
-          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
-        </is>
-      </c>
-      <c r="D356" s="11" t="n"/>
-      <c r="E356" s="92" t="n"/>
-      <c r="F356" s="31" t="n"/>
-      <c r="G356" s="53" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="101">
     <mergeCell ref="C321:E321"/>
     <mergeCell ref="C202:E202"/>
     <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A238:F238"/>
     <mergeCell ref="C297:E297"/>
-    <mergeCell ref="A239:F239"/>
     <mergeCell ref="C60:E60"/>
     <mergeCell ref="C268:E268"/>
     <mergeCell ref="C292:E292"/>
@@ -26409,25 +26386,28 @@
     <mergeCell ref="C204:E204"/>
     <mergeCell ref="C325:E325"/>
     <mergeCell ref="C206:E206"/>
+    <mergeCell ref="C143:E143"/>
     <mergeCell ref="C205:E205"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C118:E118"/>
     <mergeCell ref="C320:E320"/>
-    <mergeCell ref="C238:E238"/>
     <mergeCell ref="C176:E176"/>
     <mergeCell ref="C232:E232"/>
-    <mergeCell ref="C356:E356"/>
+    <mergeCell ref="C114:E114"/>
     <mergeCell ref="C59:E59"/>
     <mergeCell ref="C295:E295"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C178:E178"/>
+    <mergeCell ref="A269:F269"/>
     <mergeCell ref="C61:E61"/>
     <mergeCell ref="C233:E233"/>
+    <mergeCell ref="A122:F122"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C352:E352"/>
     <mergeCell ref="C296:E296"/>
-    <mergeCell ref="C352:E352"/>
-    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C170:E170"/>
+    <mergeCell ref="C348:E348"/>
     <mergeCell ref="C145:E145"/>
     <mergeCell ref="C323:E323"/>
-    <mergeCell ref="C298:E298"/>
     <mergeCell ref="C87:E87"/>
     <mergeCell ref="C267:E267"/>
     <mergeCell ref="C266:E266"/>
@@ -26435,42 +26415,38 @@
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="C89:E89"/>
     <mergeCell ref="C116:E116"/>
-    <mergeCell ref="C269:E269"/>
+    <mergeCell ref="A178:F178"/>
     <mergeCell ref="C88:E88"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C324:E324"/>
     <mergeCell ref="C231:E231"/>
+    <mergeCell ref="C63:E63"/>
     <mergeCell ref="C121:E121"/>
-    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C261:E261"/>
+    <mergeCell ref="A208:F208"/>
+    <mergeCell ref="C230:E230"/>
     <mergeCell ref="C117:E117"/>
     <mergeCell ref="C173:E173"/>
     <mergeCell ref="C236:E236"/>
     <mergeCell ref="C350:E350"/>
-    <mergeCell ref="A179:F179"/>
     <mergeCell ref="C115:E115"/>
     <mergeCell ref="C207:E207"/>
     <mergeCell ref="C262:E262"/>
     <mergeCell ref="C144:E144"/>
-    <mergeCell ref="C122:E122"/>
-    <mergeCell ref="A299:F299"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="C264:E264"/>
     <mergeCell ref="C326:E326"/>
-    <mergeCell ref="C208:E208"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="C263:E263"/>
     <mergeCell ref="C354:E354"/>
     <mergeCell ref="C30:E30"/>
-    <mergeCell ref="A328:F328"/>
     <mergeCell ref="C235:E235"/>
-    <mergeCell ref="A270:F270"/>
     <mergeCell ref="C62:E62"/>
     <mergeCell ref="C234:E234"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C172:E172"/>
     <mergeCell ref="C353:E353"/>
     <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C147:E147"/>
     <mergeCell ref="C171:E171"/>
     <mergeCell ref="C349:E349"/>
     <mergeCell ref="A65:F65"/>
@@ -26481,20 +26457,21 @@
     <mergeCell ref="C90:E90"/>
     <mergeCell ref="C120:E120"/>
     <mergeCell ref="C27:E27"/>
+    <mergeCell ref="A298:F298"/>
     <mergeCell ref="C203:E203"/>
     <mergeCell ref="C119:E119"/>
-    <mergeCell ref="A209:F209"/>
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="C174:E174"/>
-    <mergeCell ref="C327:E327"/>
+    <mergeCell ref="A147:F147"/>
+    <mergeCell ref="A327:F327"/>
     <mergeCell ref="C237:E237"/>
     <mergeCell ref="C351:E351"/>
-    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="C319:E319"/>
     <mergeCell ref="C175:E175"/>
     <mergeCell ref="C58:E58"/>
     <mergeCell ref="C294:E294"/>
-    <mergeCell ref="A123:F123"/>
-    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C290:E290"/>
+    <mergeCell ref="C200:E200"/>
     <mergeCell ref="C265:E265"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -19691,7 +19691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G355"/>
+  <dimension ref="A1:G356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.1" customWidth="1" min="1" max="1"/>
@@ -21523,17 +21523,17 @@
       </c>
       <c r="C96" s="18" t="inlineStr">
         <is>
-          <t>4.87 x 3.00</t>
+          <t>1.70 x 3.00</t>
         </is>
       </c>
       <c r="D96" s="19" t="n">
-        <v>14.61</v>
+        <v>5.1</v>
       </c>
       <c r="E96" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F96" s="80" t="n">
-        <v>292.2</v>
+        <v>102</v>
       </c>
       <c r="G96" s="53" t="n"/>
     </row>
@@ -21556,22 +21556,22 @@
       <c r="A98" s="47" t="n"/>
       <c r="B98" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (NE)</t>
+          <t>INTERIORES (SO, hall de ingreso)</t>
         </is>
       </c>
       <c r="C98" s="18" t="inlineStr">
         <is>
-          <t>3.38 x 3.00</t>
+          <t>3.17 x 3.00</t>
         </is>
       </c>
       <c r="D98" s="19" t="n">
-        <v>10.14</v>
+        <v>9.51</v>
       </c>
       <c r="E98" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F98" s="80" t="n">
-        <v>253.5</v>
+        <v>237.8</v>
       </c>
       <c r="G98" s="53" t="n"/>
     </row>
@@ -21579,22 +21579,22 @@
       <c r="A99" s="47" t="n"/>
       <c r="B99" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (NO)</t>
+          <t>INTERIORES (NE)</t>
         </is>
       </c>
       <c r="C99" s="18" t="inlineStr">
         <is>
-          <t>0.57 x 3.00</t>
+          <t>3.38 x 3.00</t>
         </is>
       </c>
       <c r="D99" s="19" t="n">
-        <v>1.71</v>
+        <v>10.14</v>
       </c>
       <c r="E99" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F99" s="80" t="n">
-        <v>42.8</v>
+        <v>253.5</v>
       </c>
       <c r="G99" s="53" t="n"/>
     </row>
@@ -21602,358 +21602,366 @@
       <c r="A100" s="47" t="n"/>
       <c r="B100" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (NE)</t>
+          <t>INTERIORES (NO)</t>
         </is>
       </c>
       <c r="C100" s="18" t="inlineStr">
         <is>
-          <t>1.49 x 3.00</t>
+          <t>0.57 x 3.00</t>
         </is>
       </c>
       <c r="D100" s="19" t="n">
-        <v>4.47</v>
+        <v>1.71</v>
       </c>
       <c r="E100" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F100" s="80" t="n">
-        <v>111.8</v>
+        <v>42.8</v>
       </c>
       <c r="G100" s="53" t="n"/>
     </row>
     <row r="101" ht="19.8" customHeight="1">
-      <c r="A101" s="50" t="n"/>
-      <c r="B101" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES (SE)</t>
+      <c r="A101" s="47" t="n"/>
+      <c r="B101" s="81" t="inlineStr">
+        <is>
+          <t>INTERIORES (NE)</t>
         </is>
       </c>
       <c r="C101" s="18" t="inlineStr">
         <is>
-          <t>1.66 x 3.00</t>
+          <t>1.49 x 3.00</t>
         </is>
       </c>
       <c r="D101" s="19" t="n">
-        <v>4.98</v>
+        <v>4.47</v>
       </c>
       <c r="E101" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F101" s="80" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="G101" s="53" t="n"/>
+    </row>
+    <row r="102" ht="19.8" customHeight="1">
+      <c r="A102" s="50" t="n"/>
+      <c r="B102" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES (SE)</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="inlineStr">
+        <is>
+          <t>1.66 x 3.00</t>
+        </is>
+      </c>
+      <c r="D102" s="19" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="E102" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F102" s="80" t="n">
         <v>124.5</v>
       </c>
-      <c r="G101" s="53" t="n"/>
-    </row>
-    <row r="102" ht="19.8" customHeight="1">
-      <c r="A102" s="36" t="inlineStr">
+      <c r="G102" s="53" t="n"/>
+    </row>
+    <row r="103" ht="19.8" customHeight="1">
+      <c r="A103" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B102" s="78" t="inlineStr">
+      <c r="B103" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C102" s="47" t="n"/>
-      <c r="D102" s="18" t="n"/>
-      <c r="E102" s="18" t="n"/>
-      <c r="F102" s="20" t="n"/>
-      <c r="G102" s="53" t="n"/>
-    </row>
-    <row r="103" ht="19.8" customHeight="1">
-      <c r="A103" s="43" t="n"/>
-      <c r="B103" s="79" t="inlineStr">
+      <c r="C103" s="47" t="n"/>
+      <c r="D103" s="18" t="n"/>
+      <c r="E103" s="18" t="n"/>
+      <c r="F103" s="20" t="n"/>
+      <c r="G103" s="53" t="n"/>
+    </row>
+    <row r="104" ht="19.8" customHeight="1">
+      <c r="A104" s="43" t="n"/>
+      <c r="B104" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C103" s="18" t="n"/>
-      <c r="D103" s="19" t="n"/>
-      <c r="E103" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F103" s="80" t="n"/>
-      <c r="G103" s="53" t="n"/>
-    </row>
-    <row r="104" ht="19.8" customHeight="1">
-      <c r="A104" s="47" t="n"/>
-      <c r="B104" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C104" s="18" t="n"/>
       <c r="D104" s="19" t="n"/>
       <c r="E104" s="59" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F104" s="80" t="n"/>
       <c r="G104" s="53" t="n"/>
     </row>
     <row r="105" ht="19.8" customHeight="1">
-      <c r="A105" s="50" t="n"/>
-      <c r="B105" s="82" t="inlineStr">
+      <c r="A105" s="47" t="n"/>
+      <c r="B105" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="n"/>
+      <c r="D105" s="19" t="n"/>
+      <c r="E105" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F105" s="80" t="n"/>
+      <c r="G105" s="53" t="n"/>
+    </row>
+    <row r="106" ht="19.8" customHeight="1">
+      <c r="A106" s="50" t="n"/>
+      <c r="B106" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C105" s="18" t="inlineStr">
+      <c r="C106" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D105" s="19" t="n">
+      <c r="D106" s="19" t="n">
         <v>7.23</v>
       </c>
-      <c r="E105" s="59" t="n">
+      <c r="E106" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F105" s="80" t="n">
+      <c r="F106" s="80" t="n">
         <v>108.5</v>
       </c>
-      <c r="G105" s="53" t="n"/>
-    </row>
-    <row r="106" ht="19.8" customHeight="1">
-      <c r="A106" s="36" t="inlineStr">
+      <c r="G106" s="53" t="n"/>
+    </row>
+    <row r="107" ht="19.8" customHeight="1">
+      <c r="A107" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B106" s="78" t="inlineStr">
+      <c r="B107" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C106" s="47" t="n"/>
-      <c r="D106" s="18" t="n"/>
-      <c r="E106" s="18" t="n"/>
-      <c r="F106" s="20" t="n"/>
-      <c r="G106" s="53" t="n"/>
-    </row>
-    <row r="107" ht="19.8" customHeight="1">
-      <c r="A107" s="43" t="n"/>
-      <c r="B107" s="79" t="inlineStr">
+      <c r="C107" s="47" t="n"/>
+      <c r="D107" s="18" t="n"/>
+      <c r="E107" s="18" t="n"/>
+      <c r="F107" s="20" t="n"/>
+      <c r="G107" s="53" t="n"/>
+    </row>
+    <row r="108" ht="19.8" customHeight="1">
+      <c r="A108" s="43" t="n"/>
+      <c r="B108" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C107" s="18" t="inlineStr">
+      <c r="C108" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D107" s="19" t="n">
+      <c r="D108" s="19" t="n">
         <v>7.23</v>
       </c>
-      <c r="E107" s="59" t="n">
+      <c r="E108" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F107" s="80" t="n">
+      <c r="F108" s="80" t="n">
         <v>72.3</v>
       </c>
-      <c r="G107" s="53" t="n"/>
-    </row>
-    <row r="108" ht="19.8" customHeight="1">
-      <c r="A108" s="50" t="n"/>
-      <c r="B108" s="82" t="inlineStr">
+      <c r="G108" s="53" t="n"/>
+    </row>
+    <row r="109" ht="19.8" customHeight="1">
+      <c r="A109" s="50" t="n"/>
+      <c r="B109" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C108" s="18" t="n"/>
-      <c r="D108" s="24" t="n"/>
-      <c r="E108" s="59" t="n">
+      <c r="C109" s="18" t="n"/>
+      <c r="D109" s="24" t="n"/>
+      <c r="E109" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F108" s="80" t="n"/>
-      <c r="G108" s="53" t="n"/>
-    </row>
-    <row r="109" ht="19.8" customHeight="1">
-      <c r="A109" s="36" t="inlineStr">
+      <c r="F109" s="80" t="n"/>
+      <c r="G109" s="53" t="n"/>
+    </row>
+    <row r="110" ht="19.8" customHeight="1">
+      <c r="A110" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B109" s="78" t="inlineStr">
+      <c r="B110" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C109" s="83" t="n"/>
-      <c r="D109" s="36" t="inlineStr">
+      <c r="C110" s="83" t="n"/>
+      <c r="D110" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E109" s="47" t="n"/>
-      <c r="F109" s="20" t="n"/>
-      <c r="G109" s="53" t="n"/>
-    </row>
-    <row r="110" ht="19.8" customHeight="1">
-      <c r="A110" s="43" t="n"/>
-      <c r="B110" s="79" t="inlineStr">
+      <c r="E110" s="47" t="n"/>
+      <c r="F110" s="20" t="n"/>
+      <c r="G110" s="53" t="n"/>
+    </row>
+    <row r="111" ht="19.8" customHeight="1">
+      <c r="A111" s="43" t="n"/>
+      <c r="B111" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C110" s="18" t="inlineStr">
+      <c r="C111" s="18" t="inlineStr">
         <is>
           <t>7.23 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D110" s="22" t="n">
+      <c r="D111" s="22" t="n">
         <v>21.69</v>
       </c>
-      <c r="E110" s="59" t="n">
+      <c r="E111" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="F110" s="80" t="n">
+      <c r="F111" s="80" t="n">
         <v>130.1</v>
       </c>
-      <c r="G110" s="53" t="n"/>
-    </row>
-    <row r="111" ht="19.8" customHeight="1">
-      <c r="A111" s="47" t="n"/>
-      <c r="B111" s="81" t="inlineStr">
+      <c r="G111" s="53" t="n"/>
+    </row>
+    <row r="112" ht="19.8" customHeight="1">
+      <c r="A112" s="47" t="n"/>
+      <c r="B112" s="81" t="inlineStr">
         <is>
           <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C111" s="18" t="n"/>
-      <c r="D111" s="19" t="n"/>
-      <c r="E111" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F111" s="80" t="n"/>
-      <c r="G111" s="53" t="n"/>
-    </row>
-    <row r="112" ht="19.8" customHeight="1">
-      <c r="A112" s="50" t="n"/>
-      <c r="B112" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C112" s="18" t="n"/>
       <c r="D112" s="19" t="n"/>
       <c r="E112" s="59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F112" s="80" t="n"/>
+      <c r="G112" s="53" t="n"/>
+    </row>
+    <row r="113" ht="19.8" customHeight="1">
+      <c r="A113" s="50" t="n"/>
+      <c r="B113" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C113" s="18" t="n"/>
+      <c r="D113" s="19" t="n"/>
+      <c r="E113" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F112" s="84" t="n"/>
-      <c r="G112" s="53" t="n"/>
-    </row>
-    <row r="113" ht="19.8" customHeight="1">
-      <c r="A113" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B113" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C113" s="47" t="n"/>
-      <c r="D113" s="18" t="n"/>
-      <c r="E113" s="20" t="n"/>
-      <c r="F113" s="85" t="n">
-        <v>1135.7</v>
-      </c>
+      <c r="F113" s="84" t="n"/>
       <c r="G113" s="53" t="n"/>
     </row>
     <row r="114" ht="19.8" customHeight="1">
       <c r="A114" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B114" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C114" s="47" t="n"/>
+      <c r="D114" s="18" t="n"/>
+      <c r="E114" s="20" t="n"/>
+      <c r="F114" s="85" t="n">
+        <v>1183.3</v>
+      </c>
+      <c r="G114" s="53" t="n"/>
+    </row>
+    <row r="115" ht="19.8" customHeight="1">
+      <c r="A115" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B114" s="78" t="inlineStr">
+      <c r="B115" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C114" s="47" t="inlineStr">
-        <is>
-          <t>1135.70  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
-        </is>
-      </c>
-      <c r="D114" s="12" t="n"/>
-      <c r="E114" s="14" t="n"/>
-      <c r="F114" s="85" t="n">
-        <v>1215.2</v>
-      </c>
-      <c r="G114" s="53" t="n"/>
-    </row>
-    <row r="115" ht="19.8" customHeight="1">
-      <c r="A115" s="43" t="n"/>
-      <c r="B115" s="86" t="inlineStr">
+      <c r="C115" s="47" t="inlineStr">
+        <is>
+          <t>1183.30  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="n"/>
+      <c r="E115" s="14" t="n"/>
+      <c r="F115" s="85" t="n">
+        <v>1266.1</v>
+      </c>
+      <c r="G115" s="53" t="n"/>
+    </row>
+    <row r="116" ht="19.8" customHeight="1">
+      <c r="A116" s="43" t="n"/>
+      <c r="B116" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C115" s="18" t="n"/>
-      <c r="D115" s="12" t="n"/>
-      <c r="E115" s="39" t="n"/>
-      <c r="F115" s="87" t="n"/>
-      <c r="G115" s="53" t="n"/>
-    </row>
-    <row r="116" ht="19.8" customHeight="1">
-      <c r="A116" s="83" t="n"/>
-      <c r="B116" s="78" t="inlineStr">
+      <c r="C116" s="18" t="n"/>
+      <c r="D116" s="12" t="n"/>
+      <c r="E116" s="39" t="n"/>
+      <c r="F116" s="87" t="n"/>
+      <c r="G116" s="53" t="n"/>
+    </row>
+    <row r="117" ht="19.8" customHeight="1">
+      <c r="A117" s="83" t="n"/>
+      <c r="B117" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C116" s="47" t="n"/>
-      <c r="D116" s="12" t="n"/>
-      <c r="E116" s="14" t="n"/>
-      <c r="F116" s="85" t="n">
-        <v>1215.2</v>
-      </c>
-      <c r="G116" s="53" t="n"/>
-    </row>
-    <row r="117" ht="19.8" customHeight="1">
-      <c r="A117" s="47" t="n"/>
-      <c r="B117" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C117" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
-      </c>
+      <c r="C117" s="47" t="n"/>
       <c r="D117" s="12" t="n"/>
-      <c r="E117" s="39" t="n"/>
-      <c r="F117" s="61" t="n"/>
+      <c r="E117" s="14" t="n"/>
+      <c r="F117" s="85" t="n">
+        <v>1266.1</v>
+      </c>
       <c r="G117" s="53" t="n"/>
     </row>
     <row r="118" ht="19.8" customHeight="1">
       <c r="A118" s="47" t="n"/>
-      <c r="B118" s="60" t="inlineStr">
-        <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C118" s="19" t="n">
-        <v>274.4</v>
+      <c r="B118" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
       </c>
       <c r="D118" s="12" t="n"/>
       <c r="E118" s="39" t="n"/>
-      <c r="F118" s="20" t="n"/>
+      <c r="F118" s="61" t="n"/>
       <c r="G118" s="53" t="n"/>
     </row>
     <row r="119" ht="19.8" customHeight="1">
       <c r="A119" s="47" t="n"/>
       <c r="B119" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
-        </is>
-      </c>
-      <c r="C119" s="59" t="n">
-        <v>5</v>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C119" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D119" s="12" t="n"/>
       <c r="E119" s="39" t="n"/>
@@ -21964,11 +21972,11 @@
       <c r="A120" s="47" t="n"/>
       <c r="B120" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C120" s="59" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="D120" s="12" t="n"/>
       <c r="E120" s="39" t="n"/>
@@ -21976,16 +21984,14 @@
       <c r="G120" s="53" t="n"/>
     </row>
     <row r="121" ht="19.8" customHeight="1">
-      <c r="A121" s="50" t="n"/>
+      <c r="A121" s="47" t="n"/>
       <c r="B121" s="60" t="inlineStr">
         <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C121" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
+          <t>Ancho del radiador (cm)</t>
+        </is>
+      </c>
+      <c r="C121" s="59" t="n">
+        <v>40</v>
       </c>
       <c r="D121" s="12" t="n"/>
       <c r="E121" s="39" t="n"/>
@@ -21993,151 +21999,145 @@
       <c r="G121" s="53" t="n"/>
     </row>
     <row r="122" ht="19.8" customHeight="1">
-      <c r="A122" s="8" t="inlineStr">
+      <c r="A122" s="50" t="n"/>
+      <c r="B122" s="60" t="inlineStr">
+        <is>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="n"/>
+      <c r="E122" s="39" t="n"/>
+      <c r="F122" s="20" t="n"/>
+      <c r="G122" s="53" t="n"/>
+    </row>
+    <row r="123" ht="19.8" customHeight="1">
+      <c r="A123" s="8" t="inlineStr">
         <is>
           <t>LOCAL  Escalera   (PB)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B122" s="11" t="n"/>
-      <c r="C122" s="11" t="n"/>
-      <c r="D122" s="11" t="n"/>
-      <c r="E122" s="11" t="n"/>
-      <c r="F122" s="42" t="n"/>
-      <c r="G122" s="53" t="n"/>
-    </row>
-    <row r="123" ht="32" customHeight="1">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="B123" s="11" t="n"/>
+      <c r="C123" s="11" t="n"/>
+      <c r="D123" s="11" t="n"/>
+      <c r="E123" s="11" t="n"/>
+      <c r="F123" s="42" t="n"/>
+      <c r="G123" s="53" t="n"/>
+    </row>
+    <row r="124" ht="32" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G123" s="53" t="n"/>
-    </row>
-    <row r="124" ht="19.8" customHeight="1">
-      <c r="A124" s="36" t="inlineStr">
+      <c r="G124" s="53" t="n"/>
+    </row>
+    <row r="125" ht="19.8" customHeight="1">
+      <c r="A125" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B124" s="78" t="inlineStr">
+      <c r="B125" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C124" s="43" t="n"/>
-      <c r="D124" s="58" t="n"/>
-      <c r="E124" s="58" t="n"/>
-      <c r="F124" s="61" t="n"/>
-      <c r="G124" s="53" t="n"/>
-    </row>
-    <row r="125" ht="19.8" customHeight="1">
-      <c r="A125" s="90" t="n"/>
-      <c r="B125" s="91" t="inlineStr">
+      <c r="C125" s="43" t="n"/>
+      <c r="D125" s="58" t="n"/>
+      <c r="E125" s="58" t="n"/>
+      <c r="F125" s="61" t="n"/>
+      <c r="G125" s="53" t="n"/>
+    </row>
+    <row r="126" ht="19.8" customHeight="1">
+      <c r="A126" s="90" t="n"/>
+      <c r="B126" s="91" t="inlineStr">
         <is>
           <t>PF05</t>
         </is>
       </c>
-      <c r="C125" s="18" t="inlineStr">
+      <c r="C126" s="18" t="inlineStr">
         <is>
           <t>0.75 x 2.52</t>
         </is>
       </c>
-      <c r="D125" s="19" t="n">
+      <c r="D126" s="19" t="n">
         <v>1.89</v>
       </c>
-      <c r="E125" s="59" t="n">
+      <c r="E126" s="59" t="n">
         <v>60</v>
       </c>
-      <c r="F125" s="80" t="n">
+      <c r="F126" s="80" t="n">
         <v>113.4</v>
       </c>
-      <c r="G125" s="53" t="n"/>
-    </row>
-    <row r="126" ht="19.8" customHeight="1">
-      <c r="A126" s="36" t="inlineStr">
+      <c r="G126" s="53" t="n"/>
+    </row>
+    <row r="127" ht="19.8" customHeight="1">
+      <c r="A127" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B126" s="78" t="inlineStr">
+      <c r="B127" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C126" s="47" t="n"/>
-      <c r="D126" s="18" t="n"/>
-      <c r="E126" s="18" t="n"/>
-      <c r="F126" s="20" t="n"/>
-      <c r="G126" s="53" t="n"/>
-    </row>
-    <row r="127" ht="19.8" customHeight="1">
-      <c r="A127" s="43" t="n"/>
-      <c r="B127" s="79" t="inlineStr">
+      <c r="C127" s="47" t="n"/>
+      <c r="D127" s="18" t="n"/>
+      <c r="E127" s="18" t="n"/>
+      <c r="F127" s="20" t="n"/>
+      <c r="G127" s="53" t="n"/>
+    </row>
+    <row r="128" ht="19.8" customHeight="1">
+      <c r="A128" s="43" t="n"/>
+      <c r="B128" s="79" t="inlineStr">
         <is>
           <t>AISLADAS</t>
         </is>
       </c>
-      <c r="C127" s="18" t="inlineStr">
+      <c r="C128" s="18" t="inlineStr">
         <is>
           <t>4.06 x 3.00</t>
         </is>
       </c>
-      <c r="D127" s="19" t="n">
+      <c r="D128" s="19" t="n">
         <v>12.18</v>
-      </c>
-      <c r="E127" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F127" s="80" t="n">
-        <v>243.6</v>
-      </c>
-      <c r="G127" s="53" t="n"/>
-    </row>
-    <row r="128" ht="19.8" customHeight="1">
-      <c r="A128" s="47" t="n"/>
-      <c r="B128" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS (SO)</t>
-        </is>
-      </c>
-      <c r="C128" s="18" t="inlineStr">
-        <is>
-          <t>1.73 x 3.00</t>
-        </is>
-      </c>
-      <c r="D128" s="19" t="n">
-        <v>5.19</v>
       </c>
       <c r="E128" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F128" s="80" t="n">
-        <v>103.8</v>
+        <v>243.6</v>
       </c>
       <c r="G128" s="53" t="n"/>
     </row>
@@ -22145,488 +22145,488 @@
       <c r="A129" s="47" t="n"/>
       <c r="B129" s="81" t="inlineStr">
         <is>
+          <t>AISLADAS (SO)</t>
+        </is>
+      </c>
+      <c r="C129" s="18" t="inlineStr">
+        <is>
+          <t>1.73 x 3.00</t>
+        </is>
+      </c>
+      <c r="D129" s="19" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="E129" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F129" s="80" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="G129" s="53" t="n"/>
+    </row>
+    <row r="130" ht="19.8" customHeight="1">
+      <c r="A130" s="47" t="n"/>
+      <c r="B130" s="81" t="inlineStr">
+        <is>
           <t>INTERIORES</t>
         </is>
       </c>
-      <c r="C129" s="18" t="inlineStr">
+      <c r="C130" s="18" t="inlineStr">
         <is>
           <t>4.06 x 3.00</t>
         </is>
       </c>
-      <c r="D129" s="19" t="n">
+      <c r="D130" s="19" t="n">
         <v>12.18</v>
-      </c>
-      <c r="E129" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F129" s="80" t="n">
-        <v>304.5</v>
-      </c>
-      <c r="G129" s="53" t="n"/>
-    </row>
-    <row r="130" ht="19.8" customHeight="1">
-      <c r="A130" s="50" t="n"/>
-      <c r="B130" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES (NE)</t>
-        </is>
-      </c>
-      <c r="C130" s="18" t="inlineStr">
-        <is>
-          <t>1.73 x 3.00</t>
-        </is>
-      </c>
-      <c r="D130" s="19" t="n">
-        <v>5.19</v>
       </c>
       <c r="E130" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F130" s="80" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="G130" s="53" t="n"/>
+    </row>
+    <row r="131" ht="19.8" customHeight="1">
+      <c r="A131" s="50" t="n"/>
+      <c r="B131" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES (NE)</t>
+        </is>
+      </c>
+      <c r="C131" s="18" t="inlineStr">
+        <is>
+          <t>1.73 x 3.00</t>
+        </is>
+      </c>
+      <c r="D131" s="19" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="E131" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F131" s="80" t="n">
         <v>129.8</v>
       </c>
-      <c r="G130" s="53" t="n"/>
-    </row>
-    <row r="131" ht="19.8" customHeight="1">
-      <c r="A131" s="36" t="inlineStr">
+      <c r="G131" s="53" t="n"/>
+    </row>
+    <row r="132" ht="19.8" customHeight="1">
+      <c r="A132" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B131" s="78" t="inlineStr">
+      <c r="B132" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C131" s="47" t="n"/>
-      <c r="D131" s="18" t="n"/>
-      <c r="E131" s="18" t="n"/>
-      <c r="F131" s="20" t="n"/>
-      <c r="G131" s="53" t="n"/>
-    </row>
-    <row r="132" ht="19.8" customHeight="1">
-      <c r="A132" s="43" t="n"/>
-      <c r="B132" s="79" t="inlineStr">
+      <c r="C132" s="47" t="n"/>
+      <c r="D132" s="18" t="n"/>
+      <c r="E132" s="18" t="n"/>
+      <c r="F132" s="20" t="n"/>
+      <c r="G132" s="53" t="n"/>
+    </row>
+    <row r="133" ht="19.8" customHeight="1">
+      <c r="A133" s="43" t="n"/>
+      <c r="B133" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C132" s="18" t="n"/>
-      <c r="D132" s="19" t="n"/>
-      <c r="E132" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F132" s="80" t="n"/>
-      <c r="G132" s="53" t="n"/>
-    </row>
-    <row r="133" ht="19.8" customHeight="1">
-      <c r="A133" s="47" t="n"/>
-      <c r="B133" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C133" s="18" t="n"/>
       <c r="D133" s="19" t="n"/>
       <c r="E133" s="59" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F133" s="80" t="n"/>
       <c r="G133" s="53" t="n"/>
     </row>
     <row r="134" ht="19.8" customHeight="1">
-      <c r="A134" s="50" t="n"/>
-      <c r="B134" s="82" t="inlineStr">
+      <c r="A134" s="47" t="n"/>
+      <c r="B134" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="n"/>
+      <c r="D134" s="19" t="n"/>
+      <c r="E134" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F134" s="80" t="n"/>
+      <c r="G134" s="53" t="n"/>
+    </row>
+    <row r="135" ht="19.8" customHeight="1">
+      <c r="A135" s="50" t="n"/>
+      <c r="B135" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C134" s="18" t="inlineStr">
+      <c r="C135" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D134" s="19" t="n">
+      <c r="D135" s="19" t="n">
         <v>7.02</v>
       </c>
-      <c r="E134" s="59" t="n">
+      <c r="E135" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F134" s="80" t="n">
+      <c r="F135" s="80" t="n">
         <v>105.3</v>
       </c>
-      <c r="G134" s="53" t="n"/>
-    </row>
-    <row r="135" ht="19.8" customHeight="1">
-      <c r="A135" s="36" t="inlineStr">
+      <c r="G135" s="53" t="n"/>
+    </row>
+    <row r="136" ht="19.8" customHeight="1">
+      <c r="A136" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B135" s="78" t="inlineStr">
+      <c r="B136" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C135" s="47" t="n"/>
-      <c r="D135" s="18" t="n"/>
-      <c r="E135" s="18" t="n"/>
-      <c r="F135" s="20" t="n"/>
-      <c r="G135" s="53" t="n"/>
-    </row>
-    <row r="136" ht="19.8" customHeight="1">
-      <c r="A136" s="43" t="n"/>
-      <c r="B136" s="79" t="inlineStr">
+      <c r="C136" s="47" t="n"/>
+      <c r="D136" s="18" t="n"/>
+      <c r="E136" s="18" t="n"/>
+      <c r="F136" s="20" t="n"/>
+      <c r="G136" s="53" t="n"/>
+    </row>
+    <row r="137" ht="19.8" customHeight="1">
+      <c r="A137" s="43" t="n"/>
+      <c r="B137" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C136" s="18" t="inlineStr">
+      <c r="C137" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D136" s="19" t="n">
+      <c r="D137" s="19" t="n">
         <v>7.02</v>
       </c>
-      <c r="E136" s="59" t="n">
+      <c r="E137" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F136" s="80" t="n">
+      <c r="F137" s="80" t="n">
         <v>70.2</v>
       </c>
-      <c r="G136" s="53" t="n"/>
-    </row>
-    <row r="137" ht="19.8" customHeight="1">
-      <c r="A137" s="50" t="n"/>
-      <c r="B137" s="82" t="inlineStr">
+      <c r="G137" s="53" t="n"/>
+    </row>
+    <row r="138" ht="19.8" customHeight="1">
+      <c r="A138" s="50" t="n"/>
+      <c r="B138" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C137" s="18" t="n"/>
-      <c r="D137" s="24" t="n"/>
-      <c r="E137" s="59" t="n">
+      <c r="C138" s="18" t="n"/>
+      <c r="D138" s="24" t="n"/>
+      <c r="E138" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F137" s="80" t="n"/>
-      <c r="G137" s="53" t="n"/>
-    </row>
-    <row r="138" ht="19.8" customHeight="1">
-      <c r="A138" s="36" t="inlineStr">
+      <c r="F138" s="80" t="n"/>
+      <c r="G138" s="53" t="n"/>
+    </row>
+    <row r="139" ht="19.8" customHeight="1">
+      <c r="A139" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B138" s="78" t="inlineStr">
+      <c r="B139" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C138" s="83" t="n"/>
-      <c r="D138" s="36" t="inlineStr">
+      <c r="C139" s="83" t="n"/>
+      <c r="D139" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E138" s="47" t="n"/>
-      <c r="F138" s="20" t="n"/>
-      <c r="G138" s="53" t="n"/>
-    </row>
-    <row r="139" ht="19.8" customHeight="1">
-      <c r="A139" s="43" t="n"/>
-      <c r="B139" s="79" t="inlineStr">
+      <c r="E139" s="47" t="n"/>
+      <c r="F139" s="20" t="n"/>
+      <c r="G139" s="53" t="n"/>
+    </row>
+    <row r="140" ht="19.8" customHeight="1">
+      <c r="A140" s="43" t="n"/>
+      <c r="B140" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C139" s="18" t="n"/>
-      <c r="D139" s="22" t="n"/>
-      <c r="E139" s="59" t="n">
+      <c r="C140" s="18" t="n"/>
+      <c r="D140" s="22" t="n"/>
+      <c r="E140" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="F139" s="80" t="n"/>
-      <c r="G139" s="53" t="n"/>
-    </row>
-    <row r="140" ht="19.8" customHeight="1">
-      <c r="A140" s="47" t="n"/>
-      <c r="B140" s="81" t="inlineStr">
+      <c r="F140" s="80" t="n"/>
+      <c r="G140" s="53" t="n"/>
+    </row>
+    <row r="141" ht="19.8" customHeight="1">
+      <c r="A141" s="47" t="n"/>
+      <c r="B141" s="81" t="inlineStr">
         <is>
           <t>DOS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C140" s="18" t="inlineStr">
+      <c r="C141" s="18" t="inlineStr">
         <is>
           <t>7.02 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D140" s="19" t="n">
+      <c r="D141" s="19" t="n">
         <v>21.06</v>
       </c>
-      <c r="E140" s="59" t="n">
+      <c r="E141" s="59" t="n">
         <v>9</v>
       </c>
-      <c r="F140" s="80" t="n">
+      <c r="F141" s="80" t="n">
         <v>189.5</v>
       </c>
-      <c r="G140" s="53" t="n"/>
-    </row>
-    <row r="141" ht="19.8" customHeight="1">
-      <c r="A141" s="50" t="n"/>
-      <c r="B141" s="82" t="inlineStr">
+      <c r="G141" s="53" t="n"/>
+    </row>
+    <row r="142" ht="19.8" customHeight="1">
+      <c r="A142" s="50" t="n"/>
+      <c r="B142" s="82" t="inlineStr">
         <is>
           <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C141" s="18" t="n"/>
-      <c r="D141" s="19" t="n"/>
-      <c r="E141" s="59" t="n">
+      <c r="C142" s="18" t="n"/>
+      <c r="D142" s="19" t="n"/>
+      <c r="E142" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F141" s="84" t="n"/>
-      <c r="G141" s="53" t="n"/>
-    </row>
-    <row r="142" ht="19.8" customHeight="1">
-      <c r="A142" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B142" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C142" s="47" t="n"/>
-      <c r="D142" s="18" t="n"/>
-      <c r="E142" s="20" t="n"/>
-      <c r="F142" s="85" t="n">
-        <v>1260.1</v>
-      </c>
+      <c r="F142" s="84" t="n"/>
       <c r="G142" s="53" t="n"/>
     </row>
     <row r="143" ht="19.8" customHeight="1">
       <c r="A143" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B143" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C143" s="47" t="n"/>
+      <c r="D143" s="18" t="n"/>
+      <c r="E143" s="20" t="n"/>
+      <c r="F143" s="85" t="n">
+        <v>1260.1</v>
+      </c>
+      <c r="G143" s="53" t="n"/>
+    </row>
+    <row r="144" ht="19.8" customHeight="1">
+      <c r="A144" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B143" s="78" t="inlineStr">
+      <c r="B144" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C143" s="47" t="inlineStr">
+      <c r="C144" s="47" t="inlineStr">
         <is>
           <t>1260.10  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D143" s="12" t="n"/>
-      <c r="E143" s="14" t="n"/>
-      <c r="F143" s="85" t="n">
+      <c r="D144" s="12" t="n"/>
+      <c r="E144" s="14" t="n"/>
+      <c r="F144" s="85" t="n">
         <v>1348.3</v>
       </c>
-      <c r="G143" s="53" t="n"/>
-    </row>
-    <row r="144" ht="19.8" customHeight="1">
-      <c r="A144" s="43" t="n"/>
-      <c r="B144" s="86" t="inlineStr">
+      <c r="G144" s="53" t="n"/>
+    </row>
+    <row r="145" ht="19.8" customHeight="1">
+      <c r="A145" s="43" t="n"/>
+      <c r="B145" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C144" s="18" t="n"/>
-      <c r="D144" s="12" t="n"/>
-      <c r="E144" s="39" t="n"/>
-      <c r="F144" s="87" t="n"/>
-      <c r="G144" s="53" t="n"/>
-    </row>
-    <row r="145" ht="19.8" customHeight="1">
-      <c r="A145" s="83" t="n"/>
-      <c r="B145" s="78" t="inlineStr">
+      <c r="C145" s="18" t="n"/>
+      <c r="D145" s="12" t="n"/>
+      <c r="E145" s="39" t="n"/>
+      <c r="F145" s="87" t="n"/>
+      <c r="G145" s="53" t="n"/>
+    </row>
+    <row r="146" ht="19.8" customHeight="1">
+      <c r="A146" s="83" t="n"/>
+      <c r="B146" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C145" s="47" t="n"/>
-      <c r="D145" s="12" t="n"/>
-      <c r="E145" s="14" t="n"/>
-      <c r="F145" s="85" t="n">
+      <c r="C146" s="47" t="n"/>
+      <c r="D146" s="12" t="n"/>
+      <c r="E146" s="14" t="n"/>
+      <c r="F146" s="85" t="n">
         <v>1348.3</v>
       </c>
-      <c r="G145" s="53" t="n"/>
-    </row>
-    <row r="146" ht="19.8" customHeight="1">
-      <c r="A146" s="89" t="n"/>
-      <c r="B146" s="78" t="inlineStr">
+      <c r="G146" s="53" t="n"/>
+    </row>
+    <row r="147" ht="19.8" customHeight="1">
+      <c r="A147" s="89" t="n"/>
+      <c r="B147" s="78" t="inlineStr">
         <is>
           <t>SIN EMISOR</t>
         </is>
       </c>
-      <c r="C146" s="47" t="inlineStr">
+      <c r="C147" s="47" t="inlineStr">
         <is>
           <t>la cubre el radiador de 14 - Play room</t>
         </is>
       </c>
-      <c r="D146" s="12" t="n"/>
-      <c r="E146" s="39" t="n"/>
-      <c r="F146" s="61" t="n"/>
-      <c r="G146" s="53" t="n"/>
-    </row>
-    <row r="147" ht="19.8" customHeight="1">
-      <c r="A147" s="8" t="inlineStr">
+      <c r="D147" s="12" t="n"/>
+      <c r="E147" s="39" t="n"/>
+      <c r="F147" s="61" t="n"/>
+      <c r="G147" s="53" t="n"/>
+    </row>
+    <row r="148" ht="19.8" customHeight="1">
+      <c r="A148" s="8" t="inlineStr">
         <is>
           <t>LOCAL  09 - Dormitorio suite   (PB)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B147" s="3" t="n"/>
-      <c r="C147" s="11" t="n"/>
-      <c r="D147" s="11" t="n"/>
-      <c r="E147" s="11" t="n"/>
-      <c r="F147" s="42" t="n"/>
-      <c r="G147" s="53" t="n"/>
-    </row>
-    <row r="148" ht="32" customHeight="1">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="B148" s="3" t="n"/>
+      <c r="C148" s="11" t="n"/>
+      <c r="D148" s="11" t="n"/>
+      <c r="E148" s="11" t="n"/>
+      <c r="F148" s="42" t="n"/>
+      <c r="G148" s="53" t="n"/>
+    </row>
+    <row r="149" ht="32" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G148" s="53" t="n"/>
-    </row>
-    <row r="149" ht="19.8" customHeight="1">
-      <c r="A149" s="36" t="inlineStr">
+      <c r="G149" s="53" t="n"/>
+    </row>
+    <row r="150" ht="19.8" customHeight="1">
+      <c r="A150" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B149" s="78" t="inlineStr">
+      <c r="B150" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C149" s="43" t="n"/>
-      <c r="D149" s="58" t="n"/>
-      <c r="E149" s="58" t="n"/>
-      <c r="F149" s="61" t="n"/>
-      <c r="G149" s="53" t="n"/>
-    </row>
-    <row r="150" ht="19.8" customHeight="1">
-      <c r="A150" s="43" t="n"/>
-      <c r="B150" s="79" t="inlineStr">
+      <c r="C150" s="43" t="n"/>
+      <c r="D150" s="58" t="n"/>
+      <c r="E150" s="58" t="n"/>
+      <c r="F150" s="61" t="n"/>
+      <c r="G150" s="53" t="n"/>
+    </row>
+    <row r="151" ht="19.8" customHeight="1">
+      <c r="A151" s="43" t="n"/>
+      <c r="B151" s="79" t="inlineStr">
         <is>
           <t>VA01</t>
         </is>
       </c>
-      <c r="C150" s="18" t="inlineStr">
+      <c r="C151" s="18" t="inlineStr">
         <is>
           <t>0.75 x 3.00</t>
         </is>
       </c>
-      <c r="D150" s="19" t="n">
+      <c r="D151" s="19" t="n">
         <v>2.25</v>
-      </c>
-      <c r="E150" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F150" s="80" t="n">
-        <v>135</v>
-      </c>
-      <c r="G150" s="53" t="n"/>
-    </row>
-    <row r="151" ht="19.8" customHeight="1">
-      <c r="A151" s="50" t="n"/>
-      <c r="B151" s="82" t="inlineStr">
-        <is>
-          <t>PV03</t>
-        </is>
-      </c>
-      <c r="C151" s="18" t="inlineStr">
-        <is>
-          <t>1.76 x 3.00</t>
-        </is>
-      </c>
-      <c r="D151" s="19" t="n">
-        <v>5.28</v>
       </c>
       <c r="E151" s="59" t="n">
         <v>60</v>
       </c>
       <c r="F151" s="80" t="n">
+        <v>135</v>
+      </c>
+      <c r="G151" s="53" t="n"/>
+    </row>
+    <row r="152" ht="19.8" customHeight="1">
+      <c r="A152" s="50" t="n"/>
+      <c r="B152" s="82" t="inlineStr">
+        <is>
+          <t>PV03</t>
+        </is>
+      </c>
+      <c r="C152" s="18" t="inlineStr">
+        <is>
+          <t>1.76 x 3.00</t>
+        </is>
+      </c>
+      <c r="D152" s="19" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="E152" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F152" s="80" t="n">
         <v>316.8</v>
       </c>
-      <c r="G151" s="53" t="n"/>
-    </row>
-    <row r="152" ht="19.8" customHeight="1">
-      <c r="A152" s="36" t="inlineStr">
+      <c r="G152" s="53" t="n"/>
+    </row>
+    <row r="153" ht="19.8" customHeight="1">
+      <c r="A153" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B152" s="78" t="inlineStr">
+      <c r="B153" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C152" s="47" t="n"/>
-      <c r="D152" s="18" t="n"/>
-      <c r="E152" s="18" t="n"/>
-      <c r="F152" s="20" t="n"/>
-      <c r="G152" s="53" t="n"/>
-    </row>
-    <row r="153" ht="19.8" customHeight="1">
-      <c r="A153" s="43" t="n"/>
-      <c r="B153" s="79" t="inlineStr">
+      <c r="C153" s="47" t="n"/>
+      <c r="D153" s="18" t="n"/>
+      <c r="E153" s="18" t="n"/>
+      <c r="F153" s="20" t="n"/>
+      <c r="G153" s="53" t="n"/>
+    </row>
+    <row r="154" ht="19.8" customHeight="1">
+      <c r="A154" s="43" t="n"/>
+      <c r="B154" s="79" t="inlineStr">
         <is>
           <t>AISLADAS (NE)</t>
-        </is>
-      </c>
-      <c r="C153" s="18" t="inlineStr">
-        <is>
-          <t>3.50 x 3.00</t>
-        </is>
-      </c>
-      <c r="D153" s="19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="E153" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F153" s="80" t="n">
-        <v>210</v>
-      </c>
-      <c r="G153" s="53" t="n"/>
-    </row>
-    <row r="154" ht="19.8" customHeight="1">
-      <c r="A154" s="47" t="n"/>
-      <c r="B154" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS (SO)</t>
         </is>
       </c>
       <c r="C154" s="18" t="inlineStr">
@@ -22649,7 +22649,7 @@
       <c r="A155" s="47" t="n"/>
       <c r="B155" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (SE)</t>
+          <t>AISLADAS (SO)</t>
         </is>
       </c>
       <c r="C155" s="18" t="inlineStr">
@@ -22672,7 +22672,7 @@
       <c r="A156" s="47" t="n"/>
       <c r="B156" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (NO)</t>
+          <t>AISLADAS (SE)</t>
         </is>
       </c>
       <c r="C156" s="18" t="inlineStr">
@@ -22684,338 +22684,346 @@
         <v>10.5</v>
       </c>
       <c r="E156" s="59" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F156" s="80" t="n">
-        <v>262.5</v>
+        <v>210</v>
       </c>
       <c r="G156" s="53" t="n"/>
     </row>
     <row r="157" ht="19.8" customHeight="1">
-      <c r="A157" s="50" t="n"/>
-      <c r="B157" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C157" s="18" t="n"/>
-      <c r="D157" s="19" t="n"/>
+      <c r="A157" s="47" t="n"/>
+      <c r="B157" s="81" t="inlineStr">
+        <is>
+          <t>INTERIORES (NO)</t>
+        </is>
+      </c>
+      <c r="C157" s="18" t="inlineStr">
+        <is>
+          <t>3.50 x 3.00</t>
+        </is>
+      </c>
+      <c r="D157" s="19" t="n">
+        <v>10.5</v>
+      </c>
       <c r="E157" s="59" t="n">
         <v>25</v>
       </c>
-      <c r="F157" s="80" t="n"/>
+      <c r="F157" s="80" t="n">
+        <v>262.5</v>
+      </c>
       <c r="G157" s="53" t="n"/>
     </row>
     <row r="158" ht="19.8" customHeight="1">
-      <c r="A158" s="36" t="inlineStr">
+      <c r="A158" s="50" t="n"/>
+      <c r="B158" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C158" s="18" t="n"/>
+      <c r="D158" s="19" t="n"/>
+      <c r="E158" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F158" s="80" t="n"/>
+      <c r="G158" s="53" t="n"/>
+    </row>
+    <row r="159" ht="19.8" customHeight="1">
+      <c r="A159" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B158" s="78" t="inlineStr">
+      <c r="B159" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C158" s="47" t="n"/>
-      <c r="D158" s="18" t="n"/>
-      <c r="E158" s="18" t="n"/>
-      <c r="F158" s="20" t="n"/>
-      <c r="G158" s="53" t="n"/>
-    </row>
-    <row r="159" ht="19.8" customHeight="1">
-      <c r="A159" s="43" t="n"/>
-      <c r="B159" s="79" t="inlineStr">
+      <c r="C159" s="47" t="n"/>
+      <c r="D159" s="18" t="n"/>
+      <c r="E159" s="18" t="n"/>
+      <c r="F159" s="20" t="n"/>
+      <c r="G159" s="53" t="n"/>
+    </row>
+    <row r="160" ht="19.8" customHeight="1">
+      <c r="A160" s="43" t="n"/>
+      <c r="B160" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C159" s="18" t="n"/>
-      <c r="D159" s="19" t="n"/>
-      <c r="E159" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F159" s="80" t="n"/>
-      <c r="G159" s="53" t="n"/>
-    </row>
-    <row r="160" ht="19.8" customHeight="1">
-      <c r="A160" s="47" t="n"/>
-      <c r="B160" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C160" s="18" t="n"/>
       <c r="D160" s="19" t="n"/>
       <c r="E160" s="59" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F160" s="80" t="n"/>
       <c r="G160" s="53" t="n"/>
     </row>
     <row r="161" ht="19.8" customHeight="1">
-      <c r="A161" s="50" t="n"/>
-      <c r="B161" s="82" t="inlineStr">
+      <c r="A161" s="47" t="n"/>
+      <c r="B161" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C161" s="18" t="n"/>
+      <c r="D161" s="19" t="n"/>
+      <c r="E161" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F161" s="80" t="n"/>
+      <c r="G161" s="53" t="n"/>
+    </row>
+    <row r="162" ht="19.8" customHeight="1">
+      <c r="A162" s="50" t="n"/>
+      <c r="B162" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C161" s="18" t="inlineStr">
+      <c r="C162" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D161" s="19" t="n">
+      <c r="D162" s="19" t="n">
         <v>12.25</v>
       </c>
-      <c r="E161" s="59" t="n">
+      <c r="E162" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F161" s="80" t="n">
+      <c r="F162" s="80" t="n">
         <v>183.8</v>
       </c>
-      <c r="G161" s="53" t="n"/>
-    </row>
-    <row r="162" ht="19.8" customHeight="1">
-      <c r="A162" s="36" t="inlineStr">
+      <c r="G162" s="53" t="n"/>
+    </row>
+    <row r="163" ht="19.8" customHeight="1">
+      <c r="A163" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B162" s="78" t="inlineStr">
+      <c r="B163" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C162" s="47" t="n"/>
-      <c r="D162" s="18" t="n"/>
-      <c r="E162" s="18" t="n"/>
-      <c r="F162" s="20" t="n"/>
-      <c r="G162" s="53" t="n"/>
-    </row>
-    <row r="163" ht="19.8" customHeight="1">
-      <c r="A163" s="43" t="n"/>
-      <c r="B163" s="79" t="inlineStr">
+      <c r="C163" s="47" t="n"/>
+      <c r="D163" s="18" t="n"/>
+      <c r="E163" s="18" t="n"/>
+      <c r="F163" s="20" t="n"/>
+      <c r="G163" s="53" t="n"/>
+    </row>
+    <row r="164" ht="19.8" customHeight="1">
+      <c r="A164" s="43" t="n"/>
+      <c r="B164" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C163" s="18" t="inlineStr">
+      <c r="C164" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D163" s="19" t="n">
+      <c r="D164" s="19" t="n">
         <v>12.25</v>
       </c>
-      <c r="E163" s="59" t="n">
+      <c r="E164" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F163" s="80" t="n">
+      <c r="F164" s="80" t="n">
         <v>122.5</v>
       </c>
-      <c r="G163" s="53" t="n"/>
-    </row>
-    <row r="164" ht="19.8" customHeight="1">
-      <c r="A164" s="50" t="n"/>
-      <c r="B164" s="82" t="inlineStr">
+      <c r="G164" s="53" t="n"/>
+    </row>
+    <row r="165" ht="19.8" customHeight="1">
+      <c r="A165" s="50" t="n"/>
+      <c r="B165" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C164" s="18" t="n"/>
-      <c r="D164" s="24" t="n"/>
-      <c r="E164" s="59" t="n">
+      <c r="C165" s="18" t="n"/>
+      <c r="D165" s="24" t="n"/>
+      <c r="E165" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F164" s="80" t="n"/>
-      <c r="G164" s="53" t="n"/>
-    </row>
-    <row r="165" ht="19.8" customHeight="1">
-      <c r="A165" s="36" t="inlineStr">
+      <c r="F165" s="80" t="n"/>
+      <c r="G165" s="53" t="n"/>
+    </row>
+    <row r="166" ht="19.8" customHeight="1">
+      <c r="A166" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B165" s="78" t="inlineStr">
+      <c r="B166" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C165" s="83" t="n"/>
-      <c r="D165" s="36" t="inlineStr">
+      <c r="C166" s="83" t="n"/>
+      <c r="D166" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E165" s="47" t="n"/>
-      <c r="F165" s="20" t="n"/>
-      <c r="G165" s="53" t="n"/>
-    </row>
-    <row r="166" ht="19.8" customHeight="1">
-      <c r="A166" s="43" t="n"/>
-      <c r="B166" s="79" t="inlineStr">
+      <c r="E166" s="47" t="n"/>
+      <c r="F166" s="20" t="n"/>
+      <c r="G166" s="53" t="n"/>
+    </row>
+    <row r="167" ht="19.8" customHeight="1">
+      <c r="A167" s="43" t="n"/>
+      <c r="B167" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C166" s="18" t="n"/>
-      <c r="D166" s="22" t="n"/>
-      <c r="E166" s="59" t="n">
+      <c r="C167" s="18" t="n"/>
+      <c r="D167" s="22" t="n"/>
+      <c r="E167" s="59" t="n">
         <v>6</v>
-      </c>
-      <c r="F166" s="80" t="n"/>
-      <c r="G166" s="53" t="n"/>
-    </row>
-    <row r="167" ht="19.8" customHeight="1">
-      <c r="A167" s="47" t="n"/>
-      <c r="B167" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C167" s="18" t="n"/>
-      <c r="D167" s="19" t="n"/>
-      <c r="E167" s="59" t="n">
-        <v>9</v>
       </c>
       <c r="F167" s="80" t="n"/>
       <c r="G167" s="53" t="n"/>
     </row>
     <row r="168" ht="19.8" customHeight="1">
-      <c r="A168" s="50" t="n"/>
-      <c r="B168" s="82" t="inlineStr">
+      <c r="A168" s="47" t="n"/>
+      <c r="B168" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C168" s="18" t="n"/>
+      <c r="D168" s="19" t="n"/>
+      <c r="E168" s="59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F168" s="80" t="n"/>
+      <c r="G168" s="53" t="n"/>
+    </row>
+    <row r="169" ht="19.8" customHeight="1">
+      <c r="A169" s="50" t="n"/>
+      <c r="B169" s="82" t="inlineStr">
         <is>
           <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C168" s="18" t="inlineStr">
+      <c r="C169" s="18" t="inlineStr">
         <is>
           <t>12.25 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D168" s="19" t="n">
+      <c r="D169" s="19" t="n">
         <v>36.75</v>
       </c>
-      <c r="E168" s="59" t="n">
+      <c r="E169" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F168" s="84" t="n">
+      <c r="F169" s="84" t="n">
         <v>441</v>
-      </c>
-      <c r="G168" s="53" t="n"/>
-    </row>
-    <row r="169" ht="19.8" customHeight="1">
-      <c r="A169" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B169" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C169" s="47" t="n"/>
-      <c r="D169" s="18" t="n"/>
-      <c r="E169" s="20" t="n"/>
-      <c r="F169" s="85" t="n">
-        <v>2091.6</v>
       </c>
       <c r="G169" s="53" t="n"/>
     </row>
     <row r="170" ht="19.8" customHeight="1">
       <c r="A170" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B170" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C170" s="47" t="n"/>
+      <c r="D170" s="18" t="n"/>
+      <c r="E170" s="20" t="n"/>
+      <c r="F170" s="85" t="n">
+        <v>2091.6</v>
+      </c>
+      <c r="G170" s="53" t="n"/>
+    </row>
+    <row r="171" ht="19.8" customHeight="1">
+      <c r="A171" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B170" s="78" t="inlineStr">
+      <c r="B171" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C170" s="47" t="inlineStr">
+      <c r="C171" s="47" t="inlineStr">
         <is>
           <t>2091.60  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D170" s="12" t="n"/>
-      <c r="E170" s="14" t="n"/>
-      <c r="F170" s="85" t="n">
+      <c r="D171" s="12" t="n"/>
+      <c r="E171" s="14" t="n"/>
+      <c r="F171" s="85" t="n">
         <v>2238</v>
       </c>
-      <c r="G170" s="53" t="n"/>
-    </row>
-    <row r="171" ht="19.8" customHeight="1">
-      <c r="A171" s="43" t="n"/>
-      <c r="B171" s="86" t="inlineStr">
+      <c r="G171" s="53" t="n"/>
+    </row>
+    <row r="172" ht="19.8" customHeight="1">
+      <c r="A172" s="43" t="n"/>
+      <c r="B172" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C171" s="18" t="n"/>
-      <c r="D171" s="12" t="n"/>
-      <c r="E171" s="39" t="n"/>
-      <c r="F171" s="87" t="n"/>
-      <c r="G171" s="53" t="n"/>
-    </row>
-    <row r="172" ht="19.8" customHeight="1">
-      <c r="A172" s="83" t="n"/>
-      <c r="B172" s="78" t="inlineStr">
+      <c r="C172" s="18" t="n"/>
+      <c r="D172" s="12" t="n"/>
+      <c r="E172" s="39" t="n"/>
+      <c r="F172" s="87" t="n"/>
+      <c r="G172" s="53" t="n"/>
+    </row>
+    <row r="173" ht="19.8" customHeight="1">
+      <c r="A173" s="83" t="n"/>
+      <c r="B173" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C172" s="47" t="n"/>
-      <c r="D172" s="12" t="n"/>
-      <c r="E172" s="14" t="n"/>
-      <c r="F172" s="85" t="n">
+      <c r="C173" s="47" t="n"/>
+      <c r="D173" s="12" t="n"/>
+      <c r="E173" s="14" t="n"/>
+      <c r="F173" s="85" t="n">
         <v>2238</v>
       </c>
-      <c r="G172" s="53" t="n"/>
-    </row>
-    <row r="173" ht="19.8" customHeight="1">
-      <c r="A173" s="47" t="n"/>
-      <c r="B173" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C173" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
-      </c>
-      <c r="D173" s="12" t="n"/>
-      <c r="E173" s="39" t="n"/>
-      <c r="F173" s="61" t="n"/>
       <c r="G173" s="53" t="n"/>
     </row>
     <row r="174" ht="19.8" customHeight="1">
       <c r="A174" s="47" t="n"/>
-      <c r="B174" s="60" t="inlineStr">
-        <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C174" s="19" t="n">
-        <v>274.4</v>
+      <c r="B174" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C174" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
       </c>
       <c r="D174" s="12" t="n"/>
       <c r="E174" s="39" t="n"/>
-      <c r="F174" s="20" t="n"/>
+      <c r="F174" s="61" t="n"/>
       <c r="G174" s="53" t="n"/>
     </row>
     <row r="175" ht="19.8" customHeight="1">
       <c r="A175" s="47" t="n"/>
       <c r="B175" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
-        </is>
-      </c>
-      <c r="C175" s="59" t="n">
-        <v>9</v>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C175" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D175" s="12" t="n"/>
       <c r="E175" s="39" t="n"/>
@@ -23026,11 +23034,11 @@
       <c r="A176" s="47" t="n"/>
       <c r="B176" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C176" s="59" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="D176" s="12" t="n"/>
       <c r="E176" s="39" t="n"/>
@@ -23038,16 +23046,14 @@
       <c r="G176" s="53" t="n"/>
     </row>
     <row r="177" ht="19.8" customHeight="1">
-      <c r="A177" s="50" t="n"/>
+      <c r="A177" s="47" t="n"/>
       <c r="B177" s="60" t="inlineStr">
         <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C177" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
+          <t>Ancho del radiador (cm)</t>
+        </is>
+      </c>
+      <c r="C177" s="59" t="n">
+        <v>72</v>
       </c>
       <c r="D177" s="12" t="n"/>
       <c r="E177" s="39" t="n"/>
@@ -23055,525 +23061,527 @@
       <c r="G177" s="53" t="n"/>
     </row>
     <row r="178" ht="19.8" customHeight="1">
-      <c r="A178" s="8" t="inlineStr">
+      <c r="A178" s="50" t="n"/>
+      <c r="B178" s="60" t="inlineStr">
+        <is>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C178" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
+      </c>
+      <c r="D178" s="12" t="n"/>
+      <c r="E178" s="39" t="n"/>
+      <c r="F178" s="20" t="n"/>
+      <c r="G178" s="53" t="n"/>
+    </row>
+    <row r="179" ht="19.8" customHeight="1">
+      <c r="A179" s="8" t="inlineStr">
         <is>
           <t>LOCAL  10 - Bano suite   (PB)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B178" s="11" t="n"/>
-      <c r="C178" s="11" t="n"/>
-      <c r="D178" s="11" t="n"/>
-      <c r="E178" s="11" t="n"/>
-      <c r="F178" s="42" t="n"/>
-      <c r="G178" s="53" t="n"/>
-    </row>
-    <row r="179" ht="32" customHeight="1">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="B179" s="11" t="n"/>
+      <c r="C179" s="11" t="n"/>
+      <c r="D179" s="11" t="n"/>
+      <c r="E179" s="11" t="n"/>
+      <c r="F179" s="42" t="n"/>
+      <c r="G179" s="53" t="n"/>
+    </row>
+    <row r="180" ht="32" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G179" s="53" t="n"/>
-    </row>
-    <row r="180" ht="19.8" customHeight="1">
-      <c r="A180" s="36" t="inlineStr">
+      <c r="G180" s="53" t="n"/>
+    </row>
+    <row r="181" ht="19.8" customHeight="1">
+      <c r="A181" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B180" s="78" t="inlineStr">
+      <c r="B181" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C180" s="43" t="n"/>
-      <c r="D180" s="58" t="n"/>
-      <c r="E180" s="58" t="n"/>
-      <c r="F180" s="61" t="n"/>
-      <c r="G180" s="53" t="n"/>
-    </row>
-    <row r="181" ht="19.8" customHeight="1">
-      <c r="A181" s="90" t="n"/>
-      <c r="B181" s="91" t="inlineStr">
+      <c r="C181" s="43" t="n"/>
+      <c r="D181" s="58" t="n"/>
+      <c r="E181" s="58" t="n"/>
+      <c r="F181" s="61" t="n"/>
+      <c r="G181" s="53" t="n"/>
+    </row>
+    <row r="182" ht="19.8" customHeight="1">
+      <c r="A182" s="90" t="n"/>
+      <c r="B182" s="91" t="inlineStr">
         <is>
           <t>VA02</t>
         </is>
       </c>
-      <c r="C181" s="18" t="inlineStr">
+      <c r="C182" s="18" t="inlineStr">
         <is>
           <t>0.75 x 2.15</t>
         </is>
       </c>
-      <c r="D181" s="19" t="n">
+      <c r="D182" s="19" t="n">
         <v>1.61</v>
       </c>
-      <c r="E181" s="59" t="n">
+      <c r="E182" s="59" t="n">
         <v>60</v>
       </c>
-      <c r="F181" s="80" t="n">
+      <c r="F182" s="80" t="n">
         <v>96.59999999999999</v>
       </c>
-      <c r="G181" s="53" t="n"/>
-    </row>
-    <row r="182" ht="19.8" customHeight="1">
-      <c r="A182" s="36" t="inlineStr">
+      <c r="G182" s="53" t="n"/>
+    </row>
+    <row r="183" ht="19.8" customHeight="1">
+      <c r="A183" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B182" s="78" t="inlineStr">
+      <c r="B183" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C182" s="47" t="n"/>
-      <c r="D182" s="18" t="n"/>
-      <c r="E182" s="18" t="n"/>
-      <c r="F182" s="20" t="n"/>
-      <c r="G182" s="53" t="n"/>
-    </row>
-    <row r="183" ht="19.8" customHeight="1">
-      <c r="A183" s="43" t="n"/>
-      <c r="B183" s="79" t="inlineStr">
+      <c r="C183" s="47" t="n"/>
+      <c r="D183" s="18" t="n"/>
+      <c r="E183" s="18" t="n"/>
+      <c r="F183" s="20" t="n"/>
+      <c r="G183" s="53" t="n"/>
+    </row>
+    <row r="184" ht="19.8" customHeight="1">
+      <c r="A184" s="43" t="n"/>
+      <c r="B184" s="79" t="inlineStr">
         <is>
           <t>AISLADAS (NE)</t>
         </is>
       </c>
-      <c r="C183" s="18" t="inlineStr">
+      <c r="C184" s="18" t="inlineStr">
         <is>
           <t>3.38 x 3.00</t>
         </is>
       </c>
-      <c r="D183" s="19" t="n">
+      <c r="D184" s="19" t="n">
         <v>10.14</v>
       </c>
-      <c r="E183" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F183" s="80" t="n">
-        <v>202.8</v>
-      </c>
-      <c r="G183" s="53" t="n"/>
-    </row>
-    <row r="184" ht="19.8" customHeight="1">
-      <c r="A184" s="47" t="n"/>
-      <c r="B184" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C184" s="18" t="n"/>
-      <c r="D184" s="19" t="n"/>
       <c r="E184" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F184" s="80" t="n"/>
+      <c r="F184" s="80" t="n">
+        <v>202.8</v>
+      </c>
       <c r="G184" s="53" t="n"/>
     </row>
     <row r="185" ht="19.8" customHeight="1">
       <c r="A185" s="47" t="n"/>
       <c r="B185" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (NO, bano visitas)</t>
-        </is>
-      </c>
-      <c r="C185" s="18" t="inlineStr">
-        <is>
-          <t>1.72 x 3.00</t>
-        </is>
-      </c>
-      <c r="D185" s="19" t="n">
-        <v>5.16</v>
-      </c>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C185" s="18" t="n"/>
+      <c r="D185" s="19" t="n"/>
       <c r="E185" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F185" s="80" t="n">
-        <v>129</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F185" s="80" t="n"/>
       <c r="G185" s="53" t="n"/>
     </row>
     <row r="186" ht="19.8" customHeight="1">
       <c r="A186" s="47" t="n"/>
       <c r="B186" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (SO)</t>
+          <t>INTERIORES (NO, bano visitas)</t>
         </is>
       </c>
       <c r="C186" s="18" t="inlineStr">
         <is>
-          <t>3.38 x 3.00</t>
+          <t>1.72 x 3.00</t>
         </is>
       </c>
       <c r="D186" s="19" t="n">
-        <v>10.14</v>
+        <v>5.16</v>
       </c>
       <c r="E186" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F186" s="80" t="n">
-        <v>253.5</v>
+        <v>129</v>
       </c>
       <c r="G186" s="53" t="n"/>
     </row>
     <row r="187" ht="19.8" customHeight="1">
-      <c r="A187" s="50" t="n"/>
-      <c r="B187" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES (SE, dormitorio suite)</t>
+      <c r="A187" s="47" t="n"/>
+      <c r="B187" s="81" t="inlineStr">
+        <is>
+          <t>INTERIORES (SO)</t>
         </is>
       </c>
       <c r="C187" s="18" t="inlineStr">
         <is>
-          <t>1.72 x 3.00</t>
+          <t>3.38 x 3.00</t>
         </is>
       </c>
       <c r="D187" s="19" t="n">
-        <v>5.16</v>
+        <v>10.14</v>
       </c>
       <c r="E187" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F187" s="80" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="G187" s="53" t="n"/>
+    </row>
+    <row r="188" ht="19.8" customHeight="1">
+      <c r="A188" s="50" t="n"/>
+      <c r="B188" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES (SE, dormitorio suite)</t>
+        </is>
+      </c>
+      <c r="C188" s="18" t="inlineStr">
+        <is>
+          <t>1.72 x 3.00</t>
+        </is>
+      </c>
+      <c r="D188" s="19" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="E188" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F188" s="80" t="n">
         <v>129</v>
       </c>
-      <c r="G187" s="53" t="n"/>
-    </row>
-    <row r="188" ht="19.8" customHeight="1">
-      <c r="A188" s="36" t="inlineStr">
+      <c r="G188" s="53" t="n"/>
+    </row>
+    <row r="189" ht="19.8" customHeight="1">
+      <c r="A189" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B188" s="78" t="inlineStr">
+      <c r="B189" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C188" s="47" t="n"/>
-      <c r="D188" s="18" t="n"/>
-      <c r="E188" s="18" t="n"/>
-      <c r="F188" s="20" t="n"/>
-      <c r="G188" s="53" t="n"/>
-    </row>
-    <row r="189" ht="19.8" customHeight="1">
-      <c r="A189" s="43" t="n"/>
-      <c r="B189" s="79" t="inlineStr">
+      <c r="C189" s="47" t="n"/>
+      <c r="D189" s="18" t="n"/>
+      <c r="E189" s="18" t="n"/>
+      <c r="F189" s="20" t="n"/>
+      <c r="G189" s="53" t="n"/>
+    </row>
+    <row r="190" ht="19.8" customHeight="1">
+      <c r="A190" s="43" t="n"/>
+      <c r="B190" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C189" s="18" t="n"/>
-      <c r="D189" s="19" t="n"/>
-      <c r="E189" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F189" s="80" t="n"/>
-      <c r="G189" s="53" t="n"/>
-    </row>
-    <row r="190" ht="19.8" customHeight="1">
-      <c r="A190" s="47" t="n"/>
-      <c r="B190" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C190" s="18" t="n"/>
       <c r="D190" s="19" t="n"/>
       <c r="E190" s="59" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F190" s="80" t="n"/>
       <c r="G190" s="53" t="n"/>
     </row>
     <row r="191" ht="19.8" customHeight="1">
-      <c r="A191" s="50" t="n"/>
-      <c r="B191" s="82" t="inlineStr">
+      <c r="A191" s="47" t="n"/>
+      <c r="B191" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C191" s="18" t="n"/>
+      <c r="D191" s="19" t="n"/>
+      <c r="E191" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F191" s="80" t="n"/>
+      <c r="G191" s="53" t="n"/>
+    </row>
+    <row r="192" ht="19.8" customHeight="1">
+      <c r="A192" s="50" t="n"/>
+      <c r="B192" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C191" s="18" t="inlineStr">
+      <c r="C192" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D191" s="19" t="n">
+      <c r="D192" s="19" t="n">
         <v>5.81</v>
       </c>
-      <c r="E191" s="59" t="n">
+      <c r="E192" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F191" s="80" t="n">
+      <c r="F192" s="80" t="n">
         <v>87.2</v>
       </c>
-      <c r="G191" s="53" t="n"/>
-    </row>
-    <row r="192" ht="19.8" customHeight="1">
-      <c r="A192" s="36" t="inlineStr">
+      <c r="G192" s="53" t="n"/>
+    </row>
+    <row r="193" ht="19.8" customHeight="1">
+      <c r="A193" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B192" s="78" t="inlineStr">
+      <c r="B193" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C192" s="47" t="n"/>
-      <c r="D192" s="18" t="n"/>
-      <c r="E192" s="18" t="n"/>
-      <c r="F192" s="20" t="n"/>
-      <c r="G192" s="53" t="n"/>
-    </row>
-    <row r="193" ht="19.8" customHeight="1">
-      <c r="A193" s="43" t="n"/>
-      <c r="B193" s="79" t="inlineStr">
+      <c r="C193" s="47" t="n"/>
+      <c r="D193" s="18" t="n"/>
+      <c r="E193" s="18" t="n"/>
+      <c r="F193" s="20" t="n"/>
+      <c r="G193" s="53" t="n"/>
+    </row>
+    <row r="194" ht="19.8" customHeight="1">
+      <c r="A194" s="43" t="n"/>
+      <c r="B194" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C193" s="18" t="inlineStr">
+      <c r="C194" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D193" s="19" t="n">
+      <c r="D194" s="19" t="n">
         <v>5.81</v>
       </c>
-      <c r="E193" s="59" t="n">
+      <c r="E194" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F193" s="80" t="n">
+      <c r="F194" s="80" t="n">
         <v>58.1</v>
       </c>
-      <c r="G193" s="53" t="n"/>
-    </row>
-    <row r="194" ht="19.8" customHeight="1">
-      <c r="A194" s="50" t="n"/>
-      <c r="B194" s="82" t="inlineStr">
+      <c r="G194" s="53" t="n"/>
+    </row>
+    <row r="195" ht="19.8" customHeight="1">
+      <c r="A195" s="50" t="n"/>
+      <c r="B195" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C194" s="18" t="n"/>
-      <c r="D194" s="24" t="n"/>
-      <c r="E194" s="59" t="n">
+      <c r="C195" s="18" t="n"/>
+      <c r="D195" s="24" t="n"/>
+      <c r="E195" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F194" s="80" t="n"/>
-      <c r="G194" s="53" t="n"/>
-    </row>
-    <row r="195" ht="19.8" customHeight="1">
-      <c r="A195" s="36" t="inlineStr">
+      <c r="F195" s="80" t="n"/>
+      <c r="G195" s="53" t="n"/>
+    </row>
+    <row r="196" ht="19.8" customHeight="1">
+      <c r="A196" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B195" s="78" t="inlineStr">
+      <c r="B196" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C195" s="83" t="n"/>
-      <c r="D195" s="36" t="inlineStr">
+      <c r="C196" s="83" t="n"/>
+      <c r="D196" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E195" s="47" t="n"/>
-      <c r="F195" s="20" t="n"/>
-      <c r="G195" s="53" t="n"/>
-    </row>
-    <row r="196" ht="19.8" customHeight="1">
-      <c r="A196" s="43" t="n"/>
-      <c r="B196" s="79" t="inlineStr">
+      <c r="E196" s="47" t="n"/>
+      <c r="F196" s="20" t="n"/>
+      <c r="G196" s="53" t="n"/>
+    </row>
+    <row r="197" ht="19.8" customHeight="1">
+      <c r="A197" s="43" t="n"/>
+      <c r="B197" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C196" s="18" t="inlineStr">
+      <c r="C197" s="18" t="inlineStr">
         <is>
           <t>5.81 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D196" s="22" t="n">
+      <c r="D197" s="22" t="n">
         <v>17.43</v>
       </c>
-      <c r="E196" s="59" t="n">
+      <c r="E197" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="F196" s="80" t="n">
+      <c r="F197" s="80" t="n">
         <v>104.6</v>
       </c>
-      <c r="G196" s="53" t="n"/>
-    </row>
-    <row r="197" ht="19.8" customHeight="1">
-      <c r="A197" s="47" t="n"/>
-      <c r="B197" s="81" t="inlineStr">
+      <c r="G197" s="53" t="n"/>
+    </row>
+    <row r="198" ht="19.8" customHeight="1">
+      <c r="A198" s="47" t="n"/>
+      <c r="B198" s="81" t="inlineStr">
         <is>
           <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C197" s="18" t="n"/>
-      <c r="D197" s="19" t="n"/>
-      <c r="E197" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F197" s="80" t="n"/>
-      <c r="G197" s="53" t="n"/>
-    </row>
-    <row r="198" ht="19.8" customHeight="1">
-      <c r="A198" s="50" t="n"/>
-      <c r="B198" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C198" s="18" t="n"/>
       <c r="D198" s="19" t="n"/>
       <c r="E198" s="59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F198" s="80" t="n"/>
+      <c r="G198" s="53" t="n"/>
+    </row>
+    <row r="199" ht="19.8" customHeight="1">
+      <c r="A199" s="50" t="n"/>
+      <c r="B199" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C199" s="18" t="n"/>
+      <c r="D199" s="19" t="n"/>
+      <c r="E199" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F198" s="84" t="n"/>
-      <c r="G198" s="53" t="n"/>
-    </row>
-    <row r="199" ht="19.8" customHeight="1">
-      <c r="A199" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B199" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C199" s="47" t="n"/>
-      <c r="D199" s="18" t="n"/>
-      <c r="E199" s="20" t="n"/>
-      <c r="F199" s="85" t="n">
-        <v>1060.8</v>
-      </c>
+      <c r="F199" s="84" t="n"/>
       <c r="G199" s="53" t="n"/>
     </row>
     <row r="200" ht="19.8" customHeight="1">
       <c r="A200" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B200" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C200" s="47" t="n"/>
+      <c r="D200" s="18" t="n"/>
+      <c r="E200" s="20" t="n"/>
+      <c r="F200" s="85" t="n">
+        <v>1060.8</v>
+      </c>
+      <c r="G200" s="53" t="n"/>
+    </row>
+    <row r="201" ht="19.8" customHeight="1">
+      <c r="A201" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B200" s="78" t="inlineStr">
+      <c r="B201" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C200" s="47" t="inlineStr">
+      <c r="C201" s="47" t="inlineStr">
         <is>
           <t>1060.80  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D200" s="12" t="n"/>
-      <c r="E200" s="14" t="n"/>
-      <c r="F200" s="85" t="n">
+      <c r="D201" s="12" t="n"/>
+      <c r="E201" s="14" t="n"/>
+      <c r="F201" s="85" t="n">
         <v>1135.1</v>
       </c>
-      <c r="G200" s="53" t="n"/>
-    </row>
-    <row r="201" ht="19.8" customHeight="1">
-      <c r="A201" s="43" t="n"/>
-      <c r="B201" s="86" t="inlineStr">
+      <c r="G201" s="53" t="n"/>
+    </row>
+    <row r="202" ht="19.8" customHeight="1">
+      <c r="A202" s="43" t="n"/>
+      <c r="B202" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C201" s="18" t="n"/>
-      <c r="D201" s="12" t="n"/>
-      <c r="E201" s="39" t="n"/>
-      <c r="F201" s="87" t="n"/>
-      <c r="G201" s="53" t="n"/>
-    </row>
-    <row r="202" ht="19.8" customHeight="1">
-      <c r="A202" s="83" t="n"/>
-      <c r="B202" s="78" t="inlineStr">
+      <c r="C202" s="18" t="n"/>
+      <c r="D202" s="12" t="n"/>
+      <c r="E202" s="39" t="n"/>
+      <c r="F202" s="87" t="n"/>
+      <c r="G202" s="53" t="n"/>
+    </row>
+    <row r="203" ht="19.8" customHeight="1">
+      <c r="A203" s="83" t="n"/>
+      <c r="B203" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C202" s="47" t="n"/>
-      <c r="D202" s="12" t="n"/>
-      <c r="E202" s="14" t="n"/>
-      <c r="F202" s="85" t="n">
+      <c r="C203" s="47" t="n"/>
+      <c r="D203" s="12" t="n"/>
+      <c r="E203" s="14" t="n"/>
+      <c r="F203" s="85" t="n">
         <v>1135.1</v>
       </c>
-      <c r="G202" s="53" t="n"/>
-    </row>
-    <row r="203" ht="19.8" customHeight="1">
-      <c r="A203" s="47" t="n"/>
-      <c r="B203" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C203" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
-      </c>
-      <c r="D203" s="12" t="n"/>
-      <c r="E203" s="39" t="n"/>
-      <c r="F203" s="61" t="n"/>
       <c r="G203" s="53" t="n"/>
     </row>
     <row r="204" ht="19.8" customHeight="1">
       <c r="A204" s="47" t="n"/>
-      <c r="B204" s="60" t="inlineStr">
-        <is>
-          <t>Kcal/h del toallero Scala/Domino 80</t>
-        </is>
-      </c>
-      <c r="C204" s="59" t="n">
-        <v>708</v>
+      <c r="B204" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C204" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
       </c>
       <c r="D204" s="12" t="n"/>
       <c r="E204" s="39" t="n"/>
-      <c r="F204" s="20" t="n"/>
+      <c r="F204" s="61" t="n"/>
       <c r="G204" s="53" t="n"/>
     </row>
     <row r="205" ht="19.8" customHeight="1">
       <c r="A205" s="47" t="n"/>
       <c r="B205" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 150</t>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
         </is>
       </c>
       <c r="C205" s="59" t="n">
-        <v>1315</v>
+        <v>708</v>
       </c>
       <c r="D205" s="12" t="n"/>
       <c r="E205" s="39" t="n"/>
@@ -23584,11 +23592,11 @@
       <c r="A206" s="47" t="n"/>
       <c r="B206" s="60" t="inlineStr">
         <is>
-          <t>Toalleros necesarios</t>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
         </is>
       </c>
       <c r="C206" s="59" t="n">
-        <v>1</v>
+        <v>1315</v>
       </c>
       <c r="D206" s="12" t="n"/>
       <c r="E206" s="39" t="n"/>
@@ -23596,16 +23604,14 @@
       <c r="G206" s="53" t="n"/>
     </row>
     <row r="207" ht="19.8" customHeight="1">
-      <c r="A207" s="50" t="n"/>
+      <c r="A207" s="47" t="n"/>
       <c r="B207" s="60" t="inlineStr">
         <is>
-          <t>Toallero adoptado</t>
-        </is>
-      </c>
-      <c r="C207" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
-        </is>
+          <t>Toalleros necesarios</t>
+        </is>
+      </c>
+      <c r="C207" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="D207" s="12" t="n"/>
       <c r="E207" s="39" t="n"/>
@@ -23613,159 +23619,153 @@
       <c r="G207" s="53" t="n"/>
     </row>
     <row r="208" ht="19.8" customHeight="1">
-      <c r="A208" s="8" t="inlineStr">
+      <c r="A208" s="50" t="n"/>
+      <c r="B208" s="60" t="inlineStr">
+        <is>
+          <t>Toallero adoptado</t>
+        </is>
+      </c>
+      <c r="C208" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
+        </is>
+      </c>
+      <c r="D208" s="12" t="n"/>
+      <c r="E208" s="39" t="n"/>
+      <c r="F208" s="20" t="n"/>
+      <c r="G208" s="53" t="n"/>
+    </row>
+    <row r="209" ht="19.8" customHeight="1">
+      <c r="A209" s="8" t="inlineStr">
         <is>
           <t>LOCAL  11 - Bano visitas   (PB)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B208" s="11" t="n"/>
-      <c r="C208" s="11" t="n"/>
-      <c r="D208" s="11" t="n"/>
-      <c r="E208" s="11" t="n"/>
-      <c r="F208" s="42" t="n"/>
-      <c r="G208" s="53" t="n"/>
-    </row>
-    <row r="209" ht="32" customHeight="1">
-      <c r="A209" s="2" t="inlineStr">
+      <c r="B209" s="11" t="n"/>
+      <c r="C209" s="11" t="n"/>
+      <c r="D209" s="11" t="n"/>
+      <c r="E209" s="11" t="n"/>
+      <c r="F209" s="42" t="n"/>
+      <c r="G209" s="53" t="n"/>
+    </row>
+    <row r="210" ht="32" customHeight="1">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C209" s="2" t="inlineStr">
+      <c r="C210" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G209" s="53" t="n"/>
-    </row>
-    <row r="210" ht="19.8" customHeight="1">
-      <c r="A210" s="36" t="inlineStr">
+      <c r="G210" s="53" t="n"/>
+    </row>
+    <row r="211" ht="19.8" customHeight="1">
+      <c r="A211" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B210" s="78" t="inlineStr">
+      <c r="B211" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C210" s="43" t="n"/>
-      <c r="D210" s="58" t="n"/>
-      <c r="E210" s="58" t="n"/>
-      <c r="F210" s="61" t="n"/>
-      <c r="G210" s="53" t="n"/>
-    </row>
-    <row r="211" ht="19.8" customHeight="1">
-      <c r="A211" s="90" t="n"/>
-      <c r="B211" s="91" t="inlineStr">
+      <c r="C211" s="43" t="n"/>
+      <c r="D211" s="58" t="n"/>
+      <c r="E211" s="58" t="n"/>
+      <c r="F211" s="61" t="n"/>
+      <c r="G211" s="53" t="n"/>
+    </row>
+    <row r="212" ht="19.8" customHeight="1">
+      <c r="A212" s="90" t="n"/>
+      <c r="B212" s="91" t="inlineStr">
         <is>
           <t>(sin aberturas)</t>
         </is>
       </c>
-      <c r="C211" s="18" t="n"/>
-      <c r="D211" s="19" t="n"/>
-      <c r="E211" s="59" t="n">
+      <c r="C212" s="18" t="n"/>
+      <c r="D212" s="19" t="n"/>
+      <c r="E212" s="59" t="n">
         <v>60</v>
       </c>
-      <c r="F211" s="80" t="n"/>
-      <c r="G211" s="53" t="n"/>
-    </row>
-    <row r="212" ht="19.8" customHeight="1">
-      <c r="A212" s="36" t="inlineStr">
+      <c r="F212" s="80" t="n"/>
+      <c r="G212" s="53" t="n"/>
+    </row>
+    <row r="213" ht="19.8" customHeight="1">
+      <c r="A213" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B212" s="78" t="inlineStr">
+      <c r="B213" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C212" s="47" t="n"/>
-      <c r="D212" s="18" t="n"/>
-      <c r="E212" s="18" t="n"/>
-      <c r="F212" s="20" t="n"/>
-      <c r="G212" s="53" t="n"/>
-    </row>
-    <row r="213" ht="19.8" customHeight="1">
-      <c r="A213" s="43" t="n"/>
-      <c r="B213" s="79" t="inlineStr">
+      <c r="C213" s="47" t="n"/>
+      <c r="D213" s="18" t="n"/>
+      <c r="E213" s="18" t="n"/>
+      <c r="F213" s="20" t="n"/>
+      <c r="G213" s="53" t="n"/>
+    </row>
+    <row r="214" ht="19.8" customHeight="1">
+      <c r="A214" s="43" t="n"/>
+      <c r="B214" s="79" t="inlineStr">
         <is>
           <t>AISLADAS</t>
         </is>
       </c>
-      <c r="C213" s="18" t="inlineStr">
+      <c r="C214" s="18" t="inlineStr">
         <is>
           <t>1.30 x 3.00</t>
         </is>
       </c>
-      <c r="D213" s="19" t="n">
+      <c r="D214" s="19" t="n">
         <v>3.9</v>
       </c>
-      <c r="E213" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F213" s="80" t="n">
-        <v>78</v>
-      </c>
-      <c r="G213" s="53" t="n"/>
-    </row>
-    <row r="214" ht="19.8" customHeight="1">
-      <c r="A214" s="47" t="n"/>
-      <c r="B214" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C214" s="18" t="n"/>
-      <c r="D214" s="19" t="n"/>
       <c r="E214" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F214" s="80" t="n"/>
+      <c r="F214" s="80" t="n">
+        <v>78</v>
+      </c>
       <c r="G214" s="53" t="n"/>
     </row>
     <row r="215" ht="19.8" customHeight="1">
       <c r="A215" s="47" t="n"/>
       <c r="B215" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C215" s="18" t="inlineStr">
-        <is>
-          <t>2.40 x 3.00</t>
-        </is>
-      </c>
-      <c r="D215" s="19" t="n">
-        <v>7.2</v>
-      </c>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C215" s="18" t="n"/>
+      <c r="D215" s="19" t="n"/>
       <c r="E215" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F215" s="80" t="n">
-        <v>180</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F215" s="80" t="n"/>
       <c r="G215" s="53" t="n"/>
     </row>
     <row r="216" ht="19.8" customHeight="1">
@@ -23792,338 +23792,346 @@
       <c r="G216" s="53" t="n"/>
     </row>
     <row r="217" ht="19.8" customHeight="1">
-      <c r="A217" s="50" t="n"/>
-      <c r="B217" s="82" t="inlineStr">
+      <c r="A217" s="47" t="n"/>
+      <c r="B217" s="81" t="inlineStr">
         <is>
           <t>INTERIORES</t>
         </is>
       </c>
       <c r="C217" s="18" t="inlineStr">
         <is>
-          <t>1.30 x 3.00</t>
+          <t>2.40 x 3.00</t>
         </is>
       </c>
       <c r="D217" s="19" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="E217" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F217" s="80" t="n">
+        <v>180</v>
+      </c>
+      <c r="G217" s="53" t="n"/>
+    </row>
+    <row r="218" ht="19.8" customHeight="1">
+      <c r="A218" s="50" t="n"/>
+      <c r="B218" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C218" s="18" t="inlineStr">
+        <is>
+          <t>1.30 x 3.00</t>
+        </is>
+      </c>
+      <c r="D218" s="19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E218" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F218" s="80" t="n">
         <v>97.5</v>
       </c>
-      <c r="G217" s="53" t="n"/>
-    </row>
-    <row r="218" ht="19.8" customHeight="1">
-      <c r="A218" s="36" t="inlineStr">
+      <c r="G218" s="53" t="n"/>
+    </row>
+    <row r="219" ht="19.8" customHeight="1">
+      <c r="A219" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B218" s="78" t="inlineStr">
+      <c r="B219" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C218" s="47" t="n"/>
-      <c r="D218" s="18" t="n"/>
-      <c r="E218" s="18" t="n"/>
-      <c r="F218" s="20" t="n"/>
-      <c r="G218" s="53" t="n"/>
-    </row>
-    <row r="219" ht="19.8" customHeight="1">
-      <c r="A219" s="43" t="n"/>
-      <c r="B219" s="79" t="inlineStr">
+      <c r="C219" s="47" t="n"/>
+      <c r="D219" s="18" t="n"/>
+      <c r="E219" s="18" t="n"/>
+      <c r="F219" s="20" t="n"/>
+      <c r="G219" s="53" t="n"/>
+    </row>
+    <row r="220" ht="19.8" customHeight="1">
+      <c r="A220" s="43" t="n"/>
+      <c r="B220" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C219" s="18" t="n"/>
-      <c r="D219" s="19" t="n"/>
-      <c r="E219" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="F219" s="80" t="n"/>
-      <c r="G219" s="53" t="n"/>
-    </row>
-    <row r="220" ht="19.8" customHeight="1">
-      <c r="A220" s="47" t="n"/>
-      <c r="B220" s="81" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
         </is>
       </c>
       <c r="C220" s="18" t="n"/>
       <c r="D220" s="19" t="n"/>
       <c r="E220" s="59" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F220" s="80" t="n"/>
       <c r="G220" s="53" t="n"/>
     </row>
     <row r="221" ht="19.8" customHeight="1">
-      <c r="A221" s="50" t="n"/>
-      <c r="B221" s="82" t="inlineStr">
+      <c r="A221" s="47" t="n"/>
+      <c r="B221" s="81" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C221" s="18" t="n"/>
+      <c r="D221" s="19" t="n"/>
+      <c r="E221" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F221" s="80" t="n"/>
+      <c r="G221" s="53" t="n"/>
+    </row>
+    <row r="222" ht="19.8" customHeight="1">
+      <c r="A222" s="50" t="n"/>
+      <c r="B222" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C221" s="18" t="inlineStr">
+      <c r="C222" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D221" s="19" t="n">
+      <c r="D222" s="19" t="n">
         <v>3.12</v>
       </c>
-      <c r="E221" s="59" t="n">
+      <c r="E222" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F221" s="80" t="n">
+      <c r="F222" s="80" t="n">
         <v>46.8</v>
       </c>
-      <c r="G221" s="53" t="n"/>
-    </row>
-    <row r="222" ht="19.8" customHeight="1">
-      <c r="A222" s="36" t="inlineStr">
+      <c r="G222" s="53" t="n"/>
+    </row>
+    <row r="223" ht="19.8" customHeight="1">
+      <c r="A223" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B222" s="78" t="inlineStr">
+      <c r="B223" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C222" s="47" t="n"/>
-      <c r="D222" s="18" t="n"/>
-      <c r="E222" s="18" t="n"/>
-      <c r="F222" s="20" t="n"/>
-      <c r="G222" s="53" t="n"/>
-    </row>
-    <row r="223" ht="19.8" customHeight="1">
-      <c r="A223" s="43" t="n"/>
-      <c r="B223" s="79" t="inlineStr">
+      <c r="C223" s="47" t="n"/>
+      <c r="D223" s="18" t="n"/>
+      <c r="E223" s="18" t="n"/>
+      <c r="F223" s="20" t="n"/>
+      <c r="G223" s="53" t="n"/>
+    </row>
+    <row r="224" ht="19.8" customHeight="1">
+      <c r="A224" s="43" t="n"/>
+      <c r="B224" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C223" s="18" t="inlineStr">
+      <c r="C224" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D223" s="19" t="n">
+      <c r="D224" s="19" t="n">
         <v>3.12</v>
       </c>
-      <c r="E223" s="59" t="n">
+      <c r="E224" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F223" s="80" t="n">
+      <c r="F224" s="80" t="n">
         <v>31.2</v>
       </c>
-      <c r="G223" s="53" t="n"/>
-    </row>
-    <row r="224" ht="19.8" customHeight="1">
-      <c r="A224" s="50" t="n"/>
-      <c r="B224" s="82" t="inlineStr">
+      <c r="G224" s="53" t="n"/>
+    </row>
+    <row r="225" ht="19.8" customHeight="1">
+      <c r="A225" s="50" t="n"/>
+      <c r="B225" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C224" s="18" t="n"/>
-      <c r="D224" s="24" t="n"/>
-      <c r="E224" s="59" t="n">
+      <c r="C225" s="18" t="n"/>
+      <c r="D225" s="24" t="n"/>
+      <c r="E225" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F224" s="80" t="n"/>
-      <c r="G224" s="53" t="n"/>
-    </row>
-    <row r="225" ht="19.8" customHeight="1">
-      <c r="A225" s="36" t="inlineStr">
+      <c r="F225" s="80" t="n"/>
+      <c r="G225" s="53" t="n"/>
+    </row>
+    <row r="226" ht="19.8" customHeight="1">
+      <c r="A226" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B225" s="78" t="inlineStr">
+      <c r="B226" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C225" s="83" t="n"/>
-      <c r="D225" s="36" t="inlineStr">
+      <c r="C226" s="83" t="n"/>
+      <c r="D226" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E225" s="47" t="n"/>
-      <c r="F225" s="20" t="n"/>
-      <c r="G225" s="53" t="n"/>
-    </row>
-    <row r="226" ht="19.8" customHeight="1">
-      <c r="A226" s="43" t="n"/>
-      <c r="B226" s="79" t="inlineStr">
+      <c r="E226" s="47" t="n"/>
+      <c r="F226" s="20" t="n"/>
+      <c r="G226" s="53" t="n"/>
+    </row>
+    <row r="227" ht="19.8" customHeight="1">
+      <c r="A227" s="43" t="n"/>
+      <c r="B227" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C226" s="18" t="inlineStr">
+      <c r="C227" s="18" t="inlineStr">
         <is>
           <t>3.12 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D226" s="22" t="n">
+      <c r="D227" s="22" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="E226" s="59" t="n">
+      <c r="E227" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="F226" s="80" t="n">
+      <c r="F227" s="80" t="n">
         <v>56.2</v>
       </c>
-      <c r="G226" s="53" t="n"/>
-    </row>
-    <row r="227" ht="19.8" customHeight="1">
-      <c r="A227" s="47" t="n"/>
-      <c r="B227" s="81" t="inlineStr">
+      <c r="G227" s="53" t="n"/>
+    </row>
+    <row r="228" ht="19.8" customHeight="1">
+      <c r="A228" s="47" t="n"/>
+      <c r="B228" s="81" t="inlineStr">
         <is>
           <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C227" s="18" t="n"/>
-      <c r="D227" s="19" t="n"/>
-      <c r="E227" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F227" s="80" t="n"/>
-      <c r="G227" s="53" t="n"/>
-    </row>
-    <row r="228" ht="19.8" customHeight="1">
-      <c r="A228" s="50" t="n"/>
-      <c r="B228" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C228" s="18" t="n"/>
       <c r="D228" s="19" t="n"/>
       <c r="E228" s="59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F228" s="80" t="n"/>
+      <c r="G228" s="53" t="n"/>
+    </row>
+    <row r="229" ht="19.8" customHeight="1">
+      <c r="A229" s="50" t="n"/>
+      <c r="B229" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C229" s="18" t="n"/>
+      <c r="D229" s="19" t="n"/>
+      <c r="E229" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F228" s="84" t="n"/>
-      <c r="G228" s="53" t="n"/>
-    </row>
-    <row r="229" ht="19.8" customHeight="1">
-      <c r="A229" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B229" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C229" s="47" t="n"/>
-      <c r="D229" s="18" t="n"/>
-      <c r="E229" s="20" t="n"/>
-      <c r="F229" s="85" t="n">
-        <v>669.7</v>
-      </c>
+      <c r="F229" s="84" t="n"/>
       <c r="G229" s="53" t="n"/>
     </row>
     <row r="230" ht="19.8" customHeight="1">
       <c r="A230" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B230" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C230" s="47" t="n"/>
+      <c r="D230" s="18" t="n"/>
+      <c r="E230" s="20" t="n"/>
+      <c r="F230" s="85" t="n">
+        <v>669.7</v>
+      </c>
+      <c r="G230" s="53" t="n"/>
+    </row>
+    <row r="231" ht="19.8" customHeight="1">
+      <c r="A231" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B230" s="78" t="inlineStr">
+      <c r="B231" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C230" s="47" t="inlineStr">
+      <c r="C231" s="47" t="inlineStr">
         <is>
           <t>669.70  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D230" s="12" t="n"/>
-      <c r="E230" s="14" t="n"/>
-      <c r="F230" s="85" t="n">
+      <c r="D231" s="12" t="n"/>
+      <c r="E231" s="14" t="n"/>
+      <c r="F231" s="85" t="n">
         <v>716.6</v>
       </c>
-      <c r="G230" s="53" t="n"/>
-    </row>
-    <row r="231" ht="19.8" customHeight="1">
-      <c r="A231" s="43" t="n"/>
-      <c r="B231" s="86" t="inlineStr">
+      <c r="G231" s="53" t="n"/>
+    </row>
+    <row r="232" ht="19.8" customHeight="1">
+      <c r="A232" s="43" t="n"/>
+      <c r="B232" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C231" s="18" t="n"/>
-      <c r="D231" s="12" t="n"/>
-      <c r="E231" s="39" t="n"/>
-      <c r="F231" s="87" t="n"/>
-      <c r="G231" s="53" t="n"/>
-    </row>
-    <row r="232" ht="19.8" customHeight="1">
-      <c r="A232" s="83" t="n"/>
-      <c r="B232" s="78" t="inlineStr">
+      <c r="C232" s="18" t="n"/>
+      <c r="D232" s="12" t="n"/>
+      <c r="E232" s="39" t="n"/>
+      <c r="F232" s="87" t="n"/>
+      <c r="G232" s="53" t="n"/>
+    </row>
+    <row r="233" ht="19.8" customHeight="1">
+      <c r="A233" s="83" t="n"/>
+      <c r="B233" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C232" s="47" t="n"/>
-      <c r="D232" s="12" t="n"/>
-      <c r="E232" s="14" t="n"/>
-      <c r="F232" s="85" t="n">
+      <c r="C233" s="47" t="n"/>
+      <c r="D233" s="12" t="n"/>
+      <c r="E233" s="14" t="n"/>
+      <c r="F233" s="85" t="n">
         <v>716.6</v>
       </c>
-      <c r="G232" s="53" t="n"/>
-    </row>
-    <row r="233" ht="19.8" customHeight="1">
-      <c r="A233" s="47" t="n"/>
-      <c r="B233" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C233" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
-      </c>
-      <c r="D233" s="12" t="n"/>
-      <c r="E233" s="39" t="n"/>
-      <c r="F233" s="61" t="n"/>
       <c r="G233" s="53" t="n"/>
     </row>
     <row r="234" ht="19.8" customHeight="1">
       <c r="A234" s="47" t="n"/>
-      <c r="B234" s="60" t="inlineStr">
-        <is>
-          <t>Kcal/h del toallero Scala/Domino 80</t>
-        </is>
-      </c>
-      <c r="C234" s="59" t="n">
-        <v>708</v>
+      <c r="B234" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C234" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
       </c>
       <c r="D234" s="12" t="n"/>
       <c r="E234" s="39" t="n"/>
-      <c r="F234" s="20" t="n"/>
+      <c r="F234" s="61" t="n"/>
       <c r="G234" s="53" t="n"/>
     </row>
     <row r="235" ht="19.8" customHeight="1">
       <c r="A235" s="47" t="n"/>
       <c r="B235" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 150</t>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
         </is>
       </c>
       <c r="C235" s="59" t="n">
-        <v>1315</v>
+        <v>708</v>
       </c>
       <c r="D235" s="12" t="n"/>
       <c r="E235" s="39" t="n"/>
@@ -24134,11 +24142,11 @@
       <c r="A236" s="47" t="n"/>
       <c r="B236" s="60" t="inlineStr">
         <is>
-          <t>Toalleros necesarios</t>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
         </is>
       </c>
       <c r="C236" s="59" t="n">
-        <v>1</v>
+        <v>1315</v>
       </c>
       <c r="D236" s="12" t="n"/>
       <c r="E236" s="39" t="n"/>
@@ -24146,16 +24154,14 @@
       <c r="G236" s="53" t="n"/>
     </row>
     <row r="237" ht="19.8" customHeight="1">
-      <c r="A237" s="50" t="n"/>
+      <c r="A237" s="47" t="n"/>
       <c r="B237" s="60" t="inlineStr">
         <is>
-          <t>Toallero adoptado</t>
-        </is>
-      </c>
-      <c r="C237" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
-        </is>
+          <t>Toalleros necesarios</t>
+        </is>
+      </c>
+      <c r="C237" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="D237" s="12" t="n"/>
       <c r="E237" s="39" t="n"/>
@@ -24163,159 +24169,153 @@
       <c r="G237" s="53" t="n"/>
     </row>
     <row r="238" ht="19.8" customHeight="1">
-      <c r="A238" s="8" t="inlineStr">
+      <c r="A238" s="50" t="n"/>
+      <c r="B238" s="60" t="inlineStr">
+        <is>
+          <t>Toallero adoptado</t>
+        </is>
+      </c>
+      <c r="C238" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
+        </is>
+      </c>
+      <c r="D238" s="12" t="n"/>
+      <c r="E238" s="39" t="n"/>
+      <c r="F238" s="20" t="n"/>
+      <c r="G238" s="53" t="n"/>
+    </row>
+    <row r="239" ht="19.8" customHeight="1">
+      <c r="A239" s="8" t="inlineStr">
         <is>
           <t>LOCAL  13 - Dormitorio Norte   (PA)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B238" s="11" t="n"/>
-      <c r="C238" s="11" t="n"/>
-      <c r="D238" s="11" t="n"/>
-      <c r="E238" s="11" t="n"/>
-      <c r="F238" s="42" t="n"/>
-      <c r="G238" s="53" t="n"/>
-    </row>
-    <row r="239" ht="32" customHeight="1">
-      <c r="A239" s="2" t="inlineStr">
+      <c r="B239" s="11" t="n"/>
+      <c r="C239" s="11" t="n"/>
+      <c r="D239" s="11" t="n"/>
+      <c r="E239" s="11" t="n"/>
+      <c r="F239" s="42" t="n"/>
+      <c r="G239" s="53" t="n"/>
+    </row>
+    <row r="240" ht="32" customHeight="1">
+      <c r="A240" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B239" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C239" s="2" t="inlineStr">
+      <c r="C240" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G239" s="53" t="n"/>
-    </row>
-    <row r="240" ht="19.8" customHeight="1">
-      <c r="A240" s="36" t="inlineStr">
+      <c r="G240" s="53" t="n"/>
+    </row>
+    <row r="241" ht="19.8" customHeight="1">
+      <c r="A241" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B240" s="78" t="inlineStr">
+      <c r="B241" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C240" s="43" t="n"/>
-      <c r="D240" s="58" t="n"/>
-      <c r="E240" s="58" t="n"/>
-      <c r="F240" s="61" t="n"/>
-      <c r="G240" s="53" t="n"/>
-    </row>
-    <row r="241" ht="19.8" customHeight="1">
-      <c r="A241" s="43" t="n"/>
-      <c r="B241" s="79" t="inlineStr">
+      <c r="C241" s="43" t="n"/>
+      <c r="D241" s="58" t="n"/>
+      <c r="E241" s="58" t="n"/>
+      <c r="F241" s="61" t="n"/>
+      <c r="G241" s="53" t="n"/>
+    </row>
+    <row r="242" ht="19.8" customHeight="1">
+      <c r="A242" s="43" t="n"/>
+      <c r="B242" s="79" t="inlineStr">
         <is>
           <t>VA04</t>
         </is>
       </c>
-      <c r="C241" s="18" t="inlineStr">
+      <c r="C242" s="18" t="inlineStr">
         <is>
           <t>2.00 x 2.52</t>
         </is>
       </c>
-      <c r="D241" s="19" t="n">
+      <c r="D242" s="19" t="n">
         <v>5.04</v>
-      </c>
-      <c r="E241" s="59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F241" s="80" t="n">
-        <v>302.4</v>
-      </c>
-      <c r="G241" s="53" t="n"/>
-    </row>
-    <row r="242" ht="19.8" customHeight="1">
-      <c r="A242" s="50" t="n"/>
-      <c r="B242" s="82" t="inlineStr">
-        <is>
-          <t>VA05</t>
-        </is>
-      </c>
-      <c r="C242" s="18" t="inlineStr">
-        <is>
-          <t>1.40 x 2.52</t>
-        </is>
-      </c>
-      <c r="D242" s="19" t="n">
-        <v>3.53</v>
       </c>
       <c r="E242" s="59" t="n">
         <v>60</v>
       </c>
       <c r="F242" s="80" t="n">
+        <v>302.4</v>
+      </c>
+      <c r="G242" s="53" t="n"/>
+    </row>
+    <row r="243" ht="19.8" customHeight="1">
+      <c r="A243" s="50" t="n"/>
+      <c r="B243" s="82" t="inlineStr">
+        <is>
+          <t>VA05</t>
+        </is>
+      </c>
+      <c r="C243" s="18" t="inlineStr">
+        <is>
+          <t>1.40 x 2.52</t>
+        </is>
+      </c>
+      <c r="D243" s="19" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="E243" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F243" s="80" t="n">
         <v>211.8</v>
       </c>
-      <c r="G242" s="53" t="n"/>
-    </row>
-    <row r="243" ht="19.8" customHeight="1">
-      <c r="A243" s="36" t="inlineStr">
+      <c r="G243" s="53" t="n"/>
+    </row>
+    <row r="244" ht="19.8" customHeight="1">
+      <c r="A244" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B243" s="78" t="inlineStr">
+      <c r="B244" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C243" s="47" t="n"/>
-      <c r="D243" s="18" t="n"/>
-      <c r="E243" s="18" t="n"/>
-      <c r="F243" s="20" t="n"/>
-      <c r="G243" s="53" t="n"/>
-    </row>
-    <row r="244" ht="19.8" customHeight="1">
-      <c r="A244" s="43" t="n"/>
-      <c r="B244" s="79" t="inlineStr">
+      <c r="C244" s="47" t="n"/>
+      <c r="D244" s="18" t="n"/>
+      <c r="E244" s="18" t="n"/>
+      <c r="F244" s="20" t="n"/>
+      <c r="G244" s="53" t="n"/>
+    </row>
+    <row r="245" ht="19.8" customHeight="1">
+      <c r="A245" s="43" t="n"/>
+      <c r="B245" s="79" t="inlineStr">
         <is>
           <t>AISLADAS (NO)</t>
-        </is>
-      </c>
-      <c r="C244" s="18" t="inlineStr">
-        <is>
-          <t>4.25 x 3.00</t>
-        </is>
-      </c>
-      <c r="D244" s="19" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="E244" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F244" s="80" t="n">
-        <v>255</v>
-      </c>
-      <c r="G244" s="53" t="n"/>
-    </row>
-    <row r="245" ht="19.8" customHeight="1">
-      <c r="A245" s="47" t="n"/>
-      <c r="B245" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS (SE)</t>
         </is>
       </c>
       <c r="C245" s="18" t="inlineStr">
@@ -24338,22 +24338,22 @@
       <c r="A246" s="47" t="n"/>
       <c r="B246" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>AISLADAS (SE)</t>
         </is>
       </c>
       <c r="C246" s="18" t="inlineStr">
         <is>
-          <t>4.00 x 3.00</t>
+          <t>4.25 x 3.00</t>
         </is>
       </c>
       <c r="D246" s="19" t="n">
-        <v>12</v>
+        <v>12.75</v>
       </c>
       <c r="E246" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F246" s="80" t="n">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="G246" s="53" t="n"/>
     </row>
@@ -24361,7 +24361,7 @@
       <c r="A247" s="47" t="n"/>
       <c r="B247" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C247" s="18" t="inlineStr">
@@ -24373,338 +24373,346 @@
         <v>12</v>
       </c>
       <c r="E247" s="59" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F247" s="80" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="G247" s="53" t="n"/>
     </row>
     <row r="248" ht="19.8" customHeight="1">
-      <c r="A248" s="50" t="n"/>
-      <c r="B248" s="82" t="inlineStr">
+      <c r="A248" s="47" t="n"/>
+      <c r="B248" s="81" t="inlineStr">
         <is>
           <t>INTERIORES</t>
         </is>
       </c>
-      <c r="C248" s="18" t="n"/>
-      <c r="D248" s="19" t="n"/>
+      <c r="C248" s="18" t="inlineStr">
+        <is>
+          <t>4.00 x 3.00</t>
+        </is>
+      </c>
+      <c r="D248" s="19" t="n">
+        <v>12</v>
+      </c>
       <c r="E248" s="59" t="n">
         <v>25</v>
       </c>
-      <c r="F248" s="80" t="n"/>
+      <c r="F248" s="80" t="n">
+        <v>300</v>
+      </c>
       <c r="G248" s="53" t="n"/>
     </row>
     <row r="249" ht="19.8" customHeight="1">
-      <c r="A249" s="36" t="inlineStr">
+      <c r="A249" s="50" t="n"/>
+      <c r="B249" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C249" s="18" t="n"/>
+      <c r="D249" s="19" t="n"/>
+      <c r="E249" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F249" s="80" t="n"/>
+      <c r="G249" s="53" t="n"/>
+    </row>
+    <row r="250" ht="19.8" customHeight="1">
+      <c r="A250" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B249" s="78" t="inlineStr">
+      <c r="B250" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C249" s="47" t="n"/>
-      <c r="D249" s="18" t="n"/>
-      <c r="E249" s="18" t="n"/>
-      <c r="F249" s="20" t="n"/>
-      <c r="G249" s="53" t="n"/>
-    </row>
-    <row r="250" ht="19.8" customHeight="1">
-      <c r="A250" s="43" t="n"/>
-      <c r="B250" s="79" t="inlineStr">
+      <c r="C250" s="47" t="n"/>
+      <c r="D250" s="18" t="n"/>
+      <c r="E250" s="18" t="n"/>
+      <c r="F250" s="20" t="n"/>
+      <c r="G250" s="53" t="n"/>
+    </row>
+    <row r="251" ht="19.8" customHeight="1">
+      <c r="A251" s="43" t="n"/>
+      <c r="B251" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
         </is>
       </c>
-      <c r="C250" s="18" t="n"/>
-      <c r="D250" s="19" t="n"/>
-      <c r="E250" s="59" t="n">
+      <c r="C251" s="18" t="n"/>
+      <c r="D251" s="19" t="n"/>
+      <c r="E251" s="59" t="n">
         <v>30</v>
       </c>
-      <c r="F250" s="80" t="n"/>
-      <c r="G250" s="53" t="n"/>
-    </row>
-    <row r="251" ht="19.8" customHeight="1">
-      <c r="A251" s="47" t="n"/>
-      <c r="B251" s="81" t="inlineStr">
+      <c r="F251" s="80" t="n"/>
+      <c r="G251" s="53" t="n"/>
+    </row>
+    <row r="252" ht="19.8" customHeight="1">
+      <c r="A252" s="47" t="n"/>
+      <c r="B252" s="81" t="inlineStr">
         <is>
           <t>TECHO AISLADO</t>
         </is>
       </c>
-      <c r="C251" s="18" t="inlineStr">
+      <c r="C252" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D251" s="19" t="n">
+      <c r="D252" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="E251" s="59" t="n">
+      <c r="E252" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F251" s="80" t="n">
+      <c r="F252" s="80" t="n">
         <v>340</v>
       </c>
-      <c r="G251" s="53" t="n"/>
-    </row>
-    <row r="252" ht="19.8" customHeight="1">
-      <c r="A252" s="50" t="n"/>
-      <c r="B252" s="82" t="inlineStr">
+      <c r="G252" s="53" t="n"/>
+    </row>
+    <row r="253" ht="19.8" customHeight="1">
+      <c r="A253" s="50" t="n"/>
+      <c r="B253" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C252" s="18" t="n"/>
-      <c r="D252" s="19" t="n"/>
-      <c r="E252" s="59" t="n">
+      <c r="C253" s="18" t="n"/>
+      <c r="D253" s="19" t="n"/>
+      <c r="E253" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F252" s="80" t="n"/>
-      <c r="G252" s="53" t="n"/>
-    </row>
-    <row r="253" ht="19.8" customHeight="1">
-      <c r="A253" s="36" t="inlineStr">
+      <c r="F253" s="80" t="n"/>
+      <c r="G253" s="53" t="n"/>
+    </row>
+    <row r="254" ht="19.8" customHeight="1">
+      <c r="A254" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B253" s="78" t="inlineStr">
+      <c r="B254" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C253" s="47" t="n"/>
-      <c r="D253" s="18" t="n"/>
-      <c r="E253" s="18" t="n"/>
-      <c r="F253" s="20" t="n"/>
-      <c r="G253" s="53" t="n"/>
-    </row>
-    <row r="254" ht="19.8" customHeight="1">
-      <c r="A254" s="43" t="n"/>
-      <c r="B254" s="79" t="inlineStr">
+      <c r="C254" s="47" t="n"/>
+      <c r="D254" s="18" t="n"/>
+      <c r="E254" s="18" t="n"/>
+      <c r="F254" s="20" t="n"/>
+      <c r="G254" s="53" t="n"/>
+    </row>
+    <row r="255" ht="19.8" customHeight="1">
+      <c r="A255" s="43" t="n"/>
+      <c r="B255" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C254" s="18" t="n"/>
-      <c r="D254" s="19" t="n"/>
-      <c r="E254" s="59" t="n">
+      <c r="C255" s="18" t="n"/>
+      <c r="D255" s="19" t="n"/>
+      <c r="E255" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F254" s="80" t="n"/>
-      <c r="G254" s="53" t="n"/>
-    </row>
-    <row r="255" ht="19.8" customHeight="1">
-      <c r="A255" s="50" t="n"/>
-      <c r="B255" s="82" t="inlineStr">
+      <c r="F255" s="80" t="n"/>
+      <c r="G255" s="53" t="n"/>
+    </row>
+    <row r="256" ht="19.8" customHeight="1">
+      <c r="A256" s="50" t="n"/>
+      <c r="B256" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C255" s="18" t="inlineStr">
+      <c r="C256" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D255" s="24" t="n">
+      <c r="D256" s="24" t="n">
         <v>17</v>
       </c>
-      <c r="E255" s="59" t="n">
+      <c r="E256" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F255" s="80" t="n">
+      <c r="F256" s="80" t="n">
         <v>255</v>
       </c>
-      <c r="G255" s="53" t="n"/>
-    </row>
-    <row r="256" ht="19.8" customHeight="1">
-      <c r="A256" s="36" t="inlineStr">
+      <c r="G256" s="53" t="n"/>
+    </row>
+    <row r="257" ht="19.8" customHeight="1">
+      <c r="A257" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B256" s="78" t="inlineStr">
+      <c r="B257" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C256" s="83" t="n"/>
-      <c r="D256" s="36" t="inlineStr">
+      <c r="C257" s="83" t="n"/>
+      <c r="D257" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E256" s="47" t="n"/>
-      <c r="F256" s="20" t="n"/>
-      <c r="G256" s="53" t="n"/>
-    </row>
-    <row r="257" ht="19.8" customHeight="1">
-      <c r="A257" s="43" t="n"/>
-      <c r="B257" s="79" t="inlineStr">
+      <c r="E257" s="47" t="n"/>
+      <c r="F257" s="20" t="n"/>
+      <c r="G257" s="53" t="n"/>
+    </row>
+    <row r="258" ht="19.8" customHeight="1">
+      <c r="A258" s="43" t="n"/>
+      <c r="B258" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C257" s="18" t="n"/>
-      <c r="D257" s="22" t="n"/>
-      <c r="E257" s="59" t="n">
+      <c r="C258" s="18" t="n"/>
+      <c r="D258" s="22" t="n"/>
+      <c r="E258" s="59" t="n">
         <v>6</v>
-      </c>
-      <c r="F257" s="80" t="n"/>
-      <c r="G257" s="53" t="n"/>
-    </row>
-    <row r="258" ht="19.8" customHeight="1">
-      <c r="A258" s="47" t="n"/>
-      <c r="B258" s="81" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C258" s="18" t="n"/>
-      <c r="D258" s="19" t="n"/>
-      <c r="E258" s="59" t="n">
-        <v>9</v>
       </c>
       <c r="F258" s="80" t="n"/>
       <c r="G258" s="53" t="n"/>
     </row>
     <row r="259" ht="19.8" customHeight="1">
-      <c r="A259" s="50" t="n"/>
-      <c r="B259" s="82" t="inlineStr">
+      <c r="A259" s="47" t="n"/>
+      <c r="B259" s="81" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C259" s="18" t="n"/>
+      <c r="D259" s="19" t="n"/>
+      <c r="E259" s="59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F259" s="80" t="n"/>
+      <c r="G259" s="53" t="n"/>
+    </row>
+    <row r="260" ht="19.8" customHeight="1">
+      <c r="A260" s="50" t="n"/>
+      <c r="B260" s="82" t="inlineStr">
         <is>
           <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C259" s="18" t="inlineStr">
+      <c r="C260" s="18" t="inlineStr">
         <is>
           <t>17.00 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D259" s="19" t="n">
+      <c r="D260" s="19" t="n">
         <v>51</v>
       </c>
-      <c r="E259" s="59" t="n">
+      <c r="E260" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F259" s="84" t="n">
+      <c r="F260" s="84" t="n">
         <v>612</v>
-      </c>
-      <c r="G259" s="53" t="n"/>
-    </row>
-    <row r="260" ht="19.8" customHeight="1">
-      <c r="A260" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B260" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C260" s="47" t="n"/>
-      <c r="D260" s="18" t="n"/>
-      <c r="E260" s="20" t="n"/>
-      <c r="F260" s="85" t="n">
-        <v>2771.2</v>
       </c>
       <c r="G260" s="53" t="n"/>
     </row>
     <row r="261" ht="19.8" customHeight="1">
       <c r="A261" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B261" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C261" s="47" t="n"/>
+      <c r="D261" s="18" t="n"/>
+      <c r="E261" s="20" t="n"/>
+      <c r="F261" s="85" t="n">
+        <v>2771.2</v>
+      </c>
+      <c r="G261" s="53" t="n"/>
+    </row>
+    <row r="262" ht="19.8" customHeight="1">
+      <c r="A262" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B261" s="78" t="inlineStr">
+      <c r="B262" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C261" s="47" t="inlineStr">
+      <c r="C262" s="47" t="inlineStr">
         <is>
           <t>2771.20  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D261" s="12" t="n"/>
-      <c r="E261" s="14" t="n"/>
-      <c r="F261" s="85" t="n">
+      <c r="D262" s="12" t="n"/>
+      <c r="E262" s="14" t="n"/>
+      <c r="F262" s="85" t="n">
         <v>2965.2</v>
       </c>
-      <c r="G261" s="53" t="n"/>
-    </row>
-    <row r="262" ht="19.8" customHeight="1">
-      <c r="A262" s="43" t="n"/>
-      <c r="B262" s="86" t="inlineStr">
+      <c r="G262" s="53" t="n"/>
+    </row>
+    <row r="263" ht="19.8" customHeight="1">
+      <c r="A263" s="43" t="n"/>
+      <c r="B263" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C262" s="18" t="n"/>
-      <c r="D262" s="12" t="n"/>
-      <c r="E262" s="39" t="n"/>
-      <c r="F262" s="87" t="n"/>
-      <c r="G262" s="53" t="n"/>
-    </row>
-    <row r="263" ht="19.8" customHeight="1">
-      <c r="A263" s="83" t="n"/>
-      <c r="B263" s="78" t="inlineStr">
+      <c r="C263" s="18" t="n"/>
+      <c r="D263" s="12" t="n"/>
+      <c r="E263" s="39" t="n"/>
+      <c r="F263" s="87" t="n"/>
+      <c r="G263" s="53" t="n"/>
+    </row>
+    <row r="264" ht="19.8" customHeight="1">
+      <c r="A264" s="83" t="n"/>
+      <c r="B264" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C263" s="47" t="n"/>
-      <c r="D263" s="12" t="n"/>
-      <c r="E263" s="14" t="n"/>
-      <c r="F263" s="85" t="n">
+      <c r="C264" s="47" t="n"/>
+      <c r="D264" s="12" t="n"/>
+      <c r="E264" s="14" t="n"/>
+      <c r="F264" s="85" t="n">
         <v>2965.2</v>
       </c>
-      <c r="G263" s="53" t="n"/>
-    </row>
-    <row r="264" ht="19.8" customHeight="1">
-      <c r="A264" s="47" t="n"/>
-      <c r="B264" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C264" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
-      </c>
-      <c r="D264" s="12" t="n"/>
-      <c r="E264" s="39" t="n"/>
-      <c r="F264" s="61" t="n"/>
       <c r="G264" s="53" t="n"/>
     </row>
     <row r="265" ht="19.8" customHeight="1">
       <c r="A265" s="47" t="n"/>
-      <c r="B265" s="60" t="inlineStr">
-        <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C265" s="19" t="n">
-        <v>274.4</v>
+      <c r="B265" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C265" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
       </c>
       <c r="D265" s="12" t="n"/>
       <c r="E265" s="39" t="n"/>
-      <c r="F265" s="20" t="n"/>
+      <c r="F265" s="61" t="n"/>
       <c r="G265" s="53" t="n"/>
     </row>
     <row r="266" ht="19.8" customHeight="1">
       <c r="A266" s="47" t="n"/>
       <c r="B266" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
-        </is>
-      </c>
-      <c r="C266" s="59" t="n">
-        <v>11</v>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C266" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D266" s="12" t="n"/>
       <c r="E266" s="39" t="n"/>
@@ -24715,11 +24723,11 @@
       <c r="A267" s="47" t="n"/>
       <c r="B267" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C267" s="59" t="n">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="D267" s="12" t="n"/>
       <c r="E267" s="39" t="n"/>
@@ -24727,16 +24735,14 @@
       <c r="G267" s="53" t="n"/>
     </row>
     <row r="268" ht="19.8" customHeight="1">
-      <c r="A268" s="50" t="n"/>
+      <c r="A268" s="47" t="n"/>
       <c r="B268" s="60" t="inlineStr">
         <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C268" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
+          <t>Ancho del radiador (cm)</t>
+        </is>
+      </c>
+      <c r="C268" s="59" t="n">
+        <v>88</v>
       </c>
       <c r="D268" s="12" t="n"/>
       <c r="E268" s="39" t="n"/>
@@ -24744,508 +24750,510 @@
       <c r="G268" s="53" t="n"/>
     </row>
     <row r="269" ht="19.8" customHeight="1">
-      <c r="A269" s="8" t="inlineStr">
+      <c r="A269" s="50" t="n"/>
+      <c r="B269" s="60" t="inlineStr">
+        <is>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C269" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
+      </c>
+      <c r="D269" s="12" t="n"/>
+      <c r="E269" s="39" t="n"/>
+      <c r="F269" s="20" t="n"/>
+      <c r="G269" s="53" t="n"/>
+    </row>
+    <row r="270" ht="19.8" customHeight="1">
+      <c r="A270" s="8" t="inlineStr">
         <is>
           <t>LOCAL  14 - Play room   (PA)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B269" s="11" t="n"/>
-      <c r="C269" s="11" t="n"/>
-      <c r="D269" s="11" t="n"/>
-      <c r="E269" s="11" t="n"/>
-      <c r="F269" s="42" t="n"/>
-      <c r="G269" s="53" t="n"/>
-    </row>
-    <row r="270" ht="32" customHeight="1">
-      <c r="A270" s="2" t="inlineStr">
+      <c r="B270" s="11" t="n"/>
+      <c r="C270" s="11" t="n"/>
+      <c r="D270" s="11" t="n"/>
+      <c r="E270" s="11" t="n"/>
+      <c r="F270" s="42" t="n"/>
+      <c r="G270" s="53" t="n"/>
+    </row>
+    <row r="271" ht="32" customHeight="1">
+      <c r="A271" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B270" s="2" t="inlineStr">
+      <c r="B271" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C270" s="2" t="inlineStr">
+      <c r="C271" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D270" s="2" t="inlineStr">
+      <c r="D271" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E270" s="2" t="inlineStr">
+      <c r="E271" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F270" s="2" t="inlineStr">
+      <c r="F271" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G270" s="53" t="n"/>
-    </row>
-    <row r="271" ht="19.8" customHeight="1">
-      <c r="A271" s="36" t="inlineStr">
+      <c r="G271" s="53" t="n"/>
+    </row>
+    <row r="272" ht="19.8" customHeight="1">
+      <c r="A272" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B271" s="78" t="inlineStr">
+      <c r="B272" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C271" s="43" t="n"/>
-      <c r="D271" s="58" t="n"/>
-      <c r="E271" s="58" t="n"/>
-      <c r="F271" s="61" t="n"/>
-      <c r="G271" s="53" t="n"/>
-    </row>
-    <row r="272" ht="19.8" customHeight="1">
-      <c r="A272" s="90" t="n"/>
-      <c r="B272" s="91" t="inlineStr">
+      <c r="C272" s="43" t="n"/>
+      <c r="D272" s="58" t="n"/>
+      <c r="E272" s="58" t="n"/>
+      <c r="F272" s="61" t="n"/>
+      <c r="G272" s="53" t="n"/>
+    </row>
+    <row r="273" ht="19.8" customHeight="1">
+      <c r="A273" s="90" t="n"/>
+      <c r="B273" s="91" t="inlineStr">
         <is>
           <t>VA04</t>
         </is>
       </c>
-      <c r="C272" s="18" t="inlineStr">
+      <c r="C273" s="18" t="inlineStr">
         <is>
           <t>2.00 x 2.52</t>
         </is>
       </c>
-      <c r="D272" s="19" t="n">
+      <c r="D273" s="19" t="n">
         <v>5.04</v>
       </c>
-      <c r="E272" s="59" t="n">
+      <c r="E273" s="59" t="n">
         <v>60</v>
       </c>
-      <c r="F272" s="80" t="n">
+      <c r="F273" s="80" t="n">
         <v>302.4</v>
       </c>
-      <c r="G272" s="53" t="n"/>
-    </row>
-    <row r="273" ht="19.8" customHeight="1">
-      <c r="A273" s="36" t="inlineStr">
+      <c r="G273" s="53" t="n"/>
+    </row>
+    <row r="274" ht="19.8" customHeight="1">
+      <c r="A274" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B273" s="78" t="inlineStr">
+      <c r="B274" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C273" s="47" t="n"/>
-      <c r="D273" s="18" t="n"/>
-      <c r="E273" s="18" t="n"/>
-      <c r="F273" s="20" t="n"/>
-      <c r="G273" s="53" t="n"/>
-    </row>
-    <row r="274" ht="19.8" customHeight="1">
-      <c r="A274" s="43" t="n"/>
-      <c r="B274" s="79" t="inlineStr">
+      <c r="C274" s="47" t="n"/>
+      <c r="D274" s="18" t="n"/>
+      <c r="E274" s="18" t="n"/>
+      <c r="F274" s="20" t="n"/>
+      <c r="G274" s="53" t="n"/>
+    </row>
+    <row r="275" ht="19.8" customHeight="1">
+      <c r="A275" s="43" t="n"/>
+      <c r="B275" s="79" t="inlineStr">
         <is>
           <t>AISLADAS (NO)</t>
         </is>
       </c>
-      <c r="C274" s="18" t="inlineStr">
+      <c r="C275" s="18" t="inlineStr">
         <is>
           <t>4.13 x 3.00</t>
         </is>
       </c>
-      <c r="D274" s="19" t="n">
+      <c r="D275" s="19" t="n">
         <v>12.39</v>
       </c>
-      <c r="E274" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F274" s="80" t="n">
-        <v>247.8</v>
-      </c>
-      <c r="G274" s="53" t="n"/>
-    </row>
-    <row r="275" ht="19.8" customHeight="1">
-      <c r="A275" s="47" t="n"/>
-      <c r="B275" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C275" s="18" t="n"/>
-      <c r="D275" s="19" t="n"/>
       <c r="E275" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F275" s="80" t="n"/>
+      <c r="F275" s="80" t="n">
+        <v>247.8</v>
+      </c>
       <c r="G275" s="53" t="n"/>
     </row>
     <row r="276" ht="19.8" customHeight="1">
       <c r="A276" s="47" t="n"/>
       <c r="B276" s="81" t="inlineStr">
         <is>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C276" s="18" t="n"/>
+      <c r="D276" s="19" t="n"/>
+      <c r="E276" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F276" s="80" t="n"/>
+      <c r="G276" s="53" t="n"/>
+    </row>
+    <row r="277" ht="19.8" customHeight="1">
+      <c r="A277" s="47" t="n"/>
+      <c r="B277" s="81" t="inlineStr">
+        <is>
           <t>INTERIORES (NE)</t>
         </is>
       </c>
-      <c r="C276" s="18" t="inlineStr">
+      <c r="C277" s="18" t="inlineStr">
         <is>
           <t>4.08 x 3.00</t>
         </is>
       </c>
-      <c r="D276" s="19" t="n">
+      <c r="D277" s="19" t="n">
         <v>12.24</v>
-      </c>
-      <c r="E276" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F276" s="80" t="n">
-        <v>306</v>
-      </c>
-      <c r="G276" s="53" t="n"/>
-    </row>
-    <row r="277" ht="19.8" customHeight="1">
-      <c r="A277" s="50" t="n"/>
-      <c r="B277" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES (SE)</t>
-        </is>
-      </c>
-      <c r="C277" s="18" t="inlineStr">
-        <is>
-          <t>4.13 x 3.00</t>
-        </is>
-      </c>
-      <c r="D277" s="19" t="n">
-        <v>12.39</v>
       </c>
       <c r="E277" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F277" s="80" t="n">
+        <v>306</v>
+      </c>
+      <c r="G277" s="53" t="n"/>
+    </row>
+    <row r="278" ht="19.8" customHeight="1">
+      <c r="A278" s="50" t="n"/>
+      <c r="B278" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES (SE)</t>
+        </is>
+      </c>
+      <c r="C278" s="18" t="inlineStr">
+        <is>
+          <t>4.13 x 3.00</t>
+        </is>
+      </c>
+      <c r="D278" s="19" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="E278" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F278" s="80" t="n">
         <v>309.8</v>
       </c>
-      <c r="G277" s="53" t="n"/>
-    </row>
-    <row r="278" ht="19.8" customHeight="1">
-      <c r="A278" s="36" t="inlineStr">
+      <c r="G278" s="53" t="n"/>
+    </row>
+    <row r="279" ht="19.8" customHeight="1">
+      <c r="A279" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B278" s="78" t="inlineStr">
+      <c r="B279" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C278" s="47" t="n"/>
-      <c r="D278" s="18" t="n"/>
-      <c r="E278" s="18" t="n"/>
-      <c r="F278" s="20" t="n"/>
-      <c r="G278" s="53" t="n"/>
-    </row>
-    <row r="279" ht="19.8" customHeight="1">
-      <c r="A279" s="43" t="n"/>
-      <c r="B279" s="79" t="inlineStr">
+      <c r="C279" s="47" t="n"/>
+      <c r="D279" s="18" t="n"/>
+      <c r="E279" s="18" t="n"/>
+      <c r="F279" s="20" t="n"/>
+      <c r="G279" s="53" t="n"/>
+    </row>
+    <row r="280" ht="19.8" customHeight="1">
+      <c r="A280" s="43" t="n"/>
+      <c r="B280" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
         </is>
       </c>
-      <c r="C279" s="18" t="n"/>
-      <c r="D279" s="19" t="n"/>
-      <c r="E279" s="59" t="n">
+      <c r="C280" s="18" t="n"/>
+      <c r="D280" s="19" t="n"/>
+      <c r="E280" s="59" t="n">
         <v>30</v>
       </c>
-      <c r="F279" s="80" t="n"/>
-      <c r="G279" s="53" t="n"/>
-    </row>
-    <row r="280" ht="19.8" customHeight="1">
-      <c r="A280" s="47" t="n"/>
-      <c r="B280" s="81" t="inlineStr">
+      <c r="F280" s="80" t="n"/>
+      <c r="G280" s="53" t="n"/>
+    </row>
+    <row r="281" ht="19.8" customHeight="1">
+      <c r="A281" s="47" t="n"/>
+      <c r="B281" s="81" t="inlineStr">
         <is>
           <t>TECHO AISLADO</t>
         </is>
       </c>
-      <c r="C280" s="18" t="inlineStr">
+      <c r="C281" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D280" s="19" t="n">
+      <c r="D281" s="19" t="n">
         <v>16.85</v>
       </c>
-      <c r="E280" s="59" t="n">
+      <c r="E281" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F280" s="80" t="n">
+      <c r="F281" s="80" t="n">
         <v>337</v>
       </c>
-      <c r="G280" s="53" t="n"/>
-    </row>
-    <row r="281" ht="19.8" customHeight="1">
-      <c r="A281" s="50" t="n"/>
-      <c r="B281" s="82" t="inlineStr">
+      <c r="G281" s="53" t="n"/>
+    </row>
+    <row r="282" ht="19.8" customHeight="1">
+      <c r="A282" s="50" t="n"/>
+      <c r="B282" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C281" s="18" t="n"/>
-      <c r="D281" s="19" t="n"/>
-      <c r="E281" s="59" t="n">
+      <c r="C282" s="18" t="n"/>
+      <c r="D282" s="19" t="n"/>
+      <c r="E282" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F281" s="80" t="n"/>
-      <c r="G281" s="53" t="n"/>
-    </row>
-    <row r="282" ht="19.8" customHeight="1">
-      <c r="A282" s="36" t="inlineStr">
+      <c r="F282" s="80" t="n"/>
+      <c r="G282" s="53" t="n"/>
+    </row>
+    <row r="283" ht="19.8" customHeight="1">
+      <c r="A283" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B282" s="78" t="inlineStr">
+      <c r="B283" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C282" s="47" t="n"/>
-      <c r="D282" s="18" t="n"/>
-      <c r="E282" s="18" t="n"/>
-      <c r="F282" s="20" t="n"/>
-      <c r="G282" s="53" t="n"/>
-    </row>
-    <row r="283" ht="19.8" customHeight="1">
-      <c r="A283" s="43" t="n"/>
-      <c r="B283" s="79" t="inlineStr">
+      <c r="C283" s="47" t="n"/>
+      <c r="D283" s="18" t="n"/>
+      <c r="E283" s="18" t="n"/>
+      <c r="F283" s="20" t="n"/>
+      <c r="G283" s="53" t="n"/>
+    </row>
+    <row r="284" ht="19.8" customHeight="1">
+      <c r="A284" s="43" t="n"/>
+      <c r="B284" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C283" s="18" t="n"/>
-      <c r="D283" s="19" t="n"/>
-      <c r="E283" s="59" t="n">
+      <c r="C284" s="18" t="n"/>
+      <c r="D284" s="19" t="n"/>
+      <c r="E284" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F283" s="80" t="n"/>
-      <c r="G283" s="53" t="n"/>
-    </row>
-    <row r="284" ht="19.8" customHeight="1">
-      <c r="A284" s="50" t="n"/>
-      <c r="B284" s="82" t="inlineStr">
+      <c r="F284" s="80" t="n"/>
+      <c r="G284" s="53" t="n"/>
+    </row>
+    <row r="285" ht="19.8" customHeight="1">
+      <c r="A285" s="50" t="n"/>
+      <c r="B285" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C284" s="18" t="inlineStr">
+      <c r="C285" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D284" s="24" t="n">
+      <c r="D285" s="24" t="n">
         <v>16.85</v>
       </c>
-      <c r="E284" s="59" t="n">
+      <c r="E285" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F284" s="80" t="n">
+      <c r="F285" s="80" t="n">
         <v>252.8</v>
       </c>
-      <c r="G284" s="53" t="n"/>
-    </row>
-    <row r="285" ht="19.8" customHeight="1">
-      <c r="A285" s="36" t="inlineStr">
+      <c r="G285" s="53" t="n"/>
+    </row>
+    <row r="286" ht="19.8" customHeight="1">
+      <c r="A286" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B285" s="78" t="inlineStr">
+      <c r="B286" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C285" s="83" t="n"/>
-      <c r="D285" s="36" t="inlineStr">
+      <c r="C286" s="83" t="n"/>
+      <c r="D286" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E285" s="47" t="n"/>
-      <c r="F285" s="20" t="n"/>
-      <c r="G285" s="53" t="n"/>
-    </row>
-    <row r="286" ht="19.8" customHeight="1">
-      <c r="A286" s="43" t="n"/>
-      <c r="B286" s="79" t="inlineStr">
+      <c r="E286" s="47" t="n"/>
+      <c r="F286" s="20" t="n"/>
+      <c r="G286" s="53" t="n"/>
+    </row>
+    <row r="287" ht="19.8" customHeight="1">
+      <c r="A287" s="43" t="n"/>
+      <c r="B287" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C286" s="18" t="inlineStr">
+      <c r="C287" s="18" t="inlineStr">
         <is>
           <t>16.85 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D286" s="22" t="n">
+      <c r="D287" s="22" t="n">
         <v>50.55</v>
       </c>
-      <c r="E286" s="59" t="n">
+      <c r="E287" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="F286" s="80" t="n">
+      <c r="F287" s="80" t="n">
         <v>303.3</v>
       </c>
-      <c r="G286" s="53" t="n"/>
-    </row>
-    <row r="287" ht="19.8" customHeight="1">
-      <c r="A287" s="47" t="n"/>
-      <c r="B287" s="81" t="inlineStr">
+      <c r="G287" s="53" t="n"/>
+    </row>
+    <row r="288" ht="19.8" customHeight="1">
+      <c r="A288" s="47" t="n"/>
+      <c r="B288" s="81" t="inlineStr">
         <is>
           <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C287" s="18" t="n"/>
-      <c r="D287" s="19" t="n"/>
-      <c r="E287" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="F287" s="80" t="n"/>
-      <c r="G287" s="53" t="n"/>
-    </row>
-    <row r="288" ht="19.8" customHeight="1">
-      <c r="A288" s="50" t="n"/>
-      <c r="B288" s="82" t="inlineStr">
-        <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
       <c r="C288" s="18" t="n"/>
       <c r="D288" s="19" t="n"/>
       <c r="E288" s="59" t="n">
+        <v>9</v>
+      </c>
+      <c r="F288" s="80" t="n"/>
+      <c r="G288" s="53" t="n"/>
+    </row>
+    <row r="289" ht="19.8" customHeight="1">
+      <c r="A289" s="50" t="n"/>
+      <c r="B289" s="82" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C289" s="18" t="n"/>
+      <c r="D289" s="19" t="n"/>
+      <c r="E289" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F288" s="84" t="n"/>
-      <c r="G288" s="53" t="n"/>
-    </row>
-    <row r="289" ht="19.8" customHeight="1">
-      <c r="A289" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B289" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C289" s="47" t="n"/>
-      <c r="D289" s="18" t="n"/>
-      <c r="E289" s="20" t="n"/>
-      <c r="F289" s="85" t="n">
-        <v>2059.1</v>
-      </c>
+      <c r="F289" s="84" t="n"/>
       <c r="G289" s="53" t="n"/>
     </row>
     <row r="290" ht="19.8" customHeight="1">
       <c r="A290" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B290" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C290" s="47" t="n"/>
+      <c r="D290" s="18" t="n"/>
+      <c r="E290" s="20" t="n"/>
+      <c r="F290" s="85" t="n">
+        <v>2059.1</v>
+      </c>
+      <c r="G290" s="53" t="n"/>
+    </row>
+    <row r="291" ht="19.8" customHeight="1">
+      <c r="A291" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B290" s="78" t="inlineStr">
+      <c r="B291" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C290" s="47" t="inlineStr">
+      <c r="C291" s="47" t="inlineStr">
         <is>
           <t>2059.10  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D290" s="12" t="n"/>
-      <c r="E290" s="14" t="n"/>
-      <c r="F290" s="85" t="n">
+      <c r="D291" s="12" t="n"/>
+      <c r="E291" s="14" t="n"/>
+      <c r="F291" s="85" t="n">
         <v>2203.2</v>
       </c>
-      <c r="G290" s="53" t="n"/>
-    </row>
-    <row r="291" ht="19.8" customHeight="1">
-      <c r="A291" s="43" t="n"/>
-      <c r="B291" s="86" t="inlineStr">
+      <c r="G291" s="53" t="n"/>
+    </row>
+    <row r="292" ht="19.8" customHeight="1">
+      <c r="A292" s="43" t="n"/>
+      <c r="B292" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C291" s="18" t="inlineStr">
+      <c r="C292" s="18" t="inlineStr">
         <is>
           <t>Escalera</t>
         </is>
       </c>
-      <c r="D291" s="12" t="n"/>
-      <c r="E291" s="39" t="n"/>
-      <c r="F291" s="87" t="n">
+      <c r="D292" s="12" t="n"/>
+      <c r="E292" s="39" t="n"/>
+      <c r="F292" s="87" t="n">
         <v>1348.3</v>
       </c>
-      <c r="G291" s="53" t="n"/>
-    </row>
-    <row r="292" ht="19.8" customHeight="1">
-      <c r="A292" s="83" t="n"/>
-      <c r="B292" s="78" t="inlineStr">
+      <c r="G292" s="53" t="n"/>
+    </row>
+    <row r="293" ht="19.8" customHeight="1">
+      <c r="A293" s="83" t="n"/>
+      <c r="B293" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C292" s="47" t="n"/>
-      <c r="D292" s="12" t="n"/>
-      <c r="E292" s="14" t="n"/>
-      <c r="F292" s="85" t="n">
+      <c r="C293" s="47" t="n"/>
+      <c r="D293" s="12" t="n"/>
+      <c r="E293" s="14" t="n"/>
+      <c r="F293" s="85" t="n">
         <v>3551.5</v>
       </c>
-      <c r="G292" s="53" t="n"/>
-    </row>
-    <row r="293" ht="19.8" customHeight="1">
-      <c r="A293" s="47" t="n"/>
-      <c r="B293" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C293" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
-      </c>
-      <c r="D293" s="12" t="n"/>
-      <c r="E293" s="39" t="n"/>
-      <c r="F293" s="61" t="n"/>
       <c r="G293" s="53" t="n"/>
     </row>
     <row r="294" ht="19.8" customHeight="1">
       <c r="A294" s="47" t="n"/>
-      <c r="B294" s="60" t="inlineStr">
-        <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C294" s="19" t="n">
-        <v>274.4</v>
+      <c r="B294" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C294" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
       </c>
       <c r="D294" s="12" t="n"/>
       <c r="E294" s="39" t="n"/>
-      <c r="F294" s="20" t="n"/>
+      <c r="F294" s="61" t="n"/>
       <c r="G294" s="53" t="n"/>
     </row>
     <row r="295" ht="19.8" customHeight="1">
       <c r="A295" s="47" t="n"/>
       <c r="B295" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
-        </is>
-      </c>
-      <c r="C295" s="59" t="n">
-        <v>13</v>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C295" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D295" s="12" t="n"/>
       <c r="E295" s="39" t="n"/>
@@ -25256,11 +25264,11 @@
       <c r="A296" s="47" t="n"/>
       <c r="B296" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C296" s="59" t="n">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="D296" s="12" t="n"/>
       <c r="E296" s="39" t="n"/>
@@ -25268,16 +25276,14 @@
       <c r="G296" s="53" t="n"/>
     </row>
     <row r="297" ht="19.8" customHeight="1">
-      <c r="A297" s="50" t="n"/>
+      <c r="A297" s="47" t="n"/>
       <c r="B297" s="60" t="inlineStr">
         <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C297" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
+          <t>Ancho del radiador (cm)</t>
+        </is>
+      </c>
+      <c r="C297" s="59" t="n">
+        <v>104</v>
       </c>
       <c r="D297" s="12" t="n"/>
       <c r="E297" s="39" t="n"/>
@@ -25285,151 +25291,145 @@
       <c r="G297" s="53" t="n"/>
     </row>
     <row r="298" ht="19.8" customHeight="1">
-      <c r="A298" s="8" t="inlineStr">
+      <c r="A298" s="50" t="n"/>
+      <c r="B298" s="60" t="inlineStr">
+        <is>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C298" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
+      </c>
+      <c r="D298" s="12" t="n"/>
+      <c r="E298" s="39" t="n"/>
+      <c r="F298" s="20" t="n"/>
+      <c r="G298" s="53" t="n"/>
+    </row>
+    <row r="299" ht="19.8" customHeight="1">
+      <c r="A299" s="8" t="inlineStr">
         <is>
           <t>LOCAL  15 - Dormitorio Sur   (PA)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B298" s="11" t="n"/>
-      <c r="C298" s="11" t="n"/>
-      <c r="D298" s="11" t="n"/>
-      <c r="E298" s="11" t="n"/>
-      <c r="F298" s="42" t="n"/>
-      <c r="G298" s="53" t="n"/>
-    </row>
-    <row r="299" ht="32" customHeight="1">
-      <c r="A299" s="2" t="inlineStr">
+      <c r="B299" s="11" t="n"/>
+      <c r="C299" s="11" t="n"/>
+      <c r="D299" s="11" t="n"/>
+      <c r="E299" s="11" t="n"/>
+      <c r="F299" s="42" t="n"/>
+      <c r="G299" s="53" t="n"/>
+    </row>
+    <row r="300" ht="32" customHeight="1">
+      <c r="A300" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B299" s="2" t="inlineStr">
+      <c r="B300" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C299" s="2" t="inlineStr">
+      <c r="C300" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D299" s="2" t="inlineStr">
+      <c r="D300" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E299" s="2" t="inlineStr">
+      <c r="E300" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F299" s="2" t="inlineStr">
+      <c r="F300" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G299" s="53" t="n"/>
-    </row>
-    <row r="300" ht="19.8" customHeight="1">
-      <c r="A300" s="36" t="inlineStr">
+      <c r="G300" s="53" t="n"/>
+    </row>
+    <row r="301" ht="19.8" customHeight="1">
+      <c r="A301" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B300" s="78" t="inlineStr">
+      <c r="B301" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C300" s="43" t="n"/>
-      <c r="D300" s="58" t="n"/>
-      <c r="E300" s="58" t="n"/>
-      <c r="F300" s="61" t="n"/>
-      <c r="G300" s="53" t="n"/>
-    </row>
-    <row r="301" ht="19.8" customHeight="1">
-      <c r="A301" s="90" t="n"/>
-      <c r="B301" s="91" t="inlineStr">
+      <c r="C301" s="43" t="n"/>
+      <c r="D301" s="58" t="n"/>
+      <c r="E301" s="58" t="n"/>
+      <c r="F301" s="61" t="n"/>
+      <c r="G301" s="53" t="n"/>
+    </row>
+    <row r="302" ht="19.8" customHeight="1">
+      <c r="A302" s="90" t="n"/>
+      <c r="B302" s="91" t="inlineStr">
         <is>
           <t>PV04</t>
         </is>
       </c>
-      <c r="C301" s="18" t="inlineStr">
+      <c r="C302" s="18" t="inlineStr">
         <is>
           <t>2.06 x 3.00</t>
         </is>
       </c>
-      <c r="D301" s="19" t="n">
+      <c r="D302" s="19" t="n">
         <v>6.18</v>
       </c>
-      <c r="E301" s="59" t="n">
+      <c r="E302" s="59" t="n">
         <v>60</v>
       </c>
-      <c r="F301" s="80" t="n">
+      <c r="F302" s="80" t="n">
         <v>370.8</v>
       </c>
-      <c r="G301" s="53" t="n"/>
-    </row>
-    <row r="302" ht="19.8" customHeight="1">
-      <c r="A302" s="36" t="inlineStr">
+      <c r="G302" s="53" t="n"/>
+    </row>
+    <row r="303" ht="19.8" customHeight="1">
+      <c r="A303" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B302" s="78" t="inlineStr">
+      <c r="B303" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C302" s="47" t="n"/>
-      <c r="D302" s="18" t="n"/>
-      <c r="E302" s="18" t="n"/>
-      <c r="F302" s="20" t="n"/>
-      <c r="G302" s="53" t="n"/>
-    </row>
-    <row r="303" ht="19.8" customHeight="1">
-      <c r="A303" s="43" t="n"/>
-      <c r="B303" s="79" t="inlineStr">
+      <c r="C303" s="47" t="n"/>
+      <c r="D303" s="18" t="n"/>
+      <c r="E303" s="18" t="n"/>
+      <c r="F303" s="20" t="n"/>
+      <c r="G303" s="53" t="n"/>
+    </row>
+    <row r="304" ht="19.8" customHeight="1">
+      <c r="A304" s="43" t="n"/>
+      <c r="B304" s="79" t="inlineStr">
         <is>
           <t>AISLADAS (SE)</t>
         </is>
       </c>
-      <c r="C303" s="18" t="inlineStr">
+      <c r="C304" s="18" t="inlineStr">
         <is>
           <t>4.05 x 3.00</t>
         </is>
       </c>
-      <c r="D303" s="19" t="n">
+      <c r="D304" s="19" t="n">
         <v>12.15</v>
-      </c>
-      <c r="E303" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F303" s="80" t="n">
-        <v>243</v>
-      </c>
-      <c r="G303" s="53" t="n"/>
-    </row>
-    <row r="304" ht="19.8" customHeight="1">
-      <c r="A304" s="47" t="n"/>
-      <c r="B304" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C304" s="18" t="inlineStr">
-        <is>
-          <t>3.50 x 3.00</t>
-        </is>
-      </c>
-      <c r="D304" s="19" t="n">
-        <v>10.5</v>
       </c>
       <c r="E304" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F304" s="80" t="n">
-        <v>210</v>
+        <v>243</v>
       </c>
       <c r="G304" s="53" t="n"/>
     </row>
@@ -25437,358 +25437,366 @@
       <c r="A305" s="47" t="n"/>
       <c r="B305" s="81" t="inlineStr">
         <is>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C305" s="18" t="inlineStr">
+        <is>
+          <t>3.50 x 3.00</t>
+        </is>
+      </c>
+      <c r="D305" s="19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E305" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F305" s="80" t="n">
+        <v>210</v>
+      </c>
+      <c r="G305" s="53" t="n"/>
+    </row>
+    <row r="306" ht="19.8" customHeight="1">
+      <c r="A306" s="47" t="n"/>
+      <c r="B306" s="81" t="inlineStr">
+        <is>
           <t>INTERIORES (NO)</t>
         </is>
       </c>
-      <c r="C305" s="18" t="inlineStr">
+      <c r="C306" s="18" t="inlineStr">
         <is>
           <t>4.05 x 3.00</t>
         </is>
       </c>
-      <c r="D305" s="19" t="n">
+      <c r="D306" s="19" t="n">
         <v>12.15</v>
-      </c>
-      <c r="E305" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F305" s="80" t="n">
-        <v>303.8</v>
-      </c>
-      <c r="G305" s="53" t="n"/>
-    </row>
-    <row r="306" ht="19.8" customHeight="1">
-      <c r="A306" s="50" t="n"/>
-      <c r="B306" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C306" s="18" t="inlineStr">
-        <is>
-          <t>3.50 x 3.00</t>
-        </is>
-      </c>
-      <c r="D306" s="19" t="n">
-        <v>10.5</v>
       </c>
       <c r="E306" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F306" s="80" t="n">
+        <v>303.8</v>
+      </c>
+      <c r="G306" s="53" t="n"/>
+    </row>
+    <row r="307" ht="19.8" customHeight="1">
+      <c r="A307" s="50" t="n"/>
+      <c r="B307" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C307" s="18" t="inlineStr">
+        <is>
+          <t>3.50 x 3.00</t>
+        </is>
+      </c>
+      <c r="D307" s="19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E307" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F307" s="80" t="n">
         <v>262.5</v>
       </c>
-      <c r="G306" s="53" t="n"/>
-    </row>
-    <row r="307" ht="19.8" customHeight="1">
-      <c r="A307" s="36" t="inlineStr">
+      <c r="G307" s="53" t="n"/>
+    </row>
+    <row r="308" ht="19.8" customHeight="1">
+      <c r="A308" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B307" s="78" t="inlineStr">
+      <c r="B308" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C307" s="47" t="n"/>
-      <c r="D307" s="18" t="n"/>
-      <c r="E307" s="18" t="n"/>
-      <c r="F307" s="20" t="n"/>
-      <c r="G307" s="53" t="n"/>
-    </row>
-    <row r="308" ht="19.8" customHeight="1">
-      <c r="A308" s="43" t="n"/>
-      <c r="B308" s="79" t="inlineStr">
+      <c r="C308" s="47" t="n"/>
+      <c r="D308" s="18" t="n"/>
+      <c r="E308" s="18" t="n"/>
+      <c r="F308" s="20" t="n"/>
+      <c r="G308" s="53" t="n"/>
+    </row>
+    <row r="309" ht="19.8" customHeight="1">
+      <c r="A309" s="43" t="n"/>
+      <c r="B309" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
         </is>
       </c>
-      <c r="C308" s="18" t="n"/>
-      <c r="D308" s="19" t="n"/>
-      <c r="E308" s="59" t="n">
+      <c r="C309" s="18" t="n"/>
+      <c r="D309" s="19" t="n"/>
+      <c r="E309" s="59" t="n">
         <v>30</v>
       </c>
-      <c r="F308" s="80" t="n"/>
-      <c r="G308" s="53" t="n"/>
-    </row>
-    <row r="309" ht="19.8" customHeight="1">
-      <c r="A309" s="47" t="n"/>
-      <c r="B309" s="81" t="inlineStr">
+      <c r="F309" s="80" t="n"/>
+      <c r="G309" s="53" t="n"/>
+    </row>
+    <row r="310" ht="19.8" customHeight="1">
+      <c r="A310" s="47" t="n"/>
+      <c r="B310" s="81" t="inlineStr">
         <is>
           <t>TECHO AISLADO</t>
         </is>
       </c>
-      <c r="C309" s="18" t="inlineStr">
+      <c r="C310" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D309" s="19" t="n">
+      <c r="D310" s="19" t="n">
         <v>14.17</v>
       </c>
-      <c r="E309" s="59" t="n">
+      <c r="E310" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F309" s="80" t="n">
+      <c r="F310" s="80" t="n">
         <v>283.4</v>
       </c>
-      <c r="G309" s="53" t="n"/>
-    </row>
-    <row r="310" ht="19.8" customHeight="1">
-      <c r="A310" s="50" t="n"/>
-      <c r="B310" s="82" t="inlineStr">
+      <c r="G310" s="53" t="n"/>
+    </row>
+    <row r="311" ht="19.8" customHeight="1">
+      <c r="A311" s="50" t="n"/>
+      <c r="B311" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C310" s="18" t="n"/>
-      <c r="D310" s="19" t="n"/>
-      <c r="E310" s="59" t="n">
+      <c r="C311" s="18" t="n"/>
+      <c r="D311" s="19" t="n"/>
+      <c r="E311" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F310" s="80" t="n"/>
-      <c r="G310" s="53" t="n"/>
-    </row>
-    <row r="311" ht="19.8" customHeight="1">
-      <c r="A311" s="36" t="inlineStr">
+      <c r="F311" s="80" t="n"/>
+      <c r="G311" s="53" t="n"/>
+    </row>
+    <row r="312" ht="19.8" customHeight="1">
+      <c r="A312" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B311" s="78" t="inlineStr">
+      <c r="B312" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C311" s="47" t="n"/>
-      <c r="D311" s="18" t="n"/>
-      <c r="E311" s="18" t="n"/>
-      <c r="F311" s="20" t="n"/>
-      <c r="G311" s="53" t="n"/>
-    </row>
-    <row r="312" ht="19.8" customHeight="1">
-      <c r="A312" s="43" t="n"/>
-      <c r="B312" s="79" t="inlineStr">
+      <c r="C312" s="47" t="n"/>
+      <c r="D312" s="18" t="n"/>
+      <c r="E312" s="18" t="n"/>
+      <c r="F312" s="20" t="n"/>
+      <c r="G312" s="53" t="n"/>
+    </row>
+    <row r="313" ht="19.8" customHeight="1">
+      <c r="A313" s="43" t="n"/>
+      <c r="B313" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C312" s="18" t="n"/>
-      <c r="D312" s="19" t="n"/>
-      <c r="E312" s="59" t="n">
+      <c r="C313" s="18" t="n"/>
+      <c r="D313" s="19" t="n"/>
+      <c r="E313" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F312" s="80" t="n"/>
-      <c r="G312" s="53" t="n"/>
-    </row>
-    <row r="313" ht="19.8" customHeight="1">
-      <c r="A313" s="50" t="n"/>
-      <c r="B313" s="82" t="inlineStr">
+      <c r="F313" s="80" t="n"/>
+      <c r="G313" s="53" t="n"/>
+    </row>
+    <row r="314" ht="19.8" customHeight="1">
+      <c r="A314" s="50" t="n"/>
+      <c r="B314" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C313" s="18" t="inlineStr">
+      <c r="C314" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D313" s="24" t="n">
+      <c r="D314" s="24" t="n">
         <v>14.17</v>
       </c>
-      <c r="E313" s="59" t="n">
+      <c r="E314" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F313" s="80" t="n">
+      <c r="F314" s="80" t="n">
         <v>212.6</v>
       </c>
-      <c r="G313" s="53" t="n"/>
-    </row>
-    <row r="314" ht="19.8" customHeight="1">
-      <c r="A314" s="36" t="inlineStr">
+      <c r="G314" s="53" t="n"/>
+    </row>
+    <row r="315" ht="19.8" customHeight="1">
+      <c r="A315" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B314" s="78" t="inlineStr">
+      <c r="B315" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C314" s="83" t="n"/>
-      <c r="D314" s="36" t="inlineStr">
+      <c r="C315" s="83" t="n"/>
+      <c r="D315" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E314" s="47" t="n"/>
-      <c r="F314" s="20" t="n"/>
-      <c r="G314" s="53" t="n"/>
-    </row>
-    <row r="315" ht="19.8" customHeight="1">
-      <c r="A315" s="43" t="n"/>
-      <c r="B315" s="79" t="inlineStr">
+      <c r="E315" s="47" t="n"/>
+      <c r="F315" s="20" t="n"/>
+      <c r="G315" s="53" t="n"/>
+    </row>
+    <row r="316" ht="19.8" customHeight="1">
+      <c r="A316" s="43" t="n"/>
+      <c r="B316" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C315" s="18" t="n"/>
-      <c r="D315" s="22" t="n"/>
-      <c r="E315" s="59" t="n">
+      <c r="C316" s="18" t="n"/>
+      <c r="D316" s="22" t="n"/>
+      <c r="E316" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="F315" s="80" t="n"/>
-      <c r="G315" s="53" t="n"/>
-    </row>
-    <row r="316" ht="19.8" customHeight="1">
-      <c r="A316" s="47" t="n"/>
-      <c r="B316" s="81" t="inlineStr">
+      <c r="F316" s="80" t="n"/>
+      <c r="G316" s="53" t="n"/>
+    </row>
+    <row r="317" ht="19.8" customHeight="1">
+      <c r="A317" s="47" t="n"/>
+      <c r="B317" s="81" t="inlineStr">
         <is>
           <t>DOS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C316" s="18" t="inlineStr">
+      <c r="C317" s="18" t="inlineStr">
         <is>
           <t>14.17 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D316" s="19" t="n">
+      <c r="D317" s="19" t="n">
         <v>42.51</v>
       </c>
-      <c r="E316" s="59" t="n">
+      <c r="E317" s="59" t="n">
         <v>9</v>
       </c>
-      <c r="F316" s="80" t="n">
+      <c r="F317" s="80" t="n">
         <v>382.6</v>
       </c>
-      <c r="G316" s="53" t="n"/>
-    </row>
-    <row r="317" ht="19.8" customHeight="1">
-      <c r="A317" s="50" t="n"/>
-      <c r="B317" s="82" t="inlineStr">
+      <c r="G317" s="53" t="n"/>
+    </row>
+    <row r="318" ht="19.8" customHeight="1">
+      <c r="A318" s="50" t="n"/>
+      <c r="B318" s="82" t="inlineStr">
         <is>
           <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C317" s="18" t="n"/>
-      <c r="D317" s="19" t="n"/>
-      <c r="E317" s="59" t="n">
+      <c r="C318" s="18" t="n"/>
+      <c r="D318" s="19" t="n"/>
+      <c r="E318" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F317" s="84" t="n"/>
-      <c r="G317" s="53" t="n"/>
-    </row>
-    <row r="318" ht="19.8" customHeight="1">
-      <c r="A318" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B318" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C318" s="47" t="n"/>
-      <c r="D318" s="18" t="n"/>
-      <c r="E318" s="20" t="n"/>
-      <c r="F318" s="85" t="n">
-        <v>2268.7</v>
-      </c>
+      <c r="F318" s="84" t="n"/>
       <c r="G318" s="53" t="n"/>
     </row>
     <row r="319" ht="19.8" customHeight="1">
       <c r="A319" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B319" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C319" s="47" t="n"/>
+      <c r="D319" s="18" t="n"/>
+      <c r="E319" s="20" t="n"/>
+      <c r="F319" s="85" t="n">
+        <v>2268.7</v>
+      </c>
+      <c r="G319" s="53" t="n"/>
+    </row>
+    <row r="320" ht="19.8" customHeight="1">
+      <c r="A320" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B319" s="78" t="inlineStr">
+      <c r="B320" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C319" s="47" t="inlineStr">
+      <c r="C320" s="47" t="inlineStr">
         <is>
           <t>2268.70  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D319" s="12" t="n"/>
-      <c r="E319" s="14" t="n"/>
-      <c r="F319" s="85" t="n">
+      <c r="D320" s="12" t="n"/>
+      <c r="E320" s="14" t="n"/>
+      <c r="F320" s="85" t="n">
         <v>2427.5</v>
       </c>
-      <c r="G319" s="53" t="n"/>
-    </row>
-    <row r="320" ht="19.8" customHeight="1">
-      <c r="A320" s="43" t="n"/>
-      <c r="B320" s="86" t="inlineStr">
+      <c r="G320" s="53" t="n"/>
+    </row>
+    <row r="321" ht="19.8" customHeight="1">
+      <c r="A321" s="43" t="n"/>
+      <c r="B321" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C320" s="18" t="n"/>
-      <c r="D320" s="12" t="n"/>
-      <c r="E320" s="39" t="n"/>
-      <c r="F320" s="87" t="n"/>
-      <c r="G320" s="53" t="n"/>
-    </row>
-    <row r="321" ht="19.8" customHeight="1">
-      <c r="A321" s="83" t="n"/>
-      <c r="B321" s="78" t="inlineStr">
+      <c r="C321" s="18" t="n"/>
+      <c r="D321" s="12" t="n"/>
+      <c r="E321" s="39" t="n"/>
+      <c r="F321" s="87" t="n"/>
+      <c r="G321" s="53" t="n"/>
+    </row>
+    <row r="322" ht="19.8" customHeight="1">
+      <c r="A322" s="83" t="n"/>
+      <c r="B322" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C321" s="47" t="n"/>
-      <c r="D321" s="12" t="n"/>
-      <c r="E321" s="14" t="n"/>
-      <c r="F321" s="85" t="n">
+      <c r="C322" s="47" t="n"/>
+      <c r="D322" s="12" t="n"/>
+      <c r="E322" s="14" t="n"/>
+      <c r="F322" s="85" t="n">
         <v>2427.5</v>
       </c>
-      <c r="G321" s="53" t="n"/>
-    </row>
-    <row r="322" ht="19.8" customHeight="1">
-      <c r="A322" s="47" t="n"/>
-      <c r="B322" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C322" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
-      </c>
-      <c r="D322" s="12" t="n"/>
-      <c r="E322" s="39" t="n"/>
-      <c r="F322" s="61" t="n"/>
       <c r="G322" s="53" t="n"/>
     </row>
     <row r="323" ht="19.8" customHeight="1">
       <c r="A323" s="47" t="n"/>
-      <c r="B323" s="60" t="inlineStr">
-        <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C323" s="19" t="n">
-        <v>274.4</v>
+      <c r="B323" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C323" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
       </c>
       <c r="D323" s="12" t="n"/>
       <c r="E323" s="39" t="n"/>
-      <c r="F323" s="20" t="n"/>
+      <c r="F323" s="61" t="n"/>
       <c r="G323" s="53" t="n"/>
     </row>
     <row r="324" ht="19.8" customHeight="1">
       <c r="A324" s="47" t="n"/>
       <c r="B324" s="60" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
-        </is>
-      </c>
-      <c r="C324" s="59" t="n">
-        <v>9</v>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C324" s="19" t="n">
+        <v>274.4</v>
       </c>
       <c r="D324" s="12" t="n"/>
       <c r="E324" s="39" t="n"/>
@@ -25799,11 +25807,11 @@
       <c r="A325" s="47" t="n"/>
       <c r="B325" s="60" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C325" s="59" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="D325" s="12" t="n"/>
       <c r="E325" s="39" t="n"/>
@@ -25811,16 +25819,14 @@
       <c r="G325" s="53" t="n"/>
     </row>
     <row r="326" ht="19.8" customHeight="1">
-      <c r="A326" s="50" t="n"/>
+      <c r="A326" s="47" t="n"/>
       <c r="B326" s="60" t="inlineStr">
         <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C326" s="18" t="inlineStr">
-        <is>
-          <t>Peisa Tropical 80-500</t>
-        </is>
+          <t>Ancho del radiador (cm)</t>
+        </is>
+      </c>
+      <c r="C326" s="59" t="n">
+        <v>72</v>
       </c>
       <c r="D326" s="12" t="n"/>
       <c r="E326" s="39" t="n"/>
@@ -25828,151 +25834,145 @@
       <c r="G326" s="53" t="n"/>
     </row>
     <row r="327" ht="19.8" customHeight="1">
-      <c r="A327" s="8" t="inlineStr">
+      <c r="A327" s="50" t="n"/>
+      <c r="B327" s="60" t="inlineStr">
+        <is>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C327" s="18" t="inlineStr">
+        <is>
+          <t>Peisa Tropical 80-500</t>
+        </is>
+      </c>
+      <c r="D327" s="12" t="n"/>
+      <c r="E327" s="39" t="n"/>
+      <c r="F327" s="20" t="n"/>
+      <c r="G327" s="53" t="n"/>
+    </row>
+    <row r="328" ht="19.8" customHeight="1">
+      <c r="A328" s="8" t="inlineStr">
         <is>
           <t>LOCAL  17 - Bano   (PA)   -   altura 3.00 m</t>
         </is>
       </c>
-      <c r="B327" s="11" t="n"/>
-      <c r="C327" s="11" t="n"/>
-      <c r="D327" s="11" t="n"/>
-      <c r="E327" s="11" t="n"/>
-      <c r="F327" s="42" t="n"/>
-      <c r="G327" s="53" t="n"/>
-    </row>
-    <row r="328" ht="32" customHeight="1">
-      <c r="A328" s="2" t="inlineStr">
+      <c r="B328" s="11" t="n"/>
+      <c r="C328" s="11" t="n"/>
+      <c r="D328" s="11" t="n"/>
+      <c r="E328" s="11" t="n"/>
+      <c r="F328" s="42" t="n"/>
+      <c r="G328" s="53" t="n"/>
+    </row>
+    <row r="329" ht="32" customHeight="1">
+      <c r="A329" s="2" t="inlineStr">
         <is>
           <t>Nro</t>
         </is>
       </c>
-      <c r="B328" s="2" t="inlineStr">
+      <c r="B329" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C328" s="2" t="inlineStr">
+      <c r="C329" s="2" t="inlineStr">
         <is>
           <t>DIMENSIONES (m)</t>
         </is>
       </c>
-      <c r="D328" s="2" t="inlineStr">
+      <c r="D329" s="2" t="inlineStr">
         <is>
           <t>AREA (m2)</t>
         </is>
       </c>
-      <c r="E328" s="2" t="inlineStr">
+      <c r="E329" s="2" t="inlineStr">
         <is>
           <t>FACTOR</t>
         </is>
       </c>
-      <c r="F328" s="2" t="inlineStr">
+      <c r="F329" s="2" t="inlineStr">
         <is>
           <t>PERDIDA CALOR (Kcal/h)</t>
         </is>
       </c>
-      <c r="G328" s="53" t="n"/>
-    </row>
-    <row r="329" ht="19.8" customHeight="1">
-      <c r="A329" s="36" t="inlineStr">
+      <c r="G329" s="53" t="n"/>
+    </row>
+    <row r="330" ht="19.8" customHeight="1">
+      <c r="A330" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B329" s="78" t="inlineStr">
+      <c r="B330" s="78" t="inlineStr">
         <is>
           <t>VENTANA</t>
         </is>
       </c>
-      <c r="C329" s="43" t="n"/>
-      <c r="D329" s="58" t="n"/>
-      <c r="E329" s="58" t="n"/>
-      <c r="F329" s="61" t="n"/>
-      <c r="G329" s="53" t="n"/>
-    </row>
-    <row r="330" ht="19.8" customHeight="1">
-      <c r="A330" s="90" t="n"/>
-      <c r="B330" s="91" t="inlineStr">
+      <c r="C330" s="43" t="n"/>
+      <c r="D330" s="58" t="n"/>
+      <c r="E330" s="58" t="n"/>
+      <c r="F330" s="61" t="n"/>
+      <c r="G330" s="53" t="n"/>
+    </row>
+    <row r="331" ht="19.8" customHeight="1">
+      <c r="A331" s="90" t="n"/>
+      <c r="B331" s="91" t="inlineStr">
         <is>
           <t>VA03</t>
         </is>
       </c>
-      <c r="C330" s="18" t="inlineStr">
+      <c r="C331" s="18" t="inlineStr">
         <is>
           <t>0.75 x 2.52</t>
         </is>
       </c>
-      <c r="D330" s="19" t="n">
+      <c r="D331" s="19" t="n">
         <v>1.89</v>
       </c>
-      <c r="E330" s="59" t="n">
+      <c r="E331" s="59" t="n">
         <v>60</v>
       </c>
-      <c r="F330" s="80" t="n">
+      <c r="F331" s="80" t="n">
         <v>113.4</v>
       </c>
-      <c r="G330" s="53" t="n"/>
-    </row>
-    <row r="331" ht="19.8" customHeight="1">
-      <c r="A331" s="36" t="inlineStr">
+      <c r="G331" s="53" t="n"/>
+    </row>
+    <row r="332" ht="19.8" customHeight="1">
+      <c r="A332" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B331" s="78" t="inlineStr">
+      <c r="B332" s="78" t="inlineStr">
         <is>
           <t>PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C331" s="47" t="n"/>
-      <c r="D331" s="18" t="n"/>
-      <c r="E331" s="18" t="n"/>
-      <c r="F331" s="20" t="n"/>
-      <c r="G331" s="53" t="n"/>
-    </row>
-    <row r="332" ht="19.8" customHeight="1">
-      <c r="A332" s="43" t="n"/>
-      <c r="B332" s="79" t="inlineStr">
+      <c r="C332" s="47" t="n"/>
+      <c r="D332" s="18" t="n"/>
+      <c r="E332" s="18" t="n"/>
+      <c r="F332" s="20" t="n"/>
+      <c r="G332" s="53" t="n"/>
+    </row>
+    <row r="333" ht="19.8" customHeight="1">
+      <c r="A333" s="43" t="n"/>
+      <c r="B333" s="79" t="inlineStr">
         <is>
           <t>AISLADAS (NE)</t>
         </is>
       </c>
-      <c r="C332" s="18" t="inlineStr">
+      <c r="C333" s="18" t="inlineStr">
         <is>
           <t>2.20 x 3.00</t>
         </is>
       </c>
-      <c r="D332" s="19" t="n">
+      <c r="D333" s="19" t="n">
         <v>6.6</v>
-      </c>
-      <c r="E332" s="59" t="n">
-        <v>20</v>
-      </c>
-      <c r="F332" s="80" t="n">
-        <v>132</v>
-      </c>
-      <c r="G332" s="53" t="n"/>
-    </row>
-    <row r="333" ht="19.8" customHeight="1">
-      <c r="A333" s="47" t="n"/>
-      <c r="B333" s="81" t="inlineStr">
-        <is>
-          <t>AISLADAS</t>
-        </is>
-      </c>
-      <c r="C333" s="18" t="inlineStr">
-        <is>
-          <t>1.60 x 3.00</t>
-        </is>
-      </c>
-      <c r="D333" s="19" t="n">
-        <v>4.8</v>
       </c>
       <c r="E333" s="59" t="n">
         <v>20</v>
       </c>
       <c r="F333" s="80" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="G333" s="53" t="n"/>
     </row>
@@ -25980,358 +25980,366 @@
       <c r="A334" s="47" t="n"/>
       <c r="B334" s="81" t="inlineStr">
         <is>
+          <t>AISLADAS</t>
+        </is>
+      </c>
+      <c r="C334" s="18" t="inlineStr">
+        <is>
+          <t>1.60 x 3.00</t>
+        </is>
+      </c>
+      <c r="D334" s="19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E334" s="59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F334" s="80" t="n">
+        <v>96</v>
+      </c>
+      <c r="G334" s="53" t="n"/>
+    </row>
+    <row r="335" ht="19.8" customHeight="1">
+      <c r="A335" s="47" t="n"/>
+      <c r="B335" s="81" t="inlineStr">
+        <is>
           <t>INTERIORES (SO)</t>
         </is>
       </c>
-      <c r="C334" s="18" t="inlineStr">
+      <c r="C335" s="18" t="inlineStr">
         <is>
           <t>2.20 x 3.00</t>
         </is>
       </c>
-      <c r="D334" s="19" t="n">
+      <c r="D335" s="19" t="n">
         <v>6.6</v>
-      </c>
-      <c r="E334" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="F334" s="80" t="n">
-        <v>165</v>
-      </c>
-      <c r="G334" s="53" t="n"/>
-    </row>
-    <row r="335" ht="19.8" customHeight="1">
-      <c r="A335" s="50" t="n"/>
-      <c r="B335" s="82" t="inlineStr">
-        <is>
-          <t>INTERIORES</t>
-        </is>
-      </c>
-      <c r="C335" s="18" t="inlineStr">
-        <is>
-          <t>1.60 x 3.00</t>
-        </is>
-      </c>
-      <c r="D335" s="19" t="n">
-        <v>4.8</v>
       </c>
       <c r="E335" s="59" t="n">
         <v>25</v>
       </c>
       <c r="F335" s="80" t="n">
+        <v>165</v>
+      </c>
+      <c r="G335" s="53" t="n"/>
+    </row>
+    <row r="336" ht="19.8" customHeight="1">
+      <c r="A336" s="50" t="n"/>
+      <c r="B336" s="82" t="inlineStr">
+        <is>
+          <t>INTERIORES</t>
+        </is>
+      </c>
+      <c r="C336" s="18" t="inlineStr">
+        <is>
+          <t>1.60 x 3.00</t>
+        </is>
+      </c>
+      <c r="D336" s="19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E336" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="F336" s="80" t="n">
         <v>120</v>
       </c>
-      <c r="G335" s="53" t="n"/>
-    </row>
-    <row r="336" ht="19.8" customHeight="1">
-      <c r="A336" s="36" t="inlineStr">
+      <c r="G336" s="53" t="n"/>
+    </row>
+    <row r="337" ht="19.8" customHeight="1">
+      <c r="A337" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B336" s="78" t="inlineStr">
+      <c r="B337" s="78" t="inlineStr">
         <is>
           <t>TECHOS O CIELORRASOS</t>
         </is>
       </c>
-      <c r="C336" s="47" t="n"/>
-      <c r="D336" s="18" t="n"/>
-      <c r="E336" s="18" t="n"/>
-      <c r="F336" s="20" t="n"/>
-      <c r="G336" s="53" t="n"/>
-    </row>
-    <row r="337" ht="19.8" customHeight="1">
-      <c r="A337" s="43" t="n"/>
-      <c r="B337" s="79" t="inlineStr">
+      <c r="C337" s="47" t="n"/>
+      <c r="D337" s="18" t="n"/>
+      <c r="E337" s="18" t="n"/>
+      <c r="F337" s="20" t="n"/>
+      <c r="G337" s="53" t="n"/>
+    </row>
+    <row r="338" ht="19.8" customHeight="1">
+      <c r="A338" s="43" t="n"/>
+      <c r="B338" s="79" t="inlineStr">
         <is>
           <t>TECHO NO AISLADO</t>
         </is>
       </c>
-      <c r="C337" s="18" t="n"/>
-      <c r="D337" s="19" t="n"/>
-      <c r="E337" s="59" t="n">
+      <c r="C338" s="18" t="n"/>
+      <c r="D338" s="19" t="n"/>
+      <c r="E338" s="59" t="n">
         <v>30</v>
       </c>
-      <c r="F337" s="80" t="n"/>
-      <c r="G337" s="53" t="n"/>
-    </row>
-    <row r="338" ht="19.8" customHeight="1">
-      <c r="A338" s="47" t="n"/>
-      <c r="B338" s="81" t="inlineStr">
+      <c r="F338" s="80" t="n"/>
+      <c r="G338" s="53" t="n"/>
+    </row>
+    <row r="339" ht="19.8" customHeight="1">
+      <c r="A339" s="47" t="n"/>
+      <c r="B339" s="81" t="inlineStr">
         <is>
           <t>TECHO AISLADO</t>
         </is>
       </c>
-      <c r="C338" s="18" t="inlineStr">
+      <c r="C339" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D338" s="19" t="n">
+      <c r="D339" s="19" t="n">
         <v>3.52</v>
       </c>
-      <c r="E338" s="59" t="n">
+      <c r="E339" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="F338" s="80" t="n">
+      <c r="F339" s="80" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="G338" s="53" t="n"/>
-    </row>
-    <row r="339" ht="19.8" customHeight="1">
-      <c r="A339" s="50" t="n"/>
-      <c r="B339" s="82" t="inlineStr">
+      <c r="G339" s="53" t="n"/>
+    </row>
+    <row r="340" ht="19.8" customHeight="1">
+      <c r="A340" s="50" t="n"/>
+      <c r="B340" s="82" t="inlineStr">
         <is>
           <t>TECHO ENTREPISO</t>
         </is>
       </c>
-      <c r="C339" s="18" t="n"/>
-      <c r="D339" s="19" t="n"/>
-      <c r="E339" s="59" t="n">
+      <c r="C340" s="18" t="n"/>
+      <c r="D340" s="19" t="n"/>
+      <c r="E340" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F339" s="80" t="n"/>
-      <c r="G339" s="53" t="n"/>
-    </row>
-    <row r="340" ht="19.8" customHeight="1">
-      <c r="A340" s="36" t="inlineStr">
+      <c r="F340" s="80" t="n"/>
+      <c r="G340" s="53" t="n"/>
+    </row>
+    <row r="341" ht="19.8" customHeight="1">
+      <c r="A341" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B340" s="78" t="inlineStr">
+      <c r="B341" s="78" t="inlineStr">
         <is>
           <t>PISO</t>
         </is>
       </c>
-      <c r="C340" s="47" t="n"/>
-      <c r="D340" s="18" t="n"/>
-      <c r="E340" s="18" t="n"/>
-      <c r="F340" s="20" t="n"/>
-      <c r="G340" s="53" t="n"/>
-    </row>
-    <row r="341" ht="19.8" customHeight="1">
-      <c r="A341" s="43" t="n"/>
-      <c r="B341" s="79" t="inlineStr">
+      <c r="C341" s="47" t="n"/>
+      <c r="D341" s="18" t="n"/>
+      <c r="E341" s="18" t="n"/>
+      <c r="F341" s="20" t="n"/>
+      <c r="G341" s="53" t="n"/>
+    </row>
+    <row r="342" ht="19.8" customHeight="1">
+      <c r="A342" s="43" t="n"/>
+      <c r="B342" s="79" t="inlineStr">
         <is>
           <t>SOBRE TIERRA</t>
         </is>
       </c>
-      <c r="C341" s="18" t="n"/>
-      <c r="D341" s="19" t="n"/>
-      <c r="E341" s="59" t="n">
+      <c r="C342" s="18" t="n"/>
+      <c r="D342" s="19" t="n"/>
+      <c r="E342" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="F341" s="80" t="n"/>
-      <c r="G341" s="53" t="n"/>
-    </row>
-    <row r="342" ht="19.8" customHeight="1">
-      <c r="A342" s="50" t="n"/>
-      <c r="B342" s="82" t="inlineStr">
+      <c r="F342" s="80" t="n"/>
+      <c r="G342" s="53" t="n"/>
+    </row>
+    <row r="343" ht="19.8" customHeight="1">
+      <c r="A343" s="50" t="n"/>
+      <c r="B343" s="82" t="inlineStr">
         <is>
           <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
-      <c r="C342" s="18" t="inlineStr">
+      <c r="C343" s="18" t="inlineStr">
         <is>
           <t>por croquis</t>
         </is>
       </c>
-      <c r="D342" s="24" t="n">
+      <c r="D343" s="24" t="n">
         <v>3.52</v>
       </c>
-      <c r="E342" s="59" t="n">
+      <c r="E343" s="59" t="n">
         <v>15</v>
       </c>
-      <c r="F342" s="80" t="n">
+      <c r="F343" s="80" t="n">
         <v>52.8</v>
       </c>
-      <c r="G342" s="53" t="n"/>
-    </row>
-    <row r="343" ht="19.8" customHeight="1">
-      <c r="A343" s="36" t="inlineStr">
+      <c r="G343" s="53" t="n"/>
+    </row>
+    <row r="344" ht="19.8" customHeight="1">
+      <c r="A344" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B343" s="78" t="inlineStr">
+      <c r="B344" s="78" t="inlineStr">
         <is>
           <t>INFILTRACION</t>
         </is>
       </c>
-      <c r="C343" s="83" t="n"/>
-      <c r="D343" s="36" t="inlineStr">
+      <c r="C344" s="83" t="n"/>
+      <c r="D344" s="36" t="inlineStr">
         <is>
           <t>VOLUMEN (m3)</t>
         </is>
       </c>
-      <c r="E343" s="47" t="n"/>
-      <c r="F343" s="20" t="n"/>
-      <c r="G343" s="53" t="n"/>
-    </row>
-    <row r="344" ht="19.8" customHeight="1">
-      <c r="A344" s="43" t="n"/>
-      <c r="B344" s="79" t="inlineStr">
+      <c r="E344" s="47" t="n"/>
+      <c r="F344" s="20" t="n"/>
+      <c r="G344" s="53" t="n"/>
+    </row>
+    <row r="345" ht="19.8" customHeight="1">
+      <c r="A345" s="43" t="n"/>
+      <c r="B345" s="79" t="inlineStr">
         <is>
           <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
-      <c r="C344" s="18" t="n"/>
-      <c r="D344" s="22" t="n"/>
-      <c r="E344" s="59" t="n">
+      <c r="C345" s="18" t="n"/>
+      <c r="D345" s="22" t="n"/>
+      <c r="E345" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="F344" s="80" t="n"/>
-      <c r="G344" s="53" t="n"/>
-    </row>
-    <row r="345" ht="19.8" customHeight="1">
-      <c r="A345" s="47" t="n"/>
-      <c r="B345" s="81" t="inlineStr">
+      <c r="F345" s="80" t="n"/>
+      <c r="G345" s="53" t="n"/>
+    </row>
+    <row r="346" ht="19.8" customHeight="1">
+      <c r="A346" s="47" t="n"/>
+      <c r="B346" s="81" t="inlineStr">
         <is>
           <t>DOS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C345" s="18" t="inlineStr">
+      <c r="C346" s="18" t="inlineStr">
         <is>
           <t>3.52 m2 x 3.00</t>
         </is>
       </c>
-      <c r="D345" s="19" t="n">
+      <c r="D346" s="19" t="n">
         <v>10.56</v>
       </c>
-      <c r="E345" s="59" t="n">
+      <c r="E346" s="59" t="n">
         <v>9</v>
       </c>
-      <c r="F345" s="80" t="n">
+      <c r="F346" s="80" t="n">
         <v>95</v>
       </c>
-      <c r="G345" s="53" t="n"/>
-    </row>
-    <row r="346" ht="19.8" customHeight="1">
-      <c r="A346" s="50" t="n"/>
-      <c r="B346" s="82" t="inlineStr">
+      <c r="G346" s="53" t="n"/>
+    </row>
+    <row r="347" ht="19.8" customHeight="1">
+      <c r="A347" s="50" t="n"/>
+      <c r="B347" s="82" t="inlineStr">
         <is>
           <t>TRES O MAS PAREDES EXTERIORES</t>
         </is>
       </c>
-      <c r="C346" s="18" t="n"/>
-      <c r="D346" s="19" t="n"/>
-      <c r="E346" s="59" t="n">
+      <c r="C347" s="18" t="n"/>
+      <c r="D347" s="19" t="n"/>
+      <c r="E347" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="F346" s="84" t="n"/>
-      <c r="G346" s="53" t="n"/>
-    </row>
-    <row r="347" ht="19.8" customHeight="1">
-      <c r="A347" s="36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B347" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C347" s="47" t="n"/>
-      <c r="D347" s="18" t="n"/>
-      <c r="E347" s="20" t="n"/>
-      <c r="F347" s="85" t="n">
-        <v>844.6</v>
-      </c>
+      <c r="F347" s="84" t="n"/>
       <c r="G347" s="53" t="n"/>
     </row>
     <row r="348" ht="19.8" customHeight="1">
       <c r="A348" s="36" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B348" s="78" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C348" s="47" t="n"/>
+      <c r="D348" s="18" t="n"/>
+      <c r="E348" s="20" t="n"/>
+      <c r="F348" s="85" t="n">
+        <v>844.6</v>
+      </c>
+      <c r="G348" s="53" t="n"/>
+    </row>
+    <row r="349" ht="19.8" customHeight="1">
+      <c r="A349" s="36" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B348" s="78" t="inlineStr">
+      <c r="B349" s="78" t="inlineStr">
         <is>
           <t>PERDIDA TOTAL</t>
         </is>
       </c>
-      <c r="C348" s="47" t="inlineStr">
+      <c r="C349" s="47" t="inlineStr">
         <is>
           <t>844.60  X  1.07 (FI)  X  1 (FO)  X  1 (FZ)</t>
         </is>
       </c>
-      <c r="D348" s="12" t="n"/>
-      <c r="E348" s="14" t="n"/>
-      <c r="F348" s="85" t="n">
+      <c r="D349" s="12" t="n"/>
+      <c r="E349" s="14" t="n"/>
+      <c r="F349" s="85" t="n">
         <v>903.7</v>
       </c>
-      <c r="G348" s="53" t="n"/>
-    </row>
-    <row r="349" ht="19.8" customHeight="1">
-      <c r="A349" s="43" t="n"/>
-      <c r="B349" s="86" t="inlineStr">
+      <c r="G349" s="53" t="n"/>
+    </row>
+    <row r="350" ht="19.8" customHeight="1">
+      <c r="A350" s="43" t="n"/>
+      <c r="B350" s="86" t="inlineStr">
         <is>
           <t>Carga de locales sin emisor</t>
         </is>
       </c>
-      <c r="C349" s="18" t="n"/>
-      <c r="D349" s="12" t="n"/>
-      <c r="E349" s="39" t="n"/>
-      <c r="F349" s="87" t="n"/>
-      <c r="G349" s="53" t="n"/>
-    </row>
-    <row r="350" ht="19.8" customHeight="1">
-      <c r="A350" s="83" t="n"/>
-      <c r="B350" s="78" t="inlineStr">
+      <c r="C350" s="18" t="n"/>
+      <c r="D350" s="12" t="n"/>
+      <c r="E350" s="39" t="n"/>
+      <c r="F350" s="87" t="n"/>
+      <c r="G350" s="53" t="n"/>
+    </row>
+    <row r="351" ht="19.8" customHeight="1">
+      <c r="A351" s="83" t="n"/>
+      <c r="B351" s="78" t="inlineStr">
         <is>
           <t>CARGA TOTAL A CUBRIR</t>
         </is>
       </c>
-      <c r="C350" s="47" t="n"/>
-      <c r="D350" s="12" t="n"/>
-      <c r="E350" s="14" t="n"/>
-      <c r="F350" s="85" t="n">
+      <c r="C351" s="47" t="n"/>
+      <c r="D351" s="12" t="n"/>
+      <c r="E351" s="14" t="n"/>
+      <c r="F351" s="85" t="n">
         <v>903.7</v>
       </c>
-      <c r="G350" s="53" t="n"/>
-    </row>
-    <row r="351" ht="19.8" customHeight="1">
-      <c r="A351" s="47" t="n"/>
-      <c r="B351" s="88" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
-        </is>
-      </c>
-      <c r="C351" s="18" t="inlineStr">
-        <is>
-          <t>86 - 20 = 66 C</t>
-        </is>
-      </c>
-      <c r="D351" s="12" t="n"/>
-      <c r="E351" s="39" t="n"/>
-      <c r="F351" s="61" t="n"/>
       <c r="G351" s="53" t="n"/>
     </row>
     <row r="352" ht="19.8" customHeight="1">
       <c r="A352" s="47" t="n"/>
-      <c r="B352" s="60" t="inlineStr">
-        <is>
-          <t>Kcal/h del toallero Scala/Domino 80</t>
-        </is>
-      </c>
-      <c r="C352" s="59" t="n">
-        <v>708</v>
+      <c r="B352" s="88" t="inlineStr">
+        <is>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C352" s="18" t="inlineStr">
+        <is>
+          <t>86 - 20 = 66 C</t>
+        </is>
       </c>
       <c r="D352" s="12" t="n"/>
       <c r="E352" s="39" t="n"/>
-      <c r="F352" s="20" t="n"/>
+      <c r="F352" s="61" t="n"/>
       <c r="G352" s="53" t="n"/>
     </row>
     <row r="353" ht="19.8" customHeight="1">
       <c r="A353" s="47" t="n"/>
       <c r="B353" s="60" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 150</t>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
         </is>
       </c>
       <c r="C353" s="59" t="n">
-        <v>1315</v>
+        <v>708</v>
       </c>
       <c r="D353" s="12" t="n"/>
       <c r="E353" s="39" t="n"/>
@@ -26342,11 +26350,11 @@
       <c r="A354" s="47" t="n"/>
       <c r="B354" s="60" t="inlineStr">
         <is>
-          <t>Toalleros necesarios</t>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
         </is>
       </c>
       <c r="C354" s="59" t="n">
-        <v>1</v>
+        <v>1315</v>
       </c>
       <c r="D354" s="12" t="n"/>
       <c r="E354" s="39" t="n"/>
@@ -26354,29 +26362,44 @@
       <c r="G354" s="53" t="n"/>
     </row>
     <row r="355" ht="19.8" customHeight="1">
-      <c r="A355" s="50" t="n"/>
-      <c r="B355" s="72" t="inlineStr">
+      <c r="A355" s="47" t="n"/>
+      <c r="B355" s="60" t="inlineStr">
+        <is>
+          <t>Toalleros necesarios</t>
+        </is>
+      </c>
+      <c r="C355" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D355" s="12" t="n"/>
+      <c r="E355" s="39" t="n"/>
+      <c r="F355" s="20" t="n"/>
+      <c r="G355" s="53" t="n"/>
+    </row>
+    <row r="356" ht="19.8" customHeight="1">
+      <c r="A356" s="50" t="n"/>
+      <c r="B356" s="72" t="inlineStr">
         <is>
           <t>Toallero adoptado</t>
         </is>
       </c>
-      <c r="C355" s="30" t="inlineStr">
+      <c r="C356" s="30" t="inlineStr">
         <is>
           <t>Peisa Scala / Domino 150  (500 x 1500 mm)</t>
         </is>
       </c>
-      <c r="D355" s="11" t="n"/>
-      <c r="E355" s="92" t="n"/>
-      <c r="F355" s="31" t="n"/>
-      <c r="G355" s="53" t="n"/>
+      <c r="D356" s="11" t="n"/>
+      <c r="E356" s="92" t="n"/>
+      <c r="F356" s="31" t="n"/>
+      <c r="G356" s="53" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="101">
     <mergeCell ref="C321:E321"/>
     <mergeCell ref="C202:E202"/>
     <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A238:F238"/>
     <mergeCell ref="C297:E297"/>
+    <mergeCell ref="A239:F239"/>
     <mergeCell ref="C60:E60"/>
     <mergeCell ref="C268:E268"/>
     <mergeCell ref="C292:E292"/>
@@ -26386,28 +26409,25 @@
     <mergeCell ref="C204:E204"/>
     <mergeCell ref="C325:E325"/>
     <mergeCell ref="C206:E206"/>
-    <mergeCell ref="C143:E143"/>
     <mergeCell ref="C205:E205"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C118:E118"/>
     <mergeCell ref="C320:E320"/>
+    <mergeCell ref="C238:E238"/>
     <mergeCell ref="C176:E176"/>
     <mergeCell ref="C232:E232"/>
-    <mergeCell ref="C114:E114"/>
+    <mergeCell ref="C356:E356"/>
     <mergeCell ref="C59:E59"/>
     <mergeCell ref="C295:E295"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A269:F269"/>
+    <mergeCell ref="C178:E178"/>
     <mergeCell ref="C61:E61"/>
     <mergeCell ref="C233:E233"/>
-    <mergeCell ref="A122:F122"/>
+    <mergeCell ref="C296:E296"/>
+    <mergeCell ref="C352:E352"/>
     <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C352:E352"/>
-    <mergeCell ref="C296:E296"/>
-    <mergeCell ref="C170:E170"/>
-    <mergeCell ref="C348:E348"/>
     <mergeCell ref="C145:E145"/>
     <mergeCell ref="C323:E323"/>
+    <mergeCell ref="C298:E298"/>
     <mergeCell ref="C87:E87"/>
     <mergeCell ref="C267:E267"/>
     <mergeCell ref="C266:E266"/>
@@ -26415,38 +26435,42 @@
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="C89:E89"/>
     <mergeCell ref="C116:E116"/>
-    <mergeCell ref="A178:F178"/>
+    <mergeCell ref="C269:E269"/>
     <mergeCell ref="C88:E88"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C324:E324"/>
     <mergeCell ref="C231:E231"/>
+    <mergeCell ref="C121:E121"/>
     <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C121:E121"/>
-    <mergeCell ref="C261:E261"/>
-    <mergeCell ref="A208:F208"/>
-    <mergeCell ref="C230:E230"/>
     <mergeCell ref="C117:E117"/>
     <mergeCell ref="C173:E173"/>
     <mergeCell ref="C236:E236"/>
     <mergeCell ref="C350:E350"/>
+    <mergeCell ref="A179:F179"/>
     <mergeCell ref="C115:E115"/>
     <mergeCell ref="C207:E207"/>
     <mergeCell ref="C262:E262"/>
     <mergeCell ref="C144:E144"/>
+    <mergeCell ref="C122:E122"/>
+    <mergeCell ref="A299:F299"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="C264:E264"/>
     <mergeCell ref="C326:E326"/>
+    <mergeCell ref="C208:E208"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="C263:E263"/>
     <mergeCell ref="C354:E354"/>
     <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A328:F328"/>
     <mergeCell ref="C235:E235"/>
+    <mergeCell ref="A270:F270"/>
     <mergeCell ref="C62:E62"/>
     <mergeCell ref="C234:E234"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C172:E172"/>
     <mergeCell ref="C353:E353"/>
     <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C147:E147"/>
     <mergeCell ref="C171:E171"/>
     <mergeCell ref="C349:E349"/>
     <mergeCell ref="A65:F65"/>
@@ -26457,21 +26481,20 @@
     <mergeCell ref="C90:E90"/>
     <mergeCell ref="C120:E120"/>
     <mergeCell ref="C27:E27"/>
-    <mergeCell ref="A298:F298"/>
     <mergeCell ref="C203:E203"/>
     <mergeCell ref="C119:E119"/>
+    <mergeCell ref="A209:F209"/>
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="C174:E174"/>
-    <mergeCell ref="A147:F147"/>
-    <mergeCell ref="A327:F327"/>
+    <mergeCell ref="C327:E327"/>
     <mergeCell ref="C237:E237"/>
     <mergeCell ref="C351:E351"/>
-    <mergeCell ref="C319:E319"/>
+    <mergeCell ref="A148:F148"/>
     <mergeCell ref="C175:E175"/>
     <mergeCell ref="C58:E58"/>
     <mergeCell ref="C294:E294"/>
-    <mergeCell ref="C290:E290"/>
-    <mergeCell ref="C200:E200"/>
+    <mergeCell ref="A123:F123"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C265:E265"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -22122,7 +22122,7 @@
       <c r="A128" s="43" t="n"/>
       <c r="B128" s="79" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>AISLADAS (NE)</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
@@ -22145,7 +22145,7 @@
       <c r="A129" s="47" t="n"/>
       <c r="B129" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS (SO)</t>
+          <t>AISLADAS</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
@@ -22168,7 +22168,7 @@
       <c r="A130" s="47" t="n"/>
       <c r="B130" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (SO)</t>
         </is>
       </c>
       <c r="C130" s="18" t="inlineStr">
@@ -22191,7 +22191,7 @@
       <c r="A131" s="50" t="n"/>
       <c r="B131" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (NE)</t>
+          <t>INTERIORES</t>
         </is>
       </c>
       <c r="C131" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -22145,7 +22145,7 @@
       <c r="A129" s="47" t="n"/>
       <c r="B129" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>AISLADAS (SE)</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
@@ -22191,7 +22191,7 @@
       <c r="A131" s="50" t="n"/>
       <c r="B131" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (NO)</t>
         </is>
       </c>
       <c r="C131" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -23734,7 +23734,7 @@
       <c r="A214" s="43" t="n"/>
       <c r="B214" s="79" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>AISLADAS (NE)</t>
         </is>
       </c>
       <c r="C214" s="18" t="inlineStr">
@@ -23772,7 +23772,7 @@
       <c r="A216" s="47" t="n"/>
       <c r="B216" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (NO)</t>
         </is>
       </c>
       <c r="C216" s="18" t="inlineStr">
@@ -23795,7 +23795,7 @@
       <c r="A217" s="47" t="n"/>
       <c r="B217" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (SE, bano suite)</t>
         </is>
       </c>
       <c r="C217" s="18" t="inlineStr">
@@ -23818,7 +23818,7 @@
       <c r="A218" s="50" t="n"/>
       <c r="B218" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (SO)</t>
         </is>
       </c>
       <c r="C218" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -19938,7 +19938,7 @@
       <c r="A12" s="47" t="n"/>
       <c r="B12" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (SE, galeria y living)</t>
+          <t>INTERIORES (SE)</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -19961,7 +19961,7 @@
       <c r="A13" s="50" t="n"/>
       <c r="B13" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (NE, deposito y lavadero)</t>
+          <t>INTERIORES (NE)</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
@@ -20496,7 +20496,7 @@
       <c r="A42" s="47" t="n"/>
       <c r="B42" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (NE, cocina)</t>
+          <t>INTERIORES (NE)</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
@@ -20519,7 +20519,7 @@
       <c r="A43" s="47" t="n"/>
       <c r="B43" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (NO, galeria)</t>
+          <t>INTERIORES (NO)</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
@@ -20542,7 +20542,7 @@
       <c r="A44" s="50" t="n"/>
       <c r="B44" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (SO, escalera y bano exterior)</t>
+          <t>INTERIORES (SO)</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
@@ -21091,7 +21091,7 @@
       <c r="A73" s="47" t="n"/>
       <c r="B73" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (NE, vestidor)</t>
+          <t>INTERIORES (NE)</t>
         </is>
       </c>
       <c r="C73" s="18" t="inlineStr">
@@ -21114,7 +21114,7 @@
       <c r="A74" s="50" t="n"/>
       <c r="B74" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (NO, living comedor)</t>
+          <t>INTERIORES (NO)</t>
         </is>
       </c>
       <c r="C74" s="18" t="inlineStr">
@@ -21556,7 +21556,7 @@
       <c r="A98" s="47" t="n"/>
       <c r="B98" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (SO, hall de ingreso)</t>
+          <t>INTERIORES (SO)</t>
         </is>
       </c>
       <c r="C98" s="18" t="inlineStr">
@@ -23222,7 +23222,7 @@
       <c r="A186" s="47" t="n"/>
       <c r="B186" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (NO, bano visitas)</t>
+          <t>INTERIORES (NO)</t>
         </is>
       </c>
       <c r="C186" s="18" t="inlineStr">
@@ -23268,7 +23268,7 @@
       <c r="A188" s="50" t="n"/>
       <c r="B188" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES (SE, dormitorio suite)</t>
+          <t>INTERIORES (SE)</t>
         </is>
       </c>
       <c r="C188" s="18" t="inlineStr">
@@ -23795,7 +23795,7 @@
       <c r="A217" s="47" t="n"/>
       <c r="B217" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES (SE, bano suite)</t>
+          <t>INTERIORES (SE)</t>
         </is>
       </c>
       <c r="C217" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -24361,7 +24361,7 @@
       <c r="A247" s="47" t="n"/>
       <c r="B247" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>AISLADAS (SO)</t>
         </is>
       </c>
       <c r="C247" s="18" t="inlineStr">
@@ -24384,7 +24384,7 @@
       <c r="A248" s="47" t="n"/>
       <c r="B248" s="81" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (NE)</t>
         </is>
       </c>
       <c r="C248" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -25437,7 +25437,7 @@
       <c r="A305" s="47" t="n"/>
       <c r="B305" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>AISLADAS (SO)</t>
         </is>
       </c>
       <c r="C305" s="18" t="inlineStr">
@@ -25483,7 +25483,7 @@
       <c r="A307" s="50" t="n"/>
       <c r="B307" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (NE)</t>
         </is>
       </c>
       <c r="C307" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -25980,7 +25980,7 @@
       <c r="A334" s="47" t="n"/>
       <c r="B334" s="81" t="inlineStr">
         <is>
-          <t>AISLADAS</t>
+          <t>AISLADAS (SE)</t>
         </is>
       </c>
       <c r="C334" s="18" t="inlineStr">
@@ -26026,7 +26026,7 @@
       <c r="A336" s="50" t="n"/>
       <c r="B336" s="82" t="inlineStr">
         <is>
-          <t>INTERIORES</t>
+          <t>INTERIORES (NO)</t>
         </is>
       </c>
       <c r="C336" s="18" t="inlineStr">

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -983,6 +983,1901 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2743200" cy="3276600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6608,7 +8503,7 @@
     <col width="17.6" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="261" customHeight="1">
       <c r="A1" s="33" t="n"/>
       <c r="B1" s="34" t="inlineStr">
         <is>
@@ -8802,6 +10697,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9801,7 +11697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="47" customHeight="1">
+    <row r="5" ht="48" customHeight="1">
       <c r="A5" s="37" t="n"/>
       <c r="B5" s="62" t="inlineStr">
         <is>
@@ -10013,7 +11909,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="19.8" customHeight="1">
+    <row r="7" ht="48" customHeight="1">
       <c r="A7" s="37" t="n"/>
       <c r="B7" s="62" t="inlineStr">
         <is>
@@ -10225,7 +12121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="19.8" customHeight="1">
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="37" t="n"/>
       <c r="B9" s="62" t="inlineStr">
         <is>
@@ -10437,7 +12333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" ht="47" customHeight="1">
+    <row r="11" ht="48" customHeight="1">
       <c r="A11" s="37" t="n"/>
       <c r="B11" s="62" t="inlineStr">
         <is>
@@ -10543,7 +12439,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" ht="47" customHeight="1">
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="37" t="n"/>
       <c r="B12" s="62" t="inlineStr">
         <is>
@@ -10759,7 +12655,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" ht="19.8" customHeight="1">
+    <row r="14" ht="48" customHeight="1">
       <c r="A14" s="37" t="n"/>
       <c r="B14" s="62" t="inlineStr">
         <is>
@@ -10861,7 +12757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
+    <row r="15" ht="48" customHeight="1">
       <c r="A15" s="37" t="n"/>
       <c r="B15" s="62" t="inlineStr">
         <is>
@@ -10967,7 +12863,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" ht="47" customHeight="1">
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" s="37" t="n"/>
       <c r="B16" s="62" t="inlineStr">
         <is>
@@ -11081,7 +12977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" ht="19.8" customHeight="1">
+    <row r="17" ht="48" customHeight="1">
       <c r="A17" s="37" t="n"/>
       <c r="B17" s="62" t="inlineStr">
         <is>
@@ -11183,7 +13079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" ht="19.8" customHeight="1">
+    <row r="18" ht="48" customHeight="1">
       <c r="A18" s="37" t="n"/>
       <c r="B18" s="62" t="inlineStr">
         <is>
@@ -11285,7 +13181,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" ht="19.8" customHeight="1">
+    <row r="19" ht="48" customHeight="1">
       <c r="A19" s="37" t="n"/>
       <c r="B19" s="62" t="inlineStr">
         <is>
@@ -11493,7 +13389,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" ht="47" customHeight="1">
+    <row r="21" ht="48" customHeight="1">
       <c r="A21" s="37" t="n"/>
       <c r="B21" s="62" t="inlineStr">
         <is>
@@ -11599,7 +13495,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" ht="47" customHeight="1">
+    <row r="22" ht="48" customHeight="1">
       <c r="A22" s="37" t="n"/>
       <c r="B22" s="62" t="inlineStr">
         <is>
@@ -11813,7 +13709,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" ht="32" customHeight="1">
+    <row r="24" ht="48" customHeight="1">
       <c r="A24" s="37" t="n"/>
       <c r="B24" s="62" t="inlineStr">
         <is>
@@ -11919,7 +13815,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" ht="19.8" customHeight="1">
+    <row r="25" ht="48" customHeight="1">
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="62" t="inlineStr">
         <is>
@@ -12029,7 +13925,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" ht="28.4" customHeight="1">
+    <row r="26" ht="48" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>TECHO</t>
@@ -12135,7 +14031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" ht="19.8" customHeight="1">
+    <row r="27" ht="48" customHeight="1">
       <c r="A27" s="37" t="n"/>
       <c r="B27" s="62" t="inlineStr">
         <is>
@@ -12237,7 +14133,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" ht="19.8" customHeight="1">
+    <row r="28" ht="48" customHeight="1">
       <c r="A28" s="37" t="n"/>
       <c r="B28" s="62" t="inlineStr">
         <is>
@@ -12339,7 +14235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" ht="19.8" customHeight="1">
+    <row r="29" ht="48" customHeight="1">
       <c r="A29" s="37" t="n"/>
       <c r="B29" s="62" t="inlineStr">
         <is>
@@ -12441,7 +14337,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" ht="47" customHeight="1">
+    <row r="30" ht="48" customHeight="1">
       <c r="A30" s="37" t="n"/>
       <c r="B30" s="62" t="inlineStr">
         <is>
@@ -12547,7 +14443,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" ht="47" customHeight="1">
+    <row r="31" ht="48" customHeight="1">
       <c r="A31" s="37" t="n"/>
       <c r="B31" s="62" t="inlineStr">
         <is>
@@ -12653,7 +14549,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" ht="19.8" customHeight="1">
+    <row r="32" ht="48" customHeight="1">
       <c r="A32" s="37" t="n"/>
       <c r="B32" s="62" t="inlineStr">
         <is>
@@ -12755,7 +14651,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" ht="19.8" customHeight="1">
+    <row r="33" ht="48" customHeight="1">
       <c r="A33" s="37" t="n"/>
       <c r="B33" s="62" t="inlineStr">
         <is>
@@ -12857,7 +14753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" ht="19.8" customHeight="1">
+    <row r="34" ht="48" customHeight="1">
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="63" t="inlineStr">
         <is>
@@ -12990,6 +14886,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13179,7 +15076,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="28.4" customHeight="1">
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>S/PB</t>
@@ -13241,7 +15138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="19.8" customHeight="1">
+    <row r="5" ht="48" customHeight="1">
       <c r="A5" s="37" t="n"/>
       <c r="B5" s="62" t="inlineStr">
         <is>
@@ -13305,7 +15202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="19.8" customHeight="1">
+    <row r="6" ht="48" customHeight="1">
       <c r="A6" s="37" t="n"/>
       <c r="B6" s="62" t="inlineStr">
         <is>
@@ -13363,7 +15260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" ht="19.8" customHeight="1">
+    <row r="7" ht="48" customHeight="1">
       <c r="A7" s="37" t="n"/>
       <c r="B7" s="62" t="inlineStr">
         <is>
@@ -13421,7 +15318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" ht="19.8" customHeight="1">
+    <row r="8" ht="48" customHeight="1">
       <c r="A8" s="37" t="n"/>
       <c r="B8" s="62" t="inlineStr">
         <is>
@@ -13479,7 +15376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" ht="19.8" customHeight="1">
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="37" t="n"/>
       <c r="B9" s="62" t="inlineStr">
         <is>
@@ -13537,7 +15434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" ht="47" customHeight="1">
+    <row r="10" ht="48" customHeight="1">
       <c r="A10" s="37" t="n"/>
       <c r="B10" s="62" t="inlineStr">
         <is>
@@ -13601,7 +15498,7 @@
         <v>0.639951021553631</v>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
+    <row r="11" ht="48" customHeight="1">
       <c r="A11" s="37" t="n"/>
       <c r="B11" s="62" t="inlineStr">
         <is>
@@ -13665,7 +15562,7 @@
         <v>0.360048978446369</v>
       </c>
     </row>
-    <row r="12" ht="19.8" customHeight="1">
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="62" t="inlineStr">
         <is>
@@ -13729,7 +15626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" ht="28.4" customHeight="1">
+    <row r="13" ht="48" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>S/PA</t>
@@ -13791,7 +15688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" ht="47" customHeight="1">
+    <row r="14" ht="48" customHeight="1">
       <c r="A14" s="37" t="n"/>
       <c r="B14" s="62" t="inlineStr">
         <is>
@@ -13855,7 +15752,7 @@
         <v>0.7008026762551089</v>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
+    <row r="15" ht="48" customHeight="1">
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="63" t="inlineStr">
         <is>
@@ -13939,6 +15836,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15151,7 +17049,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="19.8" customHeight="1">
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="56" t="inlineStr">
         <is>
           <t>VF01 (1)</t>
@@ -15233,7 +17131,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="19.8" customHeight="1">
+    <row r="5" ht="48" customHeight="1">
       <c r="A5" s="56" t="inlineStr">
         <is>
           <t>VF01 (2)</t>
@@ -15315,7 +17213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="19.8" customHeight="1">
+    <row r="6" ht="48" customHeight="1">
       <c r="A6" s="56" t="inlineStr">
         <is>
           <t>VF01 (3)</t>
@@ -15397,7 +17295,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" ht="47" customHeight="1">
+    <row r="7" ht="48" customHeight="1">
       <c r="A7" s="56" t="inlineStr">
         <is>
           <t>VF02</t>
@@ -15665,7 +17563,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" ht="19.8" customHeight="1">
+    <row r="10" ht="48" customHeight="1">
       <c r="A10" s="56" t="inlineStr">
         <is>
           <t>VF04b</t>
@@ -15747,7 +17645,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="19.8" customHeight="1">
+    <row r="11" ht="48" customHeight="1">
       <c r="A11" s="56" t="inlineStr">
         <is>
           <t>VF04c</t>
@@ -15829,7 +17727,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="19.8" customHeight="1">
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="56" t="inlineStr">
         <is>
           <t>VF05</t>
@@ -15919,7 +17817,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" ht="19.8" customHeight="1">
+    <row r="13" ht="48" customHeight="1">
       <c r="A13" s="56" t="inlineStr">
         <is>
           <t>VF06a</t>
@@ -16001,7 +17899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" ht="19.8" customHeight="1">
+    <row r="14" ht="48" customHeight="1">
       <c r="A14" s="56" t="inlineStr">
         <is>
           <t>VF06b</t>
@@ -16083,7 +17981,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" ht="19.8" customHeight="1">
+    <row r="15" ht="48" customHeight="1">
       <c r="A15" s="56" t="inlineStr">
         <is>
           <t>VF06c</t>
@@ -16165,7 +18063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" ht="19.8" customHeight="1">
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" s="56" t="inlineStr">
         <is>
           <t>VF06d</t>
@@ -16247,7 +18145,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" ht="19.8" customHeight="1">
+    <row r="17" ht="48" customHeight="1">
       <c r="A17" s="56" t="inlineStr">
         <is>
           <t>VF07</t>
@@ -16337,7 +18235,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" ht="47" customHeight="1">
+    <row r="18" ht="48" customHeight="1">
       <c r="A18" s="56" t="inlineStr">
         <is>
           <t>VF08</t>
@@ -16431,7 +18329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" ht="19.8" customHeight="1">
+    <row r="19" ht="48" customHeight="1">
       <c r="A19" s="56" t="inlineStr">
         <is>
           <t>VF09 (1)</t>
@@ -16513,7 +18411,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" ht="19.8" customHeight="1">
+    <row r="20" ht="48" customHeight="1">
       <c r="A20" s="56" t="inlineStr">
         <is>
           <t>VF09 (2)</t>
@@ -16595,7 +18493,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" ht="47" customHeight="1">
+    <row r="21" ht="48" customHeight="1">
       <c r="A21" s="56" t="inlineStr">
         <is>
           <t>VF10a</t>
@@ -16681,7 +18579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" ht="47" customHeight="1">
+    <row r="22" ht="48" customHeight="1">
       <c r="A22" s="56" t="inlineStr">
         <is>
           <t>VF10b</t>
@@ -16767,7 +18665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" ht="47" customHeight="1">
+    <row r="23" ht="48" customHeight="1">
       <c r="A23" s="56" t="inlineStr">
         <is>
           <t>VF10c</t>
@@ -16853,7 +18751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" ht="47" customHeight="1">
+    <row r="24" ht="48" customHeight="1">
       <c r="A24" s="56" t="inlineStr">
         <is>
           <t>VF11</t>
@@ -16947,7 +18845,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" ht="19.8" customHeight="1">
+    <row r="25" ht="48" customHeight="1">
       <c r="A25" s="56" t="inlineStr">
         <is>
           <t>VF12</t>
@@ -17037,7 +18935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" ht="19.8" customHeight="1">
+    <row r="26" ht="48" customHeight="1">
       <c r="A26" s="56" t="inlineStr">
         <is>
           <t>VF13</t>
@@ -17127,7 +19025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" ht="47" customHeight="1">
+    <row r="27" ht="48" customHeight="1">
       <c r="A27" s="56" t="inlineStr">
         <is>
           <t>VF14</t>
@@ -17221,7 +19119,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" ht="19.8" customHeight="1">
+    <row r="28" ht="48" customHeight="1">
       <c r="A28" s="56" t="inlineStr">
         <is>
           <t>VF15</t>
@@ -17311,7 +19209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" ht="47" customHeight="1">
+    <row r="29" ht="48" customHeight="1">
       <c r="A29" s="56" t="inlineStr">
         <is>
           <t>VF16a</t>
@@ -17397,7 +19295,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" ht="19.8" customHeight="1">
+    <row r="30" ht="48" customHeight="1">
       <c r="A30" s="56" t="inlineStr">
         <is>
           <t>VF16b</t>
@@ -17479,7 +19377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" ht="19.8" customHeight="1">
+    <row r="31" ht="48" customHeight="1">
       <c r="A31" s="56" t="inlineStr">
         <is>
           <t>VF17</t>
@@ -17569,7 +19467,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" ht="47" customHeight="1">
+    <row r="32" ht="48" customHeight="1">
       <c r="A32" s="56" t="inlineStr">
         <is>
           <t>VF18a</t>
@@ -17655,7 +19553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" ht="19.8" customHeight="1">
+    <row r="33" ht="48" customHeight="1">
       <c r="A33" s="56" t="inlineStr">
         <is>
           <t>VF18b</t>
@@ -17737,7 +19635,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" ht="47" customHeight="1">
+    <row r="34" ht="48" customHeight="1">
       <c r="A34" s="41" t="inlineStr">
         <is>
           <t>VF18c</t>
@@ -17843,6 +19741,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/planillas/planillas_estructura (para AutoCAD).xlsx
+++ b/planillas/planillas_estructura (para AutoCAD).xlsx
@@ -28347,5 +28347,18 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <rowBreaks count="11" manualBreakCount="11">
+    <brk id="33" min="0" max="16383" man="1"/>
+    <brk id="65" min="0" max="16383" man="1"/>
+    <brk id="92" min="0" max="16383" man="1"/>
+    <brk id="125" min="0" max="16383" man="1"/>
+    <brk id="151" min="0" max="16383" man="1"/>
+    <brk id="183" min="0" max="16383" man="1"/>
+    <brk id="214" min="0" max="16383" man="1"/>
+    <brk id="245" min="0" max="16383" man="1"/>
+    <brk id="277" min="0" max="16383" man="1"/>
+    <brk id="307" min="0" max="16383" man="1"/>
+    <brk id="337" min="0" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>